--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antony/projects/diy-accounting/GB Accounts 2024-25/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antony/projects/diy-accounting/GB Accounts 2025-26/GB Accounts Self Employed 2026-04-05 (Apr26) Excel 2007/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8645E79F-5AA8-E746-A94C-E29DA582049A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EF1490-7805-BF43-BAEC-193303CC9B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2860" yWindow="1860" windowWidth="21380" windowHeight="13000" tabRatio="906" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1000" yWindow="960" windowWidth="21380" windowHeight="13000" tabRatio="906" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Business Details" sheetId="17" r:id="rId1"/>
@@ -201,7 +201,7 @@
     <definedName name="Q4_IncomeOther">VitalTax!$F$6</definedName>
     <definedName name="Q4_IncomeTurnover">VitalTax!$F$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1992,12 +1992,6 @@
     <t>3. Column F automatically collects the value of direct material purchased from the monthly purchases worksheet</t>
   </si>
   <si>
-    <t>2024-25</t>
-  </si>
-  <si>
-    <t>COPY DETAILS TO HMRC FORM          Submit HMRC RETURN ONLINE                   by 31st January 2025</t>
-  </si>
-  <si>
     <t>Not captured in DIY Accounting</t>
   </si>
   <si>
@@ -2089,6 +2083,12 @@
   </si>
   <si>
     <t>Above Lower Profits Threshold (LPT)</t>
+  </si>
+  <si>
+    <t>2026-27</t>
+  </si>
+  <si>
+    <t>COPY DETAILS TO HMRC FORM          Submit HMRC RETURN ONLINE                   by 31st January 2027</t>
   </si>
 </sst>
 </file>
@@ -3941,6 +3941,48 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="24" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3952,15 +3994,6 @@
     <xf numFmtId="3" fontId="24" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3979,38 +4012,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="3" fontId="24" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -4024,142 +4112,120 @@
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="15" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="15" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="168" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
@@ -4194,72 +4260,6 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -4360,6 +4360,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -4381,22 +4399,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4408,49 +4423,34 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -6497,31 +6497,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="330" t="s">
+      <c r="A1" s="310" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="331"/>
-      <c r="C1" s="331"/>
-      <c r="D1" s="331"/>
-      <c r="E1" s="331"/>
-      <c r="F1" s="331"/>
-      <c r="G1" s="331"/>
-      <c r="H1" s="331"/>
-      <c r="I1" s="331"/>
-      <c r="J1" s="331"/>
-      <c r="K1" s="331"/>
-      <c r="L1" s="331"/>
-      <c r="M1" s="331"/>
-      <c r="N1" s="331"/>
-      <c r="O1" s="331"/>
-      <c r="P1" s="331"/>
-      <c r="Q1" s="331"/>
-      <c r="R1" s="331"/>
-      <c r="S1" s="331"/>
-      <c r="T1" s="331"/>
-      <c r="U1" s="331"/>
-      <c r="V1" s="331"/>
-      <c r="W1" s="332"/>
+      <c r="B1" s="311"/>
+      <c r="C1" s="311"/>
+      <c r="D1" s="311"/>
+      <c r="E1" s="311"/>
+      <c r="F1" s="311"/>
+      <c r="G1" s="311"/>
+      <c r="H1" s="311"/>
+      <c r="I1" s="311"/>
+      <c r="J1" s="311"/>
+      <c r="K1" s="311"/>
+      <c r="L1" s="311"/>
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
+      <c r="Q1" s="311"/>
+      <c r="R1" s="311"/>
+      <c r="S1" s="311"/>
+      <c r="T1" s="311"/>
+      <c r="U1" s="311"/>
+      <c r="V1" s="311"/>
+      <c r="W1" s="312"/>
     </row>
     <row r="2" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="177"/>
@@ -6605,25 +6605,25 @@
     <row r="5" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="180"/>
       <c r="B5" s="181"/>
-      <c r="C5" s="322"/>
-      <c r="D5" s="323"/>
-      <c r="E5" s="323"/>
-      <c r="F5" s="323"/>
-      <c r="G5" s="323"/>
-      <c r="H5" s="323"/>
-      <c r="I5" s="323"/>
-      <c r="J5" s="324"/>
+      <c r="C5" s="313"/>
+      <c r="D5" s="314"/>
+      <c r="E5" s="314"/>
+      <c r="F5" s="314"/>
+      <c r="G5" s="314"/>
+      <c r="H5" s="314"/>
+      <c r="I5" s="314"/>
+      <c r="J5" s="315"/>
       <c r="K5" s="181"/>
       <c r="L5" s="181"/>
       <c r="M5" s="181"/>
       <c r="N5" s="181"/>
-      <c r="O5" s="322"/>
-      <c r="P5" s="324"/>
+      <c r="O5" s="313"/>
+      <c r="P5" s="315"/>
       <c r="Q5" s="181"/>
-      <c r="R5" s="322"/>
-      <c r="S5" s="323"/>
-      <c r="T5" s="323"/>
-      <c r="U5" s="324"/>
+      <c r="R5" s="313"/>
+      <c r="S5" s="314"/>
+      <c r="T5" s="314"/>
+      <c r="U5" s="315"/>
       <c r="V5" s="181"/>
       <c r="W5" s="184"/>
     </row>
@@ -6655,14 +6655,14 @@
     <row r="7" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="185"/>
       <c r="B7" s="181"/>
-      <c r="C7" s="322"/>
-      <c r="D7" s="323"/>
-      <c r="E7" s="323"/>
-      <c r="F7" s="323"/>
-      <c r="G7" s="323"/>
-      <c r="H7" s="323"/>
-      <c r="I7" s="323"/>
-      <c r="J7" s="324"/>
+      <c r="C7" s="313"/>
+      <c r="D7" s="314"/>
+      <c r="E7" s="314"/>
+      <c r="F7" s="314"/>
+      <c r="G7" s="314"/>
+      <c r="H7" s="314"/>
+      <c r="I7" s="314"/>
+      <c r="J7" s="315"/>
       <c r="K7" s="181"/>
       <c r="L7" s="181"/>
       <c r="M7" s="181"/>
@@ -6703,31 +6703,31 @@
       <c r="W8" s="190"/>
     </row>
     <row r="9" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="328" t="s">
+      <c r="A9" s="308" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="328"/>
-      <c r="C9" s="328"/>
-      <c r="D9" s="328"/>
-      <c r="E9" s="328"/>
-      <c r="F9" s="328"/>
-      <c r="G9" s="328"/>
-      <c r="H9" s="328"/>
-      <c r="I9" s="328"/>
-      <c r="J9" s="328"/>
-      <c r="K9" s="328"/>
-      <c r="L9" s="328"/>
-      <c r="M9" s="328"/>
-      <c r="N9" s="328"/>
-      <c r="O9" s="328"/>
-      <c r="P9" s="328"/>
-      <c r="Q9" s="328"/>
-      <c r="R9" s="328"/>
-      <c r="S9" s="328"/>
-      <c r="T9" s="328"/>
-      <c r="U9" s="328"/>
-      <c r="V9" s="328"/>
-      <c r="W9" s="329"/>
+      <c r="B9" s="308"/>
+      <c r="C9" s="308"/>
+      <c r="D9" s="308"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="308"/>
+      <c r="G9" s="308"/>
+      <c r="H9" s="308"/>
+      <c r="I9" s="308"/>
+      <c r="J9" s="308"/>
+      <c r="K9" s="308"/>
+      <c r="L9" s="308"/>
+      <c r="M9" s="308"/>
+      <c r="N9" s="308"/>
+      <c r="O9" s="308"/>
+      <c r="P9" s="308"/>
+      <c r="Q9" s="308"/>
+      <c r="R9" s="308"/>
+      <c r="S9" s="308"/>
+      <c r="T9" s="308"/>
+      <c r="U9" s="308"/>
+      <c r="V9" s="308"/>
+      <c r="W9" s="309"/>
     </row>
     <row r="10" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="191"/>
@@ -6790,14 +6790,14 @@
     <row r="12" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="185"/>
       <c r="B12" s="181"/>
-      <c r="C12" s="322"/>
-      <c r="D12" s="323"/>
-      <c r="E12" s="323"/>
-      <c r="F12" s="323"/>
-      <c r="G12" s="323"/>
-      <c r="H12" s="323"/>
-      <c r="I12" s="323"/>
-      <c r="J12" s="324"/>
+      <c r="C12" s="313"/>
+      <c r="D12" s="314"/>
+      <c r="E12" s="314"/>
+      <c r="F12" s="314"/>
+      <c r="G12" s="314"/>
+      <c r="H12" s="314"/>
+      <c r="I12" s="314"/>
+      <c r="J12" s="315"/>
       <c r="K12" s="181"/>
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
@@ -6844,14 +6844,14 @@
     <row r="14" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="185"/>
       <c r="B14" s="181"/>
-      <c r="C14" s="322"/>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="323"/>
-      <c r="J14" s="324"/>
+      <c r="C14" s="313"/>
+      <c r="D14" s="314"/>
+      <c r="E14" s="314"/>
+      <c r="F14" s="314"/>
+      <c r="G14" s="314"/>
+      <c r="H14" s="314"/>
+      <c r="I14" s="314"/>
+      <c r="J14" s="315"/>
       <c r="K14" s="181"/>
       <c r="L14" s="181"/>
       <c r="M14" s="181"/>
@@ -6918,26 +6918,26 @@
       <c r="P16" s="182"/>
       <c r="Q16" s="182"/>
       <c r="R16" s="181"/>
-      <c r="S16" s="325">
+      <c r="S16" s="319">
         <f>Admin!B4</f>
-        <v>45388</v>
-      </c>
-      <c r="T16" s="326"/>
-      <c r="U16" s="326"/>
-      <c r="V16" s="326"/>
+        <v>45753</v>
+      </c>
+      <c r="T16" s="320"/>
+      <c r="U16" s="320"/>
+      <c r="V16" s="320"/>
       <c r="W16" s="187"/>
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="185"/>
       <c r="B17" s="181"/>
-      <c r="C17" s="322"/>
-      <c r="D17" s="323"/>
-      <c r="E17" s="323"/>
-      <c r="F17" s="323"/>
-      <c r="G17" s="323"/>
-      <c r="H17" s="323"/>
-      <c r="I17" s="323"/>
-      <c r="J17" s="324"/>
+      <c r="C17" s="313"/>
+      <c r="D17" s="314"/>
+      <c r="E17" s="314"/>
+      <c r="F17" s="314"/>
+      <c r="G17" s="314"/>
+      <c r="H17" s="314"/>
+      <c r="I17" s="314"/>
+      <c r="J17" s="315"/>
       <c r="K17" s="181"/>
       <c r="L17" s="181"/>
       <c r="M17" s="181"/>
@@ -6982,21 +6982,21 @@
     <row r="19" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A19" s="185"/>
       <c r="B19" s="181"/>
-      <c r="C19" s="322"/>
-      <c r="D19" s="323"/>
-      <c r="E19" s="323"/>
-      <c r="F19" s="323"/>
-      <c r="G19" s="323"/>
-      <c r="H19" s="323"/>
-      <c r="I19" s="323"/>
-      <c r="J19" s="324"/>
+      <c r="C19" s="313"/>
+      <c r="D19" s="314"/>
+      <c r="E19" s="314"/>
+      <c r="F19" s="314"/>
+      <c r="G19" s="314"/>
+      <c r="H19" s="314"/>
+      <c r="I19" s="314"/>
+      <c r="J19" s="315"/>
       <c r="K19" s="181"/>
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
-      <c r="N19" s="313"/>
-      <c r="O19" s="314"/>
-      <c r="P19" s="314"/>
-      <c r="Q19" s="315"/>
+      <c r="N19" s="316"/>
+      <c r="O19" s="317"/>
+      <c r="P19" s="317"/>
+      <c r="Q19" s="318"/>
       <c r="R19" s="181"/>
       <c r="S19" s="181"/>
       <c r="T19" s="181"/>
@@ -7032,14 +7032,14 @@
     <row r="21" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A21" s="185"/>
       <c r="B21" s="181"/>
-      <c r="C21" s="322"/>
-      <c r="D21" s="323"/>
-      <c r="E21" s="323"/>
-      <c r="F21" s="323"/>
-      <c r="G21" s="323"/>
-      <c r="H21" s="323"/>
-      <c r="I21" s="323"/>
-      <c r="J21" s="324"/>
+      <c r="C21" s="313"/>
+      <c r="D21" s="314"/>
+      <c r="E21" s="314"/>
+      <c r="F21" s="314"/>
+      <c r="G21" s="314"/>
+      <c r="H21" s="314"/>
+      <c r="I21" s="314"/>
+      <c r="J21" s="315"/>
       <c r="K21" s="181"/>
       <c r="L21" s="194">
         <v>7</v>
@@ -7052,13 +7052,13 @@
       <c r="P21" s="182"/>
       <c r="Q21" s="182"/>
       <c r="R21" s="181"/>
-      <c r="S21" s="325">
+      <c r="S21" s="319">
         <f>Admin!B17</f>
-        <v>45752</v>
-      </c>
-      <c r="T21" s="326"/>
-      <c r="U21" s="326"/>
-      <c r="V21" s="326"/>
+        <v>46117</v>
+      </c>
+      <c r="T21" s="320"/>
+      <c r="U21" s="320"/>
+      <c r="V21" s="320"/>
       <c r="W21" s="187"/>
     </row>
     <row r="22" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
@@ -7075,17 +7075,17 @@
       <c r="K22" s="181"/>
       <c r="L22" s="181"/>
       <c r="M22" s="181"/>
-      <c r="N22" s="327" t="s">
+      <c r="N22" s="321" t="s">
         <v>157</v>
       </c>
-      <c r="O22" s="327"/>
-      <c r="P22" s="327"/>
-      <c r="Q22" s="327"/>
-      <c r="R22" s="327"/>
-      <c r="S22" s="327"/>
-      <c r="T22" s="327"/>
-      <c r="U22" s="327"/>
-      <c r="V22" s="327"/>
+      <c r="O22" s="321"/>
+      <c r="P22" s="321"/>
+      <c r="Q22" s="321"/>
+      <c r="R22" s="321"/>
+      <c r="S22" s="321"/>
+      <c r="T22" s="321"/>
+      <c r="U22" s="321"/>
+      <c r="V22" s="321"/>
       <c r="W22" s="199"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.15">
@@ -7106,15 +7106,15 @@
       <c r="K23" s="181"/>
       <c r="L23" s="181"/>
       <c r="M23" s="181"/>
-      <c r="N23" s="327"/>
-      <c r="O23" s="327"/>
-      <c r="P23" s="327"/>
-      <c r="Q23" s="327"/>
-      <c r="R23" s="327"/>
-      <c r="S23" s="327"/>
-      <c r="T23" s="327"/>
-      <c r="U23" s="327"/>
-      <c r="V23" s="327"/>
+      <c r="N23" s="321"/>
+      <c r="O23" s="321"/>
+      <c r="P23" s="321"/>
+      <c r="Q23" s="321"/>
+      <c r="R23" s="321"/>
+      <c r="S23" s="321"/>
+      <c r="T23" s="321"/>
+      <c r="U23" s="321"/>
+      <c r="V23" s="321"/>
       <c r="W23" s="199"/>
     </row>
     <row r="24" spans="1:23" ht="14" x14ac:dyDescent="0.15">
@@ -7133,10 +7133,10 @@
       <c r="K24" s="181"/>
       <c r="L24" s="181"/>
       <c r="M24" s="181"/>
-      <c r="N24" s="313"/>
-      <c r="O24" s="314"/>
-      <c r="P24" s="314"/>
-      <c r="Q24" s="315"/>
+      <c r="N24" s="316"/>
+      <c r="O24" s="317"/>
+      <c r="P24" s="317"/>
+      <c r="Q24" s="318"/>
       <c r="R24" s="181"/>
       <c r="S24" s="181"/>
       <c r="T24" s="181"/>
@@ -7147,14 +7147,14 @@
     <row r="25" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A25" s="185"/>
       <c r="B25" s="181"/>
-      <c r="C25" s="322"/>
-      <c r="D25" s="323"/>
-      <c r="E25" s="323"/>
-      <c r="F25" s="323"/>
-      <c r="G25" s="323"/>
-      <c r="H25" s="323"/>
-      <c r="I25" s="323"/>
-      <c r="J25" s="324"/>
+      <c r="C25" s="313"/>
+      <c r="D25" s="314"/>
+      <c r="E25" s="314"/>
+      <c r="F25" s="314"/>
+      <c r="G25" s="314"/>
+      <c r="H25" s="314"/>
+      <c r="I25" s="314"/>
+      <c r="J25" s="315"/>
       <c r="K25" s="181"/>
       <c r="L25" s="194">
         <v>8</v>
@@ -7203,21 +7203,21 @@
     <row r="27" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A27" s="185"/>
       <c r="B27" s="181"/>
-      <c r="C27" s="322"/>
-      <c r="D27" s="323"/>
-      <c r="E27" s="323"/>
-      <c r="F27" s="323"/>
-      <c r="G27" s="323"/>
-      <c r="H27" s="323"/>
-      <c r="I27" s="323"/>
-      <c r="J27" s="324"/>
+      <c r="C27" s="313"/>
+      <c r="D27" s="314"/>
+      <c r="E27" s="314"/>
+      <c r="F27" s="314"/>
+      <c r="G27" s="314"/>
+      <c r="H27" s="314"/>
+      <c r="I27" s="314"/>
+      <c r="J27" s="315"/>
       <c r="K27" s="181"/>
       <c r="L27" s="181"/>
       <c r="M27" s="181"/>
-      <c r="N27" s="313"/>
-      <c r="O27" s="314"/>
-      <c r="P27" s="314"/>
-      <c r="Q27" s="315"/>
+      <c r="N27" s="316"/>
+      <c r="O27" s="317"/>
+      <c r="P27" s="317"/>
+      <c r="Q27" s="318"/>
       <c r="R27" s="181"/>
       <c r="S27" s="181"/>
       <c r="T27" s="181"/>
@@ -7286,8 +7286,8 @@
     <row r="30" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A30" s="185"/>
       <c r="B30" s="181"/>
-      <c r="C30" s="308"/>
-      <c r="D30" s="309"/>
+      <c r="C30" s="322"/>
+      <c r="D30" s="323"/>
       <c r="E30" s="181"/>
       <c r="F30" s="204"/>
       <c r="G30" s="181"/>
@@ -7351,13 +7351,13 @@
       <c r="K32" s="181"/>
       <c r="L32" s="181"/>
       <c r="M32" s="181"/>
-      <c r="N32" s="313">
+      <c r="N32" s="316">
         <f>Admin!B17</f>
-        <v>45752</v>
-      </c>
-      <c r="O32" s="314"/>
-      <c r="P32" s="314"/>
-      <c r="Q32" s="315"/>
+        <v>46117</v>
+      </c>
+      <c r="O32" s="317"/>
+      <c r="P32" s="317"/>
+      <c r="Q32" s="318"/>
       <c r="R32" s="181"/>
       <c r="S32" s="181"/>
       <c r="T32" s="181"/>
@@ -7391,31 +7391,31 @@
       <c r="W33" s="207"/>
     </row>
     <row r="34" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="316" t="s">
+      <c r="A34" s="327" t="s">
         <v>166</v>
       </c>
-      <c r="B34" s="316"/>
-      <c r="C34" s="316"/>
-      <c r="D34" s="316"/>
-      <c r="E34" s="316"/>
-      <c r="F34" s="316"/>
-      <c r="G34" s="316"/>
-      <c r="H34" s="316"/>
-      <c r="I34" s="316"/>
-      <c r="J34" s="316"/>
-      <c r="K34" s="316"/>
-      <c r="L34" s="316"/>
-      <c r="M34" s="316"/>
-      <c r="N34" s="316"/>
-      <c r="O34" s="316"/>
-      <c r="P34" s="316"/>
-      <c r="Q34" s="316"/>
-      <c r="R34" s="316"/>
-      <c r="S34" s="316"/>
-      <c r="T34" s="316"/>
-      <c r="U34" s="316"/>
-      <c r="V34" s="316"/>
-      <c r="W34" s="316"/>
+      <c r="B34" s="327"/>
+      <c r="C34" s="327"/>
+      <c r="D34" s="327"/>
+      <c r="E34" s="327"/>
+      <c r="F34" s="327"/>
+      <c r="G34" s="327"/>
+      <c r="H34" s="327"/>
+      <c r="I34" s="327"/>
+      <c r="J34" s="327"/>
+      <c r="K34" s="327"/>
+      <c r="L34" s="327"/>
+      <c r="M34" s="327"/>
+      <c r="N34" s="327"/>
+      <c r="O34" s="327"/>
+      <c r="P34" s="327"/>
+      <c r="Q34" s="327"/>
+      <c r="R34" s="327"/>
+      <c r="S34" s="327"/>
+      <c r="T34" s="327"/>
+      <c r="U34" s="327"/>
+      <c r="V34" s="327"/>
+      <c r="W34" s="327"/>
     </row>
     <row r="35" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="191"/>
@@ -7601,7 +7601,7 @@
       <c r="M41" s="181"/>
       <c r="N41" s="182" t="str">
         <f>"If you have provided the information about your " &amp; Admin!G2</f>
-        <v>If you have provided the information about your 2024-25</v>
+        <v>If you have provided the information about your 2025-26</v>
       </c>
       <c r="O41" s="182"/>
       <c r="P41" s="182"/>
@@ -7835,11 +7835,11 @@
       <c r="C50" s="209" t="s">
         <v>51</v>
       </c>
-      <c r="D50" s="317">
-        <v>0</v>
-      </c>
-      <c r="E50" s="318"/>
-      <c r="F50" s="319"/>
+      <c r="D50" s="328">
+        <v>0</v>
+      </c>
+      <c r="E50" s="329"/>
+      <c r="F50" s="330"/>
       <c r="G50" s="210" t="s">
         <v>178</v>
       </c>
@@ -7856,9 +7856,9 @@
       <c r="N50" s="209" t="s">
         <v>51</v>
       </c>
-      <c r="O50" s="317"/>
-      <c r="P50" s="320"/>
-      <c r="Q50" s="321"/>
+      <c r="O50" s="328"/>
+      <c r="P50" s="331"/>
+      <c r="Q50" s="332"/>
       <c r="R50" s="210" t="s">
         <v>178</v>
       </c>
@@ -7986,12 +7986,12 @@
       <c r="C55" s="209" t="s">
         <v>51</v>
       </c>
-      <c r="D55" s="310">
+      <c r="D55" s="324">
         <f>'SE Short'!O94</f>
         <v>0</v>
       </c>
-      <c r="E55" s="311"/>
-      <c r="F55" s="312"/>
+      <c r="E55" s="325"/>
+      <c r="F55" s="326"/>
       <c r="G55" s="210" t="s">
         <v>178</v>
       </c>
@@ -8008,12 +8008,12 @@
       <c r="N55" s="209" t="s">
         <v>51</v>
       </c>
-      <c r="O55" s="310">
+      <c r="O55" s="324">
         <f>D50-D55+'SE Short'!O106</f>
         <v>0</v>
       </c>
-      <c r="P55" s="311"/>
-      <c r="Q55" s="312"/>
+      <c r="P55" s="325"/>
+      <c r="Q55" s="326"/>
       <c r="R55" s="210" t="s">
         <v>178</v>
       </c>
@@ -8054,12 +8054,13 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A9:W9"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="R5:U5"/>
-    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="O55:Q55"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="A34:W34"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="O50:Q50"/>
     <mergeCell ref="C27:J27"/>
     <mergeCell ref="N27:Q27"/>
     <mergeCell ref="C12:J12"/>
@@ -8073,13 +8074,12 @@
     <mergeCell ref="N22:V23"/>
     <mergeCell ref="N24:Q24"/>
     <mergeCell ref="C25:J25"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="O55:Q55"/>
-    <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="A34:W34"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="O50:Q50"/>
+    <mergeCell ref="A9:W9"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="R5:U5"/>
+    <mergeCell ref="C7:J7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -8130,27 +8130,27 @@
     <row r="2" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="147"/>
       <c r="B2" s="164">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="C2" s="147"/>
-      <c r="D2" s="454" t="s">
+      <c r="D2" s="449" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="454"/>
-      <c r="F2" s="454"/>
+      <c r="E2" s="449"/>
+      <c r="F2" s="449"/>
       <c r="G2" s="287" t="str">
         <f>B23</f>
-        <v>2024-25</v>
+        <v>2025-26</v>
       </c>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
-      <c r="J2" s="449" t="s">
+      <c r="J2" s="454" t="s">
         <v>120</v>
       </c>
-      <c r="K2" s="449"/>
+      <c r="K2" s="454"/>
       <c r="L2" s="165" t="str">
         <f>G2</f>
-        <v>2024-25</v>
+        <v>2025-26</v>
       </c>
       <c r="M2" s="147"/>
       <c r="N2" s="147"/>
@@ -8320,8 +8320,8 @@
       <c r="I9" s="450" t="s">
         <v>122</v>
       </c>
-      <c r="J9" s="451"/>
-      <c r="K9" s="451"/>
+      <c r="J9" s="455"/>
+      <c r="K9" s="455"/>
       <c r="L9" s="149" t="s">
         <v>123</v>
       </c>
@@ -8358,11 +8358,11 @@
         <v>45596</v>
       </c>
       <c r="C11" s="147"/>
-      <c r="D11" s="454" t="s">
+      <c r="D11" s="449" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="454"/>
-      <c r="F11" s="454"/>
+      <c r="E11" s="449"/>
+      <c r="F11" s="449"/>
       <c r="G11" s="146" t="s">
         <v>116</v>
       </c>
@@ -8451,14 +8451,14 @@
         <v>0.1</v>
       </c>
       <c r="H14" s="147"/>
-      <c r="I14" s="452" t="s">
+      <c r="I14" s="456" t="s">
         <v>132</v>
       </c>
-      <c r="J14" s="452"/>
-      <c r="K14" s="452"/>
+      <c r="J14" s="456"/>
+      <c r="K14" s="456"/>
       <c r="L14" s="167" t="str">
         <f>G2</f>
-        <v>2024-25</v>
+        <v>2025-26</v>
       </c>
       <c r="M14" s="147"/>
       <c r="N14" s="147"/>
@@ -8511,7 +8511,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="147" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N16" s="147"/>
       <c r="O16" s="147"/>
@@ -8564,10 +8564,10 @@
         <v>45808</v>
       </c>
       <c r="C19" s="147"/>
-      <c r="D19" s="454" t="s">
+      <c r="D19" s="449" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="454"/>
+      <c r="E19" s="449"/>
       <c r="F19" s="146" t="s">
         <v>119</v>
       </c>
@@ -8575,13 +8575,13 @@
         <v>115</v>
       </c>
       <c r="H19" s="147"/>
-      <c r="I19" s="455" t="s">
+      <c r="I19" s="452" t="s">
         <v>134</v>
       </c>
-      <c r="J19" s="455"/>
-      <c r="K19" s="455"/>
+      <c r="J19" s="452"/>
+      <c r="K19" s="452"/>
       <c r="L19" s="147"/>
-      <c r="M19" s="456" t="s">
+      <c r="M19" s="451" t="s">
         <v>400</v>
       </c>
       <c r="N19" s="147"/>
@@ -8598,13 +8598,13 @@
       <c r="F20" s="146"/>
       <c r="G20" s="146"/>
       <c r="H20" s="147"/>
-      <c r="I20" s="455"/>
-      <c r="J20" s="455"/>
-      <c r="K20" s="455"/>
+      <c r="I20" s="452"/>
+      <c r="J20" s="452"/>
+      <c r="K20" s="452"/>
       <c r="L20" s="295">
         <v>0.06</v>
       </c>
-      <c r="M20" s="456"/>
+      <c r="M20" s="451"/>
       <c r="N20" s="152">
         <v>12570</v>
       </c>
@@ -8654,13 +8654,13 @@
         <v>0.25</v>
       </c>
       <c r="H22" s="147"/>
-      <c r="I22" s="455" t="s">
+      <c r="I22" s="452" t="s">
         <v>135</v>
       </c>
-      <c r="J22" s="455"/>
-      <c r="K22" s="455"/>
+      <c r="J22" s="452"/>
+      <c r="K22" s="452"/>
       <c r="L22" s="147"/>
-      <c r="M22" s="456" t="s">
+      <c r="M22" s="451" t="s">
         <v>401</v>
       </c>
       <c r="N22" s="147"/>
@@ -8668,8 +8668,10 @@
     </row>
     <row r="23" spans="1:15" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="147"/>
-      <c r="B23" s="175" t="s">
-        <v>406</v>
+      <c r="B23" s="175" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
       </c>
       <c r="C23" s="147"/>
       <c r="D23" s="147"/>
@@ -8677,13 +8679,13 @@
       <c r="F23" s="146"/>
       <c r="G23" s="170"/>
       <c r="H23" s="147"/>
-      <c r="I23" s="455"/>
-      <c r="J23" s="455"/>
-      <c r="K23" s="455"/>
+      <c r="I23" s="452"/>
+      <c r="J23" s="452"/>
+      <c r="K23" s="452"/>
       <c r="L23" s="295">
         <v>0.02</v>
       </c>
-      <c r="M23" s="456"/>
+      <c r="M23" s="451"/>
       <c r="N23" s="152">
         <v>50270</v>
       </c>
@@ -8693,14 +8695,16 @@
     </row>
     <row r="24" spans="1:15" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A24" s="147"/>
-      <c r="B24" s="175" t="s">
-        <v>437</v>
+      <c r="B24" s="175" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
       </c>
       <c r="C24" s="147"/>
-      <c r="D24" s="454" t="s">
+      <c r="D24" s="449" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="454"/>
+      <c r="E24" s="449"/>
       <c r="F24" s="147"/>
       <c r="G24" s="147"/>
       <c r="H24" s="147"/>
@@ -8790,12 +8794,19 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="I22:K23"/>
-    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="I16:K16"/>
     <mergeCell ref="I19:K20"/>
     <mergeCell ref="D19:E19"/>
@@ -8803,19 +8814,12 @@
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="I22:K23"/>
+    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8853,120 +8857,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="363" t="s">
+      <c r="A1" s="333" t="s">
         <v>306</v>
       </c>
-      <c r="B1" s="364"/>
-      <c r="C1" s="364"/>
-      <c r="D1" s="364"/>
-      <c r="E1" s="364"/>
-      <c r="F1" s="364"/>
-      <c r="G1" s="365" t="s">
-        <v>407</v>
-      </c>
-      <c r="H1" s="366"/>
-      <c r="I1" s="366"/>
-      <c r="J1" s="366"/>
-      <c r="K1" s="366"/>
-      <c r="L1" s="366"/>
-      <c r="M1" s="366"/>
-      <c r="N1" s="367"/>
-      <c r="O1" s="368" t="s">
+      <c r="B1" s="334"/>
+      <c r="C1" s="334"/>
+      <c r="D1" s="334"/>
+      <c r="E1" s="334"/>
+      <c r="F1" s="334"/>
+      <c r="G1" s="335" t="s">
+        <v>438</v>
+      </c>
+      <c r="H1" s="336"/>
+      <c r="I1" s="336"/>
+      <c r="J1" s="336"/>
+      <c r="K1" s="336"/>
+      <c r="L1" s="336"/>
+      <c r="M1" s="336"/>
+      <c r="N1" s="337"/>
+      <c r="O1" s="338" t="s">
         <v>307</v>
       </c>
-      <c r="P1" s="368"/>
-      <c r="Q1" s="368"/>
-      <c r="R1" s="368"/>
-      <c r="S1" s="368"/>
-      <c r="T1" s="368"/>
-      <c r="U1" s="368"/>
-      <c r="V1" s="368"/>
-      <c r="W1" s="368"/>
+      <c r="P1" s="338"/>
+      <c r="Q1" s="338"/>
+      <c r="R1" s="338"/>
+      <c r="S1" s="338"/>
+      <c r="T1" s="338"/>
+      <c r="U1" s="338"/>
+      <c r="V1" s="338"/>
+      <c r="W1" s="338"/>
     </row>
     <row r="2" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="364"/>
-      <c r="B2" s="364"/>
-      <c r="C2" s="364"/>
-      <c r="D2" s="364"/>
-      <c r="E2" s="364"/>
-      <c r="F2" s="364"/>
-      <c r="G2" s="366"/>
-      <c r="H2" s="366"/>
-      <c r="I2" s="366"/>
-      <c r="J2" s="366"/>
-      <c r="K2" s="366"/>
-      <c r="L2" s="366"/>
-      <c r="M2" s="366"/>
-      <c r="N2" s="367"/>
-      <c r="O2" s="369" t="s">
+      <c r="A2" s="334"/>
+      <c r="B2" s="334"/>
+      <c r="C2" s="334"/>
+      <c r="D2" s="334"/>
+      <c r="E2" s="334"/>
+      <c r="F2" s="334"/>
+      <c r="G2" s="336"/>
+      <c r="H2" s="336"/>
+      <c r="I2" s="336"/>
+      <c r="J2" s="336"/>
+      <c r="K2" s="336"/>
+      <c r="L2" s="336"/>
+      <c r="M2" s="336"/>
+      <c r="N2" s="337"/>
+      <c r="O2" s="339" t="s">
         <v>184</v>
       </c>
-      <c r="P2" s="369"/>
-      <c r="Q2" s="370">
+      <c r="P2" s="339"/>
+      <c r="Q2" s="340">
         <f>Admin!B4</f>
-        <v>45388</v>
-      </c>
-      <c r="R2" s="371"/>
-      <c r="S2" s="371"/>
-      <c r="T2" s="371"/>
+        <v>45753</v>
+      </c>
+      <c r="R2" s="341"/>
+      <c r="S2" s="341"/>
+      <c r="T2" s="341"/>
       <c r="U2" s="222" t="s">
         <v>185</v>
       </c>
-      <c r="V2" s="370">
+      <c r="V2" s="340">
         <f>Admin!B17</f>
-        <v>45752</v>
-      </c>
-      <c r="W2" s="370"/>
+        <v>46117</v>
+      </c>
+      <c r="W2" s="340"/>
     </row>
     <row r="3" spans="1:23" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="353"/>
-      <c r="B3" s="354"/>
-      <c r="C3" s="354"/>
-      <c r="D3" s="354"/>
-      <c r="E3" s="354"/>
-      <c r="F3" s="354"/>
-      <c r="G3" s="354"/>
-      <c r="H3" s="354"/>
-      <c r="I3" s="354"/>
-      <c r="J3" s="354"/>
-      <c r="K3" s="354"/>
-      <c r="L3" s="354"/>
-      <c r="M3" s="354"/>
-      <c r="N3" s="354"/>
-      <c r="O3" s="354"/>
-      <c r="P3" s="354"/>
-      <c r="Q3" s="354"/>
-      <c r="R3" s="354"/>
-      <c r="S3" s="354"/>
-      <c r="T3" s="354"/>
-      <c r="U3" s="354"/>
-      <c r="V3" s="354"/>
-      <c r="W3" s="354"/>
+      <c r="A3" s="345"/>
+      <c r="B3" s="346"/>
+      <c r="C3" s="346"/>
+      <c r="D3" s="346"/>
+      <c r="E3" s="346"/>
+      <c r="F3" s="346"/>
+      <c r="G3" s="346"/>
+      <c r="H3" s="346"/>
+      <c r="I3" s="346"/>
+      <c r="J3" s="346"/>
+      <c r="K3" s="346"/>
+      <c r="L3" s="346"/>
+      <c r="M3" s="346"/>
+      <c r="N3" s="346"/>
+      <c r="O3" s="346"/>
+      <c r="P3" s="346"/>
+      <c r="Q3" s="346"/>
+      <c r="R3" s="346"/>
+      <c r="S3" s="346"/>
+      <c r="T3" s="346"/>
+      <c r="U3" s="346"/>
+      <c r="V3" s="346"/>
+      <c r="W3" s="346"/>
     </row>
     <row r="4" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="355"/>
-      <c r="B4" s="355"/>
-      <c r="C4" s="355"/>
-      <c r="D4" s="355"/>
-      <c r="E4" s="355"/>
-      <c r="F4" s="355"/>
-      <c r="G4" s="355"/>
-      <c r="H4" s="355"/>
-      <c r="I4" s="355"/>
-      <c r="J4" s="355"/>
-      <c r="K4" s="355"/>
-      <c r="L4" s="355"/>
-      <c r="M4" s="355"/>
-      <c r="N4" s="355"/>
-      <c r="O4" s="355"/>
-      <c r="P4" s="355"/>
-      <c r="Q4" s="355"/>
-      <c r="R4" s="355"/>
-      <c r="S4" s="355"/>
-      <c r="T4" s="355"/>
-      <c r="U4" s="355"/>
-      <c r="V4" s="355"/>
-      <c r="W4" s="356"/>
+      <c r="A4" s="347"/>
+      <c r="B4" s="347"/>
+      <c r="C4" s="347"/>
+      <c r="D4" s="347"/>
+      <c r="E4" s="347"/>
+      <c r="F4" s="347"/>
+      <c r="G4" s="347"/>
+      <c r="H4" s="347"/>
+      <c r="I4" s="347"/>
+      <c r="J4" s="347"/>
+      <c r="K4" s="347"/>
+      <c r="L4" s="347"/>
+      <c r="M4" s="347"/>
+      <c r="N4" s="347"/>
+      <c r="O4" s="347"/>
+      <c r="P4" s="347"/>
+      <c r="Q4" s="347"/>
+      <c r="R4" s="347"/>
+      <c r="S4" s="347"/>
+      <c r="T4" s="347"/>
+      <c r="U4" s="347"/>
+      <c r="V4" s="347"/>
+      <c r="W4" s="348"/>
     </row>
     <row r="5" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="223"/>
@@ -9050,34 +9054,34 @@
     <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="226"/>
       <c r="B8" s="220"/>
-      <c r="C8" s="357" t="str">
+      <c r="C8" s="349" t="str">
         <f>IF('Business Details'!C5&gt;0,'Business Details'!C5:J5," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D8" s="358"/>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="G8" s="358"/>
-      <c r="H8" s="358"/>
-      <c r="I8" s="358"/>
-      <c r="J8" s="359"/>
+      <c r="D8" s="350"/>
+      <c r="E8" s="350"/>
+      <c r="F8" s="350"/>
+      <c r="G8" s="350"/>
+      <c r="H8" s="350"/>
+      <c r="I8" s="350"/>
+      <c r="J8" s="351"/>
       <c r="K8" s="220"/>
       <c r="L8" s="220"/>
       <c r="M8" s="220"/>
       <c r="N8" s="220"/>
-      <c r="O8" s="322" t="str">
+      <c r="O8" s="313" t="str">
         <f>IF('Business Details'!O5&gt;0,'Business Details'!O5," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="P8" s="324"/>
+      <c r="P8" s="315"/>
       <c r="Q8" s="181"/>
-      <c r="R8" s="322" t="str">
+      <c r="R8" s="313" t="str">
         <f>IF('Business Details'!R5&gt;0,'Business Details'!R5," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="S8" s="323"/>
-      <c r="T8" s="323"/>
-      <c r="U8" s="324"/>
+      <c r="S8" s="314"/>
+      <c r="T8" s="314"/>
+      <c r="U8" s="315"/>
       <c r="V8" s="220"/>
       <c r="W8" s="229"/>
     </row>
@@ -9107,31 +9111,31 @@
       <c r="W9" s="232"/>
     </row>
     <row r="10" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="360" t="s">
+      <c r="A10" s="352" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="360"/>
-      <c r="C10" s="360"/>
-      <c r="D10" s="360"/>
-      <c r="E10" s="360"/>
-      <c r="F10" s="360"/>
-      <c r="G10" s="360"/>
-      <c r="H10" s="360"/>
-      <c r="I10" s="360"/>
-      <c r="J10" s="360"/>
-      <c r="K10" s="360"/>
-      <c r="L10" s="360"/>
-      <c r="M10" s="360"/>
-      <c r="N10" s="360"/>
-      <c r="O10" s="360"/>
-      <c r="P10" s="360"/>
-      <c r="Q10" s="360"/>
-      <c r="R10" s="360"/>
-      <c r="S10" s="360"/>
-      <c r="T10" s="360"/>
-      <c r="U10" s="360"/>
-      <c r="V10" s="360"/>
-      <c r="W10" s="360"/>
+      <c r="B10" s="352"/>
+      <c r="C10" s="352"/>
+      <c r="D10" s="352"/>
+      <c r="E10" s="352"/>
+      <c r="F10" s="352"/>
+      <c r="G10" s="352"/>
+      <c r="H10" s="352"/>
+      <c r="I10" s="352"/>
+      <c r="J10" s="352"/>
+      <c r="K10" s="352"/>
+      <c r="L10" s="352"/>
+      <c r="M10" s="352"/>
+      <c r="N10" s="352"/>
+      <c r="O10" s="352"/>
+      <c r="P10" s="352"/>
+      <c r="Q10" s="352"/>
+      <c r="R10" s="352"/>
+      <c r="S10" s="352"/>
+      <c r="T10" s="352"/>
+      <c r="U10" s="352"/>
+      <c r="V10" s="352"/>
+      <c r="W10" s="352"/>
     </row>
     <row r="11" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="233"/>
@@ -9194,17 +9198,17 @@
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="240"/>
       <c r="B13" s="220"/>
-      <c r="C13" s="357" t="str">
+      <c r="C13" s="349" t="str">
         <f>IF('Business Details'!C17&gt;0,'Business Details'!C17," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D13" s="358"/>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="G13" s="358"/>
-      <c r="H13" s="358"/>
-      <c r="I13" s="358"/>
-      <c r="J13" s="359"/>
+      <c r="D13" s="350"/>
+      <c r="E13" s="350"/>
+      <c r="F13" s="350"/>
+      <c r="G13" s="350"/>
+      <c r="H13" s="350"/>
+      <c r="I13" s="350"/>
+      <c r="J13" s="351"/>
       <c r="K13" s="220"/>
       <c r="L13" s="220"/>
       <c r="M13" s="220"/>
@@ -9249,17 +9253,17 @@
     <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="240"/>
       <c r="B15" s="220"/>
-      <c r="C15" s="357" t="str">
+      <c r="C15" s="349" t="str">
         <f>IF('Business Details'!C19&gt;0,'Business Details'!C19," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D15" s="358"/>
-      <c r="E15" s="358"/>
-      <c r="F15" s="358"/>
-      <c r="G15" s="358"/>
-      <c r="H15" s="358"/>
-      <c r="I15" s="358"/>
-      <c r="J15" s="359"/>
+      <c r="D15" s="350"/>
+      <c r="E15" s="350"/>
+      <c r="F15" s="350"/>
+      <c r="G15" s="350"/>
+      <c r="H15" s="350"/>
+      <c r="I15" s="350"/>
+      <c r="J15" s="351"/>
       <c r="K15" s="220"/>
       <c r="L15" s="220"/>
       <c r="M15" s="220"/>
@@ -9305,17 +9309,17 @@
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="240"/>
       <c r="B17" s="220"/>
-      <c r="C17" s="357" t="str">
+      <c r="C17" s="349" t="str">
         <f>IF('Business Details'!C21&gt;0,'Business Details'!C21," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D17" s="358"/>
-      <c r="E17" s="358"/>
-      <c r="F17" s="358"/>
-      <c r="G17" s="358"/>
-      <c r="H17" s="358"/>
-      <c r="I17" s="358"/>
-      <c r="J17" s="359"/>
+      <c r="D17" s="350"/>
+      <c r="E17" s="350"/>
+      <c r="F17" s="350"/>
+      <c r="G17" s="350"/>
+      <c r="H17" s="350"/>
+      <c r="I17" s="350"/>
+      <c r="J17" s="351"/>
       <c r="K17" s="220"/>
       <c r="L17" s="236">
         <v>5</v>
@@ -9328,13 +9332,13 @@
       <c r="P17" s="227"/>
       <c r="Q17" s="227"/>
       <c r="R17" s="237"/>
-      <c r="S17" s="346">
+      <c r="S17" s="353">
         <f>Q2</f>
-        <v>45388</v>
-      </c>
-      <c r="T17" s="361"/>
-      <c r="U17" s="361"/>
-      <c r="V17" s="361"/>
+        <v>45753</v>
+      </c>
+      <c r="T17" s="354"/>
+      <c r="U17" s="354"/>
+      <c r="V17" s="354"/>
       <c r="W17" s="239"/>
     </row>
     <row r="18" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -9351,17 +9355,17 @@
       <c r="K18" s="220"/>
       <c r="L18" s="220"/>
       <c r="M18" s="220"/>
-      <c r="N18" s="362" t="s">
+      <c r="N18" s="355" t="s">
         <v>310</v>
       </c>
-      <c r="O18" s="362"/>
-      <c r="P18" s="362"/>
-      <c r="Q18" s="362"/>
-      <c r="R18" s="362"/>
-      <c r="S18" s="362"/>
-      <c r="T18" s="362"/>
-      <c r="U18" s="362"/>
-      <c r="V18" s="362"/>
+      <c r="O18" s="355"/>
+      <c r="P18" s="355"/>
+      <c r="Q18" s="355"/>
+      <c r="R18" s="355"/>
+      <c r="S18" s="355"/>
+      <c r="T18" s="355"/>
+      <c r="U18" s="355"/>
+      <c r="V18" s="355"/>
       <c r="W18" s="245"/>
     </row>
     <row r="19" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
@@ -9407,13 +9411,13 @@
       <c r="K20" s="220"/>
       <c r="L20" s="220"/>
       <c r="M20" s="220"/>
-      <c r="N20" s="348" t="str">
+      <c r="N20" s="342" t="str">
         <f>IF('Business Details'!N19&gt;0,'Business Details'!N19," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="O20" s="349"/>
-      <c r="P20" s="349"/>
-      <c r="Q20" s="352"/>
+      <c r="O20" s="343"/>
+      <c r="P20" s="343"/>
+      <c r="Q20" s="344"/>
       <c r="R20" s="227"/>
       <c r="S20" s="227"/>
       <c r="T20" s="227"/>
@@ -9449,11 +9453,11 @@
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="240"/>
       <c r="B22" s="220"/>
-      <c r="C22" s="344" t="str">
+      <c r="C22" s="359" t="str">
         <f>IF('Business Details'!C30&gt;0,'Business Details'!C30," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D22" s="345"/>
+      <c r="D22" s="360"/>
       <c r="E22" s="220"/>
       <c r="F22" s="244" t="str">
         <f>IF('Business Details'!F30&gt;0,'Business Details'!F30," ")</f>
@@ -9500,13 +9504,13 @@
       <c r="P23" s="227"/>
       <c r="Q23" s="227"/>
       <c r="R23" s="227"/>
-      <c r="S23" s="346">
+      <c r="S23" s="353">
         <f>V2</f>
-        <v>45752</v>
-      </c>
-      <c r="T23" s="338"/>
-      <c r="U23" s="347"/>
-      <c r="V23" s="347"/>
+        <v>46117</v>
+      </c>
+      <c r="T23" s="361"/>
+      <c r="U23" s="362"/>
+      <c r="V23" s="362"/>
       <c r="W23" s="239"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.15">
@@ -9583,13 +9587,13 @@
       <c r="K26" s="242"/>
       <c r="L26" s="220"/>
       <c r="M26" s="220"/>
-      <c r="N26" s="348" t="str">
+      <c r="N26" s="342" t="str">
         <f>IF('Business Details'!N24&gt;0,'Business Details'!N24," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="O26" s="349"/>
-      <c r="P26" s="349"/>
-      <c r="Q26" s="350"/>
+      <c r="O26" s="343"/>
+      <c r="P26" s="343"/>
+      <c r="Q26" s="363"/>
       <c r="R26" s="220"/>
       <c r="S26" s="220"/>
       <c r="T26" s="220"/>
@@ -9719,13 +9723,13 @@
       <c r="K31" s="220"/>
       <c r="L31" s="220"/>
       <c r="M31" s="220"/>
-      <c r="N31" s="348">
+      <c r="N31" s="342">
         <f>Admin!B17</f>
-        <v>45752</v>
-      </c>
-      <c r="O31" s="349"/>
-      <c r="P31" s="349"/>
-      <c r="Q31" s="350"/>
+        <v>46117</v>
+      </c>
+      <c r="O31" s="343"/>
+      <c r="P31" s="343"/>
+      <c r="Q31" s="363"/>
       <c r="R31" s="220"/>
       <c r="S31" s="220"/>
       <c r="T31" s="220"/>
@@ -9759,32 +9763,32 @@
       <c r="W32" s="251"/>
     </row>
     <row r="33" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="351" t="str">
+      <c r="A33" s="364" t="str">
         <f>IF(D38&gt;67000,"SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £"&amp;Admin!F26&amp;" VAT threshold","Business income - if your annual turnover was below £"&amp;Admin!F26&amp;" VAT threshold")</f>
         <v>Business income - if your annual turnover was below £90000 VAT threshold</v>
       </c>
-      <c r="B33" s="351"/>
-      <c r="C33" s="351"/>
-      <c r="D33" s="351"/>
-      <c r="E33" s="351"/>
-      <c r="F33" s="351"/>
-      <c r="G33" s="351"/>
-      <c r="H33" s="351"/>
-      <c r="I33" s="351"/>
-      <c r="J33" s="351"/>
-      <c r="K33" s="351"/>
-      <c r="L33" s="351"/>
-      <c r="M33" s="351"/>
-      <c r="N33" s="351"/>
-      <c r="O33" s="351"/>
-      <c r="P33" s="351"/>
-      <c r="Q33" s="351"/>
-      <c r="R33" s="351"/>
-      <c r="S33" s="351"/>
-      <c r="T33" s="351"/>
-      <c r="U33" s="351"/>
-      <c r="V33" s="351"/>
-      <c r="W33" s="351"/>
+      <c r="B33" s="364"/>
+      <c r="C33" s="364"/>
+      <c r="D33" s="364"/>
+      <c r="E33" s="364"/>
+      <c r="F33" s="364"/>
+      <c r="G33" s="364"/>
+      <c r="H33" s="364"/>
+      <c r="I33" s="364"/>
+      <c r="J33" s="364"/>
+      <c r="K33" s="364"/>
+      <c r="L33" s="364"/>
+      <c r="M33" s="364"/>
+      <c r="N33" s="364"/>
+      <c r="O33" s="364"/>
+      <c r="P33" s="364"/>
+      <c r="Q33" s="364"/>
+      <c r="R33" s="364"/>
+      <c r="S33" s="364"/>
+      <c r="T33" s="364"/>
+      <c r="U33" s="364"/>
+      <c r="V33" s="364"/>
+      <c r="W33" s="364"/>
     </row>
     <row r="34" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="233"/>
@@ -9904,12 +9908,12 @@
       <c r="C38" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D38" s="333">
+      <c r="D38" s="356">
         <f>'Profit &amp; Loss Account'!B9</f>
         <v>0</v>
       </c>
-      <c r="E38" s="334"/>
-      <c r="F38" s="335"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="358"/>
       <c r="G38" s="218" t="s">
         <v>178</v>
       </c>
@@ -9926,12 +9930,12 @@
       <c r="N38" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O38" s="333">
+      <c r="O38" s="356">
         <f>'Profit &amp; Loss Account'!B38</f>
         <v>0</v>
       </c>
-      <c r="P38" s="334"/>
-      <c r="Q38" s="335"/>
+      <c r="P38" s="357"/>
+      <c r="Q38" s="358"/>
       <c r="R38" s="218" t="s">
         <v>178</v>
       </c>
@@ -9971,85 +9975,85 @@
       <c r="W39" s="251"/>
     </row>
     <row r="40" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="342" t="s">
+      <c r="A40" s="365" t="s">
         <v>319</v>
       </c>
-      <c r="B40" s="342"/>
-      <c r="C40" s="342"/>
-      <c r="D40" s="342"/>
-      <c r="E40" s="342"/>
-      <c r="F40" s="342"/>
-      <c r="G40" s="342"/>
-      <c r="H40" s="342"/>
-      <c r="I40" s="342"/>
-      <c r="J40" s="342"/>
-      <c r="K40" s="342"/>
-      <c r="L40" s="342"/>
-      <c r="M40" s="342"/>
-      <c r="N40" s="342"/>
-      <c r="O40" s="342"/>
-      <c r="P40" s="342"/>
-      <c r="Q40" s="342"/>
-      <c r="R40" s="342"/>
-      <c r="S40" s="342"/>
-      <c r="T40" s="342"/>
-      <c r="U40" s="342"/>
-      <c r="V40" s="342"/>
-      <c r="W40" s="342"/>
+      <c r="B40" s="365"/>
+      <c r="C40" s="365"/>
+      <c r="D40" s="365"/>
+      <c r="E40" s="365"/>
+      <c r="F40" s="365"/>
+      <c r="G40" s="365"/>
+      <c r="H40" s="365"/>
+      <c r="I40" s="365"/>
+      <c r="J40" s="365"/>
+      <c r="K40" s="365"/>
+      <c r="L40" s="365"/>
+      <c r="M40" s="365"/>
+      <c r="N40" s="365"/>
+      <c r="O40" s="365"/>
+      <c r="P40" s="365"/>
+      <c r="Q40" s="365"/>
+      <c r="R40" s="365"/>
+      <c r="S40" s="365"/>
+      <c r="T40" s="365"/>
+      <c r="U40" s="365"/>
+      <c r="V40" s="365"/>
+      <c r="W40" s="365"/>
     </row>
     <row r="41" spans="1:23" s="254" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="336" t="s">
+      <c r="A41" s="366" t="s">
         <v>320</v>
       </c>
-      <c r="B41" s="336"/>
-      <c r="C41" s="336"/>
-      <c r="D41" s="336"/>
-      <c r="E41" s="336"/>
-      <c r="F41" s="336"/>
-      <c r="G41" s="336"/>
-      <c r="H41" s="336"/>
-      <c r="I41" s="336"/>
-      <c r="J41" s="336"/>
-      <c r="K41" s="336"/>
-      <c r="L41" s="336"/>
-      <c r="M41" s="336"/>
-      <c r="N41" s="336"/>
-      <c r="O41" s="336"/>
-      <c r="P41" s="336"/>
-      <c r="Q41" s="336"/>
-      <c r="R41" s="336"/>
-      <c r="S41" s="336"/>
-      <c r="T41" s="336"/>
-      <c r="U41" s="336"/>
-      <c r="V41" s="336"/>
-      <c r="W41" s="336"/>
+      <c r="B41" s="366"/>
+      <c r="C41" s="366"/>
+      <c r="D41" s="366"/>
+      <c r="E41" s="366"/>
+      <c r="F41" s="366"/>
+      <c r="G41" s="366"/>
+      <c r="H41" s="366"/>
+      <c r="I41" s="366"/>
+      <c r="J41" s="366"/>
+      <c r="K41" s="366"/>
+      <c r="L41" s="366"/>
+      <c r="M41" s="366"/>
+      <c r="N41" s="366"/>
+      <c r="O41" s="366"/>
+      <c r="P41" s="366"/>
+      <c r="Q41" s="366"/>
+      <c r="R41" s="366"/>
+      <c r="S41" s="366"/>
+      <c r="T41" s="366"/>
+      <c r="U41" s="366"/>
+      <c r="V41" s="366"/>
+      <c r="W41" s="366"/>
     </row>
     <row r="42" spans="1:23" s="254" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="336" t="s">
+      <c r="A42" s="366" t="s">
         <v>321</v>
       </c>
-      <c r="B42" s="336"/>
-      <c r="C42" s="336"/>
-      <c r="D42" s="336"/>
-      <c r="E42" s="336"/>
-      <c r="F42" s="336"/>
-      <c r="G42" s="336"/>
-      <c r="H42" s="336"/>
-      <c r="I42" s="336"/>
-      <c r="J42" s="336"/>
-      <c r="K42" s="336"/>
-      <c r="L42" s="336"/>
-      <c r="M42" s="336"/>
-      <c r="N42" s="336"/>
-      <c r="O42" s="336"/>
-      <c r="P42" s="336"/>
-      <c r="Q42" s="336"/>
-      <c r="R42" s="336"/>
-      <c r="S42" s="336"/>
-      <c r="T42" s="336"/>
-      <c r="U42" s="336"/>
-      <c r="V42" s="336"/>
-      <c r="W42" s="336"/>
+      <c r="B42" s="366"/>
+      <c r="C42" s="366"/>
+      <c r="D42" s="366"/>
+      <c r="E42" s="366"/>
+      <c r="F42" s="366"/>
+      <c r="G42" s="366"/>
+      <c r="H42" s="366"/>
+      <c r="I42" s="366"/>
+      <c r="J42" s="366"/>
+      <c r="K42" s="366"/>
+      <c r="L42" s="366"/>
+      <c r="M42" s="366"/>
+      <c r="N42" s="366"/>
+      <c r="O42" s="366"/>
+      <c r="P42" s="366"/>
+      <c r="Q42" s="366"/>
+      <c r="R42" s="366"/>
+      <c r="S42" s="366"/>
+      <c r="T42" s="366"/>
+      <c r="U42" s="366"/>
+      <c r="V42" s="366"/>
+      <c r="W42" s="366"/>
     </row>
     <row r="43" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="233"/>
@@ -10140,12 +10144,12 @@
       <c r="C46" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="333" t="str">
+      <c r="D46" s="356" t="str">
         <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B17," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E46" s="334"/>
-      <c r="F46" s="335"/>
+      <c r="E46" s="357"/>
+      <c r="F46" s="358"/>
       <c r="G46" s="218" t="s">
         <v>178</v>
       </c>
@@ -10162,12 +10166,12 @@
       <c r="N46" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O46" s="333" t="str">
+      <c r="O46" s="356" t="str">
         <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B28," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="P46" s="334"/>
-      <c r="Q46" s="335"/>
+      <c r="P46" s="357"/>
+      <c r="Q46" s="358"/>
       <c r="R46" s="218" t="s">
         <v>178</v>
       </c>
@@ -10297,12 +10301,12 @@
       <c r="C51" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D51" s="333" t="str">
+      <c r="D51" s="356" t="str">
         <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E51" s="334"/>
-      <c r="F51" s="335"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="358"/>
       <c r="G51" s="218" t="s">
         <v>178</v>
       </c>
@@ -10319,12 +10323,12 @@
       <c r="N51" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O51" s="333" t="str">
+      <c r="O51" s="356" t="str">
         <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="P51" s="334"/>
-      <c r="Q51" s="335"/>
+      <c r="P51" s="357"/>
+      <c r="Q51" s="358"/>
       <c r="R51" s="218" t="s">
         <v>178</v>
       </c>
@@ -10427,12 +10431,12 @@
       <c r="C55" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D55" s="333" t="str">
+      <c r="D55" s="356" t="str">
         <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B21," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E55" s="334"/>
-      <c r="F55" s="335"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="358"/>
       <c r="G55" s="218" t="s">
         <v>178</v>
       </c>
@@ -10449,12 +10453,12 @@
       <c r="N55" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O55" s="333" t="str">
+      <c r="O55" s="356" t="str">
         <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B24," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="P55" s="334"/>
-      <c r="Q55" s="335"/>
+      <c r="P55" s="357"/>
+      <c r="Q55" s="358"/>
       <c r="R55" s="218" t="s">
         <v>178</v>
       </c>
@@ -10584,12 +10588,12 @@
       <c r="C60" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D60" s="333" t="str">
+      <c r="D60" s="356" t="str">
         <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B22," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E60" s="334"/>
-      <c r="F60" s="335"/>
+      <c r="E60" s="357"/>
+      <c r="F60" s="358"/>
       <c r="G60" s="218" t="s">
         <v>178</v>
       </c>
@@ -10606,12 +10610,12 @@
       <c r="N60" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O60" s="333" t="str">
+      <c r="O60" s="356" t="str">
         <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="P60" s="334"/>
-      <c r="Q60" s="335"/>
+      <c r="P60" s="357"/>
+      <c r="Q60" s="358"/>
       <c r="R60" s="218" t="s">
         <v>178</v>
       </c>
@@ -10714,12 +10718,12 @@
       <c r="C64" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D64" s="333" t="str">
+      <c r="D64" s="356" t="str">
         <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B23," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E64" s="334"/>
-      <c r="F64" s="335"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="358"/>
       <c r="G64" s="218" t="s">
         <v>178</v>
       </c>
@@ -10736,12 +10740,12 @@
       <c r="N64" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O64" s="333">
+      <c r="O64" s="356">
         <f>'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35-'Profit &amp; Loss Account'!B34</f>
         <v>0</v>
       </c>
-      <c r="P64" s="334"/>
-      <c r="Q64" s="335"/>
+      <c r="P64" s="357"/>
+      <c r="Q64" s="358"/>
       <c r="R64" s="218" t="s">
         <v>178</v>
       </c>
@@ -10781,31 +10785,31 @@
       <c r="W65" s="251"/>
     </row>
     <row r="66" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="343" t="s">
+      <c r="A66" s="367" t="s">
         <v>213</v>
       </c>
-      <c r="B66" s="343"/>
-      <c r="C66" s="343"/>
-      <c r="D66" s="343"/>
-      <c r="E66" s="343"/>
-      <c r="F66" s="343"/>
-      <c r="G66" s="343"/>
-      <c r="H66" s="343"/>
-      <c r="I66" s="343"/>
-      <c r="J66" s="343"/>
-      <c r="K66" s="343"/>
-      <c r="L66" s="343"/>
-      <c r="M66" s="343"/>
-      <c r="N66" s="343"/>
-      <c r="O66" s="343"/>
-      <c r="P66" s="343"/>
-      <c r="Q66" s="343"/>
-      <c r="R66" s="343"/>
-      <c r="S66" s="343"/>
-      <c r="T66" s="343"/>
-      <c r="U66" s="343"/>
-      <c r="V66" s="343"/>
-      <c r="W66" s="343"/>
+      <c r="B66" s="367"/>
+      <c r="C66" s="367"/>
+      <c r="D66" s="367"/>
+      <c r="E66" s="367"/>
+      <c r="F66" s="367"/>
+      <c r="G66" s="367"/>
+      <c r="H66" s="367"/>
+      <c r="I66" s="367"/>
+      <c r="J66" s="367"/>
+      <c r="K66" s="367"/>
+      <c r="L66" s="367"/>
+      <c r="M66" s="367"/>
+      <c r="N66" s="367"/>
+      <c r="O66" s="367"/>
+      <c r="P66" s="367"/>
+      <c r="Q66" s="367"/>
+      <c r="R66" s="367"/>
+      <c r="S66" s="367"/>
+      <c r="T66" s="367"/>
+      <c r="U66" s="367"/>
+      <c r="V66" s="367"/>
+      <c r="W66" s="367"/>
     </row>
     <row r="67" spans="1:26" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="233"/>
@@ -10925,12 +10929,12 @@
       <c r="C71" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D71" s="333">
+      <c r="D71" s="356">
         <f>IF((D38+O38-O64)&gt;=0,D38+O38-O64,0)</f>
         <v>0</v>
       </c>
-      <c r="E71" s="334"/>
-      <c r="F71" s="335"/>
+      <c r="E71" s="357"/>
+      <c r="F71" s="358"/>
       <c r="G71" s="218" t="s">
         <v>178</v>
       </c>
@@ -10947,12 +10951,12 @@
       <c r="N71" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O71" s="333">
+      <c r="O71" s="356">
         <f>IF((D38+O38-O64)&lt;0,O64-D38-O38,0)</f>
         <v>0</v>
       </c>
-      <c r="P71" s="334"/>
-      <c r="Q71" s="335"/>
+      <c r="P71" s="357"/>
+      <c r="Q71" s="358"/>
       <c r="R71" s="218" t="s">
         <v>178</v>
       </c>
@@ -10994,116 +10998,116 @@
       <c r="W72" s="251"/>
     </row>
     <row r="73" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="342" t="s">
+      <c r="A73" s="365" t="s">
         <v>218</v>
       </c>
-      <c r="B73" s="342"/>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-      <c r="G73" s="342"/>
-      <c r="H73" s="342"/>
-      <c r="I73" s="342"/>
-      <c r="J73" s="342"/>
-      <c r="K73" s="342"/>
-      <c r="L73" s="342"/>
-      <c r="M73" s="342"/>
-      <c r="N73" s="342"/>
-      <c r="O73" s="342"/>
-      <c r="P73" s="342"/>
-      <c r="Q73" s="342"/>
-      <c r="R73" s="342"/>
-      <c r="S73" s="342"/>
-      <c r="T73" s="342"/>
-      <c r="U73" s="342"/>
-      <c r="V73" s="342"/>
-      <c r="W73" s="342"/>
+      <c r="B73" s="365"/>
+      <c r="C73" s="365"/>
+      <c r="D73" s="365"/>
+      <c r="E73" s="365"/>
+      <c r="F73" s="365"/>
+      <c r="G73" s="365"/>
+      <c r="H73" s="365"/>
+      <c r="I73" s="365"/>
+      <c r="J73" s="365"/>
+      <c r="K73" s="365"/>
+      <c r="L73" s="365"/>
+      <c r="M73" s="365"/>
+      <c r="N73" s="365"/>
+      <c r="O73" s="365"/>
+      <c r="P73" s="365"/>
+      <c r="Q73" s="365"/>
+      <c r="R73" s="365"/>
+      <c r="S73" s="365"/>
+      <c r="T73" s="365"/>
+      <c r="U73" s="365"/>
+      <c r="V73" s="365"/>
+      <c r="W73" s="365"/>
       <c r="Y73" s="257"/>
       <c r="Z73" s="257"/>
     </row>
     <row r="74" spans="1:26" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="336" t="s">
+      <c r="A74" s="366" t="s">
         <v>331</v>
       </c>
-      <c r="B74" s="336"/>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
-      <c r="G74" s="336"/>
-      <c r="H74" s="336"/>
-      <c r="I74" s="336"/>
-      <c r="J74" s="336"/>
-      <c r="K74" s="336"/>
-      <c r="L74" s="336"/>
-      <c r="M74" s="336"/>
-      <c r="N74" s="336"/>
-      <c r="O74" s="336"/>
-      <c r="P74" s="336"/>
-      <c r="Q74" s="336"/>
-      <c r="R74" s="336"/>
-      <c r="S74" s="336"/>
-      <c r="T74" s="336"/>
-      <c r="U74" s="336"/>
-      <c r="V74" s="336"/>
-      <c r="W74" s="336"/>
+      <c r="B74" s="366"/>
+      <c r="C74" s="366"/>
+      <c r="D74" s="366"/>
+      <c r="E74" s="366"/>
+      <c r="F74" s="366"/>
+      <c r="G74" s="366"/>
+      <c r="H74" s="366"/>
+      <c r="I74" s="366"/>
+      <c r="J74" s="366"/>
+      <c r="K74" s="366"/>
+      <c r="L74" s="366"/>
+      <c r="M74" s="366"/>
+      <c r="N74" s="366"/>
+      <c r="O74" s="366"/>
+      <c r="P74" s="366"/>
+      <c r="Q74" s="366"/>
+      <c r="R74" s="366"/>
+      <c r="S74" s="366"/>
+      <c r="T74" s="366"/>
+      <c r="U74" s="366"/>
+      <c r="V74" s="366"/>
+      <c r="W74" s="366"/>
     </row>
     <row r="75" spans="1:26" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="336" t="s">
+      <c r="A75" s="366" t="s">
         <v>332</v>
       </c>
-      <c r="B75" s="336"/>
-      <c r="C75" s="336"/>
-      <c r="D75" s="336"/>
-      <c r="E75" s="336"/>
-      <c r="F75" s="336"/>
-      <c r="G75" s="336"/>
-      <c r="H75" s="336"/>
-      <c r="I75" s="336"/>
-      <c r="J75" s="336"/>
-      <c r="K75" s="336"/>
-      <c r="L75" s="336"/>
-      <c r="M75" s="336"/>
-      <c r="N75" s="336"/>
-      <c r="O75" s="336"/>
-      <c r="P75" s="336"/>
-      <c r="Q75" s="336"/>
-      <c r="R75" s="336"/>
-      <c r="S75" s="336"/>
-      <c r="T75" s="336"/>
-      <c r="U75" s="336"/>
-      <c r="V75" s="336"/>
-      <c r="W75" s="336"/>
+      <c r="B75" s="366"/>
+      <c r="C75" s="366"/>
+      <c r="D75" s="366"/>
+      <c r="E75" s="366"/>
+      <c r="F75" s="366"/>
+      <c r="G75" s="366"/>
+      <c r="H75" s="366"/>
+      <c r="I75" s="366"/>
+      <c r="J75" s="366"/>
+      <c r="K75" s="366"/>
+      <c r="L75" s="366"/>
+      <c r="M75" s="366"/>
+      <c r="N75" s="366"/>
+      <c r="O75" s="366"/>
+      <c r="P75" s="366"/>
+      <c r="Q75" s="366"/>
+      <c r="R75" s="366"/>
+      <c r="S75" s="366"/>
+      <c r="T75" s="366"/>
+      <c r="U75" s="366"/>
+      <c r="V75" s="366"/>
+      <c r="W75" s="366"/>
       <c r="Y75" s="257"/>
       <c r="Z75" s="257"/>
     </row>
     <row r="76" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="336" t="s">
+      <c r="A76" s="366" t="s">
         <v>333</v>
       </c>
-      <c r="B76" s="336"/>
-      <c r="C76" s="336"/>
-      <c r="D76" s="336"/>
-      <c r="E76" s="336"/>
-      <c r="F76" s="336"/>
-      <c r="G76" s="336"/>
-      <c r="H76" s="336"/>
-      <c r="I76" s="336"/>
-      <c r="J76" s="336"/>
-      <c r="K76" s="336"/>
-      <c r="L76" s="336"/>
-      <c r="M76" s="336"/>
-      <c r="N76" s="336"/>
-      <c r="O76" s="336"/>
-      <c r="P76" s="336"/>
-      <c r="Q76" s="336"/>
-      <c r="R76" s="336"/>
-      <c r="S76" s="336"/>
-      <c r="T76" s="336"/>
-      <c r="U76" s="336"/>
-      <c r="V76" s="336"/>
-      <c r="W76" s="336"/>
+      <c r="B76" s="366"/>
+      <c r="C76" s="366"/>
+      <c r="D76" s="366"/>
+      <c r="E76" s="366"/>
+      <c r="F76" s="366"/>
+      <c r="G76" s="366"/>
+      <c r="H76" s="366"/>
+      <c r="I76" s="366"/>
+      <c r="J76" s="366"/>
+      <c r="K76" s="366"/>
+      <c r="L76" s="366"/>
+      <c r="M76" s="366"/>
+      <c r="N76" s="366"/>
+      <c r="O76" s="366"/>
+      <c r="P76" s="366"/>
+      <c r="Q76" s="366"/>
+      <c r="R76" s="366"/>
+      <c r="S76" s="366"/>
+      <c r="T76" s="366"/>
+      <c r="U76" s="366"/>
+      <c r="V76" s="366"/>
+      <c r="W76" s="366"/>
     </row>
     <row r="77" spans="1:26" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="233"/>
@@ -11194,12 +11198,12 @@
       <c r="C80" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D80" s="333">
+      <c r="D80" s="356">
         <f>IF(([1]Schedule!$Q$1)&gt;0,[1]Schedule!$Q$1,0)</f>
         <v>0</v>
       </c>
-      <c r="E80" s="334"/>
-      <c r="F80" s="335"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="358"/>
       <c r="G80" s="218" t="s">
         <v>178</v>
       </c>
@@ -11216,12 +11220,12 @@
       <c r="N80" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O80" s="333">
+      <c r="O80" s="356">
         <f>IF(([1]Schedule!$R$1+[1]Schedule!$Y$1)&gt;0,[1]Schedule!$R$1+[1]Schedule!$Y$1,0)</f>
         <v>0</v>
       </c>
-      <c r="P80" s="334"/>
-      <c r="Q80" s="335"/>
+      <c r="P80" s="357"/>
+      <c r="Q80" s="358"/>
       <c r="R80" s="218" t="s">
         <v>178</v>
       </c>
@@ -11353,12 +11357,12 @@
       <c r="C85" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D85" s="333">
+      <c r="D85" s="356">
         <f>IF(([1]Schedule!$R$1+[1]Schedule!$S$1)&lt;1000,[1]Schedule!$S$1,0)</f>
         <v>0</v>
       </c>
-      <c r="E85" s="334"/>
-      <c r="F85" s="335"/>
+      <c r="E85" s="357"/>
+      <c r="F85" s="358"/>
       <c r="G85" s="218" t="s">
         <v>178</v>
       </c>
@@ -11375,12 +11379,12 @@
       <c r="N85" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O85" s="333">
+      <c r="O85" s="356">
         <f>IF([1]Schedule!$Z$1&gt;0,[1]Schedule!$Z$1,0)</f>
         <v>0</v>
       </c>
-      <c r="P85" s="334"/>
-      <c r="Q85" s="335"/>
+      <c r="P85" s="357"/>
+      <c r="Q85" s="358"/>
       <c r="R85" s="218" t="s">
         <v>178</v>
       </c>
@@ -11420,85 +11424,85 @@
       <c r="W86" s="251"/>
     </row>
     <row r="87" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="341" t="s">
+      <c r="A87" s="368" t="s">
         <v>335</v>
       </c>
-      <c r="B87" s="341"/>
-      <c r="C87" s="341"/>
-      <c r="D87" s="341"/>
-      <c r="E87" s="341"/>
-      <c r="F87" s="341"/>
-      <c r="G87" s="341"/>
-      <c r="H87" s="341"/>
-      <c r="I87" s="341"/>
-      <c r="J87" s="341"/>
-      <c r="K87" s="341"/>
-      <c r="L87" s="341"/>
-      <c r="M87" s="341"/>
-      <c r="N87" s="341"/>
-      <c r="O87" s="341"/>
-      <c r="P87" s="341"/>
-      <c r="Q87" s="341"/>
-      <c r="R87" s="341"/>
-      <c r="S87" s="341"/>
-      <c r="T87" s="341"/>
-      <c r="U87" s="341"/>
-      <c r="V87" s="341"/>
-      <c r="W87" s="341"/>
+      <c r="B87" s="368"/>
+      <c r="C87" s="368"/>
+      <c r="D87" s="368"/>
+      <c r="E87" s="368"/>
+      <c r="F87" s="368"/>
+      <c r="G87" s="368"/>
+      <c r="H87" s="368"/>
+      <c r="I87" s="368"/>
+      <c r="J87" s="368"/>
+      <c r="K87" s="368"/>
+      <c r="L87" s="368"/>
+      <c r="M87" s="368"/>
+      <c r="N87" s="368"/>
+      <c r="O87" s="368"/>
+      <c r="P87" s="368"/>
+      <c r="Q87" s="368"/>
+      <c r="R87" s="368"/>
+      <c r="S87" s="368"/>
+      <c r="T87" s="368"/>
+      <c r="U87" s="368"/>
+      <c r="V87" s="368"/>
+      <c r="W87" s="368"/>
     </row>
     <row r="88" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="336" t="s">
+      <c r="A88" s="366" t="s">
         <v>336</v>
       </c>
-      <c r="B88" s="336"/>
-      <c r="C88" s="336"/>
-      <c r="D88" s="336"/>
-      <c r="E88" s="336"/>
-      <c r="F88" s="336"/>
-      <c r="G88" s="336"/>
-      <c r="H88" s="336"/>
-      <c r="I88" s="336"/>
-      <c r="J88" s="336"/>
-      <c r="K88" s="336"/>
-      <c r="L88" s="336"/>
-      <c r="M88" s="336"/>
-      <c r="N88" s="336"/>
-      <c r="O88" s="336"/>
-      <c r="P88" s="336"/>
-      <c r="Q88" s="336"/>
-      <c r="R88" s="336"/>
-      <c r="S88" s="336"/>
-      <c r="T88" s="336"/>
-      <c r="U88" s="336"/>
-      <c r="V88" s="336"/>
-      <c r="W88" s="336"/>
+      <c r="B88" s="366"/>
+      <c r="C88" s="366"/>
+      <c r="D88" s="366"/>
+      <c r="E88" s="366"/>
+      <c r="F88" s="366"/>
+      <c r="G88" s="366"/>
+      <c r="H88" s="366"/>
+      <c r="I88" s="366"/>
+      <c r="J88" s="366"/>
+      <c r="K88" s="366"/>
+      <c r="L88" s="366"/>
+      <c r="M88" s="366"/>
+      <c r="N88" s="366"/>
+      <c r="O88" s="366"/>
+      <c r="P88" s="366"/>
+      <c r="Q88" s="366"/>
+      <c r="R88" s="366"/>
+      <c r="S88" s="366"/>
+      <c r="T88" s="366"/>
+      <c r="U88" s="366"/>
+      <c r="V88" s="366"/>
+      <c r="W88" s="366"/>
     </row>
     <row r="89" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A89" s="336" t="s">
+      <c r="A89" s="366" t="s">
         <v>337</v>
       </c>
-      <c r="B89" s="336"/>
-      <c r="C89" s="336"/>
-      <c r="D89" s="336"/>
-      <c r="E89" s="336"/>
-      <c r="F89" s="336"/>
-      <c r="G89" s="336"/>
-      <c r="H89" s="336"/>
-      <c r="I89" s="336"/>
-      <c r="J89" s="336"/>
-      <c r="K89" s="336"/>
-      <c r="L89" s="336"/>
-      <c r="M89" s="336"/>
-      <c r="N89" s="336"/>
-      <c r="O89" s="336"/>
-      <c r="P89" s="336"/>
-      <c r="Q89" s="336"/>
-      <c r="R89" s="336"/>
-      <c r="S89" s="336"/>
-      <c r="T89" s="336"/>
-      <c r="U89" s="336"/>
-      <c r="V89" s="336"/>
-      <c r="W89" s="336"/>
+      <c r="B89" s="366"/>
+      <c r="C89" s="366"/>
+      <c r="D89" s="366"/>
+      <c r="E89" s="366"/>
+      <c r="F89" s="366"/>
+      <c r="G89" s="366"/>
+      <c r="H89" s="366"/>
+      <c r="I89" s="366"/>
+      <c r="J89" s="366"/>
+      <c r="K89" s="366"/>
+      <c r="L89" s="366"/>
+      <c r="M89" s="366"/>
+      <c r="N89" s="366"/>
+      <c r="O89" s="366"/>
+      <c r="P89" s="366"/>
+      <c r="Q89" s="366"/>
+      <c r="R89" s="366"/>
+      <c r="S89" s="366"/>
+      <c r="T89" s="366"/>
+      <c r="U89" s="366"/>
+      <c r="V89" s="366"/>
+      <c r="W89" s="366"/>
     </row>
     <row r="90" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="233"/>
@@ -11618,12 +11622,12 @@
       <c r="C94" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D94" s="333">
+      <c r="D94" s="356">
         <f>'Business Details'!O50</f>
         <v>0</v>
       </c>
-      <c r="E94" s="334"/>
-      <c r="F94" s="335"/>
+      <c r="E94" s="357"/>
+      <c r="F94" s="358"/>
       <c r="G94" s="218" t="s">
         <v>178</v>
       </c>
@@ -11640,12 +11644,12 @@
       <c r="N94" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O94" s="333">
+      <c r="O94" s="356">
         <f>IF(O106&gt;0,0,IF('Business Details'!D50=0,0,IF(D99&gt;'Business Details'!D50,'Business Details'!D50,D99)))</f>
         <v>0</v>
       </c>
-      <c r="P94" s="334"/>
-      <c r="Q94" s="335"/>
+      <c r="P94" s="357"/>
+      <c r="Q94" s="358"/>
       <c r="R94" s="218" t="s">
         <v>178</v>
       </c>
@@ -11777,12 +11781,12 @@
       <c r="C99" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D99" s="333">
+      <c r="D99" s="356">
         <f>IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
         <v>0</v>
       </c>
-      <c r="E99" s="334"/>
-      <c r="F99" s="335"/>
+      <c r="E99" s="357"/>
+      <c r="F99" s="358"/>
       <c r="G99" s="218" t="s">
         <v>178</v>
       </c>
@@ -11799,12 +11803,12 @@
       <c r="N99" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O99" s="333">
+      <c r="O99" s="356">
         <f>'Profit &amp; Loss Account'!B11</f>
         <v>0</v>
       </c>
-      <c r="P99" s="334"/>
-      <c r="Q99" s="335"/>
+      <c r="P99" s="357"/>
+      <c r="Q99" s="358"/>
       <c r="R99" s="218" t="s">
         <v>178</v>
       </c>
@@ -11846,31 +11850,31 @@
       <c r="W100" s="251"/>
     </row>
     <row r="101" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="342" t="s">
+      <c r="A101" s="365" t="s">
         <v>341</v>
       </c>
-      <c r="B101" s="342"/>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
-      <c r="G101" s="342"/>
-      <c r="H101" s="342"/>
-      <c r="I101" s="342"/>
-      <c r="J101" s="342"/>
-      <c r="K101" s="342"/>
-      <c r="L101" s="342"/>
-      <c r="M101" s="342"/>
-      <c r="N101" s="342"/>
-      <c r="O101" s="342"/>
-      <c r="P101" s="342"/>
-      <c r="Q101" s="342"/>
-      <c r="R101" s="342"/>
-      <c r="S101" s="342"/>
-      <c r="T101" s="342"/>
-      <c r="U101" s="342"/>
-      <c r="V101" s="342"/>
-      <c r="W101" s="342"/>
+      <c r="B101" s="365"/>
+      <c r="C101" s="365"/>
+      <c r="D101" s="365"/>
+      <c r="E101" s="365"/>
+      <c r="F101" s="365"/>
+      <c r="G101" s="365"/>
+      <c r="H101" s="365"/>
+      <c r="I101" s="365"/>
+      <c r="J101" s="365"/>
+      <c r="K101" s="365"/>
+      <c r="L101" s="365"/>
+      <c r="M101" s="365"/>
+      <c r="N101" s="365"/>
+      <c r="O101" s="365"/>
+      <c r="P101" s="365"/>
+      <c r="Q101" s="365"/>
+      <c r="R101" s="365"/>
+      <c r="S101" s="365"/>
+      <c r="T101" s="365"/>
+      <c r="U101" s="365"/>
+      <c r="V101" s="365"/>
+      <c r="W101" s="365"/>
     </row>
     <row r="102" spans="1:26" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="233"/>
@@ -11990,12 +11994,12 @@
       <c r="C106" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D106" s="333">
+      <c r="D106" s="356">
         <f>IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
         <v>0</v>
       </c>
-      <c r="E106" s="334"/>
-      <c r="F106" s="335"/>
+      <c r="E106" s="357"/>
+      <c r="F106" s="358"/>
       <c r="G106" s="218" t="s">
         <v>178</v>
       </c>
@@ -12012,12 +12016,12 @@
       <c r="N106" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O106" s="333">
+      <c r="O106" s="356">
         <f>IF((O71+D80+D85+O80-D71-O85-D94)&gt;=0,O71+D80+D85+O80-D71-O85-D94,0)</f>
         <v>0</v>
       </c>
-      <c r="P106" s="334"/>
-      <c r="Q106" s="335"/>
+      <c r="P106" s="357"/>
+      <c r="Q106" s="358"/>
       <c r="R106" s="218" t="s">
         <v>178</v>
       </c>
@@ -12057,58 +12061,58 @@
       <c r="W107" s="251"/>
     </row>
     <row r="108" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A108" s="341" t="s">
+      <c r="A108" s="368" t="s">
         <v>342</v>
       </c>
-      <c r="B108" s="341"/>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
-      <c r="G108" s="341"/>
-      <c r="H108" s="341"/>
-      <c r="I108" s="341"/>
-      <c r="J108" s="341"/>
-      <c r="K108" s="341"/>
-      <c r="L108" s="341"/>
-      <c r="M108" s="341"/>
-      <c r="N108" s="341"/>
-      <c r="O108" s="341"/>
-      <c r="P108" s="341"/>
-      <c r="Q108" s="341"/>
-      <c r="R108" s="341"/>
-      <c r="S108" s="341"/>
-      <c r="T108" s="341"/>
-      <c r="U108" s="341"/>
-      <c r="V108" s="341"/>
-      <c r="W108" s="341"/>
+      <c r="B108" s="368"/>
+      <c r="C108" s="368"/>
+      <c r="D108" s="368"/>
+      <c r="E108" s="368"/>
+      <c r="F108" s="368"/>
+      <c r="G108" s="368"/>
+      <c r="H108" s="368"/>
+      <c r="I108" s="368"/>
+      <c r="J108" s="368"/>
+      <c r="K108" s="368"/>
+      <c r="L108" s="368"/>
+      <c r="M108" s="368"/>
+      <c r="N108" s="368"/>
+      <c r="O108" s="368"/>
+      <c r="P108" s="368"/>
+      <c r="Q108" s="368"/>
+      <c r="R108" s="368"/>
+      <c r="S108" s="368"/>
+      <c r="T108" s="368"/>
+      <c r="U108" s="368"/>
+      <c r="V108" s="368"/>
+      <c r="W108" s="368"/>
     </row>
     <row r="109" spans="1:26" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="336" t="s">
+      <c r="A109" s="366" t="s">
         <v>343</v>
       </c>
-      <c r="B109" s="336"/>
-      <c r="C109" s="336"/>
-      <c r="D109" s="336"/>
-      <c r="E109" s="336"/>
-      <c r="F109" s="336"/>
-      <c r="G109" s="336"/>
-      <c r="H109" s="336"/>
-      <c r="I109" s="336"/>
-      <c r="J109" s="336"/>
-      <c r="K109" s="336"/>
-      <c r="L109" s="336"/>
-      <c r="M109" s="336"/>
-      <c r="N109" s="336"/>
-      <c r="O109" s="336"/>
-      <c r="P109" s="336"/>
-      <c r="Q109" s="336"/>
-      <c r="R109" s="336"/>
-      <c r="S109" s="336"/>
-      <c r="T109" s="336"/>
-      <c r="U109" s="336"/>
-      <c r="V109" s="336"/>
-      <c r="W109" s="336"/>
+      <c r="B109" s="366"/>
+      <c r="C109" s="366"/>
+      <c r="D109" s="366"/>
+      <c r="E109" s="366"/>
+      <c r="F109" s="366"/>
+      <c r="G109" s="366"/>
+      <c r="H109" s="366"/>
+      <c r="I109" s="366"/>
+      <c r="J109" s="366"/>
+      <c r="K109" s="366"/>
+      <c r="L109" s="366"/>
+      <c r="M109" s="366"/>
+      <c r="N109" s="366"/>
+      <c r="O109" s="366"/>
+      <c r="P109" s="366"/>
+      <c r="Q109" s="366"/>
+      <c r="R109" s="366"/>
+      <c r="S109" s="366"/>
+      <c r="T109" s="366"/>
+      <c r="U109" s="366"/>
+      <c r="V109" s="366"/>
+      <c r="W109" s="366"/>
     </row>
     <row r="110" spans="1:26" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="233"/>
@@ -12174,12 +12178,12 @@
       <c r="C112" s="227" t="s">
         <v>268</v>
       </c>
-      <c r="D112" s="337" t="str">
+      <c r="D112" s="369" t="str">
         <f>Admin!G2</f>
-        <v>2024-25</v>
-      </c>
-      <c r="E112" s="338"/>
-      <c r="F112" s="338"/>
+        <v>2025-26</v>
+      </c>
+      <c r="E112" s="361"/>
+      <c r="F112" s="361"/>
       <c r="G112" s="227"/>
       <c r="H112" s="227"/>
       <c r="I112" s="227"/>
@@ -12231,9 +12235,9 @@
       <c r="C114" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D114" s="333"/>
-      <c r="E114" s="334"/>
-      <c r="F114" s="335"/>
+      <c r="D114" s="356"/>
+      <c r="E114" s="357"/>
+      <c r="F114" s="358"/>
       <c r="G114" s="218" t="s">
         <v>178</v>
       </c>
@@ -12309,12 +12313,12 @@
       <c r="O116" s="220"/>
       <c r="P116" s="220"/>
       <c r="Q116" s="220"/>
-      <c r="R116" s="339" t="str">
+      <c r="R116" s="370" t="str">
         <f>Admin!G2</f>
-        <v>2024-25</v>
-      </c>
-      <c r="S116" s="340"/>
-      <c r="T116" s="340"/>
+        <v>2025-26</v>
+      </c>
+      <c r="S116" s="371"/>
+      <c r="T116" s="371"/>
       <c r="U116" s="227" t="s">
         <v>347</v>
       </c>
@@ -12383,9 +12387,9 @@
       <c r="C119" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D119" s="333"/>
-      <c r="E119" s="334"/>
-      <c r="F119" s="335"/>
+      <c r="D119" s="356"/>
+      <c r="E119" s="357"/>
+      <c r="F119" s="358"/>
       <c r="G119" s="218" t="s">
         <v>178</v>
       </c>
@@ -12528,12 +12532,12 @@
       <c r="C124" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D124" s="333">
+      <c r="D124" s="356">
         <f>'Business Details'!O55</f>
         <v>0</v>
       </c>
-      <c r="E124" s="334"/>
-      <c r="F124" s="335"/>
+      <c r="E124" s="357"/>
+      <c r="F124" s="358"/>
       <c r="G124" s="218" t="s">
         <v>178</v>
       </c>
@@ -12550,12 +12554,12 @@
       <c r="N124" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O124" s="333">
+      <c r="O124" s="356">
         <f>[2]Mar!$X$1</f>
         <v>0</v>
       </c>
-      <c r="P124" s="334"/>
-      <c r="Q124" s="335"/>
+      <c r="P124" s="357"/>
+      <c r="Q124" s="358"/>
       <c r="R124" s="218" t="s">
         <v>178</v>
       </c>
@@ -12596,24 +12600,41 @@
     </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="G1:N2"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="A3:W3"/>
-    <mergeCell ref="A4:W4"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="R8:U8"/>
-    <mergeCell ref="A10:W10"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="S17:V17"/>
-    <mergeCell ref="N18:V18"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="O124:Q124"/>
+    <mergeCell ref="A109:W109"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="R116:T116"/>
+    <mergeCell ref="A87:W87"/>
+    <mergeCell ref="A88:W88"/>
+    <mergeCell ref="A89:W89"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="O94:Q94"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="O106:Q106"/>
+    <mergeCell ref="A108:W108"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="O99:Q99"/>
+    <mergeCell ref="A101:W101"/>
+    <mergeCell ref="A66:W66"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="O71:Q71"/>
+    <mergeCell ref="A73:W73"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="O85:Q85"/>
+    <mergeCell ref="A74:W74"/>
+    <mergeCell ref="A75:W75"/>
+    <mergeCell ref="A76:W76"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="O80:Q80"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="O55:Q55"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="O60:Q60"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="O64:Q64"/>
     <mergeCell ref="D51:F51"/>
     <mergeCell ref="O51:Q51"/>
     <mergeCell ref="C22:D22"/>
@@ -12628,41 +12649,24 @@
     <mergeCell ref="A42:W42"/>
     <mergeCell ref="D46:F46"/>
     <mergeCell ref="O46:Q46"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="O55:Q55"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="O60:Q60"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="O64:Q64"/>
-    <mergeCell ref="A66:W66"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="O71:Q71"/>
-    <mergeCell ref="A73:W73"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="O85:Q85"/>
-    <mergeCell ref="A74:W74"/>
-    <mergeCell ref="A75:W75"/>
-    <mergeCell ref="A76:W76"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="O80:Q80"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="O106:Q106"/>
-    <mergeCell ref="A108:W108"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="O99:Q99"/>
-    <mergeCell ref="A101:W101"/>
-    <mergeCell ref="A87:W87"/>
-    <mergeCell ref="A88:W88"/>
-    <mergeCell ref="A89:W89"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="O94:Q94"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="O124:Q124"/>
-    <mergeCell ref="A109:W109"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="R116:T116"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="A3:W3"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="A10:W10"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="S17:V17"/>
+    <mergeCell ref="N18:V18"/>
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="G1:N2"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="V2:W2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -12703,120 +12707,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="363" t="s">
+      <c r="A1" s="333" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="364"/>
-      <c r="C1" s="364"/>
-      <c r="D1" s="364"/>
-      <c r="E1" s="364"/>
-      <c r="F1" s="364"/>
-      <c r="G1" s="365" t="s">
-        <v>407</v>
-      </c>
-      <c r="H1" s="366"/>
-      <c r="I1" s="366"/>
-      <c r="J1" s="366"/>
-      <c r="K1" s="366"/>
-      <c r="L1" s="366"/>
-      <c r="M1" s="366"/>
-      <c r="N1" s="398" t="s">
+      <c r="B1" s="334"/>
+      <c r="C1" s="334"/>
+      <c r="D1" s="334"/>
+      <c r="E1" s="334"/>
+      <c r="F1" s="334"/>
+      <c r="G1" s="335" t="s">
+        <v>438</v>
+      </c>
+      <c r="H1" s="336"/>
+      <c r="I1" s="336"/>
+      <c r="J1" s="336"/>
+      <c r="K1" s="336"/>
+      <c r="L1" s="336"/>
+      <c r="M1" s="336"/>
+      <c r="N1" s="372" t="s">
         <v>183</v>
       </c>
-      <c r="O1" s="398"/>
-      <c r="P1" s="398"/>
-      <c r="Q1" s="398"/>
-      <c r="R1" s="398"/>
-      <c r="S1" s="398"/>
-      <c r="T1" s="398"/>
-      <c r="U1" s="398"/>
-      <c r="V1" s="398"/>
-      <c r="W1" s="398"/>
+      <c r="O1" s="372"/>
+      <c r="P1" s="372"/>
+      <c r="Q1" s="372"/>
+      <c r="R1" s="372"/>
+      <c r="S1" s="372"/>
+      <c r="T1" s="372"/>
+      <c r="U1" s="372"/>
+      <c r="V1" s="372"/>
+      <c r="W1" s="372"/>
     </row>
     <row r="2" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="364"/>
-      <c r="B2" s="364"/>
-      <c r="C2" s="364"/>
-      <c r="D2" s="364"/>
-      <c r="E2" s="364"/>
-      <c r="F2" s="364"/>
-      <c r="G2" s="366"/>
-      <c r="H2" s="366"/>
-      <c r="I2" s="366"/>
-      <c r="J2" s="366"/>
-      <c r="K2" s="366"/>
-      <c r="L2" s="366"/>
-      <c r="M2" s="366"/>
-      <c r="N2" s="369" t="s">
+      <c r="A2" s="334"/>
+      <c r="B2" s="334"/>
+      <c r="C2" s="334"/>
+      <c r="D2" s="334"/>
+      <c r="E2" s="334"/>
+      <c r="F2" s="334"/>
+      <c r="G2" s="336"/>
+      <c r="H2" s="336"/>
+      <c r="I2" s="336"/>
+      <c r="J2" s="336"/>
+      <c r="K2" s="336"/>
+      <c r="L2" s="336"/>
+      <c r="M2" s="336"/>
+      <c r="N2" s="339" t="s">
         <v>184</v>
       </c>
-      <c r="O2" s="369"/>
-      <c r="P2" s="369"/>
-      <c r="Q2" s="370">
+      <c r="O2" s="339"/>
+      <c r="P2" s="339"/>
+      <c r="Q2" s="340">
         <f>Admin!B4</f>
-        <v>45388</v>
-      </c>
-      <c r="R2" s="371"/>
-      <c r="S2" s="371"/>
-      <c r="T2" s="371"/>
+        <v>45753</v>
+      </c>
+      <c r="R2" s="341"/>
+      <c r="S2" s="341"/>
+      <c r="T2" s="341"/>
       <c r="U2" s="222" t="s">
         <v>185</v>
       </c>
-      <c r="V2" s="370">
+      <c r="V2" s="340">
         <f>Admin!B17</f>
-        <v>45752</v>
-      </c>
-      <c r="W2" s="370"/>
+        <v>46117</v>
+      </c>
+      <c r="W2" s="340"/>
     </row>
     <row r="3" spans="1:23" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="353"/>
-      <c r="B3" s="354"/>
-      <c r="C3" s="354"/>
-      <c r="D3" s="354"/>
-      <c r="E3" s="354"/>
-      <c r="F3" s="354"/>
-      <c r="G3" s="354"/>
-      <c r="H3" s="354"/>
-      <c r="I3" s="354"/>
-      <c r="J3" s="354"/>
-      <c r="K3" s="354"/>
-      <c r="L3" s="354"/>
-      <c r="M3" s="354"/>
-      <c r="N3" s="354"/>
-      <c r="O3" s="354"/>
-      <c r="P3" s="354"/>
-      <c r="Q3" s="354"/>
-      <c r="R3" s="354"/>
-      <c r="S3" s="354"/>
-      <c r="T3" s="354"/>
-      <c r="U3" s="354"/>
-      <c r="V3" s="354"/>
-      <c r="W3" s="354"/>
+      <c r="A3" s="345"/>
+      <c r="B3" s="346"/>
+      <c r="C3" s="346"/>
+      <c r="D3" s="346"/>
+      <c r="E3" s="346"/>
+      <c r="F3" s="346"/>
+      <c r="G3" s="346"/>
+      <c r="H3" s="346"/>
+      <c r="I3" s="346"/>
+      <c r="J3" s="346"/>
+      <c r="K3" s="346"/>
+      <c r="L3" s="346"/>
+      <c r="M3" s="346"/>
+      <c r="N3" s="346"/>
+      <c r="O3" s="346"/>
+      <c r="P3" s="346"/>
+      <c r="Q3" s="346"/>
+      <c r="R3" s="346"/>
+      <c r="S3" s="346"/>
+      <c r="T3" s="346"/>
+      <c r="U3" s="346"/>
+      <c r="V3" s="346"/>
+      <c r="W3" s="346"/>
     </row>
     <row r="4" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="355"/>
-      <c r="B4" s="355"/>
-      <c r="C4" s="355"/>
-      <c r="D4" s="355"/>
-      <c r="E4" s="355"/>
-      <c r="F4" s="355"/>
-      <c r="G4" s="355"/>
-      <c r="H4" s="355"/>
-      <c r="I4" s="355"/>
-      <c r="J4" s="355"/>
-      <c r="K4" s="355"/>
-      <c r="L4" s="355"/>
-      <c r="M4" s="355"/>
-      <c r="N4" s="355"/>
-      <c r="O4" s="355"/>
-      <c r="P4" s="355"/>
-      <c r="Q4" s="355"/>
-      <c r="R4" s="355"/>
-      <c r="S4" s="355"/>
-      <c r="T4" s="355"/>
-      <c r="U4" s="355"/>
-      <c r="V4" s="355"/>
-      <c r="W4" s="356"/>
+      <c r="A4" s="347"/>
+      <c r="B4" s="347"/>
+      <c r="C4" s="347"/>
+      <c r="D4" s="347"/>
+      <c r="E4" s="347"/>
+      <c r="F4" s="347"/>
+      <c r="G4" s="347"/>
+      <c r="H4" s="347"/>
+      <c r="I4" s="347"/>
+      <c r="J4" s="347"/>
+      <c r="K4" s="347"/>
+      <c r="L4" s="347"/>
+      <c r="M4" s="347"/>
+      <c r="N4" s="347"/>
+      <c r="O4" s="347"/>
+      <c r="P4" s="347"/>
+      <c r="Q4" s="347"/>
+      <c r="R4" s="347"/>
+      <c r="S4" s="347"/>
+      <c r="T4" s="347"/>
+      <c r="U4" s="347"/>
+      <c r="V4" s="347"/>
+      <c r="W4" s="348"/>
     </row>
     <row r="5" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="223"/>
@@ -12900,34 +12904,34 @@
     <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="226"/>
       <c r="B8" s="220"/>
-      <c r="C8" s="396" t="str">
+      <c r="C8" s="374" t="str">
         <f>IF('Business Details'!C5&gt;0,'Business Details'!C5," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D8" s="388"/>
-      <c r="E8" s="388"/>
-      <c r="F8" s="388"/>
-      <c r="G8" s="388"/>
-      <c r="H8" s="388"/>
-      <c r="I8" s="388"/>
-      <c r="J8" s="397"/>
+      <c r="D8" s="375"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
+      <c r="G8" s="375"/>
+      <c r="H8" s="375"/>
+      <c r="I8" s="375"/>
+      <c r="J8" s="376"/>
       <c r="K8" s="220"/>
       <c r="L8" s="220"/>
       <c r="M8" s="220"/>
       <c r="N8" s="220"/>
-      <c r="O8" s="396" t="str">
+      <c r="O8" s="374" t="str">
         <f>IF('Business Details'!O5&gt;0,'Business Details'!O5," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="P8" s="397"/>
+      <c r="P8" s="376"/>
       <c r="Q8" s="220"/>
-      <c r="R8" s="396" t="str">
+      <c r="R8" s="374" t="str">
         <f>IF('Business Details'!R5&gt;0,'Business Details'!R5," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="S8" s="388"/>
-      <c r="T8" s="388"/>
-      <c r="U8" s="397"/>
+      <c r="S8" s="375"/>
+      <c r="T8" s="375"/>
+      <c r="U8" s="376"/>
       <c r="V8" s="220"/>
       <c r="W8" s="229"/>
     </row>
@@ -12959,17 +12963,17 @@
     <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="240"/>
       <c r="B10" s="220"/>
-      <c r="C10" s="396" t="str">
+      <c r="C10" s="374" t="str">
         <f>IF('Business Details'!C7&gt;0,'Business Details'!C7," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D10" s="388"/>
-      <c r="E10" s="388"/>
-      <c r="F10" s="388"/>
-      <c r="G10" s="388"/>
-      <c r="H10" s="388"/>
-      <c r="I10" s="388"/>
-      <c r="J10" s="397"/>
+      <c r="D10" s="375"/>
+      <c r="E10" s="375"/>
+      <c r="F10" s="375"/>
+      <c r="G10" s="375"/>
+      <c r="H10" s="375"/>
+      <c r="I10" s="375"/>
+      <c r="J10" s="376"/>
       <c r="K10" s="220"/>
       <c r="L10" s="220"/>
       <c r="M10" s="220"/>
@@ -13010,31 +13014,31 @@
       <c r="W11" s="232"/>
     </row>
     <row r="12" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="399" t="s">
+      <c r="A12" s="373" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="399"/>
-      <c r="C12" s="399"/>
-      <c r="D12" s="399"/>
-      <c r="E12" s="399"/>
-      <c r="F12" s="399"/>
-      <c r="G12" s="399"/>
-      <c r="H12" s="399"/>
-      <c r="I12" s="399"/>
-      <c r="J12" s="399"/>
-      <c r="K12" s="399"/>
-      <c r="L12" s="399"/>
-      <c r="M12" s="399"/>
-      <c r="N12" s="399"/>
-      <c r="O12" s="399"/>
-      <c r="P12" s="399"/>
-      <c r="Q12" s="399"/>
-      <c r="R12" s="399"/>
-      <c r="S12" s="399"/>
-      <c r="T12" s="399"/>
-      <c r="U12" s="399"/>
-      <c r="V12" s="399"/>
-      <c r="W12" s="360"/>
+      <c r="B12" s="373"/>
+      <c r="C12" s="373"/>
+      <c r="D12" s="373"/>
+      <c r="E12" s="373"/>
+      <c r="F12" s="373"/>
+      <c r="G12" s="373"/>
+      <c r="H12" s="373"/>
+      <c r="I12" s="373"/>
+      <c r="J12" s="373"/>
+      <c r="K12" s="373"/>
+      <c r="L12" s="373"/>
+      <c r="M12" s="373"/>
+      <c r="N12" s="373"/>
+      <c r="O12" s="373"/>
+      <c r="P12" s="373"/>
+      <c r="Q12" s="373"/>
+      <c r="R12" s="373"/>
+      <c r="S12" s="373"/>
+      <c r="T12" s="373"/>
+      <c r="U12" s="373"/>
+      <c r="V12" s="373"/>
+      <c r="W12" s="352"/>
     </row>
     <row r="13" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="233"/>
@@ -13097,17 +13101,17 @@
     <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="240"/>
       <c r="B15" s="220"/>
-      <c r="C15" s="396" t="str">
+      <c r="C15" s="374" t="str">
         <f>IF('Business Details'!C12&gt;0,'Business Details'!C12," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D15" s="388"/>
-      <c r="E15" s="388"/>
-      <c r="F15" s="388"/>
-      <c r="G15" s="388"/>
-      <c r="H15" s="388"/>
-      <c r="I15" s="388"/>
-      <c r="J15" s="397"/>
+      <c r="D15" s="375"/>
+      <c r="E15" s="375"/>
+      <c r="F15" s="375"/>
+      <c r="G15" s="375"/>
+      <c r="H15" s="375"/>
+      <c r="I15" s="375"/>
+      <c r="J15" s="376"/>
       <c r="K15" s="220"/>
       <c r="L15" s="220"/>
       <c r="M15" s="220"/>
@@ -13154,17 +13158,17 @@
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="240"/>
       <c r="B17" s="220"/>
-      <c r="C17" s="396" t="str">
+      <c r="C17" s="374" t="str">
         <f>IF('Business Details'!C14&gt;0,'Business Details'!C14," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D17" s="388"/>
-      <c r="E17" s="388"/>
-      <c r="F17" s="388"/>
-      <c r="G17" s="388"/>
-      <c r="H17" s="388"/>
-      <c r="I17" s="388"/>
-      <c r="J17" s="397"/>
+      <c r="D17" s="375"/>
+      <c r="E17" s="375"/>
+      <c r="F17" s="375"/>
+      <c r="G17" s="375"/>
+      <c r="H17" s="375"/>
+      <c r="I17" s="375"/>
+      <c r="J17" s="376"/>
       <c r="K17" s="220"/>
       <c r="L17" s="220"/>
       <c r="M17" s="220"/>
@@ -13234,29 +13238,29 @@
       <c r="P19" s="227"/>
       <c r="Q19" s="227"/>
       <c r="R19" s="220"/>
-      <c r="S19" s="346">
+      <c r="S19" s="353">
         <f>Admin!B4</f>
-        <v>45388</v>
-      </c>
-      <c r="T19" s="347"/>
-      <c r="U19" s="347"/>
-      <c r="V19" s="347"/>
+        <v>45753</v>
+      </c>
+      <c r="T19" s="362"/>
+      <c r="U19" s="362"/>
+      <c r="V19" s="362"/>
       <c r="W19" s="239"/>
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="240"/>
       <c r="B20" s="220"/>
-      <c r="C20" s="396" t="str">
+      <c r="C20" s="374" t="str">
         <f>IF('Business Details'!C17&gt;0,'Business Details'!C17," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D20" s="388"/>
-      <c r="E20" s="388"/>
-      <c r="F20" s="388"/>
-      <c r="G20" s="388"/>
-      <c r="H20" s="388"/>
-      <c r="I20" s="388"/>
-      <c r="J20" s="397"/>
+      <c r="D20" s="375"/>
+      <c r="E20" s="375"/>
+      <c r="F20" s="375"/>
+      <c r="G20" s="375"/>
+      <c r="H20" s="375"/>
+      <c r="I20" s="375"/>
+      <c r="J20" s="376"/>
       <c r="K20" s="220"/>
       <c r="L20" s="220"/>
       <c r="M20" s="220"/>
@@ -13301,27 +13305,27 @@
     <row r="22" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A22" s="240"/>
       <c r="B22" s="220"/>
-      <c r="C22" s="396" t="str">
+      <c r="C22" s="374" t="str">
         <f>IF('Business Details'!C19&gt;0,'Business Details'!C19," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D22" s="388"/>
-      <c r="E22" s="388"/>
-      <c r="F22" s="388"/>
-      <c r="G22" s="388"/>
-      <c r="H22" s="388"/>
-      <c r="I22" s="388"/>
-      <c r="J22" s="397"/>
+      <c r="D22" s="375"/>
+      <c r="E22" s="375"/>
+      <c r="F22" s="375"/>
+      <c r="G22" s="375"/>
+      <c r="H22" s="375"/>
+      <c r="I22" s="375"/>
+      <c r="J22" s="376"/>
       <c r="K22" s="220"/>
       <c r="L22" s="220"/>
       <c r="M22" s="220"/>
-      <c r="N22" s="348" t="str">
+      <c r="N22" s="342" t="str">
         <f>IF('Business Details'!N10&gt;0,'Business Details'!N19," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="O22" s="349"/>
-      <c r="P22" s="349"/>
-      <c r="Q22" s="352"/>
+      <c r="O22" s="343"/>
+      <c r="P22" s="343"/>
+      <c r="Q22" s="344"/>
       <c r="R22" s="220"/>
       <c r="S22" s="220"/>
       <c r="T22" s="220"/>
@@ -13357,17 +13361,17 @@
     <row r="24" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A24" s="240"/>
       <c r="B24" s="220"/>
-      <c r="C24" s="396" t="str">
+      <c r="C24" s="374" t="str">
         <f>IF('Business Details'!C21&gt;0,'Business Details'!C21," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D24" s="388"/>
-      <c r="E24" s="388"/>
-      <c r="F24" s="388"/>
-      <c r="G24" s="388"/>
-      <c r="H24" s="388"/>
-      <c r="I24" s="388"/>
-      <c r="J24" s="397"/>
+      <c r="D24" s="375"/>
+      <c r="E24" s="375"/>
+      <c r="F24" s="375"/>
+      <c r="G24" s="375"/>
+      <c r="H24" s="375"/>
+      <c r="I24" s="375"/>
+      <c r="J24" s="376"/>
       <c r="K24" s="220"/>
       <c r="L24" s="236">
         <v>7</v>
@@ -13380,13 +13384,13 @@
       <c r="P24" s="227"/>
       <c r="Q24" s="227"/>
       <c r="R24" s="220"/>
-      <c r="S24" s="346">
+      <c r="S24" s="353">
         <f>Admin!B17</f>
-        <v>45752</v>
-      </c>
-      <c r="T24" s="347"/>
-      <c r="U24" s="347"/>
-      <c r="V24" s="347"/>
+        <v>46117</v>
+      </c>
+      <c r="T24" s="362"/>
+      <c r="U24" s="362"/>
+      <c r="V24" s="362"/>
       <c r="W24" s="239"/>
     </row>
     <row r="25" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
@@ -13403,17 +13407,17 @@
       <c r="K25" s="220"/>
       <c r="L25" s="220"/>
       <c r="M25" s="220"/>
-      <c r="N25" s="362" t="s">
+      <c r="N25" s="355" t="s">
         <v>157</v>
       </c>
-      <c r="O25" s="362"/>
-      <c r="P25" s="362"/>
-      <c r="Q25" s="362"/>
-      <c r="R25" s="362"/>
-      <c r="S25" s="362"/>
-      <c r="T25" s="362"/>
-      <c r="U25" s="362"/>
-      <c r="V25" s="362"/>
+      <c r="O25" s="355"/>
+      <c r="P25" s="355"/>
+      <c r="Q25" s="355"/>
+      <c r="R25" s="355"/>
+      <c r="S25" s="355"/>
+      <c r="T25" s="355"/>
+      <c r="U25" s="355"/>
+      <c r="V25" s="355"/>
       <c r="W25" s="245"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.15">
@@ -13434,15 +13438,15 @@
       <c r="K26" s="220"/>
       <c r="L26" s="220"/>
       <c r="M26" s="220"/>
-      <c r="N26" s="362"/>
-      <c r="O26" s="362"/>
-      <c r="P26" s="362"/>
-      <c r="Q26" s="362"/>
-      <c r="R26" s="362"/>
-      <c r="S26" s="362"/>
-      <c r="T26" s="362"/>
-      <c r="U26" s="362"/>
-      <c r="V26" s="362"/>
+      <c r="N26" s="355"/>
+      <c r="O26" s="355"/>
+      <c r="P26" s="355"/>
+      <c r="Q26" s="355"/>
+      <c r="R26" s="355"/>
+      <c r="S26" s="355"/>
+      <c r="T26" s="355"/>
+      <c r="U26" s="355"/>
+      <c r="V26" s="355"/>
       <c r="W26" s="245"/>
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -13461,13 +13465,13 @@
       <c r="K27" s="220"/>
       <c r="L27" s="220"/>
       <c r="M27" s="220"/>
-      <c r="N27" s="348" t="str">
+      <c r="N27" s="342" t="str">
         <f>IF('Business Details'!N24&gt;0,'Business Details'!N24," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="O27" s="349"/>
-      <c r="P27" s="349"/>
-      <c r="Q27" s="352"/>
+      <c r="O27" s="343"/>
+      <c r="P27" s="343"/>
+      <c r="Q27" s="344"/>
       <c r="R27" s="220"/>
       <c r="S27" s="220"/>
       <c r="T27" s="220"/>
@@ -13478,17 +13482,17 @@
     <row r="28" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A28" s="240"/>
       <c r="B28" s="220"/>
-      <c r="C28" s="396" t="str">
+      <c r="C28" s="374" t="str">
         <f>IF('Business Details'!C25&gt;0,'Business Details'!C25," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D28" s="388"/>
-      <c r="E28" s="388"/>
-      <c r="F28" s="388"/>
-      <c r="G28" s="388"/>
-      <c r="H28" s="388"/>
-      <c r="I28" s="388"/>
-      <c r="J28" s="397"/>
+      <c r="D28" s="375"/>
+      <c r="E28" s="375"/>
+      <c r="F28" s="375"/>
+      <c r="G28" s="375"/>
+      <c r="H28" s="375"/>
+      <c r="I28" s="375"/>
+      <c r="J28" s="376"/>
       <c r="K28" s="220"/>
       <c r="L28" s="236">
         <v>8</v>
@@ -13537,27 +13541,27 @@
     <row r="30" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A30" s="240"/>
       <c r="B30" s="220"/>
-      <c r="C30" s="396" t="str">
+      <c r="C30" s="374" t="str">
         <f>IF('Business Details'!C27&gt;0,'Business Details'!C27," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D30" s="388"/>
-      <c r="E30" s="388"/>
-      <c r="F30" s="388"/>
-      <c r="G30" s="388"/>
-      <c r="H30" s="388"/>
-      <c r="I30" s="388"/>
-      <c r="J30" s="397"/>
+      <c r="D30" s="375"/>
+      <c r="E30" s="375"/>
+      <c r="F30" s="375"/>
+      <c r="G30" s="375"/>
+      <c r="H30" s="375"/>
+      <c r="I30" s="375"/>
+      <c r="J30" s="376"/>
       <c r="K30" s="220"/>
       <c r="L30" s="220"/>
       <c r="M30" s="220"/>
-      <c r="N30" s="348" t="str">
+      <c r="N30" s="342" t="str">
         <f>IF('Business Details'!N27&gt;0,'Business Details'!N27," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="O30" s="349"/>
-      <c r="P30" s="349"/>
-      <c r="Q30" s="352"/>
+      <c r="O30" s="343"/>
+      <c r="P30" s="343"/>
+      <c r="Q30" s="344"/>
       <c r="R30" s="220"/>
       <c r="S30" s="220"/>
       <c r="T30" s="220"/>
@@ -13626,11 +13630,11 @@
     <row r="33" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A33" s="240"/>
       <c r="B33" s="220"/>
-      <c r="C33" s="394" t="str">
+      <c r="C33" s="377" t="str">
         <f>IF('Business Details'!C30&gt;0,'Business Details'!C30," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D33" s="395"/>
+      <c r="D33" s="378"/>
       <c r="E33" s="267"/>
       <c r="F33" s="269" t="str">
         <f>IF('Business Details'!F30&gt;0,'Business Details'!F30," ")</f>
@@ -13697,13 +13701,13 @@
       <c r="K35" s="220"/>
       <c r="L35" s="220"/>
       <c r="M35" s="220"/>
-      <c r="N35" s="348">
+      <c r="N35" s="342">
         <f>Admin!B17</f>
-        <v>45752</v>
-      </c>
-      <c r="O35" s="349"/>
-      <c r="P35" s="349"/>
-      <c r="Q35" s="352"/>
+        <v>46117</v>
+      </c>
+      <c r="O35" s="343"/>
+      <c r="P35" s="343"/>
+      <c r="Q35" s="344"/>
       <c r="R35" s="220"/>
       <c r="S35" s="220"/>
       <c r="T35" s="220"/>
@@ -13737,31 +13741,31 @@
       <c r="W36" s="251"/>
     </row>
     <row r="37" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="341" t="s">
+      <c r="A37" s="368" t="s">
         <v>166</v>
       </c>
-      <c r="B37" s="341"/>
-      <c r="C37" s="341"/>
-      <c r="D37" s="341"/>
-      <c r="E37" s="341"/>
-      <c r="F37" s="341"/>
-      <c r="G37" s="341"/>
-      <c r="H37" s="341"/>
-      <c r="I37" s="341"/>
-      <c r="J37" s="341"/>
-      <c r="K37" s="341"/>
-      <c r="L37" s="341"/>
-      <c r="M37" s="341"/>
-      <c r="N37" s="341"/>
-      <c r="O37" s="341"/>
-      <c r="P37" s="341"/>
-      <c r="Q37" s="341"/>
-      <c r="R37" s="341"/>
-      <c r="S37" s="341"/>
-      <c r="T37" s="341"/>
-      <c r="U37" s="341"/>
-      <c r="V37" s="341"/>
-      <c r="W37" s="341"/>
+      <c r="B37" s="368"/>
+      <c r="C37" s="368"/>
+      <c r="D37" s="368"/>
+      <c r="E37" s="368"/>
+      <c r="F37" s="368"/>
+      <c r="G37" s="368"/>
+      <c r="H37" s="368"/>
+      <c r="I37" s="368"/>
+      <c r="J37" s="368"/>
+      <c r="K37" s="368"/>
+      <c r="L37" s="368"/>
+      <c r="M37" s="368"/>
+      <c r="N37" s="368"/>
+      <c r="O37" s="368"/>
+      <c r="P37" s="368"/>
+      <c r="Q37" s="368"/>
+      <c r="R37" s="368"/>
+      <c r="S37" s="368"/>
+      <c r="T37" s="368"/>
+      <c r="U37" s="368"/>
+      <c r="V37" s="368"/>
+      <c r="W37" s="368"/>
     </row>
     <row r="38" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="233"/>
@@ -14102,31 +14106,31 @@
       <c r="W49" s="251"/>
     </row>
     <row r="50" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="342" t="s">
+      <c r="A50" s="365" t="s">
         <v>186</v>
       </c>
-      <c r="B50" s="342"/>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
-      <c r="G50" s="342"/>
-      <c r="H50" s="342"/>
-      <c r="I50" s="342"/>
-      <c r="J50" s="342"/>
-      <c r="K50" s="342"/>
-      <c r="L50" s="342"/>
-      <c r="M50" s="342"/>
-      <c r="N50" s="342"/>
-      <c r="O50" s="342"/>
-      <c r="P50" s="342"/>
-      <c r="Q50" s="342"/>
-      <c r="R50" s="342"/>
-      <c r="S50" s="342"/>
-      <c r="T50" s="342"/>
-      <c r="U50" s="342"/>
-      <c r="V50" s="342"/>
-      <c r="W50" s="342"/>
+      <c r="B50" s="365"/>
+      <c r="C50" s="365"/>
+      <c r="D50" s="365"/>
+      <c r="E50" s="365"/>
+      <c r="F50" s="365"/>
+      <c r="G50" s="365"/>
+      <c r="H50" s="365"/>
+      <c r="I50" s="365"/>
+      <c r="J50" s="365"/>
+      <c r="K50" s="365"/>
+      <c r="L50" s="365"/>
+      <c r="M50" s="365"/>
+      <c r="N50" s="365"/>
+      <c r="O50" s="365"/>
+      <c r="P50" s="365"/>
+      <c r="Q50" s="365"/>
+      <c r="R50" s="365"/>
+      <c r="S50" s="365"/>
+      <c r="T50" s="365"/>
+      <c r="U50" s="365"/>
+      <c r="V50" s="365"/>
+      <c r="W50" s="365"/>
     </row>
     <row r="51" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="233"/>
@@ -14246,12 +14250,12 @@
       <c r="C55" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D55" s="333">
+      <c r="D55" s="356">
         <f>'Profit &amp; Loss Account'!B9</f>
         <v>0</v>
       </c>
-      <c r="E55" s="334"/>
-      <c r="F55" s="335"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="358"/>
       <c r="G55" s="218" t="s">
         <v>178</v>
       </c>
@@ -14268,12 +14272,12 @@
       <c r="N55" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O55" s="333">
+      <c r="O55" s="356">
         <f>'Profit &amp; Loss Account'!B38</f>
         <v>0</v>
       </c>
-      <c r="P55" s="334"/>
-      <c r="Q55" s="335"/>
+      <c r="P55" s="357"/>
+      <c r="Q55" s="358"/>
       <c r="R55" s="218" t="s">
         <v>178</v>
       </c>
@@ -14313,58 +14317,58 @@
       <c r="W56" s="251"/>
     </row>
     <row r="57" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="342" t="s">
+      <c r="A57" s="365" t="s">
         <v>191</v>
       </c>
-      <c r="B57" s="342"/>
-      <c r="C57" s="342"/>
-      <c r="D57" s="342"/>
-      <c r="E57" s="342"/>
-      <c r="F57" s="342"/>
-      <c r="G57" s="342"/>
-      <c r="H57" s="342"/>
-      <c r="I57" s="342"/>
-      <c r="J57" s="342"/>
-      <c r="K57" s="342"/>
-      <c r="L57" s="342"/>
-      <c r="M57" s="342"/>
-      <c r="N57" s="342"/>
-      <c r="O57" s="342"/>
-      <c r="P57" s="342"/>
-      <c r="Q57" s="342"/>
-      <c r="R57" s="342"/>
-      <c r="S57" s="342"/>
-      <c r="T57" s="342"/>
-      <c r="U57" s="342"/>
-      <c r="V57" s="342"/>
-      <c r="W57" s="342"/>
+      <c r="B57" s="365"/>
+      <c r="C57" s="365"/>
+      <c r="D57" s="365"/>
+      <c r="E57" s="365"/>
+      <c r="F57" s="365"/>
+      <c r="G57" s="365"/>
+      <c r="H57" s="365"/>
+      <c r="I57" s="365"/>
+      <c r="J57" s="365"/>
+      <c r="K57" s="365"/>
+      <c r="L57" s="365"/>
+      <c r="M57" s="365"/>
+      <c r="N57" s="365"/>
+      <c r="O57" s="365"/>
+      <c r="P57" s="365"/>
+      <c r="Q57" s="365"/>
+      <c r="R57" s="365"/>
+      <c r="S57" s="365"/>
+      <c r="T57" s="365"/>
+      <c r="U57" s="365"/>
+      <c r="V57" s="365"/>
+      <c r="W57" s="365"/>
     </row>
     <row r="58" spans="1:23" s="254" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="336" t="s">
+      <c r="A58" s="366" t="s">
         <v>192</v>
       </c>
-      <c r="B58" s="336"/>
-      <c r="C58" s="336"/>
-      <c r="D58" s="336"/>
-      <c r="E58" s="336"/>
-      <c r="F58" s="336"/>
-      <c r="G58" s="336"/>
-      <c r="H58" s="336"/>
-      <c r="I58" s="336"/>
-      <c r="J58" s="336"/>
-      <c r="K58" s="336"/>
-      <c r="L58" s="336"/>
-      <c r="M58" s="336"/>
-      <c r="N58" s="336"/>
-      <c r="O58" s="336"/>
-      <c r="P58" s="336"/>
-      <c r="Q58" s="336"/>
-      <c r="R58" s="336"/>
-      <c r="S58" s="336"/>
-      <c r="T58" s="336"/>
-      <c r="U58" s="336"/>
-      <c r="V58" s="336"/>
-      <c r="W58" s="336"/>
+      <c r="B58" s="366"/>
+      <c r="C58" s="366"/>
+      <c r="D58" s="366"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
+      <c r="G58" s="366"/>
+      <c r="H58" s="366"/>
+      <c r="I58" s="366"/>
+      <c r="J58" s="366"/>
+      <c r="K58" s="366"/>
+      <c r="L58" s="366"/>
+      <c r="M58" s="366"/>
+      <c r="N58" s="366"/>
+      <c r="O58" s="366"/>
+      <c r="P58" s="366"/>
+      <c r="Q58" s="366"/>
+      <c r="R58" s="366"/>
+      <c r="S58" s="366"/>
+      <c r="T58" s="366"/>
+      <c r="U58" s="366"/>
+      <c r="V58" s="366"/>
+      <c r="W58" s="366"/>
     </row>
     <row r="59" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="233"/>
@@ -14565,12 +14569,12 @@
       <c r="C66" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D66" s="333">
+      <c r="D66" s="356">
         <f>'Profit &amp; Loss Account'!B14+'Profit &amp; Loss Account'!B16</f>
         <v>0</v>
       </c>
-      <c r="E66" s="334"/>
-      <c r="F66" s="335"/>
+      <c r="E66" s="357"/>
+      <c r="F66" s="358"/>
       <c r="G66" s="218" t="s">
         <v>178</v>
       </c>
@@ -14587,9 +14591,9 @@
       <c r="N66" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O66" s="333"/>
-      <c r="P66" s="334"/>
-      <c r="Q66" s="335"/>
+      <c r="O66" s="356"/>
+      <c r="P66" s="357"/>
+      <c r="Q66" s="358"/>
       <c r="R66" s="218" t="s">
         <v>178</v>
       </c>
@@ -14690,12 +14694,12 @@
       <c r="C70" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D70" s="333">
+      <c r="D70" s="356">
         <f>'Profit &amp; Loss Account'!B15</f>
         <v>0</v>
       </c>
-      <c r="E70" s="334"/>
-      <c r="F70" s="335"/>
+      <c r="E70" s="357"/>
+      <c r="F70" s="358"/>
       <c r="G70" s="218" t="s">
         <v>178</v>
       </c>
@@ -14712,9 +14716,9 @@
       <c r="N70" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O70" s="333"/>
-      <c r="P70" s="334"/>
-      <c r="Q70" s="335"/>
+      <c r="O70" s="356"/>
+      <c r="P70" s="357"/>
+      <c r="Q70" s="358"/>
       <c r="R70" s="218" t="s">
         <v>178</v>
       </c>
@@ -14815,12 +14819,12 @@
       <c r="C74" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D74" s="333">
+      <c r="D74" s="356">
         <f>'Profit &amp; Loss Account'!B21</f>
         <v>0</v>
       </c>
-      <c r="E74" s="334"/>
-      <c r="F74" s="335"/>
+      <c r="E74" s="357"/>
+      <c r="F74" s="358"/>
       <c r="G74" s="218" t="s">
         <v>178</v>
       </c>
@@ -14837,9 +14841,9 @@
       <c r="N74" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O74" s="333"/>
-      <c r="P74" s="334"/>
-      <c r="Q74" s="335"/>
+      <c r="O74" s="356"/>
+      <c r="P74" s="357"/>
+      <c r="Q74" s="358"/>
       <c r="R74" s="218" t="s">
         <v>178</v>
       </c>
@@ -14940,12 +14944,12 @@
       <c r="C78" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="356">
         <f>'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26</f>
         <v>0</v>
       </c>
-      <c r="E78" s="334"/>
-      <c r="F78" s="335"/>
+      <c r="E78" s="357"/>
+      <c r="F78" s="358"/>
       <c r="G78" s="218" t="s">
         <v>178</v>
       </c>
@@ -14962,9 +14966,9 @@
       <c r="N78" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O78" s="333"/>
-      <c r="P78" s="334"/>
-      <c r="Q78" s="335"/>
+      <c r="O78" s="356"/>
+      <c r="P78" s="357"/>
+      <c r="Q78" s="358"/>
       <c r="R78" s="218" t="s">
         <v>178</v>
       </c>
@@ -15065,12 +15069,12 @@
       <c r="C82" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D82" s="333">
+      <c r="D82" s="356">
         <f>'Profit &amp; Loss Account'!B22</f>
         <v>0</v>
       </c>
-      <c r="E82" s="334"/>
-      <c r="F82" s="335"/>
+      <c r="E82" s="357"/>
+      <c r="F82" s="358"/>
       <c r="G82" s="218" t="s">
         <v>178</v>
       </c>
@@ -15087,9 +15091,9 @@
       <c r="N82" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O82" s="333"/>
-      <c r="P82" s="334"/>
-      <c r="Q82" s="335"/>
+      <c r="O82" s="356"/>
+      <c r="P82" s="357"/>
+      <c r="Q82" s="358"/>
       <c r="R82" s="218" t="s">
         <v>178</v>
       </c>
@@ -15190,12 +15194,12 @@
       <c r="C86" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D86" s="333">
+      <c r="D86" s="356">
         <f>'Profit &amp; Loss Account'!B23</f>
         <v>0</v>
       </c>
-      <c r="E86" s="334"/>
-      <c r="F86" s="335"/>
+      <c r="E86" s="357"/>
+      <c r="F86" s="358"/>
       <c r="G86" s="218" t="s">
         <v>178</v>
       </c>
@@ -15212,9 +15216,9 @@
       <c r="N86" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O86" s="333"/>
-      <c r="P86" s="334"/>
-      <c r="Q86" s="335"/>
+      <c r="O86" s="356"/>
+      <c r="P86" s="357"/>
+      <c r="Q86" s="358"/>
       <c r="R86" s="218" t="s">
         <v>178</v>
       </c>
@@ -15315,12 +15319,12 @@
       <c r="C90" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D90" s="333">
+      <c r="D90" s="356">
         <f>'Profit &amp; Loss Account'!B24</f>
         <v>0</v>
       </c>
-      <c r="E90" s="334"/>
-      <c r="F90" s="335"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="358"/>
       <c r="G90" s="218" t="s">
         <v>178</v>
       </c>
@@ -15337,9 +15341,9 @@
       <c r="N90" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O90" s="333"/>
-      <c r="P90" s="334"/>
-      <c r="Q90" s="335"/>
+      <c r="O90" s="356"/>
+      <c r="P90" s="357"/>
+      <c r="Q90" s="358"/>
       <c r="R90" s="218" t="s">
         <v>178</v>
       </c>
@@ -15440,12 +15444,12 @@
       <c r="C94" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D94" s="333">
+      <c r="D94" s="356">
         <f>'Profit &amp; Loss Account'!B27</f>
         <v>0</v>
       </c>
-      <c r="E94" s="334"/>
-      <c r="F94" s="335"/>
+      <c r="E94" s="357"/>
+      <c r="F94" s="358"/>
       <c r="G94" s="218" t="s">
         <v>178</v>
       </c>
@@ -15462,9 +15466,9 @@
       <c r="N94" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O94" s="333"/>
-      <c r="P94" s="334"/>
-      <c r="Q94" s="335"/>
+      <c r="O94" s="356"/>
+      <c r="P94" s="357"/>
+      <c r="Q94" s="358"/>
       <c r="R94" s="218" t="s">
         <v>178</v>
       </c>
@@ -15565,12 +15569,12 @@
       <c r="C98" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D98" s="333">
+      <c r="D98" s="356">
         <f>'Profit &amp; Loss Account'!B30</f>
         <v>0</v>
       </c>
-      <c r="E98" s="334"/>
-      <c r="F98" s="335"/>
+      <c r="E98" s="357"/>
+      <c r="F98" s="358"/>
       <c r="G98" s="218" t="s">
         <v>178</v>
       </c>
@@ -15587,9 +15591,9 @@
       <c r="N98" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O98" s="333"/>
-      <c r="P98" s="334"/>
-      <c r="Q98" s="335"/>
+      <c r="O98" s="356"/>
+      <c r="P98" s="357"/>
+      <c r="Q98" s="358"/>
       <c r="R98" s="218" t="s">
         <v>178</v>
       </c>
@@ -15690,12 +15694,12 @@
       <c r="C102" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D102" s="333">
+      <c r="D102" s="356">
         <f>'Profit &amp; Loss Account'!B31</f>
         <v>0</v>
       </c>
-      <c r="E102" s="334"/>
-      <c r="F102" s="335"/>
+      <c r="E102" s="357"/>
+      <c r="F102" s="358"/>
       <c r="G102" s="218" t="s">
         <v>178</v>
       </c>
@@ -15712,9 +15716,9 @@
       <c r="N102" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O102" s="333"/>
-      <c r="P102" s="334"/>
-      <c r="Q102" s="335"/>
+      <c r="O102" s="356"/>
+      <c r="P102" s="357"/>
+      <c r="Q102" s="358"/>
       <c r="R102" s="218" t="s">
         <v>178</v>
       </c>
@@ -15815,12 +15819,12 @@
       <c r="C106" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D106" s="333">
+      <c r="D106" s="356">
         <f>'Profit &amp; Loss Account'!B29</f>
         <v>0</v>
       </c>
-      <c r="E106" s="334"/>
-      <c r="F106" s="335"/>
+      <c r="E106" s="357"/>
+      <c r="F106" s="358"/>
       <c r="G106" s="218" t="s">
         <v>178</v>
       </c>
@@ -15837,9 +15841,9 @@
       <c r="N106" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O106" s="333"/>
-      <c r="P106" s="334"/>
-      <c r="Q106" s="335"/>
+      <c r="O106" s="356"/>
+      <c r="P106" s="357"/>
+      <c r="Q106" s="358"/>
       <c r="R106" s="218" t="s">
         <v>178</v>
       </c>
@@ -15940,12 +15944,12 @@
       <c r="C110" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D110" s="333">
+      <c r="D110" s="356">
         <f>'Profit &amp; Loss Account'!B28</f>
         <v>0</v>
       </c>
-      <c r="E110" s="334"/>
-      <c r="F110" s="335"/>
+      <c r="E110" s="357"/>
+      <c r="F110" s="358"/>
       <c r="G110" s="218" t="s">
         <v>178</v>
       </c>
@@ -15962,9 +15966,9 @@
       <c r="N110" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O110" s="333"/>
-      <c r="P110" s="334"/>
-      <c r="Q110" s="335"/>
+      <c r="O110" s="356"/>
+      <c r="P110" s="357"/>
+      <c r="Q110" s="358"/>
       <c r="R110" s="218" t="s">
         <v>178</v>
       </c>
@@ -16065,12 +16069,12 @@
       <c r="C114" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D114" s="333">
+      <c r="D114" s="356">
         <f>'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
         <v>0</v>
       </c>
-      <c r="E114" s="334"/>
-      <c r="F114" s="335"/>
+      <c r="E114" s="357"/>
+      <c r="F114" s="358"/>
       <c r="G114" s="218" t="s">
         <v>178</v>
       </c>
@@ -16087,12 +16091,12 @@
       <c r="N114" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O114" s="333">
+      <c r="O114" s="356">
         <f>'Profit &amp; Loss Account'!B34</f>
         <v>0</v>
       </c>
-      <c r="P114" s="334"/>
-      <c r="Q114" s="335"/>
+      <c r="P114" s="357"/>
+      <c r="Q114" s="358"/>
       <c r="R114" s="218" t="s">
         <v>178</v>
       </c>
@@ -16193,12 +16197,12 @@
       <c r="C118" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D118" s="333">
+      <c r="D118" s="356">
         <f>'Profit &amp; Loss Account'!B32</f>
         <v>0</v>
       </c>
-      <c r="E118" s="334"/>
-      <c r="F118" s="335"/>
+      <c r="E118" s="357"/>
+      <c r="F118" s="358"/>
       <c r="G118" s="218" t="s">
         <v>178</v>
       </c>
@@ -16215,9 +16219,9 @@
       <c r="N118" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O118" s="333"/>
-      <c r="P118" s="334"/>
-      <c r="Q118" s="335"/>
+      <c r="O118" s="356"/>
+      <c r="P118" s="357"/>
+      <c r="Q118" s="358"/>
       <c r="R118" s="218" t="s">
         <v>178</v>
       </c>
@@ -16320,12 +16324,12 @@
       <c r="C122" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D122" s="333">
+      <c r="D122" s="356">
         <f>'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35</f>
         <v>0</v>
       </c>
-      <c r="E122" s="334"/>
-      <c r="F122" s="335"/>
+      <c r="E122" s="357"/>
+      <c r="F122" s="358"/>
       <c r="G122" s="218" t="s">
         <v>178</v>
       </c>
@@ -16342,12 +16346,12 @@
       <c r="N122" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O122" s="333">
+      <c r="O122" s="356">
         <f>'Profit &amp; Loss Account'!B34</f>
         <v>0</v>
       </c>
-      <c r="P122" s="334"/>
-      <c r="Q122" s="335"/>
+      <c r="P122" s="357"/>
+      <c r="Q122" s="358"/>
       <c r="R122" s="218" t="s">
         <v>178</v>
       </c>
@@ -16387,31 +16391,31 @@
       <c r="W123" s="251"/>
     </row>
     <row r="124" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A124" s="343" t="s">
+      <c r="A124" s="367" t="s">
         <v>213</v>
       </c>
-      <c r="B124" s="343"/>
-      <c r="C124" s="343"/>
-      <c r="D124" s="343"/>
-      <c r="E124" s="343"/>
-      <c r="F124" s="343"/>
-      <c r="G124" s="343"/>
-      <c r="H124" s="343"/>
-      <c r="I124" s="343"/>
-      <c r="J124" s="343"/>
-      <c r="K124" s="343"/>
-      <c r="L124" s="343"/>
-      <c r="M124" s="343"/>
-      <c r="N124" s="343"/>
-      <c r="O124" s="343"/>
-      <c r="P124" s="343"/>
-      <c r="Q124" s="343"/>
-      <c r="R124" s="343"/>
-      <c r="S124" s="343"/>
-      <c r="T124" s="343"/>
-      <c r="U124" s="343"/>
-      <c r="V124" s="343"/>
-      <c r="W124" s="343"/>
+      <c r="B124" s="367"/>
+      <c r="C124" s="367"/>
+      <c r="D124" s="367"/>
+      <c r="E124" s="367"/>
+      <c r="F124" s="367"/>
+      <c r="G124" s="367"/>
+      <c r="H124" s="367"/>
+      <c r="I124" s="367"/>
+      <c r="J124" s="367"/>
+      <c r="K124" s="367"/>
+      <c r="L124" s="367"/>
+      <c r="M124" s="367"/>
+      <c r="N124" s="367"/>
+      <c r="O124" s="367"/>
+      <c r="P124" s="367"/>
+      <c r="Q124" s="367"/>
+      <c r="R124" s="367"/>
+      <c r="S124" s="367"/>
+      <c r="T124" s="367"/>
+      <c r="U124" s="367"/>
+      <c r="V124" s="367"/>
+      <c r="W124" s="367"/>
     </row>
     <row r="125" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="233"/>
@@ -16531,12 +16535,12 @@
       <c r="C129" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D129" s="333">
+      <c r="D129" s="356">
         <f>IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
         <v>0</v>
       </c>
-      <c r="E129" s="334"/>
-      <c r="F129" s="335"/>
+      <c r="E129" s="357"/>
+      <c r="F129" s="358"/>
       <c r="G129" s="218" t="s">
         <v>178</v>
       </c>
@@ -16553,12 +16557,12 @@
       <c r="N129" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O129" s="333">
+      <c r="O129" s="356">
         <f>IF((D55+O55-D122)&lt;0,D122-D55-O55,0)</f>
         <v>0</v>
       </c>
-      <c r="P129" s="334"/>
-      <c r="Q129" s="335"/>
+      <c r="P129" s="357"/>
+      <c r="Q129" s="358"/>
       <c r="R129" s="218" t="s">
         <v>178</v>
       </c>
@@ -16598,112 +16602,112 @@
       <c r="W130" s="251"/>
     </row>
     <row r="131" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A131" s="342" t="s">
+      <c r="A131" s="365" t="s">
         <v>218</v>
       </c>
-      <c r="B131" s="342"/>
-      <c r="C131" s="342"/>
-      <c r="D131" s="342"/>
-      <c r="E131" s="342"/>
-      <c r="F131" s="342"/>
-      <c r="G131" s="342"/>
-      <c r="H131" s="342"/>
-      <c r="I131" s="342"/>
-      <c r="J131" s="342"/>
-      <c r="K131" s="342"/>
-      <c r="L131" s="342"/>
-      <c r="M131" s="342"/>
-      <c r="N131" s="342"/>
-      <c r="O131" s="342"/>
-      <c r="P131" s="342"/>
-      <c r="Q131" s="342"/>
-      <c r="R131" s="342"/>
-      <c r="S131" s="342"/>
-      <c r="T131" s="342"/>
-      <c r="U131" s="342"/>
-      <c r="V131" s="342"/>
-      <c r="W131" s="342"/>
+      <c r="B131" s="365"/>
+      <c r="C131" s="365"/>
+      <c r="D131" s="365"/>
+      <c r="E131" s="365"/>
+      <c r="F131" s="365"/>
+      <c r="G131" s="365"/>
+      <c r="H131" s="365"/>
+      <c r="I131" s="365"/>
+      <c r="J131" s="365"/>
+      <c r="K131" s="365"/>
+      <c r="L131" s="365"/>
+      <c r="M131" s="365"/>
+      <c r="N131" s="365"/>
+      <c r="O131" s="365"/>
+      <c r="P131" s="365"/>
+      <c r="Q131" s="365"/>
+      <c r="R131" s="365"/>
+      <c r="S131" s="365"/>
+      <c r="T131" s="365"/>
+      <c r="U131" s="365"/>
+      <c r="V131" s="365"/>
+      <c r="W131" s="365"/>
     </row>
     <row r="132" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A132" s="336" t="s">
+      <c r="A132" s="366" t="s">
         <v>219</v>
       </c>
-      <c r="B132" s="336"/>
-      <c r="C132" s="336"/>
-      <c r="D132" s="336"/>
-      <c r="E132" s="336"/>
-      <c r="F132" s="336"/>
-      <c r="G132" s="336"/>
-      <c r="H132" s="336"/>
-      <c r="I132" s="336"/>
-      <c r="J132" s="336"/>
-      <c r="K132" s="336"/>
-      <c r="L132" s="336"/>
-      <c r="M132" s="336"/>
-      <c r="N132" s="336"/>
-      <c r="O132" s="336"/>
-      <c r="P132" s="336"/>
-      <c r="Q132" s="336"/>
-      <c r="R132" s="336"/>
-      <c r="S132" s="336"/>
-      <c r="T132" s="336"/>
-      <c r="U132" s="336"/>
-      <c r="V132" s="336"/>
-      <c r="W132" s="336"/>
+      <c r="B132" s="366"/>
+      <c r="C132" s="366"/>
+      <c r="D132" s="366"/>
+      <c r="E132" s="366"/>
+      <c r="F132" s="366"/>
+      <c r="G132" s="366"/>
+      <c r="H132" s="366"/>
+      <c r="I132" s="366"/>
+      <c r="J132" s="366"/>
+      <c r="K132" s="366"/>
+      <c r="L132" s="366"/>
+      <c r="M132" s="366"/>
+      <c r="N132" s="366"/>
+      <c r="O132" s="366"/>
+      <c r="P132" s="366"/>
+      <c r="Q132" s="366"/>
+      <c r="R132" s="366"/>
+      <c r="S132" s="366"/>
+      <c r="T132" s="366"/>
+      <c r="U132" s="366"/>
+      <c r="V132" s="366"/>
+      <c r="W132" s="366"/>
     </row>
     <row r="133" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A133" s="336" t="s">
+      <c r="A133" s="366" t="s">
         <v>352</v>
       </c>
-      <c r="B133" s="336"/>
-      <c r="C133" s="336"/>
-      <c r="D133" s="336"/>
-      <c r="E133" s="336"/>
-      <c r="F133" s="336"/>
-      <c r="G133" s="336"/>
-      <c r="H133" s="336"/>
-      <c r="I133" s="336"/>
-      <c r="J133" s="336"/>
-      <c r="K133" s="336"/>
-      <c r="L133" s="336"/>
-      <c r="M133" s="336"/>
-      <c r="N133" s="336"/>
-      <c r="O133" s="336"/>
-      <c r="P133" s="336"/>
-      <c r="Q133" s="336"/>
-      <c r="R133" s="336"/>
-      <c r="S133" s="336"/>
-      <c r="T133" s="336"/>
-      <c r="U133" s="336"/>
-      <c r="V133" s="336"/>
-      <c r="W133" s="336"/>
+      <c r="B133" s="366"/>
+      <c r="C133" s="366"/>
+      <c r="D133" s="366"/>
+      <c r="E133" s="366"/>
+      <c r="F133" s="366"/>
+      <c r="G133" s="366"/>
+      <c r="H133" s="366"/>
+      <c r="I133" s="366"/>
+      <c r="J133" s="366"/>
+      <c r="K133" s="366"/>
+      <c r="L133" s="366"/>
+      <c r="M133" s="366"/>
+      <c r="N133" s="366"/>
+      <c r="O133" s="366"/>
+      <c r="P133" s="366"/>
+      <c r="Q133" s="366"/>
+      <c r="R133" s="366"/>
+      <c r="S133" s="366"/>
+      <c r="T133" s="366"/>
+      <c r="U133" s="366"/>
+      <c r="V133" s="366"/>
+      <c r="W133" s="366"/>
     </row>
     <row r="134" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A134" s="336" t="s">
+      <c r="A134" s="366" t="s">
         <v>220</v>
       </c>
-      <c r="B134" s="336"/>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
-      <c r="G134" s="336"/>
-      <c r="H134" s="336"/>
-      <c r="I134" s="336"/>
-      <c r="J134" s="336"/>
-      <c r="K134" s="336"/>
-      <c r="L134" s="336"/>
-      <c r="M134" s="336"/>
-      <c r="N134" s="336"/>
-      <c r="O134" s="336"/>
-      <c r="P134" s="336"/>
-      <c r="Q134" s="336"/>
-      <c r="R134" s="336"/>
-      <c r="S134" s="336"/>
-      <c r="T134" s="336"/>
-      <c r="U134" s="336"/>
-      <c r="V134" s="336"/>
-      <c r="W134" s="336"/>
+      <c r="B134" s="366"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
+      <c r="G134" s="366"/>
+      <c r="H134" s="366"/>
+      <c r="I134" s="366"/>
+      <c r="J134" s="366"/>
+      <c r="K134" s="366"/>
+      <c r="L134" s="366"/>
+      <c r="M134" s="366"/>
+      <c r="N134" s="366"/>
+      <c r="O134" s="366"/>
+      <c r="P134" s="366"/>
+      <c r="Q134" s="366"/>
+      <c r="R134" s="366"/>
+      <c r="S134" s="366"/>
+      <c r="T134" s="366"/>
+      <c r="U134" s="366"/>
+      <c r="V134" s="366"/>
+      <c r="W134" s="366"/>
     </row>
     <row r="135" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="233"/>
@@ -16742,11 +16746,11 @@
       <c r="E136" s="227"/>
       <c r="F136" s="227"/>
       <c r="G136" s="227"/>
-      <c r="H136" s="391">
+      <c r="H136" s="379">
         <f>Admin!G4</f>
         <v>1</v>
       </c>
-      <c r="I136" s="393"/>
+      <c r="I136" s="380"/>
       <c r="J136" s="227"/>
       <c r="K136" s="227"/>
       <c r="L136" s="236">
@@ -16824,12 +16828,12 @@
       <c r="C139" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D139" s="333">
+      <c r="D139" s="356">
         <f>IF([1]Schedule!$Q$1&gt;0,[1]Schedule!$Q$1,0)</f>
         <v>0</v>
       </c>
-      <c r="E139" s="334"/>
-      <c r="F139" s="335"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="358"/>
       <c r="G139" s="218" t="s">
         <v>178</v>
       </c>
@@ -16846,12 +16850,12 @@
       <c r="N139" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O139" s="333">
+      <c r="O139" s="356">
         <f>IF(([1]Schedule!$R$1+[1]Schedule!$S$1)&lt;1000,[1]Schedule!$S$1,0)</f>
         <v>0</v>
       </c>
-      <c r="P139" s="334"/>
-      <c r="Q139" s="335"/>
+      <c r="P139" s="357"/>
+      <c r="Q139" s="358"/>
       <c r="R139" s="218" t="s">
         <v>178</v>
       </c>
@@ -16901,11 +16905,11 @@
       <c r="D141" s="227"/>
       <c r="E141" s="227"/>
       <c r="F141" s="227"/>
-      <c r="G141" s="391">
+      <c r="G141" s="379">
         <f>Admin!G5</f>
         <v>0.18</v>
       </c>
-      <c r="H141" s="392"/>
+      <c r="H141" s="381"/>
       <c r="I141" s="227" t="s">
         <v>222</v>
       </c>
@@ -16988,12 +16992,12 @@
       <c r="C144" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D144" s="333">
+      <c r="D144" s="356">
         <f>[1]Schedule!$R$1-D152</f>
         <v>0</v>
       </c>
-      <c r="E144" s="334"/>
-      <c r="F144" s="335"/>
+      <c r="E144" s="357"/>
+      <c r="F144" s="358"/>
       <c r="G144" s="218" t="s">
         <v>178</v>
       </c>
@@ -17010,12 +17014,12 @@
       <c r="N144" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O144" s="333">
+      <c r="O144" s="356">
         <f>[1]Schedule!$Y$1</f>
         <v>0</v>
       </c>
-      <c r="P144" s="334"/>
-      <c r="Q144" s="335"/>
+      <c r="P144" s="357"/>
+      <c r="Q144" s="358"/>
       <c r="R144" s="218" t="s">
         <v>178</v>
       </c>
@@ -17066,10 +17070,10 @@
       <c r="E146" s="227"/>
       <c r="F146" s="227"/>
       <c r="G146" s="227"/>
-      <c r="H146" s="391">
+      <c r="H146" s="379">
         <v>0.1</v>
       </c>
-      <c r="I146" s="393"/>
+      <c r="I146" s="380"/>
       <c r="J146" s="220"/>
       <c r="K146" s="220"/>
       <c r="L146" s="220"/>
@@ -17091,9 +17095,9 @@
       <c r="C147" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D147" s="333"/>
-      <c r="E147" s="334"/>
-      <c r="F147" s="335"/>
+      <c r="D147" s="356"/>
+      <c r="E147" s="357"/>
+      <c r="F147" s="358"/>
       <c r="G147" s="218" t="s">
         <v>178</v>
       </c>
@@ -17168,12 +17172,12 @@
       <c r="N149" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O149" s="333">
+      <c r="O149" s="356">
         <f>D139+D144+D147+D152+D156+D160+O139+O144</f>
         <v>0</v>
       </c>
-      <c r="P149" s="334"/>
-      <c r="Q149" s="335"/>
+      <c r="P149" s="357"/>
+      <c r="Q149" s="358"/>
       <c r="R149" s="218" t="s">
         <v>178</v>
       </c>
@@ -17249,12 +17253,12 @@
       <c r="C152" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D152" s="333">
+      <c r="D152" s="356">
         <f>SUM([1]Schedule!$R$38:$R$42)+SUM([1]Schedule!$R$91:$R$95)</f>
         <v>0</v>
       </c>
-      <c r="E152" s="320"/>
-      <c r="F152" s="321"/>
+      <c r="E152" s="331"/>
+      <c r="F152" s="332"/>
       <c r="G152" s="218" t="s">
         <v>178</v>
       </c>
@@ -17327,9 +17331,9 @@
       <c r="N154" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O154" s="333"/>
-      <c r="P154" s="334"/>
-      <c r="Q154" s="335"/>
+      <c r="O154" s="356"/>
+      <c r="P154" s="357"/>
+      <c r="Q154" s="358"/>
       <c r="R154" s="218" t="s">
         <v>178</v>
       </c>
@@ -17374,9 +17378,9 @@
       <c r="C156" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D156" s="333"/>
-      <c r="E156" s="320"/>
-      <c r="F156" s="321"/>
+      <c r="D156" s="356"/>
+      <c r="E156" s="331"/>
+      <c r="F156" s="332"/>
       <c r="G156" s="218" t="s">
         <v>178</v>
       </c>
@@ -17496,9 +17500,9 @@
       <c r="C160" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D160" s="333"/>
-      <c r="E160" s="334"/>
-      <c r="F160" s="335"/>
+      <c r="D160" s="356"/>
+      <c r="E160" s="357"/>
+      <c r="F160" s="358"/>
       <c r="G160" s="218" t="s">
         <v>178</v>
       </c>
@@ -17515,12 +17519,12 @@
       <c r="N160" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O160" s="333">
+      <c r="O160" s="356">
         <f>[1]Schedule!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="P160" s="334"/>
-      <c r="Q160" s="335"/>
+      <c r="P160" s="357"/>
+      <c r="Q160" s="358"/>
       <c r="R160" s="218" t="s">
         <v>178</v>
       </c>
@@ -17560,85 +17564,85 @@
       <c r="W161" s="251"/>
     </row>
     <row r="162" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A162" s="342" t="s">
+      <c r="A162" s="365" t="s">
         <v>233</v>
       </c>
-      <c r="B162" s="342"/>
-      <c r="C162" s="342"/>
-      <c r="D162" s="342"/>
-      <c r="E162" s="342"/>
-      <c r="F162" s="342"/>
-      <c r="G162" s="342"/>
-      <c r="H162" s="342"/>
-      <c r="I162" s="342"/>
-      <c r="J162" s="342"/>
-      <c r="K162" s="342"/>
-      <c r="L162" s="342"/>
-      <c r="M162" s="342"/>
-      <c r="N162" s="342"/>
-      <c r="O162" s="342"/>
-      <c r="P162" s="342"/>
-      <c r="Q162" s="342"/>
-      <c r="R162" s="342"/>
-      <c r="S162" s="342"/>
-      <c r="T162" s="342"/>
-      <c r="U162" s="342"/>
-      <c r="V162" s="342"/>
-      <c r="W162" s="342"/>
+      <c r="B162" s="365"/>
+      <c r="C162" s="365"/>
+      <c r="D162" s="365"/>
+      <c r="E162" s="365"/>
+      <c r="F162" s="365"/>
+      <c r="G162" s="365"/>
+      <c r="H162" s="365"/>
+      <c r="I162" s="365"/>
+      <c r="J162" s="365"/>
+      <c r="K162" s="365"/>
+      <c r="L162" s="365"/>
+      <c r="M162" s="365"/>
+      <c r="N162" s="365"/>
+      <c r="O162" s="365"/>
+      <c r="P162" s="365"/>
+      <c r="Q162" s="365"/>
+      <c r="R162" s="365"/>
+      <c r="S162" s="365"/>
+      <c r="T162" s="365"/>
+      <c r="U162" s="365"/>
+      <c r="V162" s="365"/>
+      <c r="W162" s="365"/>
     </row>
     <row r="163" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A163" s="336" t="s">
+      <c r="A163" s="366" t="s">
         <v>234</v>
       </c>
-      <c r="B163" s="336"/>
-      <c r="C163" s="336"/>
-      <c r="D163" s="336"/>
-      <c r="E163" s="336"/>
-      <c r="F163" s="336"/>
-      <c r="G163" s="336"/>
-      <c r="H163" s="336"/>
-      <c r="I163" s="336"/>
-      <c r="J163" s="336"/>
-      <c r="K163" s="336"/>
-      <c r="L163" s="336"/>
-      <c r="M163" s="336"/>
-      <c r="N163" s="336"/>
-      <c r="O163" s="336"/>
-      <c r="P163" s="336"/>
-      <c r="Q163" s="336"/>
-      <c r="R163" s="336"/>
-      <c r="S163" s="336"/>
-      <c r="T163" s="336"/>
-      <c r="U163" s="336"/>
-      <c r="V163" s="336"/>
-      <c r="W163" s="336"/>
+      <c r="B163" s="366"/>
+      <c r="C163" s="366"/>
+      <c r="D163" s="366"/>
+      <c r="E163" s="366"/>
+      <c r="F163" s="366"/>
+      <c r="G163" s="366"/>
+      <c r="H163" s="366"/>
+      <c r="I163" s="366"/>
+      <c r="J163" s="366"/>
+      <c r="K163" s="366"/>
+      <c r="L163" s="366"/>
+      <c r="M163" s="366"/>
+      <c r="N163" s="366"/>
+      <c r="O163" s="366"/>
+      <c r="P163" s="366"/>
+      <c r="Q163" s="366"/>
+      <c r="R163" s="366"/>
+      <c r="S163" s="366"/>
+      <c r="T163" s="366"/>
+      <c r="U163" s="366"/>
+      <c r="V163" s="366"/>
+      <c r="W163" s="366"/>
     </row>
     <row r="164" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A164" s="336" t="s">
+      <c r="A164" s="366" t="s">
         <v>360</v>
       </c>
-      <c r="B164" s="336"/>
-      <c r="C164" s="336"/>
-      <c r="D164" s="336"/>
-      <c r="E164" s="336"/>
-      <c r="F164" s="336"/>
-      <c r="G164" s="336"/>
-      <c r="H164" s="336"/>
-      <c r="I164" s="336"/>
-      <c r="J164" s="336"/>
-      <c r="K164" s="336"/>
-      <c r="L164" s="336"/>
-      <c r="M164" s="336"/>
-      <c r="N164" s="336"/>
-      <c r="O164" s="336"/>
-      <c r="P164" s="336"/>
-      <c r="Q164" s="336"/>
-      <c r="R164" s="336"/>
-      <c r="S164" s="336"/>
-      <c r="T164" s="336"/>
-      <c r="U164" s="336"/>
-      <c r="V164" s="336"/>
-      <c r="W164" s="336"/>
+      <c r="B164" s="366"/>
+      <c r="C164" s="366"/>
+      <c r="D164" s="366"/>
+      <c r="E164" s="366"/>
+      <c r="F164" s="366"/>
+      <c r="G164" s="366"/>
+      <c r="H164" s="366"/>
+      <c r="I164" s="366"/>
+      <c r="J164" s="366"/>
+      <c r="K164" s="366"/>
+      <c r="L164" s="366"/>
+      <c r="M164" s="366"/>
+      <c r="N164" s="366"/>
+      <c r="O164" s="366"/>
+      <c r="P164" s="366"/>
+      <c r="Q164" s="366"/>
+      <c r="R164" s="366"/>
+      <c r="S164" s="366"/>
+      <c r="T164" s="366"/>
+      <c r="U164" s="366"/>
+      <c r="V164" s="366"/>
+      <c r="W164" s="366"/>
     </row>
     <row r="165" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="233"/>
@@ -17758,12 +17762,12 @@
       <c r="C169" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D169" s="333">
+      <c r="D169" s="356">
         <f>'Business Details'!O50</f>
         <v>0</v>
       </c>
-      <c r="E169" s="334"/>
-      <c r="F169" s="335"/>
+      <c r="E169" s="357"/>
+      <c r="F169" s="358"/>
       <c r="G169" s="218" t="s">
         <v>178</v>
       </c>
@@ -17780,12 +17784,12 @@
       <c r="N169" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O169" s="333">
+      <c r="O169" s="356">
         <f>O149+D179</f>
         <v>0</v>
       </c>
-      <c r="P169" s="334"/>
-      <c r="Q169" s="335"/>
+      <c r="P169" s="357"/>
+      <c r="Q169" s="358"/>
       <c r="R169" s="218" t="s">
         <v>178</v>
       </c>
@@ -17917,12 +17921,12 @@
       <c r="C174" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D174" s="333">
+      <c r="D174" s="356">
         <f>O122+O154+O160+D169</f>
         <v>0</v>
       </c>
-      <c r="E174" s="334"/>
-      <c r="F174" s="335"/>
+      <c r="E174" s="357"/>
+      <c r="F174" s="358"/>
       <c r="G174" s="218" t="s">
         <v>178</v>
       </c>
@@ -17939,12 +17943,12 @@
       <c r="N174" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O174" s="333">
+      <c r="O174" s="356">
         <f>IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
         <v>0</v>
       </c>
-      <c r="P174" s="334"/>
-      <c r="Q174" s="335"/>
+      <c r="P174" s="357"/>
+      <c r="Q174" s="358"/>
       <c r="R174" s="218" t="s">
         <v>178</v>
       </c>
@@ -18076,9 +18080,9 @@
       <c r="C179" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D179" s="333"/>
-      <c r="E179" s="334"/>
-      <c r="F179" s="335"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="358"/>
       <c r="G179" s="218" t="s">
         <v>178</v>
       </c>
@@ -18095,12 +18099,12 @@
       <c r="N179" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O179" s="333">
+      <c r="O179" s="356">
         <f>IF(O174&gt;0,0,IF((D129+D174-O169)&lt;0,-(D129+D174-O169),IF((-O129+D174-O169)&lt;0,-(-O129+D174-O169),0)))</f>
         <v>0</v>
       </c>
-      <c r="P179" s="334"/>
-      <c r="Q179" s="335"/>
+      <c r="P179" s="357"/>
+      <c r="Q179" s="358"/>
       <c r="R179" s="218" t="s">
         <v>178</v>
       </c>
@@ -18140,112 +18144,112 @@
       <c r="W180" s="251"/>
     </row>
     <row r="181" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A181" s="342" t="s">
+      <c r="A181" s="365" t="s">
         <v>240</v>
       </c>
-      <c r="B181" s="342"/>
-      <c r="C181" s="342"/>
-      <c r="D181" s="342"/>
-      <c r="E181" s="342"/>
-      <c r="F181" s="342"/>
-      <c r="G181" s="342"/>
-      <c r="H181" s="342"/>
-      <c r="I181" s="342"/>
-      <c r="J181" s="342"/>
-      <c r="K181" s="342"/>
-      <c r="L181" s="342"/>
-      <c r="M181" s="342"/>
-      <c r="N181" s="342"/>
-      <c r="O181" s="342"/>
-      <c r="P181" s="342"/>
-      <c r="Q181" s="342"/>
-      <c r="R181" s="342"/>
-      <c r="S181" s="342"/>
-      <c r="T181" s="342"/>
-      <c r="U181" s="342"/>
-      <c r="V181" s="342"/>
-      <c r="W181" s="342"/>
+      <c r="B181" s="365"/>
+      <c r="C181" s="365"/>
+      <c r="D181" s="365"/>
+      <c r="E181" s="365"/>
+      <c r="F181" s="365"/>
+      <c r="G181" s="365"/>
+      <c r="H181" s="365"/>
+      <c r="I181" s="365"/>
+      <c r="J181" s="365"/>
+      <c r="K181" s="365"/>
+      <c r="L181" s="365"/>
+      <c r="M181" s="365"/>
+      <c r="N181" s="365"/>
+      <c r="O181" s="365"/>
+      <c r="P181" s="365"/>
+      <c r="Q181" s="365"/>
+      <c r="R181" s="365"/>
+      <c r="S181" s="365"/>
+      <c r="T181" s="365"/>
+      <c r="U181" s="365"/>
+      <c r="V181" s="365"/>
+      <c r="W181" s="365"/>
     </row>
     <row r="182" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A182" s="336" t="s">
+      <c r="A182" s="366" t="s">
         <v>241</v>
       </c>
-      <c r="B182" s="336"/>
-      <c r="C182" s="336"/>
-      <c r="D182" s="336"/>
-      <c r="E182" s="336"/>
-      <c r="F182" s="336"/>
-      <c r="G182" s="336"/>
-      <c r="H182" s="336"/>
-      <c r="I182" s="336"/>
-      <c r="J182" s="336"/>
-      <c r="K182" s="336"/>
-      <c r="L182" s="336"/>
-      <c r="M182" s="336"/>
-      <c r="N182" s="336"/>
-      <c r="O182" s="336"/>
-      <c r="P182" s="336"/>
-      <c r="Q182" s="336"/>
-      <c r="R182" s="336"/>
-      <c r="S182" s="336"/>
-      <c r="T182" s="336"/>
-      <c r="U182" s="336"/>
-      <c r="V182" s="336"/>
-      <c r="W182" s="336"/>
+      <c r="B182" s="366"/>
+      <c r="C182" s="366"/>
+      <c r="D182" s="366"/>
+      <c r="E182" s="366"/>
+      <c r="F182" s="366"/>
+      <c r="G182" s="366"/>
+      <c r="H182" s="366"/>
+      <c r="I182" s="366"/>
+      <c r="J182" s="366"/>
+      <c r="K182" s="366"/>
+      <c r="L182" s="366"/>
+      <c r="M182" s="366"/>
+      <c r="N182" s="366"/>
+      <c r="O182" s="366"/>
+      <c r="P182" s="366"/>
+      <c r="Q182" s="366"/>
+      <c r="R182" s="366"/>
+      <c r="S182" s="366"/>
+      <c r="T182" s="366"/>
+      <c r="U182" s="366"/>
+      <c r="V182" s="366"/>
+      <c r="W182" s="366"/>
     </row>
     <row r="183" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A183" s="336" t="s">
+      <c r="A183" s="366" t="s">
         <v>242</v>
       </c>
-      <c r="B183" s="336"/>
-      <c r="C183" s="336"/>
-      <c r="D183" s="336"/>
-      <c r="E183" s="336"/>
-      <c r="F183" s="336"/>
-      <c r="G183" s="336"/>
-      <c r="H183" s="336"/>
-      <c r="I183" s="336"/>
-      <c r="J183" s="336"/>
-      <c r="K183" s="336"/>
-      <c r="L183" s="336"/>
-      <c r="M183" s="336"/>
-      <c r="N183" s="336"/>
-      <c r="O183" s="336"/>
-      <c r="P183" s="336"/>
-      <c r="Q183" s="336"/>
-      <c r="R183" s="336"/>
-      <c r="S183" s="336"/>
-      <c r="T183" s="336"/>
-      <c r="U183" s="336"/>
-      <c r="V183" s="336"/>
-      <c r="W183" s="336"/>
+      <c r="B183" s="366"/>
+      <c r="C183" s="366"/>
+      <c r="D183" s="366"/>
+      <c r="E183" s="366"/>
+      <c r="F183" s="366"/>
+      <c r="G183" s="366"/>
+      <c r="H183" s="366"/>
+      <c r="I183" s="366"/>
+      <c r="J183" s="366"/>
+      <c r="K183" s="366"/>
+      <c r="L183" s="366"/>
+      <c r="M183" s="366"/>
+      <c r="N183" s="366"/>
+      <c r="O183" s="366"/>
+      <c r="P183" s="366"/>
+      <c r="Q183" s="366"/>
+      <c r="R183" s="366"/>
+      <c r="S183" s="366"/>
+      <c r="T183" s="366"/>
+      <c r="U183" s="366"/>
+      <c r="V183" s="366"/>
+      <c r="W183" s="366"/>
     </row>
     <row r="184" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A184" s="390" t="s">
+      <c r="A184" s="387" t="s">
         <v>243</v>
       </c>
-      <c r="B184" s="390"/>
-      <c r="C184" s="390"/>
-      <c r="D184" s="390"/>
-      <c r="E184" s="390"/>
-      <c r="F184" s="390"/>
-      <c r="G184" s="390"/>
-      <c r="H184" s="390"/>
-      <c r="I184" s="390"/>
-      <c r="J184" s="390"/>
-      <c r="K184" s="390"/>
-      <c r="L184" s="390"/>
-      <c r="M184" s="390"/>
-      <c r="N184" s="390"/>
-      <c r="O184" s="390"/>
-      <c r="P184" s="390"/>
-      <c r="Q184" s="390"/>
-      <c r="R184" s="390"/>
-      <c r="S184" s="390"/>
-      <c r="T184" s="390"/>
-      <c r="U184" s="390"/>
-      <c r="V184" s="390"/>
-      <c r="W184" s="390"/>
+      <c r="B184" s="387"/>
+      <c r="C184" s="387"/>
+      <c r="D184" s="387"/>
+      <c r="E184" s="387"/>
+      <c r="F184" s="387"/>
+      <c r="G184" s="387"/>
+      <c r="H184" s="387"/>
+      <c r="I184" s="387"/>
+      <c r="J184" s="387"/>
+      <c r="K184" s="387"/>
+      <c r="L184" s="387"/>
+      <c r="M184" s="387"/>
+      <c r="N184" s="387"/>
+      <c r="O184" s="387"/>
+      <c r="P184" s="387"/>
+      <c r="Q184" s="387"/>
+      <c r="R184" s="387"/>
+      <c r="S184" s="387"/>
+      <c r="T184" s="387"/>
+      <c r="U184" s="387"/>
+      <c r="V184" s="387"/>
+      <c r="W184" s="387"/>
     </row>
     <row r="185" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="233"/>
@@ -18308,10 +18312,10 @@
     <row r="187" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A187" s="255"/>
       <c r="B187" s="220"/>
-      <c r="C187" s="384"/>
-      <c r="D187" s="385"/>
-      <c r="E187" s="385"/>
-      <c r="F187" s="386"/>
+      <c r="C187" s="382"/>
+      <c r="D187" s="383"/>
+      <c r="E187" s="383"/>
+      <c r="F187" s="384"/>
       <c r="G187" s="227"/>
       <c r="H187" s="227"/>
       <c r="I187" s="227"/>
@@ -18336,9 +18340,9 @@
       <c r="A188" s="240"/>
       <c r="B188" s="220"/>
       <c r="C188" s="261"/>
-      <c r="D188" s="387"/>
-      <c r="E188" s="387"/>
-      <c r="F188" s="387"/>
+      <c r="D188" s="385"/>
+      <c r="E188" s="385"/>
+      <c r="F188" s="385"/>
       <c r="G188" s="218"/>
       <c r="H188" s="253"/>
       <c r="I188" s="253"/>
@@ -18393,10 +18397,10 @@
     <row r="190" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A190" s="255"/>
       <c r="B190" s="220"/>
-      <c r="C190" s="384"/>
-      <c r="D190" s="385"/>
-      <c r="E190" s="385"/>
-      <c r="F190" s="386"/>
+      <c r="C190" s="382"/>
+      <c r="D190" s="383"/>
+      <c r="E190" s="383"/>
+      <c r="F190" s="384"/>
       <c r="G190" s="227"/>
       <c r="H190" s="227"/>
       <c r="I190" s="227"/>
@@ -18410,8 +18414,8 @@
       <c r="O190" s="275" t="s">
         <v>250</v>
       </c>
-      <c r="P190" s="388"/>
-      <c r="Q190" s="389"/>
+      <c r="P190" s="375"/>
+      <c r="Q190" s="386"/>
       <c r="R190" s="218" t="s">
         <v>178</v>
       </c>
@@ -18477,7 +18481,7 @@
       <c r="P192" s="220"/>
       <c r="Q192" s="290" t="str">
         <f>Admin!G2</f>
-        <v>2024-25</v>
+        <v>2025-26</v>
       </c>
       <c r="R192" s="227" t="s">
         <v>368</v>
@@ -18536,12 +18540,12 @@
       <c r="N194" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O194" s="333">
+      <c r="O194" s="356">
         <f>O174</f>
         <v>0</v>
       </c>
-      <c r="P194" s="334"/>
-      <c r="Q194" s="335"/>
+      <c r="P194" s="357"/>
+      <c r="Q194" s="358"/>
       <c r="R194" s="218" t="s">
         <v>178</v>
       </c>
@@ -18622,8 +18626,8 @@
       <c r="D197" s="275" t="s">
         <v>250</v>
       </c>
-      <c r="E197" s="388"/>
-      <c r="F197" s="389"/>
+      <c r="E197" s="375"/>
+      <c r="F197" s="386"/>
       <c r="G197" s="218" t="s">
         <v>178</v>
       </c>
@@ -18698,12 +18702,12 @@
       <c r="N199" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O199" s="333">
+      <c r="O199" s="356">
         <f>IF(D179&gt;0,0,IF((O194+O204)&gt;'Business Details'!D50,'Business Details'!D50,(O194+O204)))</f>
         <v>0</v>
       </c>
-      <c r="P199" s="334"/>
-      <c r="Q199" s="335"/>
+      <c r="P199" s="357"/>
+      <c r="Q199" s="358"/>
       <c r="R199" s="218" t="s">
         <v>178</v>
       </c>
@@ -18748,9 +18752,9 @@
       <c r="C201" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D201" s="333"/>
-      <c r="E201" s="334"/>
-      <c r="F201" s="335"/>
+      <c r="D201" s="356"/>
+      <c r="E201" s="357"/>
+      <c r="F201" s="358"/>
       <c r="G201" s="218" t="s">
         <v>178</v>
       </c>
@@ -18852,12 +18856,12 @@
       <c r="N204" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O204" s="333">
+      <c r="O204" s="356">
         <f>'Profit &amp; Loss Account'!B11</f>
         <v>0</v>
       </c>
-      <c r="P204" s="334"/>
-      <c r="Q204" s="335"/>
+      <c r="P204" s="357"/>
+      <c r="Q204" s="358"/>
       <c r="R204" s="218" t="s">
         <v>178</v>
       </c>
@@ -18902,9 +18906,9 @@
       <c r="C206" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D206" s="333"/>
-      <c r="E206" s="334"/>
-      <c r="F206" s="335"/>
+      <c r="D206" s="356"/>
+      <c r="E206" s="357"/>
+      <c r="F206" s="358"/>
       <c r="G206" s="218" t="s">
         <v>178</v>
       </c>
@@ -19024,9 +19028,9 @@
       <c r="C210" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D210" s="333"/>
-      <c r="E210" s="334"/>
-      <c r="F210" s="335"/>
+      <c r="D210" s="356"/>
+      <c r="E210" s="357"/>
+      <c r="F210" s="358"/>
       <c r="G210" s="218" t="s">
         <v>178</v>
       </c>
@@ -19043,12 +19047,12 @@
       <c r="N210" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O210" s="333">
+      <c r="O210" s="356">
         <f>O194-O199+O204</f>
         <v>0</v>
       </c>
-      <c r="P210" s="334"/>
-      <c r="Q210" s="335"/>
+      <c r="P210" s="357"/>
+      <c r="Q210" s="358"/>
       <c r="R210" s="218" t="s">
         <v>178</v>
       </c>
@@ -19088,85 +19092,85 @@
       <c r="W211" s="251"/>
     </row>
     <row r="212" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A212" s="341" t="s">
+      <c r="A212" s="368" t="s">
         <v>260</v>
       </c>
-      <c r="B212" s="341"/>
-      <c r="C212" s="341"/>
-      <c r="D212" s="341"/>
-      <c r="E212" s="341"/>
-      <c r="F212" s="341"/>
-      <c r="G212" s="341"/>
-      <c r="H212" s="341"/>
-      <c r="I212" s="341"/>
-      <c r="J212" s="341"/>
-      <c r="K212" s="341"/>
-      <c r="L212" s="341"/>
-      <c r="M212" s="341"/>
-      <c r="N212" s="341"/>
-      <c r="O212" s="341"/>
-      <c r="P212" s="341"/>
-      <c r="Q212" s="341"/>
-      <c r="R212" s="341"/>
-      <c r="S212" s="341"/>
-      <c r="T212" s="341"/>
-      <c r="U212" s="341"/>
-      <c r="V212" s="341"/>
-      <c r="W212" s="341"/>
+      <c r="B212" s="368"/>
+      <c r="C212" s="368"/>
+      <c r="D212" s="368"/>
+      <c r="E212" s="368"/>
+      <c r="F212" s="368"/>
+      <c r="G212" s="368"/>
+      <c r="H212" s="368"/>
+      <c r="I212" s="368"/>
+      <c r="J212" s="368"/>
+      <c r="K212" s="368"/>
+      <c r="L212" s="368"/>
+      <c r="M212" s="368"/>
+      <c r="N212" s="368"/>
+      <c r="O212" s="368"/>
+      <c r="P212" s="368"/>
+      <c r="Q212" s="368"/>
+      <c r="R212" s="368"/>
+      <c r="S212" s="368"/>
+      <c r="T212" s="368"/>
+      <c r="U212" s="368"/>
+      <c r="V212" s="368"/>
+      <c r="W212" s="368"/>
     </row>
     <row r="213" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A213" s="336" t="s">
+      <c r="A213" s="366" t="s">
         <v>261</v>
       </c>
-      <c r="B213" s="336"/>
-      <c r="C213" s="336"/>
-      <c r="D213" s="336"/>
-      <c r="E213" s="336"/>
-      <c r="F213" s="336"/>
-      <c r="G213" s="336"/>
-      <c r="H213" s="336"/>
-      <c r="I213" s="336"/>
-      <c r="J213" s="336"/>
-      <c r="K213" s="336"/>
-      <c r="L213" s="336"/>
-      <c r="M213" s="336"/>
-      <c r="N213" s="336"/>
-      <c r="O213" s="336"/>
-      <c r="P213" s="336"/>
-      <c r="Q213" s="336"/>
-      <c r="R213" s="336"/>
-      <c r="S213" s="336"/>
-      <c r="T213" s="336"/>
-      <c r="U213" s="336"/>
-      <c r="V213" s="336"/>
-      <c r="W213" s="336"/>
+      <c r="B213" s="366"/>
+      <c r="C213" s="366"/>
+      <c r="D213" s="366"/>
+      <c r="E213" s="366"/>
+      <c r="F213" s="366"/>
+      <c r="G213" s="366"/>
+      <c r="H213" s="366"/>
+      <c r="I213" s="366"/>
+      <c r="J213" s="366"/>
+      <c r="K213" s="366"/>
+      <c r="L213" s="366"/>
+      <c r="M213" s="366"/>
+      <c r="N213" s="366"/>
+      <c r="O213" s="366"/>
+      <c r="P213" s="366"/>
+      <c r="Q213" s="366"/>
+      <c r="R213" s="366"/>
+      <c r="S213" s="366"/>
+      <c r="T213" s="366"/>
+      <c r="U213" s="366"/>
+      <c r="V213" s="366"/>
+      <c r="W213" s="366"/>
     </row>
     <row r="214" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A214" s="336" t="s">
+      <c r="A214" s="366" t="s">
         <v>262</v>
       </c>
-      <c r="B214" s="336"/>
-      <c r="C214" s="336"/>
-      <c r="D214" s="336"/>
-      <c r="E214" s="336"/>
-      <c r="F214" s="336"/>
-      <c r="G214" s="336"/>
-      <c r="H214" s="336"/>
-      <c r="I214" s="336"/>
-      <c r="J214" s="336"/>
-      <c r="K214" s="336"/>
-      <c r="L214" s="336"/>
-      <c r="M214" s="336"/>
-      <c r="N214" s="336"/>
-      <c r="O214" s="336"/>
-      <c r="P214" s="336"/>
-      <c r="Q214" s="336"/>
-      <c r="R214" s="336"/>
-      <c r="S214" s="336"/>
-      <c r="T214" s="336"/>
-      <c r="U214" s="336"/>
-      <c r="V214" s="336"/>
-      <c r="W214" s="336"/>
+      <c r="B214" s="366"/>
+      <c r="C214" s="366"/>
+      <c r="D214" s="366"/>
+      <c r="E214" s="366"/>
+      <c r="F214" s="366"/>
+      <c r="G214" s="366"/>
+      <c r="H214" s="366"/>
+      <c r="I214" s="366"/>
+      <c r="J214" s="366"/>
+      <c r="K214" s="366"/>
+      <c r="L214" s="366"/>
+      <c r="M214" s="366"/>
+      <c r="N214" s="366"/>
+      <c r="O214" s="366"/>
+      <c r="P214" s="366"/>
+      <c r="Q214" s="366"/>
+      <c r="R214" s="366"/>
+      <c r="S214" s="366"/>
+      <c r="T214" s="366"/>
+      <c r="U214" s="366"/>
+      <c r="V214" s="366"/>
+      <c r="W214" s="366"/>
     </row>
     <row r="215" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="233"/>
@@ -19205,7 +19209,7 @@
       <c r="E216" s="227"/>
       <c r="F216" s="289" t="str">
         <f>Admin!G2</f>
-        <v>2024-25</v>
+        <v>2025-26</v>
       </c>
       <c r="G216" s="227" t="s">
         <v>379</v>
@@ -19291,12 +19295,12 @@
       <c r="C219" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D219" s="333">
+      <c r="D219" s="356">
         <f>O179+E197-D201+D210+P190</f>
         <v>0</v>
       </c>
-      <c r="E219" s="334"/>
-      <c r="F219" s="335"/>
+      <c r="E219" s="357"/>
+      <c r="F219" s="358"/>
       <c r="G219" s="218" t="s">
         <v>178</v>
       </c>
@@ -19313,9 +19317,9 @@
       <c r="N219" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O219" s="333"/>
-      <c r="P219" s="334"/>
-      <c r="Q219" s="335"/>
+      <c r="O219" s="356"/>
+      <c r="P219" s="357"/>
+      <c r="Q219" s="358"/>
       <c r="R219" s="218" t="s">
         <v>178</v>
       </c>
@@ -19393,12 +19397,12 @@
       <c r="C222" s="227" t="s">
         <v>268</v>
       </c>
-      <c r="D222" s="337" t="str">
+      <c r="D222" s="369" t="str">
         <f>Admin!G2</f>
-        <v>2024-25</v>
-      </c>
-      <c r="E222" s="338"/>
-      <c r="F222" s="347"/>
+        <v>2025-26</v>
+      </c>
+      <c r="E222" s="361"/>
+      <c r="F222" s="362"/>
       <c r="G222" s="220"/>
       <c r="H222" s="220"/>
       <c r="I222" s="220"/>
@@ -19450,9 +19454,9 @@
       <c r="C224" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D224" s="333"/>
-      <c r="E224" s="334"/>
-      <c r="F224" s="335"/>
+      <c r="D224" s="356"/>
+      <c r="E224" s="357"/>
+      <c r="F224" s="358"/>
       <c r="G224" s="218" t="s">
         <v>178</v>
       </c>
@@ -19469,12 +19473,12 @@
       <c r="N224" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O224" s="333">
+      <c r="O224" s="356">
         <f>D219</f>
         <v>0</v>
       </c>
-      <c r="P224" s="334"/>
-      <c r="Q224" s="335"/>
+      <c r="P224" s="357"/>
+      <c r="Q224" s="358"/>
       <c r="R224" s="218" t="s">
         <v>178</v>
       </c>
@@ -19514,31 +19518,31 @@
       <c r="W225" s="251"/>
     </row>
     <row r="226" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A226" s="383" t="s">
+      <c r="A226" s="388" t="s">
         <v>270</v>
       </c>
-      <c r="B226" s="383"/>
-      <c r="C226" s="383"/>
-      <c r="D226" s="383"/>
-      <c r="E226" s="383"/>
-      <c r="F226" s="383"/>
-      <c r="G226" s="383"/>
-      <c r="H226" s="383"/>
-      <c r="I226" s="383"/>
-      <c r="J226" s="383"/>
-      <c r="K226" s="383"/>
-      <c r="L226" s="383"/>
-      <c r="M226" s="383"/>
-      <c r="N226" s="383"/>
-      <c r="O226" s="383"/>
-      <c r="P226" s="383"/>
-      <c r="Q226" s="383"/>
-      <c r="R226" s="383"/>
-      <c r="S226" s="383"/>
-      <c r="T226" s="383"/>
-      <c r="U226" s="383"/>
-      <c r="V226" s="383"/>
-      <c r="W226" s="383"/>
+      <c r="B226" s="388"/>
+      <c r="C226" s="388"/>
+      <c r="D226" s="388"/>
+      <c r="E226" s="388"/>
+      <c r="F226" s="388"/>
+      <c r="G226" s="388"/>
+      <c r="H226" s="388"/>
+      <c r="I226" s="388"/>
+      <c r="J226" s="388"/>
+      <c r="K226" s="388"/>
+      <c r="L226" s="388"/>
+      <c r="M226" s="388"/>
+      <c r="N226" s="388"/>
+      <c r="O226" s="388"/>
+      <c r="P226" s="388"/>
+      <c r="Q226" s="388"/>
+      <c r="R226" s="388"/>
+      <c r="S226" s="388"/>
+      <c r="T226" s="388"/>
+      <c r="U226" s="388"/>
+      <c r="V226" s="388"/>
+      <c r="W226" s="388"/>
     </row>
     <row r="227" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="233"/>
@@ -19656,12 +19660,12 @@
       <c r="C231" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D231" s="333">
+      <c r="D231" s="356">
         <f>[2]Mar!$X$1</f>
         <v>0</v>
       </c>
-      <c r="E231" s="334"/>
-      <c r="F231" s="335"/>
+      <c r="E231" s="357"/>
+      <c r="F231" s="358"/>
       <c r="G231" s="218" t="s">
         <v>178</v>
       </c>
@@ -19678,9 +19682,9 @@
       <c r="N231" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O231" s="333"/>
-      <c r="P231" s="334"/>
-      <c r="Q231" s="335"/>
+      <c r="O231" s="356"/>
+      <c r="P231" s="357"/>
+      <c r="Q231" s="358"/>
       <c r="R231" s="218" t="s">
         <v>178</v>
       </c>
@@ -19720,85 +19724,85 @@
       <c r="W232" s="251"/>
     </row>
     <row r="233" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A233" s="342" t="s">
+      <c r="A233" s="365" t="s">
         <v>381</v>
       </c>
-      <c r="B233" s="342"/>
-      <c r="C233" s="342"/>
-      <c r="D233" s="342"/>
-      <c r="E233" s="342"/>
-      <c r="F233" s="342"/>
-      <c r="G233" s="342"/>
-      <c r="H233" s="342"/>
-      <c r="I233" s="342"/>
-      <c r="J233" s="342"/>
-      <c r="K233" s="342"/>
-      <c r="L233" s="342"/>
-      <c r="M233" s="342"/>
-      <c r="N233" s="342"/>
-      <c r="O233" s="342"/>
-      <c r="P233" s="342"/>
-      <c r="Q233" s="342"/>
-      <c r="R233" s="342"/>
-      <c r="S233" s="342"/>
-      <c r="T233" s="342"/>
-      <c r="U233" s="342"/>
-      <c r="V233" s="342"/>
-      <c r="W233" s="342"/>
+      <c r="B233" s="365"/>
+      <c r="C233" s="365"/>
+      <c r="D233" s="365"/>
+      <c r="E233" s="365"/>
+      <c r="F233" s="365"/>
+      <c r="G233" s="365"/>
+      <c r="H233" s="365"/>
+      <c r="I233" s="365"/>
+      <c r="J233" s="365"/>
+      <c r="K233" s="365"/>
+      <c r="L233" s="365"/>
+      <c r="M233" s="365"/>
+      <c r="N233" s="365"/>
+      <c r="O233" s="365"/>
+      <c r="P233" s="365"/>
+      <c r="Q233" s="365"/>
+      <c r="R233" s="365"/>
+      <c r="S233" s="365"/>
+      <c r="T233" s="365"/>
+      <c r="U233" s="365"/>
+      <c r="V233" s="365"/>
+      <c r="W233" s="365"/>
     </row>
     <row r="234" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A234" s="336" t="s">
+      <c r="A234" s="366" t="s">
         <v>274</v>
       </c>
-      <c r="B234" s="336"/>
-      <c r="C234" s="336"/>
-      <c r="D234" s="336"/>
-      <c r="E234" s="336"/>
-      <c r="F234" s="336"/>
-      <c r="G234" s="336"/>
-      <c r="H234" s="336"/>
-      <c r="I234" s="336"/>
-      <c r="J234" s="336"/>
-      <c r="K234" s="336"/>
-      <c r="L234" s="336"/>
-      <c r="M234" s="336"/>
-      <c r="N234" s="336"/>
-      <c r="O234" s="336"/>
-      <c r="P234" s="336"/>
-      <c r="Q234" s="336"/>
-      <c r="R234" s="336"/>
-      <c r="S234" s="336"/>
-      <c r="T234" s="336"/>
-      <c r="U234" s="336"/>
-      <c r="V234" s="336"/>
-      <c r="W234" s="336"/>
+      <c r="B234" s="366"/>
+      <c r="C234" s="366"/>
+      <c r="D234" s="366"/>
+      <c r="E234" s="366"/>
+      <c r="F234" s="366"/>
+      <c r="G234" s="366"/>
+      <c r="H234" s="366"/>
+      <c r="I234" s="366"/>
+      <c r="J234" s="366"/>
+      <c r="K234" s="366"/>
+      <c r="L234" s="366"/>
+      <c r="M234" s="366"/>
+      <c r="N234" s="366"/>
+      <c r="O234" s="366"/>
+      <c r="P234" s="366"/>
+      <c r="Q234" s="366"/>
+      <c r="R234" s="366"/>
+      <c r="S234" s="366"/>
+      <c r="T234" s="366"/>
+      <c r="U234" s="366"/>
+      <c r="V234" s="366"/>
+      <c r="W234" s="366"/>
     </row>
     <row r="235" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A235" s="336" t="s">
+      <c r="A235" s="366" t="s">
         <v>382</v>
       </c>
-      <c r="B235" s="336"/>
-      <c r="C235" s="336"/>
-      <c r="D235" s="336"/>
-      <c r="E235" s="336"/>
-      <c r="F235" s="336"/>
-      <c r="G235" s="336"/>
-      <c r="H235" s="336"/>
-      <c r="I235" s="336"/>
-      <c r="J235" s="336"/>
-      <c r="K235" s="336"/>
-      <c r="L235" s="336"/>
-      <c r="M235" s="336"/>
-      <c r="N235" s="336"/>
-      <c r="O235" s="336"/>
-      <c r="P235" s="336"/>
-      <c r="Q235" s="336"/>
-      <c r="R235" s="336"/>
-      <c r="S235" s="336"/>
-      <c r="T235" s="336"/>
-      <c r="U235" s="336"/>
-      <c r="V235" s="336"/>
-      <c r="W235" s="336"/>
+      <c r="B235" s="366"/>
+      <c r="C235" s="366"/>
+      <c r="D235" s="366"/>
+      <c r="E235" s="366"/>
+      <c r="F235" s="366"/>
+      <c r="G235" s="366"/>
+      <c r="H235" s="366"/>
+      <c r="I235" s="366"/>
+      <c r="J235" s="366"/>
+      <c r="K235" s="366"/>
+      <c r="L235" s="366"/>
+      <c r="M235" s="366"/>
+      <c r="N235" s="366"/>
+      <c r="O235" s="366"/>
+      <c r="P235" s="366"/>
+      <c r="Q235" s="366"/>
+      <c r="R235" s="366"/>
+      <c r="S235" s="366"/>
+      <c r="T235" s="366"/>
+      <c r="U235" s="366"/>
+      <c r="V235" s="366"/>
+      <c r="W235" s="366"/>
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A236" s="233"/>
@@ -19943,9 +19947,9 @@
       <c r="C241" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D241" s="333"/>
-      <c r="E241" s="334"/>
-      <c r="F241" s="335"/>
+      <c r="D241" s="356"/>
+      <c r="E241" s="357"/>
+      <c r="F241" s="358"/>
       <c r="G241" s="218" t="s">
         <v>178</v>
       </c>
@@ -19962,9 +19966,9 @@
       <c r="N241" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O241" s="333"/>
-      <c r="P241" s="334"/>
-      <c r="Q241" s="335"/>
+      <c r="O241" s="356"/>
+      <c r="P241" s="357"/>
+      <c r="Q241" s="358"/>
       <c r="R241" s="218" t="s">
         <v>178</v>
       </c>
@@ -20067,9 +20071,9 @@
       <c r="C245" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D245" s="333"/>
-      <c r="E245" s="334"/>
-      <c r="F245" s="335"/>
+      <c r="D245" s="356"/>
+      <c r="E245" s="357"/>
+      <c r="F245" s="358"/>
       <c r="G245" s="218" t="s">
         <v>178</v>
       </c>
@@ -20086,9 +20090,9 @@
       <c r="N245" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O245" s="333"/>
-      <c r="P245" s="334"/>
-      <c r="Q245" s="335"/>
+      <c r="O245" s="356"/>
+      <c r="P245" s="357"/>
+      <c r="Q245" s="358"/>
       <c r="R245" s="218" t="s">
         <v>178</v>
       </c>
@@ -20191,9 +20195,9 @@
       <c r="C249" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D249" s="333"/>
-      <c r="E249" s="334"/>
-      <c r="F249" s="335"/>
+      <c r="D249" s="356"/>
+      <c r="E249" s="357"/>
+      <c r="F249" s="358"/>
       <c r="G249" s="218" t="s">
         <v>178</v>
       </c>
@@ -20210,9 +20214,9 @@
       <c r="N249" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O249" s="333"/>
-      <c r="P249" s="334"/>
-      <c r="Q249" s="335"/>
+      <c r="O249" s="356"/>
+      <c r="P249" s="357"/>
+      <c r="Q249" s="358"/>
       <c r="R249" s="218" t="s">
         <v>178</v>
       </c>
@@ -20313,9 +20317,9 @@
       <c r="C253" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D253" s="333"/>
-      <c r="E253" s="334"/>
-      <c r="F253" s="335"/>
+      <c r="D253" s="356"/>
+      <c r="E253" s="357"/>
+      <c r="F253" s="358"/>
       <c r="G253" s="218" t="s">
         <v>178</v>
       </c>
@@ -20393,9 +20397,9 @@
       <c r="O255" s="284" t="s">
         <v>250</v>
       </c>
-      <c r="P255" s="333"/>
-      <c r="Q255" s="334"/>
-      <c r="R255" s="335"/>
+      <c r="P255" s="356"/>
+      <c r="Q255" s="357"/>
+      <c r="R255" s="358"/>
       <c r="S255" s="218" t="s">
         <v>178</v>
       </c>
@@ -20439,9 +20443,9 @@
       <c r="C257" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D257" s="333"/>
-      <c r="E257" s="334"/>
-      <c r="F257" s="335"/>
+      <c r="D257" s="356"/>
+      <c r="E257" s="357"/>
+      <c r="F257" s="358"/>
       <c r="G257" s="218" t="s">
         <v>178</v>
       </c>
@@ -20557,9 +20561,9 @@
       <c r="C261" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D261" s="333"/>
-      <c r="E261" s="334"/>
-      <c r="F261" s="335"/>
+      <c r="D261" s="356"/>
+      <c r="E261" s="357"/>
+      <c r="F261" s="358"/>
       <c r="G261" s="218" t="s">
         <v>178</v>
       </c>
@@ -20579,9 +20583,9 @@
       <c r="O261" s="275" t="s">
         <v>250</v>
       </c>
-      <c r="P261" s="333"/>
-      <c r="Q261" s="334"/>
-      <c r="R261" s="335"/>
+      <c r="P261" s="356"/>
+      <c r="Q261" s="357"/>
+      <c r="R261" s="358"/>
       <c r="S261" s="218" t="s">
         <v>178</v>
       </c>
@@ -20683,9 +20687,9 @@
       <c r="C265" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D265" s="333"/>
-      <c r="E265" s="334"/>
-      <c r="F265" s="335"/>
+      <c r="D265" s="356"/>
+      <c r="E265" s="357"/>
+      <c r="F265" s="358"/>
       <c r="G265" s="218" t="s">
         <v>178</v>
       </c>
@@ -20705,9 +20709,9 @@
       <c r="O265" s="275" t="s">
         <v>250</v>
       </c>
-      <c r="P265" s="333"/>
-      <c r="Q265" s="334"/>
-      <c r="R265" s="335"/>
+      <c r="P265" s="356"/>
+      <c r="Q265" s="357"/>
+      <c r="R265" s="358"/>
       <c r="S265" s="218" t="s">
         <v>178</v>
       </c>
@@ -20809,9 +20813,9 @@
       <c r="C269" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D269" s="333"/>
-      <c r="E269" s="334"/>
-      <c r="F269" s="335"/>
+      <c r="D269" s="356"/>
+      <c r="E269" s="357"/>
+      <c r="F269" s="358"/>
       <c r="G269" s="218" t="s">
         <v>178</v>
       </c>
@@ -20828,9 +20832,9 @@
       <c r="N269" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O269" s="333"/>
-      <c r="P269" s="334"/>
-      <c r="Q269" s="335"/>
+      <c r="O269" s="356"/>
+      <c r="P269" s="357"/>
+      <c r="Q269" s="358"/>
       <c r="R269" s="218" t="s">
         <v>178</v>
       </c>
@@ -20940,9 +20944,9 @@
       <c r="N273" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O273" s="333"/>
-      <c r="P273" s="334"/>
-      <c r="Q273" s="335"/>
+      <c r="O273" s="356"/>
+      <c r="P273" s="357"/>
+      <c r="Q273" s="358"/>
       <c r="R273" s="218" t="s">
         <v>178</v>
       </c>
@@ -21055,9 +21059,9 @@
       <c r="O277" s="275" t="s">
         <v>250</v>
       </c>
-      <c r="P277" s="333"/>
-      <c r="Q277" s="334"/>
-      <c r="R277" s="335"/>
+      <c r="P277" s="356"/>
+      <c r="Q277" s="357"/>
+      <c r="R277" s="358"/>
       <c r="S277" s="218" t="s">
         <v>178</v>
       </c>
@@ -21096,90 +21100,90 @@
       <c r="W278" s="251"/>
     </row>
     <row r="279" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A279" s="341" t="s">
+      <c r="A279" s="368" t="s">
         <v>295</v>
       </c>
-      <c r="B279" s="341"/>
-      <c r="C279" s="341"/>
-      <c r="D279" s="341"/>
-      <c r="E279" s="341"/>
-      <c r="F279" s="341"/>
-      <c r="G279" s="341"/>
-      <c r="H279" s="341"/>
-      <c r="I279" s="341"/>
-      <c r="J279" s="341"/>
-      <c r="K279" s="341"/>
-      <c r="L279" s="341"/>
-      <c r="M279" s="341"/>
-      <c r="N279" s="341"/>
-      <c r="O279" s="341"/>
-      <c r="P279" s="341"/>
-      <c r="Q279" s="341"/>
-      <c r="R279" s="341"/>
-      <c r="S279" s="341"/>
-      <c r="T279" s="341"/>
-      <c r="U279" s="341"/>
-      <c r="V279" s="341"/>
-      <c r="W279" s="341"/>
+      <c r="B279" s="368"/>
+      <c r="C279" s="368"/>
+      <c r="D279" s="368"/>
+      <c r="E279" s="368"/>
+      <c r="F279" s="368"/>
+      <c r="G279" s="368"/>
+      <c r="H279" s="368"/>
+      <c r="I279" s="368"/>
+      <c r="J279" s="368"/>
+      <c r="K279" s="368"/>
+      <c r="L279" s="368"/>
+      <c r="M279" s="368"/>
+      <c r="N279" s="368"/>
+      <c r="O279" s="368"/>
+      <c r="P279" s="368"/>
+      <c r="Q279" s="368"/>
+      <c r="R279" s="368"/>
+      <c r="S279" s="368"/>
+      <c r="T279" s="368"/>
+      <c r="U279" s="368"/>
+      <c r="V279" s="368"/>
+      <c r="W279" s="368"/>
     </row>
     <row r="280" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A280" s="336" t="s">
+      <c r="A280" s="366" t="s">
         <v>296</v>
       </c>
-      <c r="B280" s="382"/>
-      <c r="C280" s="382"/>
-      <c r="D280" s="382"/>
-      <c r="E280" s="382"/>
-      <c r="F280" s="382"/>
-      <c r="G280" s="382"/>
-      <c r="H280" s="382"/>
-      <c r="I280" s="382"/>
+      <c r="B280" s="399"/>
+      <c r="C280" s="399"/>
+      <c r="D280" s="399"/>
+      <c r="E280" s="399"/>
+      <c r="F280" s="399"/>
+      <c r="G280" s="399"/>
+      <c r="H280" s="399"/>
+      <c r="I280" s="399"/>
       <c r="J280" s="285">
         <f>Admin!N4</f>
         <v>12570</v>
       </c>
-      <c r="K280" s="336" t="s">
+      <c r="K280" s="366" t="s">
         <v>297</v>
       </c>
-      <c r="L280" s="354"/>
-      <c r="M280" s="354"/>
-      <c r="N280" s="354"/>
-      <c r="O280" s="354"/>
-      <c r="P280" s="354"/>
-      <c r="Q280" s="354"/>
-      <c r="R280" s="354"/>
-      <c r="S280" s="354"/>
-      <c r="T280" s="354"/>
-      <c r="U280" s="354"/>
-      <c r="V280" s="354"/>
-      <c r="W280" s="354"/>
+      <c r="L280" s="346"/>
+      <c r="M280" s="346"/>
+      <c r="N280" s="346"/>
+      <c r="O280" s="346"/>
+      <c r="P280" s="346"/>
+      <c r="Q280" s="346"/>
+      <c r="R280" s="346"/>
+      <c r="S280" s="346"/>
+      <c r="T280" s="346"/>
+      <c r="U280" s="346"/>
+      <c r="V280" s="346"/>
+      <c r="W280" s="346"/>
     </row>
     <row r="281" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A281" s="381" t="s">
+      <c r="A281" s="398" t="s">
         <v>383</v>
       </c>
-      <c r="B281" s="381"/>
-      <c r="C281" s="381"/>
-      <c r="D281" s="381"/>
-      <c r="E281" s="381"/>
-      <c r="F281" s="381"/>
-      <c r="G281" s="381"/>
-      <c r="H281" s="381"/>
-      <c r="I281" s="381"/>
-      <c r="J281" s="381"/>
-      <c r="K281" s="381"/>
-      <c r="L281" s="381"/>
-      <c r="M281" s="381"/>
-      <c r="N281" s="381"/>
-      <c r="O281" s="381"/>
-      <c r="P281" s="381"/>
-      <c r="Q281" s="381"/>
-      <c r="R281" s="381"/>
-      <c r="S281" s="381"/>
-      <c r="T281" s="381"/>
-      <c r="U281" s="381"/>
-      <c r="V281" s="381"/>
-      <c r="W281" s="381"/>
+      <c r="B281" s="398"/>
+      <c r="C281" s="398"/>
+      <c r="D281" s="398"/>
+      <c r="E281" s="398"/>
+      <c r="F281" s="398"/>
+      <c r="G281" s="398"/>
+      <c r="H281" s="398"/>
+      <c r="I281" s="398"/>
+      <c r="J281" s="398"/>
+      <c r="K281" s="398"/>
+      <c r="L281" s="398"/>
+      <c r="M281" s="398"/>
+      <c r="N281" s="398"/>
+      <c r="O281" s="398"/>
+      <c r="P281" s="398"/>
+      <c r="Q281" s="398"/>
+      <c r="R281" s="398"/>
+      <c r="S281" s="398"/>
+      <c r="T281" s="398"/>
+      <c r="U281" s="398"/>
+      <c r="V281" s="398"/>
+      <c r="W281" s="398"/>
     </row>
     <row r="282" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="233"/>
@@ -21310,9 +21314,9 @@
       <c r="N286" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O286" s="333"/>
-      <c r="P286" s="334"/>
-      <c r="Q286" s="335"/>
+      <c r="O286" s="356"/>
+      <c r="P286" s="357"/>
+      <c r="Q286" s="358"/>
       <c r="R286" s="218" t="s">
         <v>178</v>
       </c>
@@ -21362,12 +21366,12 @@
       <c r="D288" s="220"/>
       <c r="E288" s="220"/>
       <c r="F288" s="220"/>
-      <c r="G288" s="339" t="str">
+      <c r="G288" s="370" t="str">
         <f>Admin!G2</f>
-        <v>2024-25</v>
-      </c>
-      <c r="H288" s="340"/>
-      <c r="I288" s="340"/>
+        <v>2025-26</v>
+      </c>
+      <c r="H288" s="371"/>
+      <c r="I288" s="371"/>
       <c r="J288" s="220" t="s">
         <v>302</v>
       </c>
@@ -21515,31 +21519,31 @@
       <c r="W293" s="251"/>
     </row>
     <row r="294" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A294" s="342" t="s">
+      <c r="A294" s="365" t="s">
         <v>304</v>
       </c>
-      <c r="B294" s="342"/>
-      <c r="C294" s="342"/>
-      <c r="D294" s="342"/>
-      <c r="E294" s="342"/>
-      <c r="F294" s="342"/>
-      <c r="G294" s="342"/>
-      <c r="H294" s="342"/>
-      <c r="I294" s="342"/>
-      <c r="J294" s="342"/>
-      <c r="K294" s="342"/>
-      <c r="L294" s="342"/>
-      <c r="M294" s="342"/>
-      <c r="N294" s="342"/>
-      <c r="O294" s="342"/>
-      <c r="P294" s="342"/>
-      <c r="Q294" s="342"/>
-      <c r="R294" s="342"/>
-      <c r="S294" s="342"/>
-      <c r="T294" s="342"/>
-      <c r="U294" s="342"/>
-      <c r="V294" s="342"/>
-      <c r="W294" s="342"/>
+      <c r="B294" s="365"/>
+      <c r="C294" s="365"/>
+      <c r="D294" s="365"/>
+      <c r="E294" s="365"/>
+      <c r="F294" s="365"/>
+      <c r="G294" s="365"/>
+      <c r="H294" s="365"/>
+      <c r="I294" s="365"/>
+      <c r="J294" s="365"/>
+      <c r="K294" s="365"/>
+      <c r="L294" s="365"/>
+      <c r="M294" s="365"/>
+      <c r="N294" s="365"/>
+      <c r="O294" s="365"/>
+      <c r="P294" s="365"/>
+      <c r="Q294" s="365"/>
+      <c r="R294" s="365"/>
+      <c r="S294" s="365"/>
+      <c r="T294" s="365"/>
+      <c r="U294" s="365"/>
+      <c r="V294" s="365"/>
+      <c r="W294" s="365"/>
     </row>
     <row r="295" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295" s="233"/>
@@ -21623,651 +21627,651 @@
     <row r="298" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A298" s="240"/>
       <c r="B298" s="220"/>
-      <c r="C298" s="372"/>
-      <c r="D298" s="373"/>
-      <c r="E298" s="373"/>
-      <c r="F298" s="373"/>
-      <c r="G298" s="373"/>
-      <c r="H298" s="373"/>
-      <c r="I298" s="373"/>
-      <c r="J298" s="373"/>
-      <c r="K298" s="373"/>
-      <c r="L298" s="373"/>
-      <c r="M298" s="373"/>
-      <c r="N298" s="373"/>
-      <c r="O298" s="373"/>
-      <c r="P298" s="373"/>
-      <c r="Q298" s="373"/>
-      <c r="R298" s="373"/>
-      <c r="S298" s="373"/>
-      <c r="T298" s="373"/>
-      <c r="U298" s="373"/>
-      <c r="V298" s="374"/>
+      <c r="C298" s="389"/>
+      <c r="D298" s="390"/>
+      <c r="E298" s="390"/>
+      <c r="F298" s="390"/>
+      <c r="G298" s="390"/>
+      <c r="H298" s="390"/>
+      <c r="I298" s="390"/>
+      <c r="J298" s="390"/>
+      <c r="K298" s="390"/>
+      <c r="L298" s="390"/>
+      <c r="M298" s="390"/>
+      <c r="N298" s="390"/>
+      <c r="O298" s="390"/>
+      <c r="P298" s="390"/>
+      <c r="Q298" s="390"/>
+      <c r="R298" s="390"/>
+      <c r="S298" s="390"/>
+      <c r="T298" s="390"/>
+      <c r="U298" s="390"/>
+      <c r="V298" s="391"/>
       <c r="W298" s="243"/>
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A299" s="240"/>
       <c r="B299" s="220"/>
-      <c r="C299" s="375"/>
-      <c r="D299" s="376"/>
-      <c r="E299" s="376"/>
-      <c r="F299" s="376"/>
-      <c r="G299" s="376"/>
-      <c r="H299" s="376"/>
-      <c r="I299" s="376"/>
-      <c r="J299" s="376"/>
-      <c r="K299" s="376"/>
-      <c r="L299" s="376"/>
-      <c r="M299" s="376"/>
-      <c r="N299" s="376"/>
-      <c r="O299" s="376"/>
-      <c r="P299" s="376"/>
-      <c r="Q299" s="376"/>
-      <c r="R299" s="376"/>
-      <c r="S299" s="376"/>
-      <c r="T299" s="376"/>
-      <c r="U299" s="376"/>
-      <c r="V299" s="377"/>
+      <c r="C299" s="392"/>
+      <c r="D299" s="393"/>
+      <c r="E299" s="393"/>
+      <c r="F299" s="393"/>
+      <c r="G299" s="393"/>
+      <c r="H299" s="393"/>
+      <c r="I299" s="393"/>
+      <c r="J299" s="393"/>
+      <c r="K299" s="393"/>
+      <c r="L299" s="393"/>
+      <c r="M299" s="393"/>
+      <c r="N299" s="393"/>
+      <c r="O299" s="393"/>
+      <c r="P299" s="393"/>
+      <c r="Q299" s="393"/>
+      <c r="R299" s="393"/>
+      <c r="S299" s="393"/>
+      <c r="T299" s="393"/>
+      <c r="U299" s="393"/>
+      <c r="V299" s="394"/>
       <c r="W299" s="243"/>
     </row>
     <row r="300" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A300" s="240"/>
       <c r="B300" s="220"/>
-      <c r="C300" s="375"/>
-      <c r="D300" s="376"/>
-      <c r="E300" s="376"/>
-      <c r="F300" s="376"/>
-      <c r="G300" s="376"/>
-      <c r="H300" s="376"/>
-      <c r="I300" s="376"/>
-      <c r="J300" s="376"/>
-      <c r="K300" s="376"/>
-      <c r="L300" s="376"/>
-      <c r="M300" s="376"/>
-      <c r="N300" s="376"/>
-      <c r="O300" s="376"/>
-      <c r="P300" s="376"/>
-      <c r="Q300" s="376"/>
-      <c r="R300" s="376"/>
-      <c r="S300" s="376"/>
-      <c r="T300" s="376"/>
-      <c r="U300" s="376"/>
-      <c r="V300" s="377"/>
+      <c r="C300" s="392"/>
+      <c r="D300" s="393"/>
+      <c r="E300" s="393"/>
+      <c r="F300" s="393"/>
+      <c r="G300" s="393"/>
+      <c r="H300" s="393"/>
+      <c r="I300" s="393"/>
+      <c r="J300" s="393"/>
+      <c r="K300" s="393"/>
+      <c r="L300" s="393"/>
+      <c r="M300" s="393"/>
+      <c r="N300" s="393"/>
+      <c r="O300" s="393"/>
+      <c r="P300" s="393"/>
+      <c r="Q300" s="393"/>
+      <c r="R300" s="393"/>
+      <c r="S300" s="393"/>
+      <c r="T300" s="393"/>
+      <c r="U300" s="393"/>
+      <c r="V300" s="394"/>
       <c r="W300" s="243"/>
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A301" s="240"/>
       <c r="B301" s="220"/>
-      <c r="C301" s="375"/>
-      <c r="D301" s="376"/>
-      <c r="E301" s="376"/>
-      <c r="F301" s="376"/>
-      <c r="G301" s="376"/>
-      <c r="H301" s="376"/>
-      <c r="I301" s="376"/>
-      <c r="J301" s="376"/>
-      <c r="K301" s="376"/>
-      <c r="L301" s="376"/>
-      <c r="M301" s="376"/>
-      <c r="N301" s="376"/>
-      <c r="O301" s="376"/>
-      <c r="P301" s="376"/>
-      <c r="Q301" s="376"/>
-      <c r="R301" s="376"/>
-      <c r="S301" s="376"/>
-      <c r="T301" s="376"/>
-      <c r="U301" s="376"/>
-      <c r="V301" s="377"/>
+      <c r="C301" s="392"/>
+      <c r="D301" s="393"/>
+      <c r="E301" s="393"/>
+      <c r="F301" s="393"/>
+      <c r="G301" s="393"/>
+      <c r="H301" s="393"/>
+      <c r="I301" s="393"/>
+      <c r="J301" s="393"/>
+      <c r="K301" s="393"/>
+      <c r="L301" s="393"/>
+      <c r="M301" s="393"/>
+      <c r="N301" s="393"/>
+      <c r="O301" s="393"/>
+      <c r="P301" s="393"/>
+      <c r="Q301" s="393"/>
+      <c r="R301" s="393"/>
+      <c r="S301" s="393"/>
+      <c r="T301" s="393"/>
+      <c r="U301" s="393"/>
+      <c r="V301" s="394"/>
       <c r="W301" s="243"/>
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A302" s="240"/>
       <c r="B302" s="220"/>
-      <c r="C302" s="375"/>
-      <c r="D302" s="376"/>
-      <c r="E302" s="376"/>
-      <c r="F302" s="376"/>
-      <c r="G302" s="376"/>
-      <c r="H302" s="376"/>
-      <c r="I302" s="376"/>
-      <c r="J302" s="376"/>
-      <c r="K302" s="376"/>
-      <c r="L302" s="376"/>
-      <c r="M302" s="376"/>
-      <c r="N302" s="376"/>
-      <c r="O302" s="376"/>
-      <c r="P302" s="376"/>
-      <c r="Q302" s="376"/>
-      <c r="R302" s="376"/>
-      <c r="S302" s="376"/>
-      <c r="T302" s="376"/>
-      <c r="U302" s="376"/>
-      <c r="V302" s="377"/>
+      <c r="C302" s="392"/>
+      <c r="D302" s="393"/>
+      <c r="E302" s="393"/>
+      <c r="F302" s="393"/>
+      <c r="G302" s="393"/>
+      <c r="H302" s="393"/>
+      <c r="I302" s="393"/>
+      <c r="J302" s="393"/>
+      <c r="K302" s="393"/>
+      <c r="L302" s="393"/>
+      <c r="M302" s="393"/>
+      <c r="N302" s="393"/>
+      <c r="O302" s="393"/>
+      <c r="P302" s="393"/>
+      <c r="Q302" s="393"/>
+      <c r="R302" s="393"/>
+      <c r="S302" s="393"/>
+      <c r="T302" s="393"/>
+      <c r="U302" s="393"/>
+      <c r="V302" s="394"/>
       <c r="W302" s="243"/>
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A303" s="240"/>
       <c r="B303" s="220"/>
-      <c r="C303" s="375"/>
-      <c r="D303" s="376"/>
-      <c r="E303" s="376"/>
-      <c r="F303" s="376"/>
-      <c r="G303" s="376"/>
-      <c r="H303" s="376"/>
-      <c r="I303" s="376"/>
-      <c r="J303" s="376"/>
-      <c r="K303" s="376"/>
-      <c r="L303" s="376"/>
-      <c r="M303" s="376"/>
-      <c r="N303" s="376"/>
-      <c r="O303" s="376"/>
-      <c r="P303" s="376"/>
-      <c r="Q303" s="376"/>
-      <c r="R303" s="376"/>
-      <c r="S303" s="376"/>
-      <c r="T303" s="376"/>
-      <c r="U303" s="376"/>
-      <c r="V303" s="377"/>
+      <c r="C303" s="392"/>
+      <c r="D303" s="393"/>
+      <c r="E303" s="393"/>
+      <c r="F303" s="393"/>
+      <c r="G303" s="393"/>
+      <c r="H303" s="393"/>
+      <c r="I303" s="393"/>
+      <c r="J303" s="393"/>
+      <c r="K303" s="393"/>
+      <c r="L303" s="393"/>
+      <c r="M303" s="393"/>
+      <c r="N303" s="393"/>
+      <c r="O303" s="393"/>
+      <c r="P303" s="393"/>
+      <c r="Q303" s="393"/>
+      <c r="R303" s="393"/>
+      <c r="S303" s="393"/>
+      <c r="T303" s="393"/>
+      <c r="U303" s="393"/>
+      <c r="V303" s="394"/>
       <c r="W303" s="243"/>
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A304" s="240"/>
       <c r="B304" s="220"/>
-      <c r="C304" s="375"/>
-      <c r="D304" s="376"/>
-      <c r="E304" s="376"/>
-      <c r="F304" s="376"/>
-      <c r="G304" s="376"/>
-      <c r="H304" s="376"/>
-      <c r="I304" s="376"/>
-      <c r="J304" s="376"/>
-      <c r="K304" s="376"/>
-      <c r="L304" s="376"/>
-      <c r="M304" s="376"/>
-      <c r="N304" s="376"/>
-      <c r="O304" s="376"/>
-      <c r="P304" s="376"/>
-      <c r="Q304" s="376"/>
-      <c r="R304" s="376"/>
-      <c r="S304" s="376"/>
-      <c r="T304" s="376"/>
-      <c r="U304" s="376"/>
-      <c r="V304" s="377"/>
+      <c r="C304" s="392"/>
+      <c r="D304" s="393"/>
+      <c r="E304" s="393"/>
+      <c r="F304" s="393"/>
+      <c r="G304" s="393"/>
+      <c r="H304" s="393"/>
+      <c r="I304" s="393"/>
+      <c r="J304" s="393"/>
+      <c r="K304" s="393"/>
+      <c r="L304" s="393"/>
+      <c r="M304" s="393"/>
+      <c r="N304" s="393"/>
+      <c r="O304" s="393"/>
+      <c r="P304" s="393"/>
+      <c r="Q304" s="393"/>
+      <c r="R304" s="393"/>
+      <c r="S304" s="393"/>
+      <c r="T304" s="393"/>
+      <c r="U304" s="393"/>
+      <c r="V304" s="394"/>
       <c r="W304" s="243"/>
     </row>
     <row r="305" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A305" s="240"/>
       <c r="B305" s="220"/>
-      <c r="C305" s="375"/>
-      <c r="D305" s="376"/>
-      <c r="E305" s="376"/>
-      <c r="F305" s="376"/>
-      <c r="G305" s="376"/>
-      <c r="H305" s="376"/>
-      <c r="I305" s="376"/>
-      <c r="J305" s="376"/>
-      <c r="K305" s="376"/>
-      <c r="L305" s="376"/>
-      <c r="M305" s="376"/>
-      <c r="N305" s="376"/>
-      <c r="O305" s="376"/>
-      <c r="P305" s="376"/>
-      <c r="Q305" s="376"/>
-      <c r="R305" s="376"/>
-      <c r="S305" s="376"/>
-      <c r="T305" s="376"/>
-      <c r="U305" s="376"/>
-      <c r="V305" s="377"/>
+      <c r="C305" s="392"/>
+      <c r="D305" s="393"/>
+      <c r="E305" s="393"/>
+      <c r="F305" s="393"/>
+      <c r="G305" s="393"/>
+      <c r="H305" s="393"/>
+      <c r="I305" s="393"/>
+      <c r="J305" s="393"/>
+      <c r="K305" s="393"/>
+      <c r="L305" s="393"/>
+      <c r="M305" s="393"/>
+      <c r="N305" s="393"/>
+      <c r="O305" s="393"/>
+      <c r="P305" s="393"/>
+      <c r="Q305" s="393"/>
+      <c r="R305" s="393"/>
+      <c r="S305" s="393"/>
+      <c r="T305" s="393"/>
+      <c r="U305" s="393"/>
+      <c r="V305" s="394"/>
       <c r="W305" s="243"/>
     </row>
     <row r="306" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A306" s="240"/>
       <c r="B306" s="220"/>
-      <c r="C306" s="375"/>
-      <c r="D306" s="376"/>
-      <c r="E306" s="376"/>
-      <c r="F306" s="376"/>
-      <c r="G306" s="376"/>
-      <c r="H306" s="376"/>
-      <c r="I306" s="376"/>
-      <c r="J306" s="376"/>
-      <c r="K306" s="376"/>
-      <c r="L306" s="376"/>
-      <c r="M306" s="376"/>
-      <c r="N306" s="376"/>
-      <c r="O306" s="376"/>
-      <c r="P306" s="376"/>
-      <c r="Q306" s="376"/>
-      <c r="R306" s="376"/>
-      <c r="S306" s="376"/>
-      <c r="T306" s="376"/>
-      <c r="U306" s="376"/>
-      <c r="V306" s="377"/>
+      <c r="C306" s="392"/>
+      <c r="D306" s="393"/>
+      <c r="E306" s="393"/>
+      <c r="F306" s="393"/>
+      <c r="G306" s="393"/>
+      <c r="H306" s="393"/>
+      <c r="I306" s="393"/>
+      <c r="J306" s="393"/>
+      <c r="K306" s="393"/>
+      <c r="L306" s="393"/>
+      <c r="M306" s="393"/>
+      <c r="N306" s="393"/>
+      <c r="O306" s="393"/>
+      <c r="P306" s="393"/>
+      <c r="Q306" s="393"/>
+      <c r="R306" s="393"/>
+      <c r="S306" s="393"/>
+      <c r="T306" s="393"/>
+      <c r="U306" s="393"/>
+      <c r="V306" s="394"/>
       <c r="W306" s="243"/>
     </row>
     <row r="307" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A307" s="240"/>
       <c r="B307" s="220"/>
-      <c r="C307" s="375"/>
-      <c r="D307" s="376"/>
-      <c r="E307" s="376"/>
-      <c r="F307" s="376"/>
-      <c r="G307" s="376"/>
-      <c r="H307" s="376"/>
-      <c r="I307" s="376"/>
-      <c r="J307" s="376"/>
-      <c r="K307" s="376"/>
-      <c r="L307" s="376"/>
-      <c r="M307" s="376"/>
-      <c r="N307" s="376"/>
-      <c r="O307" s="376"/>
-      <c r="P307" s="376"/>
-      <c r="Q307" s="376"/>
-      <c r="R307" s="376"/>
-      <c r="S307" s="376"/>
-      <c r="T307" s="376"/>
-      <c r="U307" s="376"/>
-      <c r="V307" s="377"/>
+      <c r="C307" s="392"/>
+      <c r="D307" s="393"/>
+      <c r="E307" s="393"/>
+      <c r="F307" s="393"/>
+      <c r="G307" s="393"/>
+      <c r="H307" s="393"/>
+      <c r="I307" s="393"/>
+      <c r="J307" s="393"/>
+      <c r="K307" s="393"/>
+      <c r="L307" s="393"/>
+      <c r="M307" s="393"/>
+      <c r="N307" s="393"/>
+      <c r="O307" s="393"/>
+      <c r="P307" s="393"/>
+      <c r="Q307" s="393"/>
+      <c r="R307" s="393"/>
+      <c r="S307" s="393"/>
+      <c r="T307" s="393"/>
+      <c r="U307" s="393"/>
+      <c r="V307" s="394"/>
       <c r="W307" s="243"/>
     </row>
     <row r="308" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A308" s="240"/>
       <c r="B308" s="220"/>
-      <c r="C308" s="375"/>
-      <c r="D308" s="376"/>
-      <c r="E308" s="376"/>
-      <c r="F308" s="376"/>
-      <c r="G308" s="376"/>
-      <c r="H308" s="376"/>
-      <c r="I308" s="376"/>
-      <c r="J308" s="376"/>
-      <c r="K308" s="376"/>
-      <c r="L308" s="376"/>
-      <c r="M308" s="376"/>
-      <c r="N308" s="376"/>
-      <c r="O308" s="376"/>
-      <c r="P308" s="376"/>
-      <c r="Q308" s="376"/>
-      <c r="R308" s="376"/>
-      <c r="S308" s="376"/>
-      <c r="T308" s="376"/>
-      <c r="U308" s="376"/>
-      <c r="V308" s="377"/>
+      <c r="C308" s="392"/>
+      <c r="D308" s="393"/>
+      <c r="E308" s="393"/>
+      <c r="F308" s="393"/>
+      <c r="G308" s="393"/>
+      <c r="H308" s="393"/>
+      <c r="I308" s="393"/>
+      <c r="J308" s="393"/>
+      <c r="K308" s="393"/>
+      <c r="L308" s="393"/>
+      <c r="M308" s="393"/>
+      <c r="N308" s="393"/>
+      <c r="O308" s="393"/>
+      <c r="P308" s="393"/>
+      <c r="Q308" s="393"/>
+      <c r="R308" s="393"/>
+      <c r="S308" s="393"/>
+      <c r="T308" s="393"/>
+      <c r="U308" s="393"/>
+      <c r="V308" s="394"/>
       <c r="W308" s="243"/>
     </row>
     <row r="309" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A309" s="240"/>
       <c r="B309" s="220"/>
-      <c r="C309" s="375"/>
-      <c r="D309" s="376"/>
-      <c r="E309" s="376"/>
-      <c r="F309" s="376"/>
-      <c r="G309" s="376"/>
-      <c r="H309" s="376"/>
-      <c r="I309" s="376"/>
-      <c r="J309" s="376"/>
-      <c r="K309" s="376"/>
-      <c r="L309" s="376"/>
-      <c r="M309" s="376"/>
-      <c r="N309" s="376"/>
-      <c r="O309" s="376"/>
-      <c r="P309" s="376"/>
-      <c r="Q309" s="376"/>
-      <c r="R309" s="376"/>
-      <c r="S309" s="376"/>
-      <c r="T309" s="376"/>
-      <c r="U309" s="376"/>
-      <c r="V309" s="377"/>
+      <c r="C309" s="392"/>
+      <c r="D309" s="393"/>
+      <c r="E309" s="393"/>
+      <c r="F309" s="393"/>
+      <c r="G309" s="393"/>
+      <c r="H309" s="393"/>
+      <c r="I309" s="393"/>
+      <c r="J309" s="393"/>
+      <c r="K309" s="393"/>
+      <c r="L309" s="393"/>
+      <c r="M309" s="393"/>
+      <c r="N309" s="393"/>
+      <c r="O309" s="393"/>
+      <c r="P309" s="393"/>
+      <c r="Q309" s="393"/>
+      <c r="R309" s="393"/>
+      <c r="S309" s="393"/>
+      <c r="T309" s="393"/>
+      <c r="U309" s="393"/>
+      <c r="V309" s="394"/>
       <c r="W309" s="243"/>
     </row>
     <row r="310" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A310" s="240"/>
       <c r="B310" s="220"/>
-      <c r="C310" s="375"/>
-      <c r="D310" s="376"/>
-      <c r="E310" s="376"/>
-      <c r="F310" s="376"/>
-      <c r="G310" s="376"/>
-      <c r="H310" s="376"/>
-      <c r="I310" s="376"/>
-      <c r="J310" s="376"/>
-      <c r="K310" s="376"/>
-      <c r="L310" s="376"/>
-      <c r="M310" s="376"/>
-      <c r="N310" s="376"/>
-      <c r="O310" s="376"/>
-      <c r="P310" s="376"/>
-      <c r="Q310" s="376"/>
-      <c r="R310" s="376"/>
-      <c r="S310" s="376"/>
-      <c r="T310" s="376"/>
-      <c r="U310" s="376"/>
-      <c r="V310" s="377"/>
+      <c r="C310" s="392"/>
+      <c r="D310" s="393"/>
+      <c r="E310" s="393"/>
+      <c r="F310" s="393"/>
+      <c r="G310" s="393"/>
+      <c r="H310" s="393"/>
+      <c r="I310" s="393"/>
+      <c r="J310" s="393"/>
+      <c r="K310" s="393"/>
+      <c r="L310" s="393"/>
+      <c r="M310" s="393"/>
+      <c r="N310" s="393"/>
+      <c r="O310" s="393"/>
+      <c r="P310" s="393"/>
+      <c r="Q310" s="393"/>
+      <c r="R310" s="393"/>
+      <c r="S310" s="393"/>
+      <c r="T310" s="393"/>
+      <c r="U310" s="393"/>
+      <c r="V310" s="394"/>
       <c r="W310" s="243"/>
     </row>
     <row r="311" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A311" s="240"/>
       <c r="B311" s="220"/>
-      <c r="C311" s="375"/>
-      <c r="D311" s="376"/>
-      <c r="E311" s="376"/>
-      <c r="F311" s="376"/>
-      <c r="G311" s="376"/>
-      <c r="H311" s="376"/>
-      <c r="I311" s="376"/>
-      <c r="J311" s="376"/>
-      <c r="K311" s="376"/>
-      <c r="L311" s="376"/>
-      <c r="M311" s="376"/>
-      <c r="N311" s="376"/>
-      <c r="O311" s="376"/>
-      <c r="P311" s="376"/>
-      <c r="Q311" s="376"/>
-      <c r="R311" s="376"/>
-      <c r="S311" s="376"/>
-      <c r="T311" s="376"/>
-      <c r="U311" s="376"/>
-      <c r="V311" s="377"/>
+      <c r="C311" s="392"/>
+      <c r="D311" s="393"/>
+      <c r="E311" s="393"/>
+      <c r="F311" s="393"/>
+      <c r="G311" s="393"/>
+      <c r="H311" s="393"/>
+      <c r="I311" s="393"/>
+      <c r="J311" s="393"/>
+      <c r="K311" s="393"/>
+      <c r="L311" s="393"/>
+      <c r="M311" s="393"/>
+      <c r="N311" s="393"/>
+      <c r="O311" s="393"/>
+      <c r="P311" s="393"/>
+      <c r="Q311" s="393"/>
+      <c r="R311" s="393"/>
+      <c r="S311" s="393"/>
+      <c r="T311" s="393"/>
+      <c r="U311" s="393"/>
+      <c r="V311" s="394"/>
       <c r="W311" s="243"/>
     </row>
     <row r="312" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A312" s="240"/>
       <c r="B312" s="220"/>
-      <c r="C312" s="375"/>
-      <c r="D312" s="376"/>
-      <c r="E312" s="376"/>
-      <c r="F312" s="376"/>
-      <c r="G312" s="376"/>
-      <c r="H312" s="376"/>
-      <c r="I312" s="376"/>
-      <c r="J312" s="376"/>
-      <c r="K312" s="376"/>
-      <c r="L312" s="376"/>
-      <c r="M312" s="376"/>
-      <c r="N312" s="376"/>
-      <c r="O312" s="376"/>
-      <c r="P312" s="376"/>
-      <c r="Q312" s="376"/>
-      <c r="R312" s="376"/>
-      <c r="S312" s="376"/>
-      <c r="T312" s="376"/>
-      <c r="U312" s="376"/>
-      <c r="V312" s="377"/>
+      <c r="C312" s="392"/>
+      <c r="D312" s="393"/>
+      <c r="E312" s="393"/>
+      <c r="F312" s="393"/>
+      <c r="G312" s="393"/>
+      <c r="H312" s="393"/>
+      <c r="I312" s="393"/>
+      <c r="J312" s="393"/>
+      <c r="K312" s="393"/>
+      <c r="L312" s="393"/>
+      <c r="M312" s="393"/>
+      <c r="N312" s="393"/>
+      <c r="O312" s="393"/>
+      <c r="P312" s="393"/>
+      <c r="Q312" s="393"/>
+      <c r="R312" s="393"/>
+      <c r="S312" s="393"/>
+      <c r="T312" s="393"/>
+      <c r="U312" s="393"/>
+      <c r="V312" s="394"/>
       <c r="W312" s="243"/>
     </row>
     <row r="313" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A313" s="240"/>
       <c r="B313" s="220"/>
-      <c r="C313" s="375"/>
-      <c r="D313" s="376"/>
-      <c r="E313" s="376"/>
-      <c r="F313" s="376"/>
-      <c r="G313" s="376"/>
-      <c r="H313" s="376"/>
-      <c r="I313" s="376"/>
-      <c r="J313" s="376"/>
-      <c r="K313" s="376"/>
-      <c r="L313" s="376"/>
-      <c r="M313" s="376"/>
-      <c r="N313" s="376"/>
-      <c r="O313" s="376"/>
-      <c r="P313" s="376"/>
-      <c r="Q313" s="376"/>
-      <c r="R313" s="376"/>
-      <c r="S313" s="376"/>
-      <c r="T313" s="376"/>
-      <c r="U313" s="376"/>
-      <c r="V313" s="377"/>
+      <c r="C313" s="392"/>
+      <c r="D313" s="393"/>
+      <c r="E313" s="393"/>
+      <c r="F313" s="393"/>
+      <c r="G313" s="393"/>
+      <c r="H313" s="393"/>
+      <c r="I313" s="393"/>
+      <c r="J313" s="393"/>
+      <c r="K313" s="393"/>
+      <c r="L313" s="393"/>
+      <c r="M313" s="393"/>
+      <c r="N313" s="393"/>
+      <c r="O313" s="393"/>
+      <c r="P313" s="393"/>
+      <c r="Q313" s="393"/>
+      <c r="R313" s="393"/>
+      <c r="S313" s="393"/>
+      <c r="T313" s="393"/>
+      <c r="U313" s="393"/>
+      <c r="V313" s="394"/>
       <c r="W313" s="243"/>
     </row>
     <row r="314" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A314" s="240"/>
       <c r="B314" s="220"/>
-      <c r="C314" s="375"/>
-      <c r="D314" s="376"/>
-      <c r="E314" s="376"/>
-      <c r="F314" s="376"/>
-      <c r="G314" s="376"/>
-      <c r="H314" s="376"/>
-      <c r="I314" s="376"/>
-      <c r="J314" s="376"/>
-      <c r="K314" s="376"/>
-      <c r="L314" s="376"/>
-      <c r="M314" s="376"/>
-      <c r="N314" s="376"/>
-      <c r="O314" s="376"/>
-      <c r="P314" s="376"/>
-      <c r="Q314" s="376"/>
-      <c r="R314" s="376"/>
-      <c r="S314" s="376"/>
-      <c r="T314" s="376"/>
-      <c r="U314" s="376"/>
-      <c r="V314" s="377"/>
+      <c r="C314" s="392"/>
+      <c r="D314" s="393"/>
+      <c r="E314" s="393"/>
+      <c r="F314" s="393"/>
+      <c r="G314" s="393"/>
+      <c r="H314" s="393"/>
+      <c r="I314" s="393"/>
+      <c r="J314" s="393"/>
+      <c r="K314" s="393"/>
+      <c r="L314" s="393"/>
+      <c r="M314" s="393"/>
+      <c r="N314" s="393"/>
+      <c r="O314" s="393"/>
+      <c r="P314" s="393"/>
+      <c r="Q314" s="393"/>
+      <c r="R314" s="393"/>
+      <c r="S314" s="393"/>
+      <c r="T314" s="393"/>
+      <c r="U314" s="393"/>
+      <c r="V314" s="394"/>
       <c r="W314" s="243"/>
     </row>
     <row r="315" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A315" s="240"/>
       <c r="B315" s="220"/>
-      <c r="C315" s="375"/>
-      <c r="D315" s="376"/>
-      <c r="E315" s="376"/>
-      <c r="F315" s="376"/>
-      <c r="G315" s="376"/>
-      <c r="H315" s="376"/>
-      <c r="I315" s="376"/>
-      <c r="J315" s="376"/>
-      <c r="K315" s="376"/>
-      <c r="L315" s="376"/>
-      <c r="M315" s="376"/>
-      <c r="N315" s="376"/>
-      <c r="O315" s="376"/>
-      <c r="P315" s="376"/>
-      <c r="Q315" s="376"/>
-      <c r="R315" s="376"/>
-      <c r="S315" s="376"/>
-      <c r="T315" s="376"/>
-      <c r="U315" s="376"/>
-      <c r="V315" s="377"/>
+      <c r="C315" s="392"/>
+      <c r="D315" s="393"/>
+      <c r="E315" s="393"/>
+      <c r="F315" s="393"/>
+      <c r="G315" s="393"/>
+      <c r="H315" s="393"/>
+      <c r="I315" s="393"/>
+      <c r="J315" s="393"/>
+      <c r="K315" s="393"/>
+      <c r="L315" s="393"/>
+      <c r="M315" s="393"/>
+      <c r="N315" s="393"/>
+      <c r="O315" s="393"/>
+      <c r="P315" s="393"/>
+      <c r="Q315" s="393"/>
+      <c r="R315" s="393"/>
+      <c r="S315" s="393"/>
+      <c r="T315" s="393"/>
+      <c r="U315" s="393"/>
+      <c r="V315" s="394"/>
       <c r="W315" s="243"/>
     </row>
     <row r="316" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A316" s="240"/>
       <c r="B316" s="220"/>
-      <c r="C316" s="375"/>
-      <c r="D316" s="376"/>
-      <c r="E316" s="376"/>
-      <c r="F316" s="376"/>
-      <c r="G316" s="376"/>
-      <c r="H316" s="376"/>
-      <c r="I316" s="376"/>
-      <c r="J316" s="376"/>
-      <c r="K316" s="376"/>
-      <c r="L316" s="376"/>
-      <c r="M316" s="376"/>
-      <c r="N316" s="376"/>
-      <c r="O316" s="376"/>
-      <c r="P316" s="376"/>
-      <c r="Q316" s="376"/>
-      <c r="R316" s="376"/>
-      <c r="S316" s="376"/>
-      <c r="T316" s="376"/>
-      <c r="U316" s="376"/>
-      <c r="V316" s="377"/>
+      <c r="C316" s="392"/>
+      <c r="D316" s="393"/>
+      <c r="E316" s="393"/>
+      <c r="F316" s="393"/>
+      <c r="G316" s="393"/>
+      <c r="H316" s="393"/>
+      <c r="I316" s="393"/>
+      <c r="J316" s="393"/>
+      <c r="K316" s="393"/>
+      <c r="L316" s="393"/>
+      <c r="M316" s="393"/>
+      <c r="N316" s="393"/>
+      <c r="O316" s="393"/>
+      <c r="P316" s="393"/>
+      <c r="Q316" s="393"/>
+      <c r="R316" s="393"/>
+      <c r="S316" s="393"/>
+      <c r="T316" s="393"/>
+      <c r="U316" s="393"/>
+      <c r="V316" s="394"/>
       <c r="W316" s="243"/>
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A317" s="240"/>
       <c r="B317" s="220"/>
-      <c r="C317" s="375"/>
-      <c r="D317" s="376"/>
-      <c r="E317" s="376"/>
-      <c r="F317" s="376"/>
-      <c r="G317" s="376"/>
-      <c r="H317" s="376"/>
-      <c r="I317" s="376"/>
-      <c r="J317" s="376"/>
-      <c r="K317" s="376"/>
-      <c r="L317" s="376"/>
-      <c r="M317" s="376"/>
-      <c r="N317" s="376"/>
-      <c r="O317" s="376"/>
-      <c r="P317" s="376"/>
-      <c r="Q317" s="376"/>
-      <c r="R317" s="376"/>
-      <c r="S317" s="376"/>
-      <c r="T317" s="376"/>
-      <c r="U317" s="376"/>
-      <c r="V317" s="377"/>
+      <c r="C317" s="392"/>
+      <c r="D317" s="393"/>
+      <c r="E317" s="393"/>
+      <c r="F317" s="393"/>
+      <c r="G317" s="393"/>
+      <c r="H317" s="393"/>
+      <c r="I317" s="393"/>
+      <c r="J317" s="393"/>
+      <c r="K317" s="393"/>
+      <c r="L317" s="393"/>
+      <c r="M317" s="393"/>
+      <c r="N317" s="393"/>
+      <c r="O317" s="393"/>
+      <c r="P317" s="393"/>
+      <c r="Q317" s="393"/>
+      <c r="R317" s="393"/>
+      <c r="S317" s="393"/>
+      <c r="T317" s="393"/>
+      <c r="U317" s="393"/>
+      <c r="V317" s="394"/>
       <c r="W317" s="243"/>
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A318" s="240"/>
       <c r="B318" s="220"/>
-      <c r="C318" s="375"/>
-      <c r="D318" s="376"/>
-      <c r="E318" s="376"/>
-      <c r="F318" s="376"/>
-      <c r="G318" s="376"/>
-      <c r="H318" s="376"/>
-      <c r="I318" s="376"/>
-      <c r="J318" s="376"/>
-      <c r="K318" s="376"/>
-      <c r="L318" s="376"/>
-      <c r="M318" s="376"/>
-      <c r="N318" s="376"/>
-      <c r="O318" s="376"/>
-      <c r="P318" s="376"/>
-      <c r="Q318" s="376"/>
-      <c r="R318" s="376"/>
-      <c r="S318" s="376"/>
-      <c r="T318" s="376"/>
-      <c r="U318" s="376"/>
-      <c r="V318" s="377"/>
+      <c r="C318" s="392"/>
+      <c r="D318" s="393"/>
+      <c r="E318" s="393"/>
+      <c r="F318" s="393"/>
+      <c r="G318" s="393"/>
+      <c r="H318" s="393"/>
+      <c r="I318" s="393"/>
+      <c r="J318" s="393"/>
+      <c r="K318" s="393"/>
+      <c r="L318" s="393"/>
+      <c r="M318" s="393"/>
+      <c r="N318" s="393"/>
+      <c r="O318" s="393"/>
+      <c r="P318" s="393"/>
+      <c r="Q318" s="393"/>
+      <c r="R318" s="393"/>
+      <c r="S318" s="393"/>
+      <c r="T318" s="393"/>
+      <c r="U318" s="393"/>
+      <c r="V318" s="394"/>
       <c r="W318" s="243"/>
     </row>
     <row r="319" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A319" s="240"/>
       <c r="B319" s="220"/>
-      <c r="C319" s="375"/>
-      <c r="D319" s="376"/>
-      <c r="E319" s="376"/>
-      <c r="F319" s="376"/>
-      <c r="G319" s="376"/>
-      <c r="H319" s="376"/>
-      <c r="I319" s="376"/>
-      <c r="J319" s="376"/>
-      <c r="K319" s="376"/>
-      <c r="L319" s="376"/>
-      <c r="M319" s="376"/>
-      <c r="N319" s="376"/>
-      <c r="O319" s="376"/>
-      <c r="P319" s="376"/>
-      <c r="Q319" s="376"/>
-      <c r="R319" s="376"/>
-      <c r="S319" s="376"/>
-      <c r="T319" s="376"/>
-      <c r="U319" s="376"/>
-      <c r="V319" s="377"/>
+      <c r="C319" s="392"/>
+      <c r="D319" s="393"/>
+      <c r="E319" s="393"/>
+      <c r="F319" s="393"/>
+      <c r="G319" s="393"/>
+      <c r="H319" s="393"/>
+      <c r="I319" s="393"/>
+      <c r="J319" s="393"/>
+      <c r="K319" s="393"/>
+      <c r="L319" s="393"/>
+      <c r="M319" s="393"/>
+      <c r="N319" s="393"/>
+      <c r="O319" s="393"/>
+      <c r="P319" s="393"/>
+      <c r="Q319" s="393"/>
+      <c r="R319" s="393"/>
+      <c r="S319" s="393"/>
+      <c r="T319" s="393"/>
+      <c r="U319" s="393"/>
+      <c r="V319" s="394"/>
       <c r="W319" s="243"/>
     </row>
     <row r="320" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A320" s="240"/>
       <c r="B320" s="220"/>
-      <c r="C320" s="375"/>
-      <c r="D320" s="376"/>
-      <c r="E320" s="376"/>
-      <c r="F320" s="376"/>
-      <c r="G320" s="376"/>
-      <c r="H320" s="376"/>
-      <c r="I320" s="376"/>
-      <c r="J320" s="376"/>
-      <c r="K320" s="376"/>
-      <c r="L320" s="376"/>
-      <c r="M320" s="376"/>
-      <c r="N320" s="376"/>
-      <c r="O320" s="376"/>
-      <c r="P320" s="376"/>
-      <c r="Q320" s="376"/>
-      <c r="R320" s="376"/>
-      <c r="S320" s="376"/>
-      <c r="T320" s="376"/>
-      <c r="U320" s="376"/>
-      <c r="V320" s="377"/>
+      <c r="C320" s="392"/>
+      <c r="D320" s="393"/>
+      <c r="E320" s="393"/>
+      <c r="F320" s="393"/>
+      <c r="G320" s="393"/>
+      <c r="H320" s="393"/>
+      <c r="I320" s="393"/>
+      <c r="J320" s="393"/>
+      <c r="K320" s="393"/>
+      <c r="L320" s="393"/>
+      <c r="M320" s="393"/>
+      <c r="N320" s="393"/>
+      <c r="O320" s="393"/>
+      <c r="P320" s="393"/>
+      <c r="Q320" s="393"/>
+      <c r="R320" s="393"/>
+      <c r="S320" s="393"/>
+      <c r="T320" s="393"/>
+      <c r="U320" s="393"/>
+      <c r="V320" s="394"/>
       <c r="W320" s="243"/>
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A321" s="240"/>
       <c r="B321" s="220"/>
-      <c r="C321" s="375"/>
-      <c r="D321" s="376"/>
-      <c r="E321" s="376"/>
-      <c r="F321" s="376"/>
-      <c r="G321" s="376"/>
-      <c r="H321" s="376"/>
-      <c r="I321" s="376"/>
-      <c r="J321" s="376"/>
-      <c r="K321" s="376"/>
-      <c r="L321" s="376"/>
-      <c r="M321" s="376"/>
-      <c r="N321" s="376"/>
-      <c r="O321" s="376"/>
-      <c r="P321" s="376"/>
-      <c r="Q321" s="376"/>
-      <c r="R321" s="376"/>
-      <c r="S321" s="376"/>
-      <c r="T321" s="376"/>
-      <c r="U321" s="376"/>
-      <c r="V321" s="377"/>
+      <c r="C321" s="392"/>
+      <c r="D321" s="393"/>
+      <c r="E321" s="393"/>
+      <c r="F321" s="393"/>
+      <c r="G321" s="393"/>
+      <c r="H321" s="393"/>
+      <c r="I321" s="393"/>
+      <c r="J321" s="393"/>
+      <c r="K321" s="393"/>
+      <c r="L321" s="393"/>
+      <c r="M321" s="393"/>
+      <c r="N321" s="393"/>
+      <c r="O321" s="393"/>
+      <c r="P321" s="393"/>
+      <c r="Q321" s="393"/>
+      <c r="R321" s="393"/>
+      <c r="S321" s="393"/>
+      <c r="T321" s="393"/>
+      <c r="U321" s="393"/>
+      <c r="V321" s="394"/>
       <c r="W321" s="243"/>
     </row>
     <row r="322" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A322" s="240"/>
       <c r="B322" s="220"/>
-      <c r="C322" s="375"/>
-      <c r="D322" s="376"/>
-      <c r="E322" s="376"/>
-      <c r="F322" s="376"/>
-      <c r="G322" s="376"/>
-      <c r="H322" s="376"/>
-      <c r="I322" s="376"/>
-      <c r="J322" s="376"/>
-      <c r="K322" s="376"/>
-      <c r="L322" s="376"/>
-      <c r="M322" s="376"/>
-      <c r="N322" s="376"/>
-      <c r="O322" s="376"/>
-      <c r="P322" s="376"/>
-      <c r="Q322" s="376"/>
-      <c r="R322" s="376"/>
-      <c r="S322" s="376"/>
-      <c r="T322" s="376"/>
-      <c r="U322" s="376"/>
-      <c r="V322" s="377"/>
+      <c r="C322" s="392"/>
+      <c r="D322" s="393"/>
+      <c r="E322" s="393"/>
+      <c r="F322" s="393"/>
+      <c r="G322" s="393"/>
+      <c r="H322" s="393"/>
+      <c r="I322" s="393"/>
+      <c r="J322" s="393"/>
+      <c r="K322" s="393"/>
+      <c r="L322" s="393"/>
+      <c r="M322" s="393"/>
+      <c r="N322" s="393"/>
+      <c r="O322" s="393"/>
+      <c r="P322" s="393"/>
+      <c r="Q322" s="393"/>
+      <c r="R322" s="393"/>
+      <c r="S322" s="393"/>
+      <c r="T322" s="393"/>
+      <c r="U322" s="393"/>
+      <c r="V322" s="394"/>
       <c r="W322" s="243"/>
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A323" s="240"/>
       <c r="B323" s="220"/>
-      <c r="C323" s="378"/>
-      <c r="D323" s="379"/>
-      <c r="E323" s="379"/>
-      <c r="F323" s="379"/>
-      <c r="G323" s="379"/>
-      <c r="H323" s="379"/>
-      <c r="I323" s="379"/>
-      <c r="J323" s="379"/>
-      <c r="K323" s="379"/>
-      <c r="L323" s="379"/>
-      <c r="M323" s="379"/>
-      <c r="N323" s="379"/>
-      <c r="O323" s="379"/>
-      <c r="P323" s="379"/>
-      <c r="Q323" s="379"/>
-      <c r="R323" s="379"/>
-      <c r="S323" s="379"/>
-      <c r="T323" s="379"/>
-      <c r="U323" s="379"/>
-      <c r="V323" s="380"/>
+      <c r="C323" s="395"/>
+      <c r="D323" s="396"/>
+      <c r="E323" s="396"/>
+      <c r="F323" s="396"/>
+      <c r="G323" s="396"/>
+      <c r="H323" s="396"/>
+      <c r="I323" s="396"/>
+      <c r="J323" s="396"/>
+      <c r="K323" s="396"/>
+      <c r="L323" s="396"/>
+      <c r="M323" s="396"/>
+      <c r="N323" s="396"/>
+      <c r="O323" s="396"/>
+      <c r="P323" s="396"/>
+      <c r="Q323" s="396"/>
+      <c r="R323" s="396"/>
+      <c r="S323" s="396"/>
+      <c r="T323" s="396"/>
+      <c r="U323" s="396"/>
+      <c r="V323" s="397"/>
       <c r="W323" s="243"/>
     </row>
     <row r="324" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
@@ -22297,121 +22301,16 @@
     </row>
   </sheetData>
   <mergeCells count="149">
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="G1:M2"/>
-    <mergeCell ref="N1:W1"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="A12:W12"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="N22:Q22"/>
-    <mergeCell ref="A3:W3"/>
-    <mergeCell ref="A4:W4"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="R8:U8"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="N35:Q35"/>
-    <mergeCell ref="A37:W37"/>
-    <mergeCell ref="A50:W50"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="O55:Q55"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="S24:V24"/>
-    <mergeCell ref="N25:V26"/>
-    <mergeCell ref="N27:Q27"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="C30:J30"/>
-    <mergeCell ref="N30:Q30"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="O74:Q74"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="O78:Q78"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="O82:Q82"/>
-    <mergeCell ref="A57:W57"/>
-    <mergeCell ref="A58:W58"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="O66:Q66"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="O70:Q70"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="O98:Q98"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="O102:Q102"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="O106:Q106"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="O86:Q86"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="O90:Q90"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="O94:Q94"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="O122:Q122"/>
-    <mergeCell ref="A124:W124"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="O129:Q129"/>
-    <mergeCell ref="A131:W131"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="O110:Q110"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="O114:Q114"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="O118:Q118"/>
-    <mergeCell ref="A132:W132"/>
-    <mergeCell ref="A133:W133"/>
-    <mergeCell ref="A134:W134"/>
-    <mergeCell ref="H136:I136"/>
-    <mergeCell ref="O149:Q149"/>
-    <mergeCell ref="O154:Q154"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="O139:Q139"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="O144:Q144"/>
-    <mergeCell ref="A162:W162"/>
-    <mergeCell ref="A163:W163"/>
-    <mergeCell ref="A164:W164"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="O169:Q169"/>
-    <mergeCell ref="D174:F174"/>
-    <mergeCell ref="O174:Q174"/>
-    <mergeCell ref="G141:H141"/>
-    <mergeCell ref="H146:I146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="O160:Q160"/>
-    <mergeCell ref="C187:F187"/>
-    <mergeCell ref="D188:F188"/>
-    <mergeCell ref="C190:F190"/>
-    <mergeCell ref="P190:Q190"/>
-    <mergeCell ref="O194:Q194"/>
-    <mergeCell ref="E197:F197"/>
-    <mergeCell ref="D179:F179"/>
-    <mergeCell ref="O179:Q179"/>
-    <mergeCell ref="A181:W181"/>
-    <mergeCell ref="A182:W182"/>
-    <mergeCell ref="A183:W183"/>
-    <mergeCell ref="A184:W184"/>
-    <mergeCell ref="A212:W212"/>
-    <mergeCell ref="A213:W213"/>
-    <mergeCell ref="A214:W214"/>
-    <mergeCell ref="D219:F219"/>
-    <mergeCell ref="O219:Q219"/>
-    <mergeCell ref="D222:F222"/>
-    <mergeCell ref="O199:Q199"/>
-    <mergeCell ref="D201:F201"/>
-    <mergeCell ref="O204:Q204"/>
-    <mergeCell ref="D206:F206"/>
-    <mergeCell ref="D210:F210"/>
-    <mergeCell ref="O210:Q210"/>
+    <mergeCell ref="C298:V323"/>
+    <mergeCell ref="A281:W281"/>
+    <mergeCell ref="O286:Q286"/>
+    <mergeCell ref="G288:I288"/>
+    <mergeCell ref="A294:W294"/>
+    <mergeCell ref="O273:Q273"/>
+    <mergeCell ref="P277:R277"/>
+    <mergeCell ref="A279:W279"/>
+    <mergeCell ref="A280:I280"/>
+    <mergeCell ref="K280:W280"/>
     <mergeCell ref="D265:F265"/>
     <mergeCell ref="P265:R265"/>
     <mergeCell ref="D269:F269"/>
@@ -22436,16 +22335,121 @@
     <mergeCell ref="D231:F231"/>
     <mergeCell ref="O231:Q231"/>
     <mergeCell ref="A233:W233"/>
-    <mergeCell ref="C298:V323"/>
-    <mergeCell ref="A281:W281"/>
-    <mergeCell ref="O286:Q286"/>
-    <mergeCell ref="G288:I288"/>
-    <mergeCell ref="A294:W294"/>
-    <mergeCell ref="O273:Q273"/>
-    <mergeCell ref="P277:R277"/>
-    <mergeCell ref="A279:W279"/>
-    <mergeCell ref="A280:I280"/>
-    <mergeCell ref="K280:W280"/>
+    <mergeCell ref="A212:W212"/>
+    <mergeCell ref="A213:W213"/>
+    <mergeCell ref="A214:W214"/>
+    <mergeCell ref="D219:F219"/>
+    <mergeCell ref="O219:Q219"/>
+    <mergeCell ref="D222:F222"/>
+    <mergeCell ref="O199:Q199"/>
+    <mergeCell ref="D201:F201"/>
+    <mergeCell ref="O204:Q204"/>
+    <mergeCell ref="D206:F206"/>
+    <mergeCell ref="D210:F210"/>
+    <mergeCell ref="O210:Q210"/>
+    <mergeCell ref="C187:F187"/>
+    <mergeCell ref="D188:F188"/>
+    <mergeCell ref="C190:F190"/>
+    <mergeCell ref="P190:Q190"/>
+    <mergeCell ref="O194:Q194"/>
+    <mergeCell ref="E197:F197"/>
+    <mergeCell ref="D179:F179"/>
+    <mergeCell ref="O179:Q179"/>
+    <mergeCell ref="A181:W181"/>
+    <mergeCell ref="A182:W182"/>
+    <mergeCell ref="A183:W183"/>
+    <mergeCell ref="A184:W184"/>
+    <mergeCell ref="A162:W162"/>
+    <mergeCell ref="A163:W163"/>
+    <mergeCell ref="A164:W164"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="O169:Q169"/>
+    <mergeCell ref="D174:F174"/>
+    <mergeCell ref="O174:Q174"/>
+    <mergeCell ref="G141:H141"/>
+    <mergeCell ref="H146:I146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="O160:Q160"/>
+    <mergeCell ref="A132:W132"/>
+    <mergeCell ref="A133:W133"/>
+    <mergeCell ref="A134:W134"/>
+    <mergeCell ref="H136:I136"/>
+    <mergeCell ref="O149:Q149"/>
+    <mergeCell ref="O154:Q154"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="O139:Q139"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="O144:Q144"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="O122:Q122"/>
+    <mergeCell ref="A124:W124"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="O129:Q129"/>
+    <mergeCell ref="A131:W131"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="O110:Q110"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="O114:Q114"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="O118:Q118"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="O98:Q98"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="O102:Q102"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="O106:Q106"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="O86:Q86"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="O90:Q90"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="O94:Q94"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="O74:Q74"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="O78:Q78"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="O82:Q82"/>
+    <mergeCell ref="A57:W57"/>
+    <mergeCell ref="A58:W58"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="O66:Q66"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="O70:Q70"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="N35:Q35"/>
+    <mergeCell ref="A37:W37"/>
+    <mergeCell ref="A50:W50"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="O55:Q55"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="S24:V24"/>
+    <mergeCell ref="N25:V26"/>
+    <mergeCell ref="N27:Q27"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="N30:Q30"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="N22:Q22"/>
+    <mergeCell ref="A3:W3"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="G1:M2"/>
+    <mergeCell ref="N1:W1"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="A12:W12"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="C17:J17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -22501,51 +22505,51 @@
       </c>
       <c r="C2" s="401">
         <f>Admin!B5</f>
-        <v>45412</v>
+        <v>45777</v>
       </c>
       <c r="D2" s="400">
         <f>Admin!B6</f>
-        <v>45443</v>
+        <v>45808</v>
       </c>
       <c r="E2" s="400">
         <f>Admin!B7</f>
-        <v>45473</v>
+        <v>45838</v>
       </c>
       <c r="F2" s="401">
         <f>Admin!B8</f>
-        <v>45504</v>
+        <v>45869</v>
       </c>
       <c r="G2" s="400">
         <f>Admin!B9</f>
-        <v>45535</v>
+        <v>45900</v>
       </c>
       <c r="H2" s="400">
         <f>Admin!B10</f>
-        <v>45565</v>
+        <v>45930</v>
       </c>
       <c r="I2" s="401">
         <f>Admin!B11</f>
-        <v>45596</v>
+        <v>45961</v>
       </c>
       <c r="J2" s="400">
         <f>Admin!B12</f>
-        <v>45626</v>
+        <v>45991</v>
       </c>
       <c r="K2" s="400">
         <f>Admin!B13</f>
-        <v>45657</v>
+        <v>46022</v>
       </c>
       <c r="L2" s="401">
         <f>Admin!B14</f>
-        <v>45688</v>
+        <v>46053</v>
       </c>
       <c r="M2" s="400">
         <f>Admin!B15</f>
-        <v>45716</v>
+        <v>46081</v>
       </c>
       <c r="N2" s="400">
         <f>Admin!B16</f>
-        <v>45747</v>
+        <v>46112</v>
       </c>
       <c r="O2" s="24"/>
     </row>
@@ -22553,7 +22557,7 @@
       <c r="A3" s="404"/>
       <c r="B3" s="158">
         <f>Admin!B$17</f>
-        <v>45752</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="402"/>
       <c r="D3" s="400"/>
@@ -24802,25 +24806,25 @@
     <row r="2" spans="1:10" s="306" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="298"/>
       <c r="B2" s="405" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C2" s="405" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D2" s="405" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E2" s="405" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F2" s="405" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G2" s="405" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H2" s="405" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I2" s="298"/>
     </row>
@@ -24849,7 +24853,7 @@
     <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" s="298"/>
       <c r="B5" s="298" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C5" s="304">
         <f>SUM('Profit &amp; Loss Account'!C5:E7)</f>
@@ -24877,7 +24881,7 @@
     <row r="6" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="298"/>
       <c r="B6" s="298" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C6" s="304">
         <f>SUM('Profit &amp; Loss Account'!C8:E8)+SUM('Profit &amp; Loss Account'!C11:E11)+SUM('Profit &amp; Loss Account'!C38:E38)</f>
@@ -24905,7 +24909,7 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" s="298"/>
       <c r="B7" s="298" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C7" s="304">
         <f>SUM('Profit &amp; Loss Account'!C14:E14)+SUM('Profit &amp; Loss Account'!C16:E16)</f>
@@ -24955,7 +24959,7 @@
     <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" s="298"/>
       <c r="B10" s="300" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C10" s="298"/>
       <c r="D10" s="298"/>
@@ -24979,7 +24983,7 @@
     <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" s="298"/>
       <c r="B12" s="298" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C12" s="299">
         <f>SUM('Profit &amp; Loss Account'!C21:E21)</f>
@@ -25007,7 +25011,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" s="298"/>
       <c r="B13" s="298" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C13" s="299">
         <f>SUM('Profit &amp; Loss Account'!C22:E22)</f>
@@ -25035,7 +25039,7 @@
     <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" s="298"/>
       <c r="B14" s="298" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C14" s="299">
         <f>SUM('Profit &amp; Loss Account'!C23:E23)</f>
@@ -25063,7 +25067,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" s="298"/>
       <c r="B15" s="298" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C15" s="299">
         <f>SUM('Profit &amp; Loss Account'!C24:E24)</f>
@@ -25091,7 +25095,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" s="298"/>
       <c r="B16" s="298" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C16" s="299">
         <f>SUM('Profit &amp; Loss Account'!C31:E31)</f>
@@ -25119,7 +25123,7 @@
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="298"/>
       <c r="B17" s="298" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C17" s="299">
         <f>SUM('Profit &amp; Loss Account'!C25:E26)</f>
@@ -25147,7 +25151,7 @@
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="298"/>
       <c r="B18" s="298" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C18" s="299">
         <f>SUM('Profit &amp; Loss Account'!C27:E27)</f>
@@ -25175,7 +25179,7 @@
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="298"/>
       <c r="B19" s="298" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C19" s="299">
         <f>SUM('Profit &amp; Loss Account'!C28:E28)</f>
@@ -25203,7 +25207,7 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="298"/>
       <c r="B20" s="298" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C20" s="299">
         <f>SUM('Profit &amp; Loss Account'!C29:E29)</f>
@@ -25231,7 +25235,7 @@
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="298"/>
       <c r="B21" s="298" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C21" s="299">
         <f>SUM('Profit &amp; Loss Account'!C30:E30)</f>
@@ -25259,7 +25263,7 @@
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="298"/>
       <c r="B22" s="298" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C22" s="299">
         <f>SUM('Profit &amp; Loss Account'!C32:E32)</f>
@@ -25298,7 +25302,7 @@
     <row r="24" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="298"/>
       <c r="B24" s="298" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C24" s="299">
         <f>SUM('Profit &amp; Loss Account'!C15:E15)</f>
@@ -25326,7 +25330,7 @@
     <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" s="298"/>
       <c r="B25" s="298" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C25" s="299">
         <v>0</v>
@@ -25345,7 +25349,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I25" s="298"/>
     </row>
@@ -25402,7 +25406,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A29" s="298"/>
       <c r="B29" s="300" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C29" s="302">
         <f>SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C25,C26)</f>
@@ -25498,7 +25502,7 @@
     <row r="36" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A36" s="298"/>
       <c r="B36" s="298" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C36" s="299">
         <v>0</v>
@@ -25517,14 +25521,14 @@
         <v>0</v>
       </c>
       <c r="H36" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I36" s="298"/>
     </row>
     <row r="37" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="298"/>
       <c r="B37" s="298" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C37" s="299">
         <v>0</v>
@@ -25543,14 +25547,14 @@
         <v>0</v>
       </c>
       <c r="H37" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I37" s="298"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A38" s="298"/>
       <c r="B38" s="298" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C38" s="299">
         <v>0</v>
@@ -25569,14 +25573,14 @@
         <v>0</v>
       </c>
       <c r="H38" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I38" s="298"/>
     </row>
     <row r="39" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="298"/>
       <c r="B39" s="298" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C39" s="299">
         <v>0</v>
@@ -25595,14 +25599,14 @@
         <v>0</v>
       </c>
       <c r="H39" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I39" s="298"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A40" s="298"/>
       <c r="B40" s="298" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C40" s="299">
         <v>0</v>
@@ -25621,14 +25625,14 @@
         <v>0</v>
       </c>
       <c r="H40" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I40" s="298"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A41" s="298"/>
       <c r="B41" s="298" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C41" s="299">
         <v>0</v>
@@ -25647,14 +25651,14 @@
         <v>0</v>
       </c>
       <c r="H41" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I41" s="298"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A42" s="298"/>
       <c r="B42" s="298" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C42" s="299">
         <v>0</v>
@@ -25673,14 +25677,14 @@
         <v>0</v>
       </c>
       <c r="H42" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I42" s="298"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A43" s="298"/>
       <c r="B43" s="298" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C43" s="299">
         <v>0</v>
@@ -25699,14 +25703,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I43" s="298"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A44" s="298"/>
       <c r="B44" s="298" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C44" s="299">
         <v>0</v>
@@ -25725,14 +25729,14 @@
         <v>0</v>
       </c>
       <c r="H44" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I44" s="298"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A45" s="298"/>
       <c r="B45" s="298" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C45" s="299">
         <v>0</v>
@@ -25751,14 +25755,14 @@
         <v>0</v>
       </c>
       <c r="H45" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I45" s="298"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A46" s="298"/>
       <c r="B46" s="298" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C46" s="299">
         <v>0</v>
@@ -25777,14 +25781,14 @@
         <v>0</v>
       </c>
       <c r="H46" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I46" s="298"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A47" s="298"/>
       <c r="B47" s="298" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C47" s="299">
         <v>0</v>
@@ -25803,14 +25807,14 @@
         <v>0</v>
       </c>
       <c r="H47" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I47" s="298"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A48" s="298"/>
       <c r="B48" s="298" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C48" s="299">
         <v>0</v>
@@ -25829,7 +25833,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I48" s="298"/>
     </row>
@@ -25855,14 +25859,14 @@
         <v>0</v>
       </c>
       <c r="H49" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I49" s="298"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A50" s="298"/>
       <c r="B50" s="298" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C50" s="299">
         <v>0</v>
@@ -25881,7 +25885,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I50" s="298"/>
     </row>
@@ -25955,7 +25959,7 @@
       </c>
       <c r="C2" s="143" t="str">
         <f>Admin!L2</f>
-        <v>2024-25</v>
+        <v>2025-26</v>
       </c>
       <c r="D2" s="406" t="s">
         <v>16</v>
@@ -26004,7 +26008,7 @@
       </c>
       <c r="C6" s="108" t="str">
         <f>C2</f>
-        <v>2024-25</v>
+        <v>2025-26</v>
       </c>
       <c r="D6" s="100"/>
       <c r="E6" s="120">
@@ -26120,7 +26124,7 @@
       </c>
       <c r="C13" s="419">
         <f>Admin!B21</f>
-        <v>46053</v>
+        <v>46418</v>
       </c>
       <c r="D13" s="420"/>
       <c r="E13" s="99"/>
@@ -26268,7 +26272,7 @@
       </c>
       <c r="C25" s="153" t="str">
         <f>Admin!B24</f>
-        <v>2025-26</v>
+        <v>2026-27</v>
       </c>
       <c r="D25" s="110" t="s">
         <v>3</v>
@@ -26288,7 +26292,7 @@
       <c r="C26" s="108"/>
       <c r="D26" s="111">
         <f>Admin!B21</f>
-        <v>46053</v>
+        <v>46418</v>
       </c>
       <c r="E26" s="291">
         <f>E25/2</f>
@@ -26305,7 +26309,7 @@
       <c r="C27" s="108"/>
       <c r="D27" s="111">
         <f>Admin!B22</f>
-        <v>46234</v>
+        <v>46599</v>
       </c>
       <c r="E27" s="291">
         <f>E25/2</f>
@@ -26514,7 +26518,7 @@
       <c r="A4" s="20"/>
       <c r="B4" s="21">
         <f>Admin!B5</f>
-        <v>45412</v>
+        <v>45777</v>
       </c>
       <c r="C4" s="22">
         <f>[6]Apr!$M$1</f>
@@ -26554,7 +26558,7 @@
       <c r="A5" s="20"/>
       <c r="B5" s="21">
         <f>Admin!B6</f>
-        <v>45443</v>
+        <v>45808</v>
       </c>
       <c r="C5" s="22">
         <f>[6]May!$M$1</f>
@@ -26592,7 +26596,7 @@
       <c r="A6" s="20"/>
       <c r="B6" s="21">
         <f>Admin!B7</f>
-        <v>45473</v>
+        <v>45838</v>
       </c>
       <c r="C6" s="22">
         <f>[6]Jun!$M$1</f>
@@ -26630,7 +26634,7 @@
       <c r="A7" s="20"/>
       <c r="B7" s="21">
         <f>Admin!B8</f>
-        <v>45504</v>
+        <v>45869</v>
       </c>
       <c r="C7" s="22">
         <f>[6]Jul!$M$1</f>
@@ -26668,7 +26672,7 @@
       <c r="A8" s="20"/>
       <c r="B8" s="21">
         <f>Admin!B9</f>
-        <v>45535</v>
+        <v>45900</v>
       </c>
       <c r="C8" s="22">
         <f>[6]Aug!$M$1</f>
@@ -26708,7 +26712,7 @@
       <c r="A9" s="20"/>
       <c r="B9" s="21">
         <f>Admin!B10</f>
-        <v>45565</v>
+        <v>45930</v>
       </c>
       <c r="C9" s="22">
         <f>[6]Sep!$M$1</f>
@@ -26746,7 +26750,7 @@
       <c r="A10" s="20"/>
       <c r="B10" s="21">
         <f>Admin!B11</f>
-        <v>45596</v>
+        <v>45961</v>
       </c>
       <c r="C10" s="22">
         <f>[6]Oct!$M$1</f>
@@ -26784,7 +26788,7 @@
       <c r="A11" s="20"/>
       <c r="B11" s="21">
         <f>Admin!B12</f>
-        <v>45626</v>
+        <v>45991</v>
       </c>
       <c r="C11" s="22">
         <f>[6]Nov!$M$1</f>
@@ -26822,7 +26826,7 @@
       <c r="A12" s="20"/>
       <c r="B12" s="21">
         <f>Admin!B13</f>
-        <v>45657</v>
+        <v>46022</v>
       </c>
       <c r="C12" s="22">
         <f>[6]Dec!$M$1</f>
@@ -26860,7 +26864,7 @@
       <c r="A13" s="20"/>
       <c r="B13" s="21">
         <f>Admin!B14</f>
-        <v>45688</v>
+        <v>46053</v>
       </c>
       <c r="C13" s="22">
         <f>[6]Jan!$M$1</f>
@@ -26898,7 +26902,7 @@
       <c r="A14" s="20"/>
       <c r="B14" s="21">
         <f>Admin!B15</f>
-        <v>45716</v>
+        <v>46081</v>
       </c>
       <c r="C14" s="22">
         <f>[6]Feb!$M$1</f>
@@ -26936,7 +26940,7 @@
       <c r="A15" s="20"/>
       <c r="B15" s="21">
         <f>Admin!B16</f>
-        <v>45747</v>
+        <v>46112</v>
       </c>
       <c r="C15" s="22">
         <f>[6]Mar!$M$1</f>
@@ -27046,29 +27050,29 @@
       <c r="E1" s="32"/>
       <c r="F1" s="32"/>
       <c r="G1" s="32"/>
-      <c r="H1" s="435" t="s">
+      <c r="H1" s="428" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="436"/>
-      <c r="J1" s="436"/>
-      <c r="K1" s="436"/>
-      <c r="L1" s="437"/>
+      <c r="I1" s="429"/>
+      <c r="J1" s="429"/>
+      <c r="K1" s="429"/>
+      <c r="L1" s="430"/>
       <c r="M1" s="32"/>
-      <c r="N1" s="435" t="s">
+      <c r="N1" s="428" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="436"/>
-      <c r="P1" s="436"/>
-      <c r="Q1" s="436"/>
-      <c r="R1" s="437"/>
+      <c r="O1" s="429"/>
+      <c r="P1" s="429"/>
+      <c r="Q1" s="429"/>
+      <c r="R1" s="430"/>
       <c r="S1" s="32"/>
-      <c r="T1" s="435" t="s">
+      <c r="T1" s="428" t="s">
         <v>31</v>
       </c>
-      <c r="U1" s="436"/>
-      <c r="V1" s="436"/>
-      <c r="W1" s="436"/>
-      <c r="X1" s="437"/>
+      <c r="U1" s="429"/>
+      <c r="V1" s="429"/>
+      <c r="W1" s="429"/>
+      <c r="X1" s="430"/>
       <c r="Y1" s="33"/>
       <c r="Z1" s="32"/>
       <c r="AA1" s="32"/>
@@ -27138,12 +27142,12 @@
         <v>43</v>
       </c>
       <c r="AC2" s="44"/>
-      <c r="AD2" s="438" t="s">
+      <c r="AD2" s="431" t="s">
         <v>44</v>
       </c>
-      <c r="AE2" s="439"/>
-      <c r="AF2" s="439"/>
-      <c r="AG2" s="440"/>
+      <c r="AE2" s="432"/>
+      <c r="AF2" s="432"/>
+      <c r="AG2" s="433"/>
       <c r="AH2" s="44"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.15">
@@ -27176,23 +27180,23 @@
       <c r="AA3" s="48"/>
       <c r="AB3" s="48"/>
       <c r="AC3" s="24"/>
-      <c r="AD3" s="428" t="s">
+      <c r="AD3" s="434" t="s">
         <v>404</v>
       </c>
-      <c r="AE3" s="431"/>
-      <c r="AF3" s="431"/>
-      <c r="AG3" s="431"/>
+      <c r="AE3" s="437"/>
+      <c r="AF3" s="437"/>
+      <c r="AG3" s="437"/>
       <c r="AH3" s="24"/>
     </row>
     <row r="4" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A4" s="20"/>
-      <c r="B4" s="432" t="s">
+      <c r="B4" s="438" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="433"/>
-      <c r="D4" s="433"/>
-      <c r="E4" s="434"/>
-      <c r="F4" s="434"/>
+      <c r="C4" s="439"/>
+      <c r="D4" s="439"/>
+      <c r="E4" s="440"/>
+      <c r="F4" s="440"/>
       <c r="G4" s="48"/>
       <c r="H4" s="52">
         <v>0</v>
@@ -27222,10 +27226,10 @@
       <c r="AA4" s="48"/>
       <c r="AB4" s="48"/>
       <c r="AC4" s="24"/>
-      <c r="AD4" s="430"/>
-      <c r="AE4" s="431"/>
-      <c r="AF4" s="431"/>
-      <c r="AG4" s="431"/>
+      <c r="AD4" s="436"/>
+      <c r="AE4" s="437"/>
+      <c r="AF4" s="437"/>
+      <c r="AG4" s="437"/>
       <c r="AH4" s="24"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.15">
@@ -27258,17 +27262,17 @@
       <c r="AA5" s="54"/>
       <c r="AB5" s="54"/>
       <c r="AC5" s="24"/>
-      <c r="AD5" s="430"/>
-      <c r="AE5" s="431"/>
-      <c r="AF5" s="431"/>
-      <c r="AG5" s="431"/>
+      <c r="AD5" s="436"/>
+      <c r="AE5" s="437"/>
+      <c r="AF5" s="437"/>
+      <c r="AG5" s="437"/>
       <c r="AH5" s="24"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A6" s="20"/>
       <c r="B6" s="58">
         <f>Admin!B4</f>
-        <v>45388</v>
+        <v>45753</v>
       </c>
       <c r="C6" s="59"/>
       <c r="D6" s="60">
@@ -27300,10 +27304,10 @@
       <c r="AA6" s="54"/>
       <c r="AB6" s="62"/>
       <c r="AC6" s="24"/>
-      <c r="AD6" s="430"/>
-      <c r="AE6" s="431"/>
-      <c r="AF6" s="431"/>
-      <c r="AG6" s="431"/>
+      <c r="AD6" s="436"/>
+      <c r="AE6" s="437"/>
+      <c r="AF6" s="437"/>
+      <c r="AG6" s="437"/>
       <c r="AH6" s="24"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.15">
@@ -27336,17 +27340,17 @@
       <c r="AA7" s="54"/>
       <c r="AB7" s="54"/>
       <c r="AC7" s="24"/>
-      <c r="AD7" s="430"/>
-      <c r="AE7" s="431"/>
-      <c r="AF7" s="431"/>
-      <c r="AG7" s="431"/>
+      <c r="AD7" s="436"/>
+      <c r="AE7" s="437"/>
+      <c r="AF7" s="437"/>
+      <c r="AG7" s="437"/>
       <c r="AH7" s="24"/>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A8" s="20"/>
       <c r="B8" s="58">
         <f>Admin!B5</f>
-        <v>45412</v>
+        <v>45777</v>
       </c>
       <c r="C8" s="59"/>
       <c r="D8" s="60">
@@ -27414,10 +27418,10 @@
         <v>0</v>
       </c>
       <c r="AC8" s="24"/>
-      <c r="AD8" s="430"/>
-      <c r="AE8" s="431"/>
-      <c r="AF8" s="431"/>
-      <c r="AG8" s="431"/>
+      <c r="AD8" s="436"/>
+      <c r="AE8" s="437"/>
+      <c r="AF8" s="437"/>
+      <c r="AG8" s="437"/>
       <c r="AH8" s="24"/>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.15">
@@ -27450,17 +27454,17 @@
       <c r="AA9" s="54"/>
       <c r="AB9" s="54"/>
       <c r="AC9" s="24"/>
-      <c r="AD9" s="430"/>
-      <c r="AE9" s="431"/>
-      <c r="AF9" s="431"/>
-      <c r="AG9" s="431"/>
+      <c r="AD9" s="436"/>
+      <c r="AE9" s="437"/>
+      <c r="AF9" s="437"/>
+      <c r="AG9" s="437"/>
       <c r="AH9" s="24"/>
     </row>
     <row r="10" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="20"/>
       <c r="B10" s="58">
         <f>Admin!B6</f>
-        <v>45443</v>
+        <v>45808</v>
       </c>
       <c r="C10" s="59"/>
       <c r="D10" s="60">
@@ -27564,19 +27568,19 @@
       <c r="AA11" s="54"/>
       <c r="AB11" s="54"/>
       <c r="AC11" s="24"/>
-      <c r="AD11" s="428" t="s">
+      <c r="AD11" s="434" t="s">
         <v>46</v>
       </c>
-      <c r="AE11" s="431"/>
-      <c r="AF11" s="431"/>
-      <c r="AG11" s="431"/>
+      <c r="AE11" s="437"/>
+      <c r="AF11" s="437"/>
+      <c r="AG11" s="437"/>
       <c r="AH11" s="24"/>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A12" s="20"/>
       <c r="B12" s="58">
         <f>Admin!B7</f>
-        <v>45473</v>
+        <v>45838</v>
       </c>
       <c r="C12" s="59"/>
       <c r="D12" s="60">
@@ -27644,10 +27648,10 @@
         <v>0</v>
       </c>
       <c r="AC12" s="24"/>
-      <c r="AD12" s="430"/>
-      <c r="AE12" s="431"/>
-      <c r="AF12" s="431"/>
-      <c r="AG12" s="431"/>
+      <c r="AD12" s="436"/>
+      <c r="AE12" s="437"/>
+      <c r="AF12" s="437"/>
+      <c r="AG12" s="437"/>
       <c r="AH12" s="24"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.15">
@@ -27680,17 +27684,17 @@
       <c r="AA13" s="54"/>
       <c r="AB13" s="54"/>
       <c r="AC13" s="24"/>
-      <c r="AD13" s="430"/>
-      <c r="AE13" s="431"/>
-      <c r="AF13" s="431"/>
-      <c r="AG13" s="431"/>
+      <c r="AD13" s="436"/>
+      <c r="AE13" s="437"/>
+      <c r="AF13" s="437"/>
+      <c r="AG13" s="437"/>
       <c r="AH13" s="24"/>
     </row>
     <row r="14" spans="1:34" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="20"/>
       <c r="B14" s="58">
         <f>Admin!B8</f>
-        <v>45504</v>
+        <v>45869</v>
       </c>
       <c r="C14" s="59"/>
       <c r="D14" s="60">
@@ -27794,19 +27798,19 @@
       <c r="AA15" s="54"/>
       <c r="AB15" s="54"/>
       <c r="AC15" s="24"/>
-      <c r="AD15" s="428" t="s">
+      <c r="AD15" s="434" t="s">
         <v>405</v>
       </c>
-      <c r="AE15" s="429"/>
-      <c r="AF15" s="429"/>
-      <c r="AG15" s="429"/>
+      <c r="AE15" s="435"/>
+      <c r="AF15" s="435"/>
+      <c r="AG15" s="435"/>
       <c r="AH15" s="24"/>
     </row>
     <row r="16" spans="1:34" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="20"/>
       <c r="B16" s="58">
         <f>Admin!B9</f>
-        <v>45535</v>
+        <v>45900</v>
       </c>
       <c r="C16" s="59"/>
       <c r="D16" s="60">
@@ -27874,10 +27878,10 @@
         <v>0</v>
       </c>
       <c r="AC16" s="24"/>
-      <c r="AD16" s="428"/>
-      <c r="AE16" s="429"/>
-      <c r="AF16" s="429"/>
-      <c r="AG16" s="429"/>
+      <c r="AD16" s="434"/>
+      <c r="AE16" s="435"/>
+      <c r="AF16" s="435"/>
+      <c r="AG16" s="435"/>
       <c r="AH16" s="24"/>
     </row>
     <row r="17" spans="1:34" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -27910,17 +27914,17 @@
       <c r="AA17" s="54"/>
       <c r="AB17" s="54"/>
       <c r="AC17" s="24"/>
-      <c r="AD17" s="428"/>
-      <c r="AE17" s="429"/>
-      <c r="AF17" s="429"/>
-      <c r="AG17" s="429"/>
+      <c r="AD17" s="434"/>
+      <c r="AE17" s="435"/>
+      <c r="AF17" s="435"/>
+      <c r="AG17" s="435"/>
       <c r="AH17" s="24"/>
     </row>
     <row r="18" spans="1:34" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="20"/>
       <c r="B18" s="58">
         <f>Admin!B10</f>
-        <v>45565</v>
+        <v>45930</v>
       </c>
       <c r="C18" s="59"/>
       <c r="D18" s="60">
@@ -28024,19 +28028,19 @@
       <c r="AA19" s="54"/>
       <c r="AB19" s="54"/>
       <c r="AC19" s="24"/>
-      <c r="AD19" s="428" t="s">
+      <c r="AD19" s="434" t="s">
         <v>47</v>
       </c>
-      <c r="AE19" s="429"/>
-      <c r="AF19" s="429"/>
-      <c r="AG19" s="429"/>
+      <c r="AE19" s="435"/>
+      <c r="AF19" s="435"/>
+      <c r="AG19" s="435"/>
       <c r="AH19" s="24"/>
     </row>
     <row r="20" spans="1:34" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="20"/>
       <c r="B20" s="58">
         <f>Admin!B11</f>
-        <v>45596</v>
+        <v>45961</v>
       </c>
       <c r="C20" s="59"/>
       <c r="D20" s="60">
@@ -28104,10 +28108,10 @@
         <v>0</v>
       </c>
       <c r="AC20" s="24"/>
-      <c r="AD20" s="428"/>
-      <c r="AE20" s="429"/>
-      <c r="AF20" s="429"/>
-      <c r="AG20" s="429"/>
+      <c r="AD20" s="434"/>
+      <c r="AE20" s="435"/>
+      <c r="AF20" s="435"/>
+      <c r="AG20" s="435"/>
       <c r="AH20" s="24"/>
     </row>
     <row r="21" spans="1:34" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -28140,17 +28144,17 @@
       <c r="AA21" s="54"/>
       <c r="AB21" s="54"/>
       <c r="AC21" s="24"/>
-      <c r="AD21" s="428"/>
-      <c r="AE21" s="429"/>
-      <c r="AF21" s="429"/>
-      <c r="AG21" s="429"/>
+      <c r="AD21" s="434"/>
+      <c r="AE21" s="435"/>
+      <c r="AF21" s="435"/>
+      <c r="AG21" s="435"/>
       <c r="AH21" s="24"/>
     </row>
     <row r="22" spans="1:34" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="20"/>
       <c r="B22" s="58">
         <f>Admin!B12</f>
-        <v>45626</v>
+        <v>45991</v>
       </c>
       <c r="C22" s="59"/>
       <c r="D22" s="60">
@@ -28254,19 +28258,19 @@
       <c r="AA23" s="54"/>
       <c r="AB23" s="54"/>
       <c r="AC23" s="24"/>
-      <c r="AD23" s="428" t="s">
+      <c r="AD23" s="434" t="s">
         <v>48</v>
       </c>
-      <c r="AE23" s="429"/>
-      <c r="AF23" s="429"/>
-      <c r="AG23" s="429"/>
+      <c r="AE23" s="435"/>
+      <c r="AF23" s="435"/>
+      <c r="AG23" s="435"/>
       <c r="AH23" s="24"/>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A24" s="20"/>
       <c r="B24" s="58">
         <f>Admin!B13</f>
-        <v>45657</v>
+        <v>46022</v>
       </c>
       <c r="C24" s="59"/>
       <c r="D24" s="60">
@@ -28334,10 +28338,10 @@
         <v>0</v>
       </c>
       <c r="AC24" s="24"/>
-      <c r="AD24" s="428"/>
-      <c r="AE24" s="429"/>
-      <c r="AF24" s="429"/>
-      <c r="AG24" s="429"/>
+      <c r="AD24" s="434"/>
+      <c r="AE24" s="435"/>
+      <c r="AF24" s="435"/>
+      <c r="AG24" s="435"/>
       <c r="AH24" s="24"/>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.15">
@@ -28370,17 +28374,17 @@
       <c r="AA25" s="54"/>
       <c r="AB25" s="54"/>
       <c r="AC25" s="24"/>
-      <c r="AD25" s="428"/>
-      <c r="AE25" s="429"/>
-      <c r="AF25" s="429"/>
-      <c r="AG25" s="429"/>
+      <c r="AD25" s="434"/>
+      <c r="AE25" s="435"/>
+      <c r="AF25" s="435"/>
+      <c r="AG25" s="435"/>
       <c r="AH25" s="24"/>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A26" s="20"/>
       <c r="B26" s="58">
         <f>Admin!B14</f>
-        <v>45688</v>
+        <v>46053</v>
       </c>
       <c r="C26" s="59"/>
       <c r="D26" s="60">
@@ -28448,10 +28452,10 @@
         <v>0</v>
       </c>
       <c r="AC26" s="24"/>
-      <c r="AD26" s="430"/>
-      <c r="AE26" s="431"/>
-      <c r="AF26" s="431"/>
-      <c r="AG26" s="431"/>
+      <c r="AD26" s="436"/>
+      <c r="AE26" s="437"/>
+      <c r="AF26" s="437"/>
+      <c r="AG26" s="437"/>
       <c r="AH26" s="24"/>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.15">
@@ -28494,7 +28498,7 @@
       <c r="A28" s="20"/>
       <c r="B28" s="58">
         <f>Admin!B15</f>
-        <v>45716</v>
+        <v>46081</v>
       </c>
       <c r="C28" s="59"/>
       <c r="D28" s="60">
@@ -28562,12 +28566,12 @@
         <v>0</v>
       </c>
       <c r="AC28" s="24"/>
-      <c r="AD28" s="428" t="s">
+      <c r="AD28" s="434" t="s">
         <v>49</v>
       </c>
-      <c r="AE28" s="429"/>
-      <c r="AF28" s="429"/>
-      <c r="AG28" s="429"/>
+      <c r="AE28" s="435"/>
+      <c r="AF28" s="435"/>
+      <c r="AG28" s="435"/>
       <c r="AH28" s="24"/>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.15">
@@ -28600,17 +28604,17 @@
       <c r="AA29" s="54"/>
       <c r="AB29" s="54"/>
       <c r="AC29" s="24"/>
-      <c r="AD29" s="428"/>
-      <c r="AE29" s="429"/>
-      <c r="AF29" s="429"/>
-      <c r="AG29" s="429"/>
+      <c r="AD29" s="434"/>
+      <c r="AE29" s="435"/>
+      <c r="AF29" s="435"/>
+      <c r="AG29" s="435"/>
       <c r="AH29" s="24"/>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A30" s="20"/>
       <c r="B30" s="58">
         <f>Admin!B17</f>
-        <v>45752</v>
+        <v>46117</v>
       </c>
       <c r="C30" s="59"/>
       <c r="D30" s="60">
@@ -28678,10 +28682,10 @@
         <v>0</v>
       </c>
       <c r="AC30" s="24"/>
-      <c r="AD30" s="430"/>
-      <c r="AE30" s="431"/>
-      <c r="AF30" s="431"/>
-      <c r="AG30" s="431"/>
+      <c r="AD30" s="436"/>
+      <c r="AE30" s="437"/>
+      <c r="AF30" s="437"/>
+      <c r="AG30" s="437"/>
       <c r="AH30" s="24"/>
     </row>
     <row r="31" spans="1:34" ht="13" thickBot="1" x14ac:dyDescent="0.2">
@@ -28722,17 +28726,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="N1:R1"/>
-    <mergeCell ref="T1:X1"/>
-    <mergeCell ref="AD2:AG2"/>
-    <mergeCell ref="AD19:AG21"/>
     <mergeCell ref="AD28:AG30"/>
     <mergeCell ref="AD3:AG9"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="AD11:AG13"/>
     <mergeCell ref="AD15:AG17"/>
     <mergeCell ref="AD23:AG26"/>
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="T1:X1"/>
+    <mergeCell ref="AD2:AG2"/>
+    <mergeCell ref="AD19:AG21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28776,7 +28780,7 @@
     </row>
     <row r="2" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="23"/>
-      <c r="B2" s="447" t="s">
+      <c r="B2" s="441" t="s">
         <v>143</v>
       </c>
       <c r="C2" s="157" t="s">
@@ -28784,60 +28788,60 @@
       </c>
       <c r="D2" s="401">
         <f>Admin!B5</f>
-        <v>45412</v>
+        <v>45777</v>
       </c>
       <c r="E2" s="400">
         <f>Admin!B6</f>
-        <v>45443</v>
+        <v>45808</v>
       </c>
       <c r="F2" s="400">
         <f>Admin!B7</f>
-        <v>45473</v>
+        <v>45838</v>
       </c>
       <c r="G2" s="400">
         <f>Admin!B8</f>
-        <v>45504</v>
+        <v>45869</v>
       </c>
       <c r="H2" s="400">
         <f>Admin!B9</f>
-        <v>45535</v>
+        <v>45900</v>
       </c>
       <c r="I2" s="400">
         <f>Admin!B10</f>
-        <v>45565</v>
+        <v>45930</v>
       </c>
       <c r="J2" s="400">
         <f>Admin!B11</f>
-        <v>45596</v>
+        <v>45961</v>
       </c>
       <c r="K2" s="400">
         <f>Admin!B12</f>
-        <v>45626</v>
+        <v>45991</v>
       </c>
       <c r="L2" s="400">
         <f>Admin!B13</f>
-        <v>45657</v>
+        <v>46022</v>
       </c>
       <c r="M2" s="400">
         <f>Admin!B14</f>
-        <v>45688</v>
+        <v>46053</v>
       </c>
       <c r="N2" s="400">
         <f>Admin!B15</f>
-        <v>45716</v>
+        <v>46081</v>
       </c>
       <c r="O2" s="400">
         <f>Admin!B16</f>
-        <v>45747</v>
+        <v>46112</v>
       </c>
       <c r="P2" s="23"/>
     </row>
     <row r="3" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="23"/>
-      <c r="B3" s="448"/>
+      <c r="B3" s="442"/>
       <c r="C3" s="158">
         <f>Admin!B$17</f>
-        <v>45752</v>
+        <v>46117</v>
       </c>
       <c r="D3" s="402"/>
       <c r="E3" s="400"/>
@@ -28855,7 +28859,7 @@
     </row>
     <row r="4" spans="1:16" ht="13" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="23"/>
-      <c r="B4" s="446"/>
+      <c r="B4" s="443"/>
       <c r="C4" s="156" t="s">
         <v>51</v>
       </c>
@@ -29487,51 +29491,51 @@
       </c>
       <c r="D19" s="401">
         <f t="shared" ref="D19:O19" si="3">D2</f>
-        <v>45412</v>
+        <v>45777</v>
       </c>
       <c r="E19" s="401">
         <f t="shared" si="3"/>
-        <v>45443</v>
+        <v>45808</v>
       </c>
       <c r="F19" s="401">
         <f t="shared" si="3"/>
-        <v>45473</v>
+        <v>45838</v>
       </c>
       <c r="G19" s="401">
         <f t="shared" si="3"/>
-        <v>45504</v>
+        <v>45869</v>
       </c>
       <c r="H19" s="401">
         <f t="shared" si="3"/>
-        <v>45535</v>
+        <v>45900</v>
       </c>
       <c r="I19" s="401">
         <f t="shared" si="3"/>
-        <v>45565</v>
+        <v>45930</v>
       </c>
       <c r="J19" s="401">
         <f t="shared" si="3"/>
-        <v>45596</v>
+        <v>45961</v>
       </c>
       <c r="K19" s="401">
         <f t="shared" si="3"/>
-        <v>45626</v>
+        <v>45991</v>
       </c>
       <c r="L19" s="401">
         <f t="shared" si="3"/>
-        <v>45657</v>
+        <v>46022</v>
       </c>
       <c r="M19" s="401">
         <f t="shared" si="3"/>
-        <v>45688</v>
+        <v>46053</v>
       </c>
       <c r="N19" s="401">
         <f t="shared" si="3"/>
-        <v>45716</v>
+        <v>46081</v>
       </c>
       <c r="O19" s="401">
         <f t="shared" si="3"/>
-        <v>45747</v>
+        <v>46112</v>
       </c>
       <c r="P19" s="23"/>
     </row>
@@ -29540,25 +29544,25 @@
       <c r="B20" s="445"/>
       <c r="C20" s="158">
         <f>Admin!B$17</f>
-        <v>45752</v>
-      </c>
-      <c r="D20" s="441"/>
-      <c r="E20" s="441"/>
-      <c r="F20" s="441"/>
-      <c r="G20" s="441"/>
-      <c r="H20" s="441"/>
-      <c r="I20" s="441"/>
-      <c r="J20" s="441"/>
-      <c r="K20" s="441"/>
-      <c r="L20" s="441"/>
-      <c r="M20" s="441"/>
-      <c r="N20" s="441"/>
-      <c r="O20" s="441"/>
+        <v>46117</v>
+      </c>
+      <c r="D20" s="446"/>
+      <c r="E20" s="446"/>
+      <c r="F20" s="446"/>
+      <c r="G20" s="446"/>
+      <c r="H20" s="446"/>
+      <c r="I20" s="446"/>
+      <c r="J20" s="446"/>
+      <c r="K20" s="446"/>
+      <c r="L20" s="446"/>
+      <c r="M20" s="446"/>
+      <c r="N20" s="446"/>
+      <c r="O20" s="446"/>
       <c r="P20" s="23"/>
     </row>
     <row r="21" spans="1:16" ht="13" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="23"/>
-      <c r="B21" s="446"/>
+      <c r="B21" s="443"/>
       <c r="C21" s="129">
         <f>SUM(D21:O21)</f>
         <v>0</v>
@@ -30195,10 +30199,10 @@
     </row>
     <row r="36" spans="1:16" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="23"/>
-      <c r="B36" s="442" t="s">
+      <c r="B36" s="447" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="443"/>
+      <c r="C36" s="448"/>
       <c r="D36" s="23"/>
       <c r="E36" s="23"/>
       <c r="F36" s="23"/>
@@ -30458,12 +30462,11 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="L19:L20"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="D19:D20"/>
@@ -30480,11 +30483,12 @@
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -8219,13 +8219,21 @@
         <v>0.18</v>
       </c>
       <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
+      <c r="I5" s="450" t="inlineStr">
+        <is>
+          <t>Personal allowance taper threshold</t>
+        </is>
+      </c>
       <c r="J5" s="147"/>
       <c r="K5" s="147"/>
       <c r="L5" s="147"/>
       <c r="M5" s="147"/>
-      <c r="N5" s="146"/>
-      <c r="O5" s="146"/>
+      <c r="N5" s="152">
+        <v>100000</v>
+      </c>
+      <c r="O5" s="146" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="6" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="147"/>
@@ -8298,13 +8306,21 @@
         <v>3000</v>
       </c>
       <c r="H8" s="147"/>
-      <c r="I8" s="147"/>
+      <c r="I8" s="450" t="inlineStr">
+        <is>
+          <t>Additional rate applicable above the higher rate limit</t>
+        </is>
+      </c>
       <c r="J8" s="147"/>
       <c r="K8" s="147"/>
       <c r="L8" s="147"/>
       <c r="M8" s="147"/>
-      <c r="N8" s="146"/>
-      <c r="O8" s="146"/>
+      <c r="N8" s="148">
+        <v>0.45</v>
+      </c>
+      <c r="O8" s="146" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="9" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="147"/>
@@ -8402,7 +8418,7 @@
       </c>
       <c r="J12" s="147"/>
       <c r="K12" s="151">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L12" s="146">
         <v>37701</v>
@@ -8428,12 +8444,22 @@
         <v>0</v>
       </c>
       <c r="H13" s="147"/>
-      <c r="I13" s="147"/>
+      <c r="I13" s="147" t="inlineStr">
+        <is>
+          <t>Additional rate</t>
+        </is>
+      </c>
       <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="147"/>
+      <c r="K13" s="151">
+        <v>0.45</v>
+      </c>
+      <c r="L13" s="146">
+        <v>125141</v>
+      </c>
       <c r="M13" s="147"/>
-      <c r="N13" s="147"/>
+      <c r="N13" s="152">
+        <v>125140</v>
+      </c>
       <c r="O13" s="147"/>
     </row>
     <row r="14" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -8793,7 +8819,9 @@
       <c r="O28" s="147"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="28">
+    <mergeCell ref="I5:M5"/>
+    <mergeCell ref="I8:M8"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="I4:M4"/>
     <mergeCell ref="I6:M6"/>
@@ -26012,7 +26040,7 @@
       </c>
       <c r="D6" s="100"/>
       <c r="E6" s="120">
-        <f>IF((E5&gt;0),Admin!N$4,0)</f>
+        <f>IF(E5&lt;=0,0,MAX(0,Admin!N$4-MAX(0,E5-Admin!N$5)/2))</f>
         <v>0</v>
       </c>
       <c r="F6" s="122"/>
@@ -26056,21 +26084,21 @@
       <c r="H8" s="137"/>
       <c r="M8" s="293"/>
     </row>
-    <row r="9" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="96"/>
       <c r="B9" s="108" t="s">
         <v>128</v>
       </c>
       <c r="C9" s="108">
-        <f>Admin!N$12</f>
-        <v>37701</v>
+        <f>Admin!M$11</f>
+        <v>37700</v>
       </c>
       <c r="D9" s="144">
         <f>Admin!N$7</f>
         <v>0.4</v>
       </c>
       <c r="E9" s="99">
-        <f>IF((E7&gt;C9),((E7-C9)*D9),0)</f>
+        <f>IF(E7&gt;C9,(MIN(E7,C10)-C9)*D9,0)</f>
         <v>0</v>
       </c>
       <c r="F9" s="122"/>
@@ -26079,28 +26107,36 @@
     </row>
     <row r="10" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="96"/>
-      <c r="B10" s="114" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="139"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="292">
-        <f>SUM(E8:E9)</f>
+      <c r="B10" s="108" t="inlineStr">
+        <is>
+          <t>Income Tax third band</t>
+        </is>
+      </c>
+      <c r="C10" s="108">
+        <f>Admin!N$13</f>
+        <v>125140</v>
+      </c>
+      <c r="D10" s="144">
+        <f>Admin!N$8</f>
+        <v>0.45</v>
+      </c>
+      <c r="E10" s="99">
+        <f>IF(E7&gt;C10,(E7-C10)*D10,0)</f>
         <v>0</v>
       </c>
       <c r="F10" s="122"/>
       <c r="G10" s="120"/>
       <c r="M10" s="293"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="96"/>
-      <c r="B11" s="108" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="108"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="99">
-        <f>-[2]Mar!$X$1</f>
+      <c r="B11" s="114" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="139"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="292">
+        <f>SUM(E8:E10)</f>
         <v>0</v>
       </c>
       <c r="F11" s="123"/>
@@ -26109,10 +26145,15 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="96"/>
-      <c r="B12" s="108"/>
+      <c r="B12" s="108" t="s">
+        <v>4</v>
+      </c>
       <c r="C12" s="108"/>
       <c r="D12" s="101"/>
-      <c r="E12" s="99"/>
+      <c r="E12" s="99">
+        <f>-[2]Mar!$X$1</f>
+        <v>0</v>
+      </c>
       <c r="F12" s="123"/>
       <c r="G12" s="121"/>
       <c r="M12" s="293"/>
@@ -26196,7 +26237,7 @@
       <c r="C18" s="422"/>
       <c r="D18" s="103"/>
       <c r="E18" s="292">
-        <f>SUM(E10:E17)</f>
+        <f>SUM(E11:E17)</f>
         <v>0</v>
       </c>
       <c r="F18" s="122"/>

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -8744,7 +8744,9 @@
     </row>
     <row r="25" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="147"/>
-      <c r="B25" s="171"/>
+      <c r="B25" s="164">
+        <v>45869</v>
+      </c>
       <c r="C25" s="147"/>
       <c r="D25" s="147"/>
       <c r="E25" s="147"/>

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -30335,7 +30335,7 @@
         <v>89</v>
       </c>
       <c r="C40" s="128">
-        <f>Admin!N$4</f>
+        <f>IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
         <v>12570</v>
       </c>
       <c r="D40" s="23"/>
@@ -30381,7 +30381,7 @@
         <v>91</v>
       </c>
       <c r="C42" s="128">
-        <f>IF((C41&gt;0),(IF((C41&lt;Admin!N$12),C41*Admin!N$6,Admin!N$12*Admin!N$6)),0)</f>
+        <f>IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
         <v>0</v>
       </c>
       <c r="D42" s="138"/>
@@ -30404,7 +30404,7 @@
         <v>92</v>
       </c>
       <c r="C43" s="128">
-        <f>IF((C41&gt;Admin!N$12),((C41-Admin!N$12)*Admin!N$7),0)</f>
+        <f>IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
         <v>0</v>
       </c>
       <c r="D43" s="23"/>
@@ -30423,11 +30423,13 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A44" s="23"/>
-      <c r="B44" s="87" t="s">
-        <v>93</v>
+      <c r="B44" s="87" t="inlineStr">
+        <is>
+          <t>Tax at additional rate</t>
+        </is>
       </c>
       <c r="C44" s="128">
-        <f>IF((C41&gt;0),IF(C41&gt;Admin!N12,Admin!N12*Admin!L20+(C41-Admin!N12)*Admin!L23,C41*Admin!L$20),0)</f>
+        <f>IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
         <v>0</v>
       </c>
       <c r="D44" s="23"/>
@@ -30444,10 +30446,15 @@
       <c r="O44" s="23"/>
       <c r="P44" s="23"/>
     </row>
-    <row r="45" spans="1:16" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A45" s="23"/>
-      <c r="B45" s="87"/>
-      <c r="C45" s="128"/>
+      <c r="B45" s="87" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="128">
+        <f>IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
+        <v>0</v>
+      </c>
       <c r="D45" s="23"/>
       <c r="E45" s="23"/>
       <c r="F45" s="23"/>
@@ -30468,7 +30475,7 @@
         <v>94</v>
       </c>
       <c r="C46" s="131">
-        <f>C42+C43+C44</f>
+        <f>C42+C43+C44+C45</f>
         <v>0</v>
       </c>
       <c r="D46" s="23"/>

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -8293,18 +8293,10 @@
         <v>45504</v>
       </c>
       <c r="C8" s="147"/>
-      <c r="D8" s="147" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="152">
-        <v>12000</v>
-      </c>
-      <c r="F8" s="147" t="s">
-        <v>113</v>
-      </c>
-      <c r="G8" s="152">
-        <v>3000</v>
-      </c>
+      <c r="D8" s="147"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="152"/>
       <c r="H8" s="147"/>
       <c r="I8" s="450" t="inlineStr">
         <is>
@@ -8938,7 +8930,7 @@
       <c r="P2" s="339"/>
       <c r="Q2" s="340">
         <f>Admin!B4</f>
-        <v>45753</v>
+        <v>45388</v>
       </c>
       <c r="R2" s="341"/>
       <c r="S2" s="341"/>
@@ -9364,7 +9356,7 @@
       <c r="R17" s="237"/>
       <c r="S17" s="353">
         <f>Q2</f>
-        <v>45753</v>
+        <v>45388</v>
       </c>
       <c r="T17" s="354"/>
       <c r="U17" s="354"/>
@@ -12788,7 +12780,7 @@
       <c r="P2" s="339"/>
       <c r="Q2" s="340">
         <f>Admin!B4</f>
-        <v>45753</v>
+        <v>45388</v>
       </c>
       <c r="R2" s="341"/>
       <c r="S2" s="341"/>
@@ -12798,7 +12790,7 @@
       </c>
       <c r="V2" s="340">
         <f>Admin!B17</f>
-        <v>46117</v>
+        <v>45752</v>
       </c>
       <c r="W2" s="340"/>
     </row>
@@ -30336,7 +30328,7 @@
       </c>
       <c r="C40" s="128">
         <f>IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
-        <v>12570</v>
+        <v>0</v>
       </c>
       <c r="D40" s="23"/>
       <c r="E40" s="23"/>

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -7447,8 +7447,10 @@
         <v>10</v>
       </c>
       <c r="B36" s="181"/>
-      <c r="C36" s="182" t="s">
-        <v>167</v>
+      <c r="C36" s="182" t="inlineStr">
+        <is>
+          <t>If you used traditional accounting rather than cash basis to</t>
+        </is>
       </c>
       <c r="D36" s="182"/>
       <c r="E36" s="182"/>
@@ -7459,11 +7461,13 @@
       <c r="J36" s="182"/>
       <c r="K36" s="182"/>
       <c r="L36" s="194">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M36" s="181"/>
-      <c r="N36" s="182" t="s">
-        <v>168</v>
+      <c r="N36" s="182" t="inlineStr">
+        <is>
+          <t>If special arrangements apply, put 'X' in the box - read the</t>
+        </is>
       </c>
       <c r="O36" s="182"/>
       <c r="P36" s="182"/>
@@ -7478,8 +7482,10 @@
     <row r="37" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A37" s="185"/>
       <c r="B37" s="181"/>
-      <c r="C37" s="182" t="s">
-        <v>169</v>
+      <c r="C37" s="182" t="inlineStr">
+        <is>
+          <t>calculate your income and expenses, put 'X' in the box</t>
+        </is>
       </c>
       <c r="D37" s="182"/>
       <c r="E37" s="182"/>
@@ -7491,8 +7497,10 @@
       <c r="K37" s="182"/>
       <c r="L37" s="181"/>
       <c r="M37" s="181"/>
-      <c r="N37" s="182" t="s">
-        <v>170</v>
+      <c r="N37" s="182" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
       </c>
       <c r="O37" s="182"/>
       <c r="P37" s="182"/>
@@ -7580,12 +7588,12 @@
       <c r="W40" s="197"/>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A41" s="194">
-        <v>11</v>
-      </c>
+      <c r="A41" s="194"/>
       <c r="B41" s="181"/>
-      <c r="C41" s="182" t="s">
-        <v>171</v>
+      <c r="C41" s="182" t="inlineStr">
+        <is>
+          <t>Boxes 11 and 12 are not in use</t>
+        </is>
       </c>
       <c r="D41" s="182"/>
       <c r="E41" s="182"/>
@@ -7596,7 +7604,7 @@
       <c r="J41" s="182"/>
       <c r="K41" s="182"/>
       <c r="L41" s="194">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M41" s="181"/>
       <c r="N41" s="182" t="str">
@@ -7616,9 +7624,7 @@
     <row r="42" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A42" s="185"/>
       <c r="B42" s="181"/>
-      <c r="C42" s="182" t="s">
-        <v>173</v>
-      </c>
+      <c r="C42" s="182"/>
       <c r="D42" s="182"/>
       <c r="E42" s="182"/>
       <c r="F42" s="182"/>
@@ -7629,8 +7635,10 @@
       <c r="K42" s="182"/>
       <c r="L42" s="181"/>
       <c r="M42" s="181"/>
-      <c r="N42" s="182" t="s">
-        <v>174</v>
+      <c r="N42" s="182" t="inlineStr">
+        <is>
+          <t>profit on last year's Tax Return put 'X' in the box</t>
+        </is>
       </c>
       <c r="O42" s="182"/>
       <c r="P42" s="182"/>
@@ -7656,9 +7664,7 @@
       <c r="K43" s="181"/>
       <c r="L43" s="181"/>
       <c r="M43" s="181"/>
-      <c r="N43" s="182" t="s">
-        <v>170</v>
-      </c>
+      <c r="N43" s="182"/>
       <c r="O43" s="182"/>
       <c r="P43" s="182"/>
       <c r="Q43" s="182"/>
@@ -13107,8 +13113,10 @@
         <v>5</v>
       </c>
       <c r="M14" s="220"/>
-      <c r="N14" s="227" t="s">
-        <v>150</v>
+      <c r="N14" s="227" t="inlineStr">
+        <is>
+          <t>If the details in boxes 1, 2, 3 or 4 have changed in the last 12</t>
+        </is>
       </c>
       <c r="O14" s="227"/>
       <c r="P14" s="227"/>
@@ -13137,8 +13145,10 @@
       <c r="K15" s="220"/>
       <c r="L15" s="220"/>
       <c r="M15" s="220"/>
-      <c r="N15" s="241" t="s">
-        <v>151</v>
+      <c r="N15" s="241" t="inlineStr">
+        <is>
+          <t>months, put 'X' in the box and give details in the 'Any other</t>
+        </is>
       </c>
       <c r="O15" s="227"/>
       <c r="P15" s="227"/>
@@ -13164,8 +13174,10 @@
       <c r="K16" s="220"/>
       <c r="L16" s="220"/>
       <c r="M16" s="220"/>
-      <c r="N16" s="227" t="s">
-        <v>152</v>
+      <c r="N16" s="227" t="inlineStr">
+        <is>
+          <t>information' box</t>
+        </is>
       </c>
       <c r="O16" s="268"/>
       <c r="P16" s="268"/>
@@ -13621,8 +13633,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="220"/>
-      <c r="C32" s="241" t="s">
-        <v>162</v>
+      <c r="C32" s="241" t="inlineStr">
+        <is>
+          <t>Postcode of your business address</t>
+        </is>
       </c>
       <c r="D32" s="227"/>
       <c r="E32" s="227"/>
@@ -13669,8 +13683,10 @@
       <c r="K33" s="220"/>
       <c r="L33" s="220"/>
       <c r="M33" s="220"/>
-      <c r="N33" s="227" t="s">
-        <v>164</v>
+      <c r="N33" s="227" t="inlineStr">
+        <is>
+          <t>of your accounting period - read the notes if you have</t>
+        </is>
       </c>
       <c r="O33" s="227"/>
       <c r="P33" s="227"/>
@@ -13696,8 +13712,10 @@
       <c r="K34" s="220"/>
       <c r="L34" s="220"/>
       <c r="M34" s="220"/>
-      <c r="N34" s="246" t="s">
-        <v>165</v>
+      <c r="N34" s="246" t="inlineStr">
+        <is>
+          <t>filled in box 6 or 7</t>
+        </is>
       </c>
       <c r="O34" s="246"/>
       <c r="P34" s="227"/>
@@ -13819,8 +13837,10 @@
         <v>10</v>
       </c>
       <c r="B39" s="220"/>
-      <c r="C39" s="227" t="s">
-        <v>167</v>
+      <c r="C39" s="227" t="inlineStr">
+        <is>
+          <t>If you used traditional accounting rather than cash basis to</t>
+        </is>
       </c>
       <c r="D39" s="227"/>
       <c r="E39" s="227"/>
@@ -13831,11 +13851,13 @@
       <c r="J39" s="227"/>
       <c r="K39" s="227"/>
       <c r="L39" s="236">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M39" s="220"/>
-      <c r="N39" s="227" t="s">
-        <v>168</v>
+      <c r="N39" s="227" t="inlineStr">
+        <is>
+          <t>If special arrangements apply, put 'X' in the box - read the</t>
+        </is>
       </c>
       <c r="O39" s="227"/>
       <c r="P39" s="227"/>
@@ -13850,8 +13872,10 @@
     <row r="40" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A40" s="240"/>
       <c r="B40" s="220"/>
-      <c r="C40" s="227" t="s">
-        <v>169</v>
+      <c r="C40" s="227" t="inlineStr">
+        <is>
+          <t>calculate your income and expenses, put 'X' in the box</t>
+        </is>
       </c>
       <c r="D40" s="227"/>
       <c r="E40" s="227"/>
@@ -13863,8 +13887,10 @@
       <c r="K40" s="227"/>
       <c r="L40" s="220"/>
       <c r="M40" s="220"/>
-      <c r="N40" s="227" t="s">
-        <v>170</v>
+      <c r="N40" s="227" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
       </c>
       <c r="O40" s="227"/>
       <c r="P40" s="227"/>
@@ -13958,12 +13984,12 @@
       <c r="W43" s="243"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A44" s="236">
-        <v>11</v>
-      </c>
+      <c r="A44" s="236"/>
       <c r="B44" s="220"/>
-      <c r="C44" s="227" t="s">
-        <v>171</v>
+      <c r="C44" s="227" t="inlineStr">
+        <is>
+          <t>Boxes 11 and 12 are not in use</t>
+        </is>
       </c>
       <c r="D44" s="227"/>
       <c r="E44" s="227"/>
@@ -13974,11 +14000,12 @@
       <c r="J44" s="227"/>
       <c r="K44" s="227"/>
       <c r="L44" s="236">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M44" s="220"/>
-      <c r="N44" s="227" t="s">
-        <v>172</v>
+      <c r="N44" s="227" t="str">
+        <f>"If you provided the information about your "&amp;Admin!G2</f>
+        <v>If you provided the information about your 2025-26</v>
       </c>
       <c r="O44" s="227"/>
       <c r="P44" s="227"/>
@@ -13993,9 +14020,7 @@
     <row r="45" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A45" s="240"/>
       <c r="B45" s="220"/>
-      <c r="C45" s="227" t="s">
-        <v>173</v>
-      </c>
+      <c r="C45" s="227"/>
       <c r="D45" s="227"/>
       <c r="E45" s="227"/>
       <c r="F45" s="227"/>
@@ -14006,8 +14031,10 @@
       <c r="K45" s="227"/>
       <c r="L45" s="220"/>
       <c r="M45" s="220"/>
-      <c r="N45" s="227" t="s">
-        <v>174</v>
+      <c r="N45" s="227" t="inlineStr">
+        <is>
+          <t>profit on last year's tax return, put 'X' in the box</t>
+        </is>
       </c>
       <c r="O45" s="227"/>
       <c r="P45" s="227"/>
@@ -14033,9 +14060,7 @@
       <c r="K46" s="220"/>
       <c r="L46" s="220"/>
       <c r="M46" s="220"/>
-      <c r="N46" s="227" t="s">
-        <v>170</v>
-      </c>
+      <c r="N46" s="227"/>
       <c r="O46" s="227"/>
       <c r="P46" s="227"/>
       <c r="Q46" s="227"/>
@@ -14074,10 +14099,7 @@
     <row r="48" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A48" s="240"/>
       <c r="B48" s="220"/>
-      <c r="C48" s="272" t="str">
-        <f>IF('Business Details'!C45="x","x"," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="C48" s="272"/>
       <c r="D48" s="220"/>
       <c r="E48" s="220"/>
       <c r="F48" s="220"/>
@@ -14181,7 +14203,7 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A52" s="236">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B52" s="220"/>
       <c r="C52" s="227" t="s">
@@ -14196,11 +14218,13 @@
       <c r="J52" s="227"/>
       <c r="K52" s="227"/>
       <c r="L52" s="236">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M52" s="220"/>
-      <c r="N52" s="227" t="s">
-        <v>188</v>
+      <c r="N52" s="227" t="inlineStr">
+        <is>
+          <t>Any other business income not included in box 15</t>
+        </is>
       </c>
       <c r="O52" s="227"/>
       <c r="P52" s="227"/>
@@ -14228,9 +14252,7 @@
       <c r="K53" s="220"/>
       <c r="L53" s="220"/>
       <c r="M53" s="220"/>
-      <c r="N53" s="246" t="s">
-        <v>190</v>
-      </c>
+      <c r="N53" s="246"/>
       <c r="O53" s="220"/>
       <c r="P53" s="220"/>
       <c r="Q53" s="220"/>
@@ -14366,8 +14388,10 @@
       <c r="W57" s="365"/>
     </row>
     <row r="58" spans="1:23" s="254" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="366" t="s">
-        <v>192</v>
+      <c r="A58" s="366" t="inlineStr">
+        <is>
+          <t>Please read the 'Self-employment (full) notes' before filling in this section.</t>
+        </is>
       </c>
       <c r="B58" s="366"/>
       <c r="C58" s="366"/>
@@ -14449,8 +14473,10 @@
     <row r="61" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A61" s="240"/>
       <c r="B61" s="220"/>
-      <c r="C61" s="227" t="s">
-        <v>193</v>
+      <c r="C61" s="227" t="inlineStr">
+        <is>
+          <t>If your annual turnover was below £90,000, you may</t>
+        </is>
       </c>
       <c r="D61" s="227"/>
       <c r="E61" s="227"/>
@@ -14462,8 +14488,10 @@
       <c r="K61" s="227"/>
       <c r="L61" s="227"/>
       <c r="M61" s="227"/>
-      <c r="N61" s="227" t="s">
-        <v>194</v>
+      <c r="N61" s="227" t="inlineStr">
+        <is>
+          <t>Use this column if the figures in boxes 17 to 30</t>
+        </is>
       </c>
       <c r="O61" s="227"/>
       <c r="P61" s="227"/>
@@ -14478,8 +14506,10 @@
     <row r="62" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A62" s="240"/>
       <c r="B62" s="220"/>
-      <c r="C62" s="227" t="s">
-        <v>195</v>
+      <c r="C62" s="227" t="inlineStr">
+        <is>
+          <t>just put your total expenses in box 31</t>
+        </is>
       </c>
       <c r="D62" s="227"/>
       <c r="E62" s="227"/>
@@ -14531,11 +14561,13 @@
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A64" s="236">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B64" s="220"/>
-      <c r="C64" s="227" t="s">
-        <v>197</v>
+      <c r="C64" s="227" t="inlineStr">
+        <is>
+          <t>Cost of goods bought for resale or goods used</t>
+        </is>
       </c>
       <c r="D64" s="227"/>
       <c r="E64" s="227"/>
@@ -14546,7 +14578,7 @@
       <c r="J64" s="227"/>
       <c r="K64" s="227"/>
       <c r="L64" s="236">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M64" s="220"/>
       <c r="N64" s="220"/>
@@ -14656,7 +14688,7 @@
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A68" s="236">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B68" s="220"/>
       <c r="C68" s="227" t="s">
@@ -14671,7 +14703,7 @@
       <c r="J68" s="227"/>
       <c r="K68" s="227"/>
       <c r="L68" s="236">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M68" s="220"/>
       <c r="N68" s="220"/>
@@ -14781,7 +14813,7 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A72" s="236">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B72" s="220"/>
       <c r="C72" s="227" t="s">
@@ -14796,7 +14828,7 @@
       <c r="J72" s="227"/>
       <c r="K72" s="227"/>
       <c r="L72" s="236">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M72" s="220"/>
       <c r="N72" s="220"/>
@@ -14906,11 +14938,13 @@
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A76" s="236">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B76" s="220"/>
-      <c r="C76" s="227" t="s">
-        <v>200</v>
+      <c r="C76" s="227" t="inlineStr">
+        <is>
+          <t>Car, van and travel expenses</t>
+        </is>
       </c>
       <c r="D76" s="227"/>
       <c r="E76" s="227"/>
@@ -14921,7 +14955,7 @@
       <c r="J76" s="227"/>
       <c r="K76" s="227"/>
       <c r="L76" s="236">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M76" s="220"/>
       <c r="N76" s="220"/>
@@ -15031,7 +15065,7 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A80" s="236">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B80" s="220"/>
       <c r="C80" s="227" t="s">
@@ -15046,7 +15080,7 @@
       <c r="J80" s="227"/>
       <c r="K80" s="227"/>
       <c r="L80" s="236">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M80" s="220"/>
       <c r="N80" s="220"/>
@@ -15156,11 +15190,13 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A84" s="236">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B84" s="220"/>
-      <c r="C84" s="227" t="s">
-        <v>202</v>
+      <c r="C84" s="227" t="inlineStr">
+        <is>
+          <t>Repairs and maintenance of property and equipment</t>
+        </is>
       </c>
       <c r="D84" s="227"/>
       <c r="E84" s="227"/>
@@ -15171,7 +15207,7 @@
       <c r="J84" s="227"/>
       <c r="K84" s="227"/>
       <c r="L84" s="236">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M84" s="220"/>
       <c r="N84" s="220"/>
@@ -15281,11 +15317,13 @@
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A88" s="236">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B88" s="220"/>
-      <c r="C88" s="227" t="s">
-        <v>203</v>
+      <c r="C88" s="227" t="inlineStr">
+        <is>
+          <t>Phone, fax, stationery and other office costs</t>
+        </is>
       </c>
       <c r="D88" s="227"/>
       <c r="E88" s="227"/>
@@ -15296,7 +15334,7 @@
       <c r="J88" s="227"/>
       <c r="K88" s="227"/>
       <c r="L88" s="236">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M88" s="220"/>
       <c r="N88" s="220"/>
@@ -15406,7 +15444,7 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A92" s="236">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B92" s="220"/>
       <c r="C92" s="227" t="s">
@@ -15421,7 +15459,7 @@
       <c r="J92" s="227"/>
       <c r="K92" s="227"/>
       <c r="L92" s="236">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M92" s="220"/>
       <c r="N92" s="220"/>
@@ -15531,7 +15569,7 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A96" s="236">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B96" s="220"/>
       <c r="C96" s="227" t="s">
@@ -15546,7 +15584,7 @@
       <c r="J96" s="227"/>
       <c r="K96" s="227"/>
       <c r="L96" s="236">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M96" s="220"/>
       <c r="N96" s="220"/>
@@ -15656,7 +15694,7 @@
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A100" s="236">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B100" s="220"/>
       <c r="C100" s="227" t="s">
@@ -15671,7 +15709,7 @@
       <c r="J100" s="227"/>
       <c r="K100" s="227"/>
       <c r="L100" s="236">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M100" s="220"/>
       <c r="N100" s="220"/>
@@ -15781,7 +15819,7 @@
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A104" s="236">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B104" s="220"/>
       <c r="C104" s="227" t="s">
@@ -15796,7 +15834,7 @@
       <c r="J104" s="227"/>
       <c r="K104" s="227"/>
       <c r="L104" s="236">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M104" s="220"/>
       <c r="N104" s="220"/>
@@ -15906,7 +15944,7 @@
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A108" s="236">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B108" s="220"/>
       <c r="C108" s="227" t="s">
@@ -15921,7 +15959,7 @@
       <c r="J108" s="227"/>
       <c r="K108" s="227"/>
       <c r="L108" s="236">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M108" s="220"/>
       <c r="N108" s="220"/>
@@ -16031,11 +16069,13 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A112" s="236">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B112" s="220"/>
-      <c r="C112" s="227" t="s">
-        <v>209</v>
+      <c r="C112" s="227" t="inlineStr">
+        <is>
+          <t>Depreciation and loss or profit on sale of assets</t>
+        </is>
       </c>
       <c r="D112" s="227"/>
       <c r="E112" s="227"/>
@@ -16046,7 +16086,7 @@
       <c r="J112" s="227"/>
       <c r="K112" s="227"/>
       <c r="L112" s="236">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M112" s="220"/>
       <c r="N112" s="220"/>
@@ -16159,7 +16199,7 @@
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A116" s="236">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B116" s="220"/>
       <c r="C116" s="227" t="s">
@@ -16174,7 +16214,7 @@
       <c r="J116" s="227"/>
       <c r="K116" s="227"/>
       <c r="L116" s="236">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M116" s="220"/>
       <c r="N116" s="220"/>
@@ -16284,11 +16324,13 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A120" s="236">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B120" s="220"/>
-      <c r="C120" s="227" t="s">
-        <v>211</v>
+      <c r="C120" s="227" t="inlineStr">
+        <is>
+          <t>Total expenses (total of boxes 17 to 30)</t>
+        </is>
       </c>
       <c r="D120" s="227"/>
       <c r="E120" s="227"/>
@@ -16299,11 +16341,13 @@
       <c r="J120" s="227"/>
       <c r="K120" s="227"/>
       <c r="L120" s="236">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M120" s="220"/>
-      <c r="N120" s="227" t="s">
-        <v>212</v>
+      <c r="N120" s="227" t="inlineStr">
+        <is>
+          <t>Total disallowable expenses (total of boxes 32 to 45)</t>
+        </is>
       </c>
       <c r="O120" s="220"/>
       <c r="P120" s="220"/>
@@ -16466,7 +16510,7 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A126" s="236">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B126" s="220"/>
       <c r="C126" s="227" t="s">
@@ -16481,11 +16525,13 @@
       <c r="J126" s="227"/>
       <c r="K126" s="227"/>
       <c r="L126" s="236">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M126" s="220"/>
-      <c r="N126" s="227" t="s">
-        <v>215</v>
+      <c r="N126" s="227" t="inlineStr">
+        <is>
+          <t>Or, net loss - if your expenses are more than your</t>
+        </is>
       </c>
       <c r="O126" s="220"/>
       <c r="P126" s="220"/>
@@ -16500,8 +16546,10 @@
     <row r="127" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A127" s="240"/>
       <c r="B127" s="220"/>
-      <c r="C127" s="246" t="s">
-        <v>216</v>
+      <c r="C127" s="246" t="inlineStr">
+        <is>
+          <t>expenses (if box 15 + box 16 minus box 31 is positive)</t>
+        </is>
       </c>
       <c r="D127" s="227"/>
       <c r="E127" s="227"/>
@@ -16513,8 +16561,10 @@
       <c r="K127" s="227"/>
       <c r="L127" s="220"/>
       <c r="M127" s="220"/>
-      <c r="N127" s="227" t="s">
-        <v>217</v>
+      <c r="N127" s="227" t="inlineStr">
+        <is>
+          <t>business income (if box 31 minus (box 15 + box 16) is positive)</t>
+        </is>
       </c>
       <c r="O127" s="220"/>
       <c r="P127" s="220"/>
@@ -16651,8 +16701,10 @@
       <c r="W131" s="365"/>
     </row>
     <row r="132" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A132" s="366" t="s">
-        <v>219</v>
+      <c r="A132" s="366" t="inlineStr">
+        <is>
+          <t>There are 'capital' tax allowances for vehicles, equipment and certain buildings used in your business (do not include the cost</t>
+        </is>
       </c>
       <c r="B132" s="366"/>
       <c r="C132" s="366"/>
@@ -16678,8 +16730,10 @@
       <c r="W132" s="366"/>
     </row>
     <row r="133" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A133" s="366" t="s">
-        <v>352</v>
+      <c r="A133" s="366" t="inlineStr">
+        <is>
+          <t>of these in your business expenses). Please read the 'Self-employment (full) notes' and use the examples to work out your</t>
+        </is>
       </c>
       <c r="B133" s="366"/>
       <c r="C133" s="366"/>
@@ -16705,8 +16759,10 @@
       <c r="W133" s="366"/>
     </row>
     <row r="134" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A134" s="366" t="s">
-        <v>220</v>
+      <c r="A134" s="366" t="inlineStr">
+        <is>
+          <t>capital allowances.</t>
+        </is>
       </c>
       <c r="B134" s="366"/>
       <c r="C134" s="366"/>
@@ -16758,20 +16814,19 @@
     </row>
     <row r="136" spans="1:23" ht="13" x14ac:dyDescent="0.15">
       <c r="A136" s="236">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B136" s="220"/>
-      <c r="C136" s="288" t="s">
-        <v>349</v>
+      <c r="C136" s="288" t="inlineStr">
+        <is>
+          <t>Annual Investment Allowance</t>
+        </is>
       </c>
       <c r="D136" s="227"/>
       <c r="E136" s="227"/>
       <c r="F136" s="227"/>
       <c r="G136" s="227"/>
-      <c r="H136" s="379">
-        <f>Admin!G4</f>
-        <v>1</v>
-      </c>
+      <c r="H136" s="379"/>
       <c r="I136" s="380"/>
       <c r="J136" s="227"/>
       <c r="K136" s="227"/>
@@ -16779,8 +16834,10 @@
         <v>54</v>
       </c>
       <c r="M136" s="220"/>
-      <c r="N136" s="227" t="s">
-        <v>223</v>
+      <c r="N136" s="227" t="inlineStr">
+        <is>
+          <t>Electric charge-point allowance</t>
+        </is>
       </c>
       <c r="O136" s="220"/>
       <c r="P136" s="220"/>
@@ -16806,9 +16863,7 @@
       <c r="K137" s="227"/>
       <c r="L137" s="227"/>
       <c r="M137" s="220"/>
-      <c r="N137" s="246" t="s">
-        <v>353</v>
-      </c>
+      <c r="N137" s="246"/>
       <c r="O137" s="258"/>
       <c r="P137" s="258"/>
       <c r="Q137" s="258"/>
@@ -16872,10 +16927,7 @@
       <c r="N139" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O139" s="356">
-        <f>IF(([1]Schedule!$R$1+[1]Schedule!$S$1)&lt;1000,[1]Schedule!$S$1,0)</f>
-        <v>0</v>
-      </c>
+      <c r="O139" s="356"/>
       <c r="P139" s="357"/>
       <c r="Q139" s="358"/>
       <c r="R139" s="218" t="s">
@@ -16918,11 +16970,13 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A141" s="236">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B141" s="220"/>
-      <c r="C141" s="227" t="s">
-        <v>221</v>
+      <c r="C141" s="227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capital allowances at </t>
+        </is>
       </c>
       <c r="D141" s="227"/>
       <c r="E141" s="227"/>
@@ -16932,8 +16986,10 @@
         <v>0.18</v>
       </c>
       <c r="H141" s="381"/>
-      <c r="I141" s="227" t="s">
-        <v>222</v>
+      <c r="I141" s="227" t="inlineStr">
+        <is>
+          <t>on equipment, including cars with lower CO2</t>
+        </is>
       </c>
       <c r="J141" s="227"/>
       <c r="K141" s="227"/>
@@ -16941,8 +16997,10 @@
         <v>55</v>
       </c>
       <c r="M141" s="220"/>
-      <c r="N141" s="227" t="s">
-        <v>225</v>
+      <c r="N141" s="227" t="inlineStr">
+        <is>
+          <t>100% and other enhanced capital allowances</t>
+        </is>
       </c>
       <c r="O141" s="220"/>
       <c r="P141" s="220"/>
@@ -16957,8 +17015,10 @@
     <row r="142" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="255"/>
       <c r="B142" s="220"/>
-      <c r="C142" s="227" t="s">
-        <v>224</v>
+      <c r="C142" s="227" t="inlineStr">
+        <is>
+          <t>emissions</t>
+        </is>
       </c>
       <c r="D142" s="227"/>
       <c r="E142" s="227"/>
@@ -16970,9 +17030,7 @@
       <c r="K142" s="227"/>
       <c r="L142" s="227"/>
       <c r="M142" s="220"/>
-      <c r="N142" s="227" t="s">
-        <v>226</v>
-      </c>
+      <c r="N142" s="227"/>
       <c r="O142" s="220"/>
       <c r="P142" s="220"/>
       <c r="Q142" s="220"/>
@@ -17015,7 +17073,7 @@
         <v>51</v>
       </c>
       <c r="D144" s="356">
-        <f>[1]Schedule!$R$1-D152</f>
+        <f>[1]Schedule!$R$1</f>
         <v>0</v>
       </c>
       <c r="E144" s="357"/>
@@ -17037,7 +17095,7 @@
         <v>51</v>
       </c>
       <c r="O144" s="356">
-        <f>[1]Schedule!$Y$1</f>
+        <f>IF(([1]Schedule!$R$1+[1]Schedule!$S$1)&lt;1000,[1]Schedule!$S$1,0)</f>
         <v>0</v>
       </c>
       <c r="P144" s="357"/>
@@ -17082,19 +17140,19 @@
     </row>
     <row r="146" spans="1:23" ht="13" x14ac:dyDescent="0.15">
       <c r="A146" s="236">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B146" s="220"/>
-      <c r="C146" s="288" t="s">
-        <v>354</v>
+      <c r="C146" s="288" t="inlineStr">
+        <is>
+          <t>Capital allowances at 6% on equipment, including cars with higher CO2 emissions</t>
+        </is>
       </c>
       <c r="D146" s="227"/>
       <c r="E146" s="227"/>
       <c r="F146" s="227"/>
       <c r="G146" s="227"/>
-      <c r="H146" s="379">
-        <v>0.1</v>
-      </c>
+      <c r="H146" s="379"/>
       <c r="I146" s="380"/>
       <c r="J146" s="220"/>
       <c r="K146" s="220"/>
@@ -17135,8 +17193,10 @@
         <v>56</v>
       </c>
       <c r="M147" s="220"/>
-      <c r="N147" s="227" t="s">
-        <v>355</v>
+      <c r="N147" s="227" t="inlineStr">
+        <is>
+          <t>Allowances on sale or cessation of business use (where you</t>
+        </is>
       </c>
       <c r="O147" s="220"/>
       <c r="P147" s="220"/>
@@ -17162,7 +17222,11 @@
       <c r="K148" s="220"/>
       <c r="L148" s="227"/>
       <c r="M148" s="220"/>
-      <c r="N148" s="220"/>
+      <c r="N148" s="227" t="inlineStr">
+        <is>
+          <t>have disposed of assets for less than their tax value)</t>
+        </is>
+      </c>
       <c r="O148" s="220"/>
       <c r="P148" s="220"/>
       <c r="Q148" s="220"/>
@@ -17175,11 +17239,13 @@
     </row>
     <row r="149" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A149" s="236">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B149" s="220"/>
-      <c r="C149" s="227" t="s">
-        <v>227</v>
+      <c r="C149" s="227" t="inlineStr">
+        <is>
+          <t>Zero-emission goods vehicle allowance</t>
+        </is>
       </c>
       <c r="D149" s="227"/>
       <c r="E149" s="227"/>
@@ -17195,7 +17261,7 @@
         <v>51</v>
       </c>
       <c r="O149" s="356">
-        <f>D139+D144+D147+D152+D156+D160+O139+O144</f>
+        <f>[1]Schedule!$Y$1</f>
         <v>0</v>
       </c>
       <c r="P149" s="357"/>
@@ -17216,9 +17282,7 @@
     <row r="150" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="240"/>
       <c r="B150" s="220"/>
-      <c r="C150" s="227" t="s">
-        <v>228</v>
-      </c>
+      <c r="C150" s="227"/>
       <c r="D150" s="220"/>
       <c r="E150" s="220"/>
       <c r="F150" s="220"/>
@@ -17256,8 +17320,10 @@
         <v>57</v>
       </c>
       <c r="M151" s="220"/>
-      <c r="N151" s="227" t="s">
-        <v>230</v>
+      <c r="N151" s="227" t="inlineStr">
+        <is>
+          <t>Total capital allowances (total of boxes 49 to 56)</t>
+        </is>
       </c>
       <c r="O151" s="220"/>
       <c r="P151" s="220"/>
@@ -17275,10 +17341,7 @@
       <c r="C152" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D152" s="356">
-        <f>SUM([1]Schedule!$R$38:$R$42)+SUM([1]Schedule!$R$91:$R$95)</f>
-        <v>0</v>
-      </c>
+      <c r="D152" s="356"/>
       <c r="E152" s="331"/>
       <c r="F152" s="332"/>
       <c r="G152" s="218" t="s">
@@ -17294,9 +17357,7 @@
       <c r="K152" s="220"/>
       <c r="L152" s="220"/>
       <c r="M152" s="220"/>
-      <c r="N152" s="227" t="s">
-        <v>231</v>
-      </c>
+      <c r="N152" s="227"/>
       <c r="O152" s="220"/>
       <c r="P152" s="220"/>
       <c r="Q152" s="220"/>
@@ -17334,11 +17395,13 @@
     </row>
     <row r="154" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A154" s="236">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="B154" s="220"/>
-      <c r="C154" s="227" t="s">
-        <v>229</v>
+      <c r="C154" s="227" t="inlineStr">
+        <is>
+          <t>Zero-emission car allowance</t>
+        </is>
       </c>
       <c r="D154" s="227"/>
       <c r="E154" s="227"/>
@@ -17353,7 +17416,10 @@
       <c r="N154" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O154" s="356"/>
+      <c r="O154" s="356">
+        <f>D139+D144+D147+D152+D156+D160+O139+O144+O149</f>
+        <v>0</v>
+      </c>
       <c r="P154" s="357"/>
       <c r="Q154" s="358"/>
       <c r="R154" s="218" t="s">
@@ -17415,11 +17481,13 @@
       <c r="J156" s="220"/>
       <c r="K156" s="220"/>
       <c r="L156" s="236">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M156" s="220"/>
-      <c r="N156" s="227" t="s">
-        <v>356</v>
+      <c r="N156" s="227" t="inlineStr">
+        <is>
+          <t>Balancing charge on sales of assets or on the cessation of</t>
+        </is>
       </c>
       <c r="O156" s="220"/>
       <c r="P156" s="220"/>
@@ -17436,8 +17504,10 @@
         <v>53</v>
       </c>
       <c r="B157" s="220"/>
-      <c r="C157" s="227" t="s">
-        <v>232</v>
+      <c r="C157" s="227" t="inlineStr">
+        <is>
+          <t>The Structures and Buildings Allowance</t>
+        </is>
       </c>
       <c r="D157" s="227"/>
       <c r="E157" s="227"/>
@@ -17449,8 +17519,10 @@
       <c r="K157" s="227"/>
       <c r="L157" s="220"/>
       <c r="M157" s="220"/>
-      <c r="N157" s="227" t="s">
-        <v>357</v>
+      <c r="N157" s="227" t="inlineStr">
+        <is>
+          <t>business use (including where Business Premises Renovation</t>
+        </is>
       </c>
       <c r="O157" s="220"/>
       <c r="P157" s="220"/>
@@ -17465,9 +17537,7 @@
     <row r="158" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A158" s="240"/>
       <c r="B158" s="220"/>
-      <c r="C158" s="227" t="s">
-        <v>358</v>
-      </c>
+      <c r="C158" s="227"/>
       <c r="D158" s="220"/>
       <c r="E158" s="220"/>
       <c r="F158" s="220"/>
@@ -17478,8 +17548,10 @@
       <c r="K158" s="220"/>
       <c r="L158" s="220"/>
       <c r="M158" s="220"/>
-      <c r="N158" s="227" t="s">
-        <v>359</v>
+      <c r="N158" s="227" t="inlineStr">
+        <is>
+          <t>Allowance has been claimed)</t>
+        </is>
       </c>
       <c r="O158" s="220"/>
       <c r="P158" s="220"/>
@@ -17613,8 +17685,10 @@
       <c r="W162" s="365"/>
     </row>
     <row r="163" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A163" s="366" t="s">
-        <v>234</v>
+      <c r="A163" s="366" t="inlineStr">
+        <is>
+          <t>You may have to adjust your net profit or loss for disallowable expenses or capital allowances to arrive at your taxable profit</t>
+        </is>
       </c>
       <c r="B163" s="366"/>
       <c r="C163" s="366"/>
@@ -17640,8 +17714,10 @@
       <c r="W163" s="366"/>
     </row>
     <row r="164" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A164" s="366" t="s">
-        <v>360</v>
+      <c r="A164" s="366" t="inlineStr">
+        <is>
+          <t>or your loss for tax purposes. Please read the 'Self-employment (full) notes' and fill in the boxes below that apply.</t>
+        </is>
       </c>
       <c r="B164" s="366"/>
       <c r="C164" s="366"/>
@@ -17693,11 +17769,13 @@
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A166" s="236">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B166" s="220"/>
-      <c r="C166" s="227" t="s">
-        <v>361</v>
+      <c r="C166" s="227" t="inlineStr">
+        <is>
+          <t>Goods and services for your own use</t>
+        </is>
       </c>
       <c r="D166" s="227"/>
       <c r="E166" s="227"/>
@@ -17708,7 +17786,7 @@
       <c r="J166" s="227"/>
       <c r="K166" s="227"/>
       <c r="L166" s="236">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M166" s="220"/>
       <c r="N166" s="227" t="s">
@@ -17727,9 +17805,7 @@
     <row r="167" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A167" s="255"/>
       <c r="B167" s="220"/>
-      <c r="C167" s="227" t="s">
-        <v>236</v>
-      </c>
+      <c r="C167" s="227"/>
       <c r="D167" s="227"/>
       <c r="E167" s="227"/>
       <c r="F167" s="227"/>
@@ -17740,8 +17816,10 @@
       <c r="K167" s="227"/>
       <c r="L167" s="227"/>
       <c r="M167" s="220"/>
-      <c r="N167" s="227" t="s">
-        <v>362</v>
+      <c r="N167" s="227" t="inlineStr">
+        <is>
+          <t>net loss (box 57 + box 62)</t>
+        </is>
       </c>
       <c r="O167" s="258"/>
       <c r="P167" s="258"/>
@@ -17807,7 +17885,7 @@
         <v>51</v>
       </c>
       <c r="O169" s="356">
-        <f>O149+D179</f>
+        <f>O154+D179</f>
         <v>0</v>
       </c>
       <c r="P169" s="357"/>
@@ -17852,7 +17930,7 @@
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A171" s="236">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B171" s="220"/>
       <c r="C171" s="227" t="s">
@@ -17867,11 +17945,13 @@
       <c r="J171" s="227"/>
       <c r="K171" s="227"/>
       <c r="L171" s="236">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M171" s="220"/>
-      <c r="N171" s="227" t="s">
-        <v>363</v>
+      <c r="N171" s="227" t="inlineStr">
+        <is>
+          <t>Net business profit for tax purposes (if box 47 + box 61</t>
+        </is>
       </c>
       <c r="O171" s="220"/>
       <c r="P171" s="220"/>
@@ -17886,8 +17966,10 @@
     <row r="172" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="255"/>
       <c r="B172" s="220"/>
-      <c r="C172" s="227" t="s">
-        <v>364</v>
+      <c r="C172" s="227" t="inlineStr">
+        <is>
+          <t>(box 46 + box 59 + box 60)</t>
+        </is>
       </c>
       <c r="D172" s="227"/>
       <c r="E172" s="227"/>
@@ -17899,8 +17981,10 @@
       <c r="K172" s="227"/>
       <c r="L172" s="227"/>
       <c r="M172" s="220"/>
-      <c r="N172" s="227" t="s">
-        <v>365</v>
+      <c r="N172" s="227" t="inlineStr">
+        <is>
+          <t>minus (box 48 + box 63) is positive)</t>
+        </is>
       </c>
       <c r="O172" s="220"/>
       <c r="P172" s="220"/>
@@ -17944,7 +18028,7 @@
         <v>51</v>
       </c>
       <c r="D174" s="356">
-        <f>O122+O154+O160+D169</f>
+        <f>O122+O160+D169</f>
         <v>0</v>
       </c>
       <c r="E174" s="357"/>
@@ -18011,7 +18095,7 @@
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A176" s="236">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B176" s="220"/>
       <c r="C176" s="227" t="s">
@@ -18026,11 +18110,13 @@
       <c r="J176" s="227"/>
       <c r="K176" s="227"/>
       <c r="L176" s="236">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M176" s="220"/>
-      <c r="N176" s="227" t="s">
-        <v>366</v>
+      <c r="N176" s="227" t="inlineStr">
+        <is>
+          <t>Net business loss for tax purposes (if box 48 + box 63</t>
+        </is>
       </c>
       <c r="O176" s="220"/>
       <c r="P176" s="220"/>
@@ -18058,8 +18144,10 @@
       <c r="K177" s="220"/>
       <c r="L177" s="220"/>
       <c r="M177" s="220"/>
-      <c r="N177" s="227" t="s">
-        <v>367</v>
+      <c r="N177" s="227" t="inlineStr">
+        <is>
+          <t>minus (box 47 + box 61) is positive)</t>
+        </is>
       </c>
       <c r="O177" s="220"/>
       <c r="P177" s="220"/>
@@ -18193,8 +18281,10 @@
       <c r="W181" s="365"/>
     </row>
     <row r="182" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A182" s="366" t="s">
-        <v>241</v>
+      <c r="A182" s="366" t="inlineStr">
+        <is>
+          <t>Please read the 'Self-employment (full) notes' and fill in the boxes below that apply. If your accounting date is not between</t>
+        </is>
       </c>
       <c r="B182" s="366"/>
       <c r="C182" s="366"/>
@@ -18220,8 +18310,10 @@
       <c r="W182" s="366"/>
     </row>
     <row r="183" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A183" s="366" t="s">
-        <v>242</v>
+      <c r="A183" s="366" t="inlineStr">
+        <is>
+          <t>31 March and 5 April you will need to apportion profits from each accounting period to the tax year - use box 68 to adjust</t>
+        </is>
       </c>
       <c r="B183" s="366"/>
       <c r="C183" s="366"/>
@@ -18247,8 +18339,10 @@
       <c r="W183" s="366"/>
     </row>
     <row r="184" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A184" s="387" t="s">
-        <v>243</v>
+      <c r="A184" s="387" t="inlineStr">
+        <is>
+          <t>your tax profit (box 64) or loss (box 65) accordingly.</t>
+        </is>
       </c>
       <c r="B184" s="387"/>
       <c r="C184" s="387"/>
@@ -18299,12 +18393,12 @@
       <c r="W185" s="235"/>
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A186" s="236">
-        <v>65</v>
-      </c>
+      <c r="A186" s="236"/>
       <c r="B186" s="220"/>
-      <c r="C186" s="227" t="s">
-        <v>244</v>
+      <c r="C186" s="227" t="inlineStr">
+        <is>
+          <t>Boxes 66 and 67 are not in use</t>
+        </is>
       </c>
       <c r="D186" s="227"/>
       <c r="E186" s="227"/>
@@ -18315,7 +18409,7 @@
       <c r="J186" s="227"/>
       <c r="K186" s="227"/>
       <c r="L186" s="236">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M186" s="220"/>
       <c r="N186" s="227" t="s">
@@ -18372,8 +18466,10 @@
       <c r="K188" s="220"/>
       <c r="L188" s="227"/>
       <c r="M188" s="220"/>
-      <c r="N188" s="248" t="s">
-        <v>247</v>
+      <c r="N188" s="248" t="inlineStr">
+        <is>
+          <t>adjustment needs to be taken off the profit figure, put a</t>
+        </is>
       </c>
       <c r="O188" s="220"/>
       <c r="P188" s="220"/>
@@ -18386,13 +18482,9 @@
       <c r="W188" s="243"/>
     </row>
     <row r="189" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A189" s="236">
-        <v>66</v>
-      </c>
+      <c r="A189" s="236"/>
       <c r="B189" s="220"/>
-      <c r="C189" s="227" t="s">
-        <v>248</v>
-      </c>
+      <c r="C189" s="227"/>
       <c r="D189" s="220"/>
       <c r="E189" s="220"/>
       <c r="F189" s="220"/>
@@ -18478,11 +18570,13 @@
     </row>
     <row r="192" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="236">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B192" s="220"/>
-      <c r="C192" s="227" t="s">
-        <v>251</v>
+      <c r="C192" s="227" t="inlineStr">
+        <is>
+          <t>Adjustment where your accounting period was not 12 months</t>
+        </is>
       </c>
       <c r="D192" s="259"/>
       <c r="E192" s="259"/>
@@ -18493,11 +18587,13 @@
       <c r="J192" s="220"/>
       <c r="K192" s="220"/>
       <c r="L192" s="236">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M192" s="220"/>
-      <c r="N192" s="227" t="s">
-        <v>252</v>
+      <c r="N192" s="227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted profit for </t>
+        </is>
       </c>
       <c r="O192" s="220"/>
       <c r="P192" s="220"/>
@@ -18505,9 +18601,7 @@
         <f>Admin!G2</f>
         <v>2025-26</v>
       </c>
-      <c r="R192" s="227" t="s">
-        <v>368</v>
-      </c>
+      <c r="R192" s="227"/>
       <c r="S192" s="220"/>
       <c r="T192" s="220"/>
       <c r="U192" s="220"/>
@@ -18517,8 +18611,10 @@
     <row r="193" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="240"/>
       <c r="B193" s="220"/>
-      <c r="C193" s="227" t="s">
-        <v>253</v>
+      <c r="C193" s="227" t="inlineStr">
+        <is>
+          <t>long or ended before 31 March - if the adjustment needs to be</t>
+        </is>
       </c>
       <c r="D193" s="227"/>
       <c r="E193" s="227"/>
@@ -18530,8 +18626,10 @@
       <c r="K193" s="227"/>
       <c r="L193" s="227"/>
       <c r="M193" s="227"/>
-      <c r="N193" s="241" t="s">
-        <v>369</v>
+      <c r="N193" s="241" t="inlineStr">
+        <is>
+          <t>- see the working sheet in the notes</t>
+        </is>
       </c>
       <c r="O193" s="259"/>
       <c r="P193" s="259"/>
@@ -18546,8 +18644,10 @@
     <row r="194" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A194" s="240"/>
       <c r="B194" s="220"/>
-      <c r="C194" s="241" t="s">
-        <v>254</v>
+      <c r="C194" s="241" t="inlineStr">
+        <is>
+          <t>taken off the profit figure, put a minus sign (-) in the box</t>
+        </is>
       </c>
       <c r="D194" s="227"/>
       <c r="E194" s="227"/>
@@ -18584,9 +18684,7 @@
     <row r="195" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="240"/>
       <c r="B195" s="220"/>
-      <c r="C195" s="227" t="s">
-        <v>255</v>
-      </c>
+      <c r="C195" s="227"/>
       <c r="D195" s="220"/>
       <c r="E195" s="220"/>
       <c r="F195" s="220"/>
@@ -18611,9 +18709,7 @@
     <row r="196" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A196" s="255"/>
       <c r="B196" s="220"/>
-      <c r="C196" s="227" t="s">
-        <v>256</v>
-      </c>
+      <c r="C196" s="227"/>
       <c r="D196" s="227"/>
       <c r="E196" s="227"/>
       <c r="F196" s="227"/>
@@ -18623,11 +18719,13 @@
       <c r="J196" s="227"/>
       <c r="K196" s="227"/>
       <c r="L196" s="236">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M196" s="220"/>
-      <c r="N196" s="227" t="s">
-        <v>257</v>
+      <c r="N196" s="227" t="inlineStr">
+        <is>
+          <t>Loss brought forward from earlier years set off against</t>
+        </is>
       </c>
       <c r="O196" s="220"/>
       <c r="P196" s="220"/>
@@ -18663,8 +18761,10 @@
       <c r="K197" s="220"/>
       <c r="L197" s="220"/>
       <c r="M197" s="220"/>
-      <c r="N197" s="241" t="s">
-        <v>370</v>
+      <c r="N197" s="241" t="inlineStr">
+        <is>
+          <t>this year's adjusted profit</t>
+        </is>
       </c>
       <c r="O197" s="220"/>
       <c r="P197" s="220"/>
@@ -18690,9 +18790,7 @@
       <c r="K198" s="220"/>
       <c r="L198" s="220"/>
       <c r="M198" s="220"/>
-      <c r="N198" s="246" t="s">
-        <v>371</v>
-      </c>
+      <c r="N198" s="246"/>
       <c r="O198" s="220"/>
       <c r="P198" s="220"/>
       <c r="Q198" s="220"/>
@@ -18704,12 +18802,12 @@
       <c r="W198" s="243"/>
     </row>
     <row r="199" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A199" s="236">
-        <v>68</v>
-      </c>
+      <c r="A199" s="236"/>
       <c r="B199" s="220"/>
-      <c r="C199" s="227" t="s">
-        <v>372</v>
+      <c r="C199" s="227" t="inlineStr">
+        <is>
+          <t>Boxes 69 and 70 are not in use</t>
+        </is>
       </c>
       <c r="D199" s="220"/>
       <c r="E199" s="220"/>
@@ -18771,29 +18869,23 @@
     <row r="201" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A201" s="240"/>
       <c r="B201" s="220"/>
-      <c r="C201" s="217" t="s">
-        <v>51</v>
-      </c>
+      <c r="C201" s="217"/>
       <c r="D201" s="356"/>
       <c r="E201" s="357"/>
       <c r="F201" s="358"/>
-      <c r="G201" s="218" t="s">
-        <v>178</v>
-      </c>
-      <c r="H201" s="219">
-        <v>0</v>
-      </c>
-      <c r="I201" s="219">
-        <v>0</v>
-      </c>
+      <c r="G201" s="218"/>
+      <c r="H201" s="219"/>
+      <c r="I201" s="219"/>
       <c r="J201" s="220"/>
       <c r="K201" s="220"/>
       <c r="L201" s="236">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M201" s="220"/>
-      <c r="N201" s="227" t="s">
-        <v>258</v>
+      <c r="N201" s="227" t="inlineStr">
+        <is>
+          <t>Any other business income not included in</t>
+        </is>
       </c>
       <c r="O201" s="220"/>
       <c r="P201" s="220"/>
@@ -18819,8 +18911,10 @@
       <c r="K202" s="220"/>
       <c r="L202" s="220"/>
       <c r="M202" s="220"/>
-      <c r="N202" s="227" t="s">
-        <v>373</v>
+      <c r="N202" s="227" t="inlineStr">
+        <is>
+          <t>boxes 15, 16 or 60</t>
+        </is>
       </c>
       <c r="O202" s="220"/>
       <c r="P202" s="220"/>
@@ -18833,13 +18927,9 @@
       <c r="W202" s="243"/>
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A203" s="236">
-        <v>69</v>
-      </c>
+      <c r="A203" s="236"/>
       <c r="B203" s="220"/>
-      <c r="C203" s="227" t="s">
-        <v>374</v>
-      </c>
+      <c r="C203" s="227"/>
       <c r="D203" s="227"/>
       <c r="E203" s="227"/>
       <c r="F203" s="227"/>
@@ -18925,29 +19015,23 @@
     <row r="206" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A206" s="240"/>
       <c r="B206" s="220"/>
-      <c r="C206" s="217" t="s">
-        <v>51</v>
-      </c>
+      <c r="C206" s="217"/>
       <c r="D206" s="356"/>
       <c r="E206" s="357"/>
       <c r="F206" s="358"/>
-      <c r="G206" s="218" t="s">
-        <v>178</v>
-      </c>
-      <c r="H206" s="219">
-        <v>0</v>
-      </c>
-      <c r="I206" s="219">
-        <v>0</v>
-      </c>
+      <c r="G206" s="218"/>
+      <c r="H206" s="219"/>
+      <c r="I206" s="219"/>
       <c r="J206" s="220"/>
       <c r="K206" s="220"/>
       <c r="L206" s="236">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M206" s="220"/>
-      <c r="N206" s="227" t="s">
-        <v>375</v>
+      <c r="N206" s="227" t="inlineStr">
+        <is>
+          <t>Total taxable profits from this business</t>
+        </is>
       </c>
       <c r="O206" s="220"/>
       <c r="P206" s="220"/>
@@ -18973,8 +19057,10 @@
       <c r="K207" s="220"/>
       <c r="L207" s="220"/>
       <c r="M207" s="220"/>
-      <c r="N207" s="227" t="s">
-        <v>376</v>
+      <c r="N207" s="227" t="inlineStr">
+        <is>
+          <t>- see the working sheet in the notes</t>
+        </is>
       </c>
       <c r="O207" s="220"/>
       <c r="P207" s="220"/>
@@ -18988,11 +19074,13 @@
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A208" s="236">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B208" s="220"/>
-      <c r="C208" s="227" t="s">
-        <v>259</v>
+      <c r="C208" s="227" t="inlineStr">
+        <is>
+          <t>Adjustment for change of accounting practice</t>
+        </is>
       </c>
       <c r="D208" s="227"/>
       <c r="E208" s="227"/>
@@ -19004,9 +19092,7 @@
       <c r="K208" s="227"/>
       <c r="L208" s="220"/>
       <c r="M208" s="220"/>
-      <c r="N208" s="246" t="s">
-        <v>377</v>
-      </c>
+      <c r="N208" s="246"/>
       <c r="O208" s="220"/>
       <c r="P208" s="220"/>
       <c r="Q208" s="220"/>
@@ -19020,9 +19106,7 @@
     <row r="209" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A209" s="240"/>
       <c r="B209" s="220"/>
-      <c r="C209" s="248" t="s">
-        <v>378</v>
-      </c>
+      <c r="C209" s="248"/>
       <c r="D209" s="220"/>
       <c r="E209" s="220"/>
       <c r="F209" s="220"/>
@@ -19141,8 +19225,10 @@
       <c r="W212" s="368"/>
     </row>
     <row r="213" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A213" s="366" t="s">
-        <v>261</v>
+      <c r="A213" s="366" t="inlineStr">
+        <is>
+          <t>If you have made a net loss for tax purposes (in box 65), or because of box 68, or if you have losses from previous years,</t>
+        </is>
       </c>
       <c r="B213" s="366"/>
       <c r="C213" s="366"/>
@@ -19168,8 +19254,10 @@
       <c r="W213" s="366"/>
     </row>
     <row r="214" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A214" s="366" t="s">
-        <v>262</v>
+      <c r="A214" s="366" t="inlineStr">
+        <is>
+          <t>read the 'Self-employment (full) notes' and fill in boxes 77 to 80 as appropriate.</t>
+        </is>
       </c>
       <c r="B214" s="366"/>
       <c r="C214" s="366"/>
@@ -19221,11 +19309,13 @@
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A216" s="236">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B216" s="220"/>
-      <c r="C216" s="227" t="s">
-        <v>263</v>
+      <c r="C216" s="227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted loss for </t>
+        </is>
       </c>
       <c r="D216" s="227"/>
       <c r="E216" s="227"/>
@@ -19233,15 +19323,17 @@
         <f>Admin!G2</f>
         <v>2025-26</v>
       </c>
-      <c r="G216" s="227" t="s">
-        <v>379</v>
+      <c r="G216" s="227" t="inlineStr">
+        <is>
+          <t>- see the working sheet in the notes</t>
+        </is>
       </c>
       <c r="H216" s="227"/>
       <c r="I216" s="227"/>
       <c r="J216" s="220"/>
       <c r="K216" s="227"/>
       <c r="L216" s="236">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M216" s="220"/>
       <c r="N216" s="227" t="s">
@@ -19260,9 +19352,7 @@
     <row r="217" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="255"/>
       <c r="B217" s="220"/>
-      <c r="C217" s="227" t="s">
-        <v>380</v>
-      </c>
+      <c r="C217" s="227"/>
       <c r="D217" s="227"/>
       <c r="E217" s="227"/>
       <c r="F217" s="227"/>
@@ -19318,7 +19408,7 @@
         <v>51</v>
       </c>
       <c r="D219" s="356">
-        <f>O179+E197-D201+D210+P190</f>
+        <f>O179+E197+D210+P190</f>
         <v>0</v>
       </c>
       <c r="E219" s="357"/>
@@ -19382,7 +19472,7 @@
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A221" s="236">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B221" s="220"/>
       <c r="C221" s="227" t="s">
@@ -19397,7 +19487,7 @@
       <c r="J221" s="227"/>
       <c r="K221" s="227"/>
       <c r="L221" s="236">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M221" s="220"/>
       <c r="N221" s="227" t="s">
@@ -19540,8 +19630,10 @@
       <c r="W225" s="251"/>
     </row>
     <row r="226" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A226" s="388" t="s">
-        <v>270</v>
+      <c r="A226" s="388" t="inlineStr">
+        <is>
+          <t>CIS deductions and tax taken off</t>
+        </is>
       </c>
       <c r="B226" s="388"/>
       <c r="C226" s="388"/>
@@ -19593,11 +19685,13 @@
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A228" s="236">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B228" s="220"/>
-      <c r="C228" s="227" t="s">
-        <v>271</v>
+      <c r="C228" s="227" t="inlineStr">
+        <is>
+          <t>Total Construction Industry Scheme (CIS) deductions taken from</t>
+        </is>
       </c>
       <c r="D228" s="227"/>
       <c r="E228" s="227"/>
@@ -19608,7 +19702,7 @@
       <c r="J228" s="227"/>
       <c r="K228" s="227"/>
       <c r="L228" s="236">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M228" s="220"/>
       <c r="N228" s="227" t="s">
@@ -19627,8 +19721,10 @@
     <row r="229" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="255"/>
       <c r="B229" s="220"/>
-      <c r="C229" s="227" t="s">
-        <v>273</v>
+      <c r="C229" s="227" t="inlineStr">
+        <is>
+          <t>your payments by contractors - CIS subcontractors only</t>
+        </is>
       </c>
       <c r="D229" s="227"/>
       <c r="E229" s="227"/>
@@ -19773,8 +19869,10 @@
       <c r="W233" s="365"/>
     </row>
     <row r="234" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A234" s="366" t="s">
-        <v>274</v>
+      <c r="A234" s="366" t="inlineStr">
+        <is>
+          <t>If your business accounts include a balance sheet showing the assets, liabilities and capital of the business, fill in the relevant</t>
+        </is>
       </c>
       <c r="B234" s="366"/>
       <c r="C234" s="366"/>
@@ -19800,8 +19898,10 @@
       <c r="W234" s="366"/>
     </row>
     <row r="235" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A235" s="366" t="s">
-        <v>382</v>
+      <c r="A235" s="366" t="inlineStr">
+        <is>
+          <t>boxes below. If you do not have a balance sheet, go to box 100.</t>
+        </is>
       </c>
       <c r="B235" s="366"/>
       <c r="C235" s="366"/>
@@ -19907,7 +20007,7 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A239" s="236">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B239" s="220"/>
       <c r="C239" s="227" t="s">
@@ -19922,7 +20022,7 @@
       <c r="J239" s="227"/>
       <c r="K239" s="227"/>
       <c r="L239" s="236">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M239" s="220"/>
       <c r="N239" s="227" t="s">
@@ -20031,7 +20131,7 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A243" s="236">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B243" s="220"/>
       <c r="C243" s="227" t="s">
@@ -20046,7 +20146,7 @@
       <c r="J243" s="227"/>
       <c r="K243" s="227"/>
       <c r="L243" s="236">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M243" s="220"/>
       <c r="N243" s="227" t="s">
@@ -20155,7 +20255,7 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A247" s="236">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B247" s="220"/>
       <c r="C247" s="227" t="s">
@@ -20170,7 +20270,7 @@
       <c r="J247" s="227"/>
       <c r="K247" s="227"/>
       <c r="L247" s="236">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M247" s="220"/>
       <c r="N247" s="227" t="s">
@@ -20279,7 +20379,7 @@
     </row>
     <row r="251" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A251" s="236">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B251" s="220"/>
       <c r="C251" s="227" t="s">
@@ -20354,11 +20454,13 @@
       <c r="J253" s="220"/>
       <c r="K253" s="220"/>
       <c r="L253" s="236">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M253" s="220"/>
-      <c r="N253" s="227" t="s">
-        <v>285</v>
+      <c r="N253" s="227" t="inlineStr">
+        <is>
+          <t>Net business assets (box 90 minus (boxes 91 to 93))</t>
+        </is>
       </c>
       <c r="O253" s="220"/>
       <c r="P253" s="220"/>
@@ -20397,11 +20499,13 @@
     </row>
     <row r="255" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A255" s="236">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B255" s="220"/>
-      <c r="C255" s="227" t="s">
-        <v>286</v>
+      <c r="C255" s="227" t="inlineStr">
+        <is>
+          <t>Bank or building society balances</t>
+        </is>
       </c>
       <c r="D255" s="227"/>
       <c r="E255" s="227"/>
@@ -20521,7 +20625,7 @@
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A259" s="236">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B259" s="220"/>
       <c r="C259" s="227" t="s">
@@ -20536,7 +20640,7 @@
       <c r="J259" s="227"/>
       <c r="K259" s="227"/>
       <c r="L259" s="236">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M259" s="220"/>
       <c r="N259" s="227" t="s">
@@ -20647,7 +20751,7 @@
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A263" s="236">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B263" s="220"/>
       <c r="C263" s="227" t="s">
@@ -20662,11 +20766,13 @@
       <c r="J263" s="227"/>
       <c r="K263" s="227"/>
       <c r="L263" s="236">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M263" s="220"/>
-      <c r="N263" s="227" t="s">
-        <v>291</v>
+      <c r="N263" s="227" t="inlineStr">
+        <is>
+          <t>Net profit or loss (box 47 or box 48)</t>
+        </is>
       </c>
       <c r="O263" s="220"/>
       <c r="P263" s="220"/>
@@ -20773,11 +20879,13 @@
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A267" s="236">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B267" s="220"/>
-      <c r="C267" s="227" t="s">
-        <v>292</v>
+      <c r="C267" s="227" t="inlineStr">
+        <is>
+          <t>Total assets (total of boxes 83 to 89)</t>
+        </is>
       </c>
       <c r="D267" s="227"/>
       <c r="E267" s="227"/>
@@ -20788,7 +20896,7 @@
       <c r="J267" s="227"/>
       <c r="K267" s="227"/>
       <c r="L267" s="236">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M267" s="220"/>
       <c r="N267" s="227" t="s">
@@ -20908,7 +21016,7 @@
       <c r="J271" s="227"/>
       <c r="K271" s="227"/>
       <c r="L271" s="236">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M271" s="220"/>
       <c r="N271" s="227" t="s">
@@ -21020,7 +21128,7 @@
       <c r="J275" s="227"/>
       <c r="K275" s="227"/>
       <c r="L275" s="236">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M275" s="220"/>
       <c r="N275" s="227" t="s">
@@ -21122,8 +21230,10 @@
       <c r="W278" s="251"/>
     </row>
     <row r="279" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A279" s="368" t="s">
-        <v>295</v>
+      <c r="A279" s="368" t="inlineStr">
+        <is>
+          <t>Class 2 and Class 4 National Insurance contributions (NICs)</t>
+        </is>
       </c>
       <c r="B279" s="368"/>
       <c r="C279" s="368"/>
@@ -21149,8 +21259,10 @@
       <c r="W279" s="368"/>
     </row>
     <row r="280" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A280" s="366" t="s">
-        <v>296</v>
+      <c r="A280" s="366" t="inlineStr">
+        <is>
+          <t>If your self employed profits are more than £</t>
+        </is>
       </c>
       <c r="B280" s="399"/>
       <c r="C280" s="399"/>
@@ -21161,11 +21273,13 @@
       <c r="H280" s="399"/>
       <c r="I280" s="399"/>
       <c r="J280" s="285">
-        <f>Admin!N4</f>
+        <f>Admin!N20</f>
         <v>12570</v>
       </c>
-      <c r="K280" s="366" t="s">
-        <v>297</v>
+      <c r="K280" s="366" t="inlineStr">
+        <is>
+          <t>you must pay Class 4 NICs (unless you are exempt) - read the notes.</t>
+        </is>
       </c>
       <c r="L280" s="346"/>
       <c r="M280" s="346"/>
@@ -21181,8 +21295,10 @@
       <c r="W280" s="346"/>
     </row>
     <row r="281" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A281" s="398" t="s">
-        <v>383</v>
+      <c r="A281" s="398" t="inlineStr">
+        <is>
+          <t>If your total profits are below the Class 2 small profits threshold you do not have to pay Class 2 NICs, but you may pay them voluntarily.</t>
+        </is>
       </c>
       <c r="B281" s="398"/>
       <c r="C281" s="398"/>
@@ -21234,11 +21350,13 @@
     </row>
     <row r="283" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A283" s="236">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B283" s="220"/>
-      <c r="C283" s="227" t="s">
-        <v>298</v>
+      <c r="C283" s="227" t="inlineStr">
+        <is>
+          <t>If your total profits are below the Class 2 small profits threshold</t>
+        </is>
       </c>
       <c r="D283" s="220"/>
       <c r="E283" s="220"/>
@@ -21249,7 +21367,7 @@
       <c r="J283" s="220"/>
       <c r="K283" s="220"/>
       <c r="L283" s="236">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M283" s="220"/>
       <c r="N283" s="227" t="s">
@@ -21268,8 +21386,10 @@
     <row r="284" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A284" s="240"/>
       <c r="B284" s="220"/>
-      <c r="C284" s="227" t="s">
-        <v>384</v>
+      <c r="C284" s="227" t="inlineStr">
+        <is>
+          <t>and you choose to pay Class 2 NICs voluntarily, put 'X' in the box</t>
+        </is>
       </c>
       <c r="D284" s="220"/>
       <c r="E284" s="220"/>
@@ -21379,24 +21499,21 @@
     </row>
     <row r="288" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A288" s="236">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B288" s="220"/>
-      <c r="C288" s="227" t="s">
-        <v>301</v>
+      <c r="C288" s="227" t="inlineStr">
+        <is>
+          <t>If you are exempt from paying Class 4 NICs, put 'X' in the box</t>
+        </is>
       </c>
       <c r="D288" s="220"/>
       <c r="E288" s="220"/>
       <c r="F288" s="220"/>
-      <c r="G288" s="370" t="str">
-        <f>Admin!G2</f>
-        <v>2025-26</v>
-      </c>
+      <c r="G288" s="370"/>
       <c r="H288" s="371"/>
       <c r="I288" s="371"/>
-      <c r="J288" s="220" t="s">
-        <v>302</v>
-      </c>
+      <c r="J288" s="220"/>
       <c r="K288" s="220"/>
       <c r="L288" s="220"/>
       <c r="M288" s="220"/>
@@ -21414,8 +21531,10 @@
     <row r="289" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A289" s="240"/>
       <c r="B289" s="220"/>
-      <c r="C289" s="227" t="s">
-        <v>385</v>
+      <c r="C289" s="227" t="inlineStr">
+        <is>
+          <t>- read the notes</t>
+        </is>
       </c>
       <c r="D289" s="220"/>
       <c r="E289" s="220"/>
@@ -21441,9 +21560,7 @@
     <row r="290" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A290" s="240"/>
       <c r="B290" s="220"/>
-      <c r="C290" s="220" t="s">
-        <v>303</v>
-      </c>
+      <c r="C290" s="220"/>
       <c r="D290" s="220"/>
       <c r="E290" s="220"/>
       <c r="F290" s="220"/>
@@ -21594,11 +21711,13 @@
     </row>
     <row r="296" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A296" s="236">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B296" s="220"/>
-      <c r="C296" s="227" t="s">
-        <v>305</v>
+      <c r="C296" s="227" t="inlineStr">
+        <is>
+          <t>Please give any other information in this space</t>
+        </is>
       </c>
       <c r="D296" s="220"/>
       <c r="E296" s="220"/>

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -16513,8 +16513,10 @@
         <v>47</v>
       </c>
       <c r="B126" s="220"/>
-      <c r="C126" s="227" t="s">
-        <v>214</v>
+      <c r="C126" s="227" t="inlineStr">
+        <is>
+          <t>Net profit - if your business income is more than your</t>
+        </is>
       </c>
       <c r="D126" s="227"/>
       <c r="E126" s="227"/>

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -7703,7 +7703,7 @@
     <row r="45" spans="1:23" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="185"/>
       <c r="B45" s="181"/>
-      <c r="C45" s="196"/>
+      <c r="C45" s="181"/>
       <c r="D45" s="181"/>
       <c r="E45" s="181"/>
       <c r="F45" s="181"/>
@@ -14099,7 +14099,7 @@
     <row r="48" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A48" s="240"/>
       <c r="B48" s="220"/>
-      <c r="C48" s="272"/>
+      <c r="C48" s="227"/>
       <c r="D48" s="220"/>
       <c r="E48" s="220"/>
       <c r="F48" s="220"/>
@@ -18430,10 +18430,10 @@
     <row r="187" spans="1:23" ht="14" x14ac:dyDescent="0.15">
       <c r="A187" s="255"/>
       <c r="B187" s="220"/>
-      <c r="C187" s="382"/>
-      <c r="D187" s="383"/>
-      <c r="E187" s="383"/>
-      <c r="F187" s="384"/>
+      <c r="C187" s="227"/>
+      <c r="D187" s="227"/>
+      <c r="E187" s="227"/>
+      <c r="F187" s="227"/>
       <c r="G187" s="227"/>
       <c r="H187" s="227"/>
       <c r="I187" s="227"/>
@@ -18457,13 +18457,13 @@
     <row r="188" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="240"/>
       <c r="B188" s="220"/>
-      <c r="C188" s="261"/>
+      <c r="C188" s="227"/>
       <c r="D188" s="385"/>
       <c r="E188" s="385"/>
       <c r="F188" s="385"/>
       <c r="G188" s="218"/>
-      <c r="H188" s="253"/>
-      <c r="I188" s="253"/>
+      <c r="H188" s="227"/>
+      <c r="I188" s="227"/>
       <c r="J188" s="220"/>
       <c r="K188" s="220"/>
       <c r="L188" s="227"/>
@@ -18513,10 +18513,10 @@
     <row r="190" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A190" s="255"/>
       <c r="B190" s="220"/>
-      <c r="C190" s="382"/>
-      <c r="D190" s="383"/>
-      <c r="E190" s="383"/>
-      <c r="F190" s="384"/>
+      <c r="C190" s="227"/>
+      <c r="D190" s="227"/>
+      <c r="E190" s="227"/>
+      <c r="F190" s="227"/>
       <c r="G190" s="227"/>
       <c r="H190" s="227"/>
       <c r="I190" s="227"/>
@@ -18871,13 +18871,13 @@
     <row r="201" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A201" s="240"/>
       <c r="B201" s="220"/>
-      <c r="C201" s="217"/>
-      <c r="D201" s="356"/>
-      <c r="E201" s="357"/>
-      <c r="F201" s="358"/>
+      <c r="C201" s="227"/>
+      <c r="D201" s="227"/>
+      <c r="E201" s="227"/>
+      <c r="F201" s="227"/>
       <c r="G201" s="218"/>
-      <c r="H201" s="219"/>
-      <c r="I201" s="219"/>
+      <c r="H201" s="227"/>
+      <c r="I201" s="227"/>
       <c r="J201" s="220"/>
       <c r="K201" s="220"/>
       <c r="L201" s="236">
@@ -19017,13 +19017,13 @@
     <row r="206" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A206" s="240"/>
       <c r="B206" s="220"/>
-      <c r="C206" s="217"/>
-      <c r="D206" s="356"/>
-      <c r="E206" s="357"/>
-      <c r="F206" s="358"/>
+      <c r="C206" s="227"/>
+      <c r="D206" s="227"/>
+      <c r="E206" s="227"/>
+      <c r="F206" s="227"/>
       <c r="G206" s="218"/>
-      <c r="H206" s="219"/>
-      <c r="I206" s="219"/>
+      <c r="H206" s="227"/>
+      <c r="I206" s="227"/>
       <c r="J206" s="220"/>
       <c r="K206" s="220"/>
       <c r="L206" s="236">

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -12743,8 +12743,9 @@
       <c r="D1" s="334"/>
       <c r="E1" s="334"/>
       <c r="F1" s="334"/>
-      <c r="G1" s="335" t="s">
-        <v>438</v>
+      <c r="G1" s="335" t="str">
+        <f>"COPY DETAILS TO HMRC FORM          Submit HMRC RETURN ONLINE                   by 31st January "&amp;TEXT(Admin!B21,"yyyy")</f>
+        <v>COPY DETAILS TO HMRC FORM          Submit HMRC RETURN ONLINE                   by 31st January 2026</v>
       </c>
       <c r="H1" s="336"/>
       <c r="I1" s="336"/>

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -216,7 +216,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="440">
   <si>
     <t>Depreciation</t>
   </si>
@@ -1465,7 +1465,7 @@
     <t>page SESN 2 of the notes</t>
   </si>
   <si>
-    <t>Any other business income not included in box 8</t>
+    <t>Any other business income not included in box 9</t>
   </si>
   <si>
     <t>Allowable business expenses</t>
@@ -1489,11 +1489,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> to see which expenses are allowed for tax purposes. If your annual turnover was below £30,000</t>
+      <t xml:space="preserve"> to see which expenses are allowed for tax purposes. If your annual turnover was below the VAT threshold shown above</t>
     </r>
   </si>
   <si>
-    <t>you may just put your total expenses in box 19, rather than filling in the whole section.</t>
+    <t>you may just put your total expenses in box 20, rather than filling in the whole section.</t>
   </si>
   <si>
     <r>
@@ -1546,14 +1546,14 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>total of boxes 10 to 18</t>
+      <t>total of boxes 11 to 19</t>
     </r>
   </si>
   <si>
-    <t>expenses (box 8 + box 9 minus box 19)</t>
-  </si>
-  <si>
-    <t>income (box 8 + box 9 minus box 19 is negative)</t>
+    <t>expenses (box 9 + box 10 minus box 20)</t>
+  </si>
+  <si>
+    <t>income (box 9 + box 10 minus box 20 is negative)</t>
   </si>
   <si>
     <t>There are 'capital' tax allowances for vehicles and equipment used in your business (you should not have included the cost of</t>
@@ -1629,7 +1629,7 @@
     </r>
   </si>
   <si>
-    <t>Any other business income not included in boxes 8 or 9</t>
+    <t>Any other business income not included in boxes 9 or 10</t>
   </si>
   <si>
     <t xml:space="preserve"> - for example, Business Start-up Allowance</t>
@@ -1642,7 +1642,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">If you have made a loss for tax purposes (box 29), read page SESN 7 of the </t>
+      <t xml:space="preserve">If you have made a loss for tax purposes (box 32), read page SESN 7 of the </t>
     </r>
     <r>
       <rPr>
@@ -1659,7 +1659,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> and fill in boxes 30 to 32 as appropriate.</t>
+      <t xml:space="preserve"> and fill in boxes 33 to 35 as appropriate.</t>
     </r>
   </si>
   <si>
@@ -1924,26 +1924,26 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>up to the amount in box 27</t>
+      <t>up to the amount in box 28</t>
     </r>
   </si>
   <si>
-    <t>Net business profit for tax purposes (if box 20 + box 25 +</t>
-  </si>
-  <si>
-    <t>box 26 minus boxes 21 to 24) is positive)</t>
+    <t>Net business profit for tax purposes (if box 21 + box 26 +</t>
+  </si>
+  <si>
+    <t>box 27 minus boxes 22 to 25) is positive)</t>
   </si>
   <si>
     <t>Total taxable profits from this business</t>
   </si>
   <si>
-    <t>Net business loss for tax purposes (if boxes 21 to 24</t>
-  </si>
-  <si>
-    <t>if box 27 + box 29 minus box 28 is positive</t>
-  </si>
-  <si>
-    <t>minus (box 20 + box 25 + box 26) is positive)</t>
+    <t>Net business loss for tax purposes (if boxes 22 to 25</t>
+  </si>
+  <si>
+    <t>if box 28 + box 30 minus box 29 is positive</t>
+  </si>
+  <si>
+    <t>minus (box 21 + box 26 + box 27) is positive)</t>
   </si>
   <si>
     <r>
@@ -2089,6 +2089,9 @@
   </si>
   <si>
     <t>COPY DETAILS TO HMRC FORM          Submit HMRC RETURN ONLINE                   by 31st January 2027</t>
+  </si>
+  <si>
+    <t>choose to pay Class 2 NICs voluntarily, put 'X' in the box</t>
   </si>
 </sst>
 </file>
@@ -8537,8 +8540,12 @@
       <c r="M16" s="147" t="s">
         <v>436</v>
       </c>
-      <c r="N16" s="147"/>
-      <c r="O16" s="147"/>
+      <c r="N16" s="152">
+        <v>6725</v>
+      </c>
+      <c r="O16" s="146" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="17" spans="1:15" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="147"/>
@@ -9792,7 +9799,7 @@
     </row>
     <row r="33" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="364" t="str">
-        <f>IF(D38&gt;67000,"SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £"&amp;Admin!F26&amp;" VAT threshold","Business income - if your annual turnover was below £"&amp;Admin!F26&amp;" VAT threshold")</f>
+        <f>IF(D38&gt;Admin!F26,"SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £"&amp;Admin!F26&amp;" VAT threshold","Business income - if your annual turnover was below £"&amp;Admin!F26&amp;" VAT threshold")</f>
         <v>Business income - if your annual turnover was below £90000 VAT threshold</v>
       </c>
       <c r="B33" s="364"/>
@@ -9845,7 +9852,7 @@
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A35" s="236">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35" s="220"/>
       <c r="C35" s="227" t="s">
@@ -9860,7 +9867,7 @@
       <c r="J35" s="227"/>
       <c r="K35" s="227"/>
       <c r="L35" s="236">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M35" s="220"/>
       <c r="N35" s="227" t="s">
@@ -10110,7 +10117,7 @@
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A44" s="236">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B44" s="220"/>
       <c r="C44" s="227" t="s">
@@ -10125,7 +10132,7 @@
       <c r="J44" s="227"/>
       <c r="K44" s="227"/>
       <c r="L44" s="236">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M44" s="220"/>
       <c r="N44" s="227" t="s">
@@ -10173,7 +10180,7 @@
         <v>51</v>
       </c>
       <c r="D46" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B17," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B17," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="E46" s="357"/>
@@ -10195,7 +10202,7 @@
         <v>51</v>
       </c>
       <c r="O46" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B28," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B28," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="P46" s="357"/>
@@ -10240,7 +10247,7 @@
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A48" s="236">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B48" s="220"/>
       <c r="C48" s="227" t="s">
@@ -10255,7 +10262,7 @@
       <c r="J48" s="227"/>
       <c r="K48" s="227"/>
       <c r="L48" s="236">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M48" s="220"/>
       <c r="N48" s="227" t="s">
@@ -10330,7 +10337,7 @@
         <v>51</v>
       </c>
       <c r="D51" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="E51" s="357"/>
@@ -10352,7 +10359,7 @@
         <v>51</v>
       </c>
       <c r="O51" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="P51" s="357"/>
@@ -10397,7 +10404,7 @@
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A53" s="236">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" s="220"/>
       <c r="C53" s="227" t="s">
@@ -10412,7 +10419,7 @@
       <c r="J53" s="227"/>
       <c r="K53" s="227"/>
       <c r="L53" s="236">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M53" s="220"/>
       <c r="N53" s="227" t="s">
@@ -10460,7 +10467,7 @@
         <v>51</v>
       </c>
       <c r="D55" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B21," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B21," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="E55" s="357"/>
@@ -10482,7 +10489,7 @@
         <v>51</v>
       </c>
       <c r="O55" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B24," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B24," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="P55" s="357"/>
@@ -10527,7 +10534,7 @@
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A57" s="236">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B57" s="220"/>
       <c r="C57" s="227" t="s">
@@ -10542,7 +10549,7 @@
       <c r="J57" s="227"/>
       <c r="K57" s="227"/>
       <c r="L57" s="236">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M57" s="220"/>
       <c r="N57" s="227" t="s">
@@ -10617,7 +10624,7 @@
         <v>51</v>
       </c>
       <c r="D60" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B22," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B22," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="E60" s="357"/>
@@ -10639,7 +10646,7 @@
         <v>51</v>
       </c>
       <c r="O60" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="P60" s="357"/>
@@ -10684,7 +10691,7 @@
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A62" s="236">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B62" s="220"/>
       <c r="C62" s="227" t="s">
@@ -10699,7 +10706,7 @@
       <c r="J62" s="227"/>
       <c r="K62" s="227"/>
       <c r="L62" s="236">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M62" s="220"/>
       <c r="N62" s="227" t="s">
@@ -10747,7 +10754,7 @@
         <v>51</v>
       </c>
       <c r="D64" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B23," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B23," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="E64" s="357"/>
@@ -10866,7 +10873,7 @@
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A68" s="236">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B68" s="220"/>
       <c r="C68" s="227" t="s">
@@ -10881,7 +10888,7 @@
       <c r="J68" s="227"/>
       <c r="K68" s="227"/>
       <c r="L68" s="236">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M68" s="220"/>
       <c r="N68" s="227" t="s">
@@ -11164,7 +11171,7 @@
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A78" s="236">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B78" s="220"/>
       <c r="C78" s="227" t="s">
@@ -11179,7 +11186,7 @@
       <c r="J78" s="227"/>
       <c r="K78" s="227"/>
       <c r="L78" s="236">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M78" s="220"/>
       <c r="N78" s="227" t="s">
@@ -11294,7 +11301,7 @@
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A82" s="236">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B82" s="220"/>
       <c r="C82" s="227" t="s">
@@ -11309,7 +11316,7 @@
       <c r="J82" s="220"/>
       <c r="K82" s="220"/>
       <c r="L82" s="236">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M82" s="220"/>
       <c r="N82" s="227" t="s">
@@ -11559,7 +11566,7 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A91" s="236">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B91" s="220"/>
       <c r="C91" s="227" t="s">
@@ -11574,7 +11581,7 @@
       <c r="J91" s="227"/>
       <c r="K91" s="227"/>
       <c r="L91" s="236">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M91" s="220"/>
       <c r="N91" s="227" t="s">
@@ -11718,7 +11725,7 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A96" s="236">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B96" s="220"/>
       <c r="C96" s="227" t="s">
@@ -11733,7 +11740,7 @@
       <c r="J96" s="227"/>
       <c r="K96" s="227"/>
       <c r="L96" s="236">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M96" s="220"/>
       <c r="N96" s="227" t="s">
@@ -11931,7 +11938,7 @@
     </row>
     <row r="103" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A103" s="236">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B103" s="220"/>
       <c r="C103" s="227" t="s">
@@ -11946,7 +11953,7 @@
       <c r="J103" s="227"/>
       <c r="K103" s="227"/>
       <c r="L103" s="236">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M103" s="220"/>
       <c r="N103" s="227" t="s">
@@ -12169,7 +12176,7 @@
     </row>
     <row r="111" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A111" s="236">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B111" s="220"/>
       <c r="C111" s="227" t="s">
@@ -12184,11 +12191,12 @@
       <c r="J111" s="227"/>
       <c r="K111" s="227"/>
       <c r="L111" s="236">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M111" s="220"/>
-      <c r="N111" s="227" t="s">
-        <v>345</v>
+      <c r="N111" s="227" t="str">
+        <f>"If your total profits for "&amp;Admin!G2&amp;" are less than £"&amp;TEXT(Admin!N16,"#,##0")&amp;" and you"</f>
+        <v>If your total profits for 2024-25 are less than £6,725 and you</v>
       </c>
       <c r="O111" s="220"/>
       <c r="P111" s="220"/>
@@ -12220,7 +12228,7 @@
       <c r="L112" s="227"/>
       <c r="M112" s="220"/>
       <c r="N112" s="227" t="s">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="O112" s="258"/>
       <c r="P112" s="258"/>
@@ -12317,7 +12325,7 @@
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A116" s="236">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B116" s="220"/>
       <c r="C116" s="227" t="s">
@@ -12332,24 +12340,19 @@
       <c r="J116" s="227"/>
       <c r="K116" s="227"/>
       <c r="L116" s="236">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M116" s="220"/>
       <c r="N116" s="227" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="O116" s="220"/>
       <c r="P116" s="220"/>
       <c r="Q116" s="220"/>
-      <c r="R116" s="370" t="str">
-        <f>Admin!G2</f>
-        <v>2025-26</v>
-      </c>
+      <c r="R116" s="370"/>
       <c r="S116" s="371"/>
       <c r="T116" s="371"/>
-      <c r="U116" s="227" t="s">
-        <v>347</v>
-      </c>
+      <c r="U116" s="227"/>
       <c r="V116" s="220"/>
       <c r="W116" s="243"/>
     </row>
@@ -12370,7 +12373,7 @@
       <c r="L117" s="227"/>
       <c r="M117" s="220"/>
       <c r="N117" s="227" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O117" s="220"/>
       <c r="P117" s="220"/>
@@ -12396,9 +12399,7 @@
       <c r="K118" s="227"/>
       <c r="L118" s="227"/>
       <c r="M118" s="220"/>
-      <c r="N118" s="248" t="s">
-        <v>236</v>
-      </c>
+      <c r="N118" s="248"/>
       <c r="O118" s="220"/>
       <c r="P118" s="220"/>
       <c r="Q118" s="220"/>
@@ -12469,7 +12470,7 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A121" s="236">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B121" s="220"/>
       <c r="C121" s="227" t="s">
@@ -12484,7 +12485,7 @@
       <c r="J121" s="227"/>
       <c r="K121" s="227"/>
       <c r="L121" s="236">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M121" s="220"/>
       <c r="N121" s="227" t="s">

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -216,7 +216,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="442">
   <si>
     <t>Depreciation</t>
   </si>
@@ -2092,6 +2092,12 @@
   </si>
   <si>
     <t>choose to pay Class 2 NICs voluntarily, put 'X' in the box</t>
+  </si>
+  <si>
+    <t>Copyright (C) 2006-2026 DIY Accounting Limited</t>
+  </si>
+  <si>
+    <t>Licensed under the PolyForm Internal Use License 1.0.0 with an additional grant for accountants. Free to use, source available: https://spreadsheets.diyaccounting.co.uk</t>
   </si>
 </sst>
 </file>
@@ -6475,7 +6481,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="176" customWidth="1"/>
@@ -8060,6 +8066,16 @@
       <c r="U56" s="206"/>
       <c r="V56" s="206"/>
       <c r="W56" s="207"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>441</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="26">

--- a/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2025-04-05 (Apr25) Excel 2007/Financialaccounts.xlsx
@@ -419,7 +419,7 @@
     <t>Repairs &amp; Maintenance</t>
   </si>
   <si>
-    <t>Advertising &amp; Promotion</t>
+    <t>Advertising Promotion &amp; Entertainment</t>
   </si>
   <si>
     <t>Legal &amp; Professional Fees</t>
@@ -1992,7 +1992,7 @@
     <t>3. Column F automatically collects the value of direct material purchased from the monthly purchases worksheet</t>
   </si>
   <si>
-    <t>Not captured in DIY Accounting</t>
+    <t>Enter the % of this category that is private use or otherwise disallowable</t>
   </si>
   <si>
     <t>Other</t>
@@ -10196,7 +10196,7 @@
         <v>51</v>
       </c>
       <c r="D46" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B17," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B17-'SE Full'!O66-'SE Full'!O70," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="E46" s="357"/>
@@ -10218,7 +10218,7 @@
         <v>51</v>
       </c>
       <c r="O46" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B28," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B28-'SE Full'!O110," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="P46" s="357"/>
@@ -10353,7 +10353,7 @@
         <v>51</v>
       </c>
       <c r="D51" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26-'SE Full'!O78," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="E51" s="357"/>
@@ -10375,7 +10375,7 @@
         <v>51</v>
       </c>
       <c r="O51" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31-'SE Full'!O98-'SE Full'!O102," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="P51" s="357"/>
@@ -10483,7 +10483,7 @@
         <v>51</v>
       </c>
       <c r="D55" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B21," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B21-'SE Full'!O74," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="E55" s="357"/>
@@ -10505,7 +10505,7 @@
         <v>51</v>
       </c>
       <c r="O55" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B24," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B24-'SE Full'!O90," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="P55" s="357"/>
@@ -10640,7 +10640,7 @@
         <v>51</v>
       </c>
       <c r="D60" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B22," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B22-'SE Full'!O82," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="E60" s="357"/>
@@ -10662,7 +10662,7 @@
         <v>51</v>
       </c>
       <c r="O60" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33-'SE Full'!O94-'SE Full'!O106-'SE Full'!O118," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="P60" s="357"/>
@@ -10770,7 +10770,7 @@
         <v>51</v>
       </c>
       <c r="D64" s="356" t="str">
-        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B23," ")</f>
+        <f>IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B23-'SE Full'!O86," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="E64" s="357"/>
@@ -10792,7 +10792,7 @@
         <v>51</v>
       </c>
       <c r="O64" s="356">
-        <f>'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35-'Profit &amp; Loss Account'!B34</f>
+        <f>'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35-'SE Full'!O122</f>
         <v>0</v>
       </c>
       <c r="P64" s="357"/>
@@ -14663,7 +14663,10 @@
       <c r="N66" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O66" s="356"/>
+      <c r="O66" s="356">
+        <f>VitalTax!G36</f>
+        <v>0</v>
+      </c>
       <c r="P66" s="357"/>
       <c r="Q66" s="358"/>
       <c r="R66" s="218" t="s">
@@ -14788,7 +14791,10 @@
       <c r="N70" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O70" s="356"/>
+      <c r="O70" s="356">
+        <f>VitalTax!G37</f>
+        <v>0</v>
+      </c>
       <c r="P70" s="357"/>
       <c r="Q70" s="358"/>
       <c r="R70" s="218" t="s">
@@ -14913,7 +14919,10 @@
       <c r="N74" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O74" s="356"/>
+      <c r="O74" s="356">
+        <f>VitalTax!G38</f>
+        <v>0</v>
+      </c>
       <c r="P74" s="357"/>
       <c r="Q74" s="358"/>
       <c r="R74" s="218" t="s">
@@ -15040,7 +15049,10 @@
       <c r="N78" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O78" s="356"/>
+      <c r="O78" s="356">
+        <f>VitalTax!G39</f>
+        <v>0</v>
+      </c>
       <c r="P78" s="357"/>
       <c r="Q78" s="358"/>
       <c r="R78" s="218" t="s">
@@ -15165,7 +15177,10 @@
       <c r="N82" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O82" s="356"/>
+      <c r="O82" s="356">
+        <f>VitalTax!G40</f>
+        <v>0</v>
+      </c>
       <c r="P82" s="357"/>
       <c r="Q82" s="358"/>
       <c r="R82" s="218" t="s">
@@ -15292,7 +15307,10 @@
       <c r="N86" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O86" s="356"/>
+      <c r="O86" s="356">
+        <f>VitalTax!G41</f>
+        <v>0</v>
+      </c>
       <c r="P86" s="357"/>
       <c r="Q86" s="358"/>
       <c r="R86" s="218" t="s">
@@ -15419,7 +15437,10 @@
       <c r="N90" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O90" s="356"/>
+      <c r="O90" s="356">
+        <f>VitalTax!G42</f>
+        <v>0</v>
+      </c>
       <c r="P90" s="357"/>
       <c r="Q90" s="358"/>
       <c r="R90" s="218" t="s">
@@ -15544,7 +15565,10 @@
       <c r="N94" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O94" s="356"/>
+      <c r="O94" s="356">
+        <f>VitalTax!G43+VitalTax!G44</f>
+        <v>0</v>
+      </c>
       <c r="P94" s="357"/>
       <c r="Q94" s="358"/>
       <c r="R94" s="218" t="s">
@@ -15669,7 +15693,10 @@
       <c r="N98" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O98" s="356"/>
+      <c r="O98" s="356">
+        <f>VitalTax!G45</f>
+        <v>0</v>
+      </c>
       <c r="P98" s="357"/>
       <c r="Q98" s="358"/>
       <c r="R98" s="218" t="s">
@@ -15794,7 +15821,10 @@
       <c r="N102" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O102" s="356"/>
+      <c r="O102" s="356">
+        <f>VitalTax!G46</f>
+        <v>0</v>
+      </c>
       <c r="P102" s="357"/>
       <c r="Q102" s="358"/>
       <c r="R102" s="218" t="s">
@@ -15919,7 +15949,10 @@
       <c r="N106" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O106" s="356"/>
+      <c r="O106" s="356">
+        <f>VitalTax!G47</f>
+        <v>0</v>
+      </c>
       <c r="P106" s="357"/>
       <c r="Q106" s="358"/>
       <c r="R106" s="218" t="s">
@@ -16044,7 +16077,10 @@
       <c r="N110" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O110" s="356"/>
+      <c r="O110" s="356">
+        <f>VitalTax!G48</f>
+        <v>0</v>
+      </c>
       <c r="P110" s="357"/>
       <c r="Q110" s="358"/>
       <c r="R110" s="218" t="s">
@@ -16299,7 +16335,10 @@
       <c r="N118" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="O118" s="356"/>
+      <c r="O118" s="356">
+        <f>VitalTax!G50</f>
+        <v>0</v>
+      </c>
       <c r="P118" s="357"/>
       <c r="Q118" s="358"/>
       <c r="R118" s="218" t="s">
@@ -16431,7 +16470,7 @@
         <v>51</v>
       </c>
       <c r="O122" s="356">
-        <f>'Profit &amp; Loss Account'!B34</f>
+        <f>O66+O70+O74+O78+O82+O86+O90+O94+O98+O102+O106+O110+O114+O118</f>
         <v>0</v>
       </c>
       <c r="P122" s="357"/>
@@ -22630,7 +22669,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.83203125" style="90" customWidth="1"/>
@@ -23861,51 +23900,51 @@
         <v>0</v>
       </c>
       <c r="C27" s="75">
-        <f>[3]Apr!$Y$1</f>
+        <f>[3]Apr!$Y$1+[3]Apr!$AC$1</f>
         <v>0</v>
       </c>
       <c r="D27" s="75">
-        <f>[3]May!$Y$1</f>
+        <f>[3]May!$Y$1+[3]May!$AC$1</f>
         <v>0</v>
       </c>
       <c r="E27" s="78">
-        <f>[3]Jun!$Y$1</f>
+        <f>[3]Jun!$Y$1+[3]Jun!$AC$1</f>
         <v>0</v>
       </c>
       <c r="F27" s="75">
-        <f>[3]Jul!$Y$1</f>
+        <f>[3]Jul!$Y$1+[3]Jul!$AC$1</f>
         <v>0</v>
       </c>
       <c r="G27" s="75">
-        <f>[3]Aug!$Y$1</f>
+        <f>[3]Aug!$Y$1+[3]Aug!$AC$1</f>
         <v>0</v>
       </c>
       <c r="H27" s="78">
-        <f>[3]Sep!$Y$1</f>
+        <f>[3]Sep!$Y$1+[3]Sep!$AC$1</f>
         <v>0</v>
       </c>
       <c r="I27" s="75">
-        <f>[3]Oct!$Y$1</f>
+        <f>[3]Oct!$Y$1+[3]Oct!$AC$1</f>
         <v>0</v>
       </c>
       <c r="J27" s="75">
-        <f>[3]Nov!$Y$1</f>
+        <f>[3]Nov!$Y$1+[3]Nov!$AC$1</f>
         <v>0</v>
       </c>
       <c r="K27" s="78">
-        <f>[3]Dec!$Y$1</f>
+        <f>[3]Dec!$Y$1+[3]Dec!$AC$1</f>
         <v>0</v>
       </c>
       <c r="L27" s="75">
-        <f>[3]Jan!$Y$1</f>
+        <f>[3]Jan!$Y$1+[3]Jan!$AC$1</f>
         <v>0</v>
       </c>
       <c r="M27" s="75">
-        <f>[3]Feb!$Y$1</f>
+        <f>[3]Feb!$Y$1+[3]Feb!$AC$1</f>
         <v>0</v>
       </c>
       <c r="N27" s="75">
-        <f>[3]Mar!$Y$1</f>
+        <f>[3]Mar!$Y$1+[3]Mar!$AC$1</f>
         <v>0</v>
       </c>
       <c r="O27" s="24"/>
@@ -24907,6 +24946,66 @@
       <c r="M47" s="28"/>
       <c r="N47" s="28"/>
       <c r="O47" s="29"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A49" s="87" t="inlineStr">
+        <is>
+          <t>Business Entertainment (memo)</t>
+        </is>
+      </c>
+      <c r="B49" s="62">
+        <f>SUM(C49:N49)</f>
+        <v>0</v>
+      </c>
+      <c r="C49" s="75">
+        <f>[3]Apr!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="75">
+        <f>[3]May!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="78">
+        <f>[3]Jun!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="75">
+        <f>[3]Jul!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="75">
+        <f>[3]Aug!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="78">
+        <f>[3]Sep!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="75">
+        <f>[3]Oct!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="75">
+        <f>[3]Nov!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="78">
+        <f>[3]Dec!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="75">
+        <f>[3]Jan!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="75">
+        <f>[3]Feb!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="78">
+        <f>[3]Mar!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="O49" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -25494,24 +25593,26 @@
         <v>412</v>
       </c>
       <c r="C25" s="299">
+        <f>SUM('Profit &amp; Loss Account'!C49:E49)</f>
         <v>0</v>
       </c>
       <c r="D25" s="299">
+        <f>SUM('Profit &amp; Loss Account'!F49:H49)</f>
         <v>0</v>
       </c>
       <c r="E25" s="299">
+        <f>SUM('Profit &amp; Loss Account'!I49:K49)</f>
         <v>0</v>
       </c>
       <c r="F25" s="299">
+        <f>SUM('Profit &amp; Loss Account'!L49:N49)</f>
         <v>0</v>
       </c>
       <c r="G25" s="299">
         <f>SUM(C25:F25)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="298" t="s">
-        <v>406</v>
-      </c>
+      <c r="H25" s="298"/>
       <c r="I25" s="298"/>
     </row>
     <row r="26" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
@@ -25570,23 +25671,23 @@
         <v>421</v>
       </c>
       <c r="C29" s="302">
-        <f>SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C25,C26)</f>
+        <f>SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C26)</f>
         <v>0</v>
       </c>
       <c r="D29" s="302">
-        <f>SUM(D7,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D24,D25,D26)</f>
+        <f>SUM(D7,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D24,D26)</f>
         <v>0</v>
       </c>
       <c r="E29" s="302">
-        <f>SUM(E7,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E24,E25,E26)</f>
+        <f>SUM(E7,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E24,E26)</f>
         <v>0</v>
       </c>
       <c r="F29" s="302">
-        <f>SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F25,F26)</f>
+        <f>SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F26)</f>
         <v>0</v>
       </c>
       <c r="G29" s="302">
-        <f>SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G25,G26)</f>
+        <f>SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G26)</f>
         <v>0</v>
       </c>
       <c r="H29" s="301"/>
@@ -25666,15 +25767,19 @@
         <v>420</v>
       </c>
       <c r="C36" s="299">
+        <f>C7*$I$36</f>
         <v>0</v>
       </c>
       <c r="D36" s="299">
+        <f>D7*$I$36</f>
         <v>0</v>
       </c>
       <c r="E36" s="299">
+        <f>E7*$I$36</f>
         <v>0</v>
       </c>
       <c r="F36" s="299">
+        <f>F7*$I$36</f>
         <v>0</v>
       </c>
       <c r="G36" s="299">
@@ -25692,15 +25797,19 @@
         <v>419</v>
       </c>
       <c r="C37" s="299">
+        <f>C24*$I$37</f>
         <v>0</v>
       </c>
       <c r="D37" s="299">
+        <f>D24*$I$37</f>
         <v>0</v>
       </c>
       <c r="E37" s="299">
+        <f>E24*$I$37</f>
         <v>0</v>
       </c>
       <c r="F37" s="299">
+        <f>F24*$I$37</f>
         <v>0</v>
       </c>
       <c r="G37" s="299">
@@ -25718,15 +25827,19 @@
         <v>418</v>
       </c>
       <c r="C38" s="299">
+        <f>C12*$I$38</f>
         <v>0</v>
       </c>
       <c r="D38" s="299">
+        <f>D12*$I$38</f>
         <v>0</v>
       </c>
       <c r="E38" s="299">
+        <f>E12*$I$38</f>
         <v>0</v>
       </c>
       <c r="F38" s="299">
+        <f>F12*$I$38</f>
         <v>0</v>
       </c>
       <c r="G38" s="299">
@@ -25744,15 +25857,19 @@
         <v>417</v>
       </c>
       <c r="C39" s="299">
+        <f>C17*$I$39</f>
         <v>0</v>
       </c>
       <c r="D39" s="299">
+        <f>D17*$I$39</f>
         <v>0</v>
       </c>
       <c r="E39" s="299">
+        <f>E17*$I$39</f>
         <v>0</v>
       </c>
       <c r="F39" s="299">
+        <f>F17*$I$39</f>
         <v>0</v>
       </c>
       <c r="G39" s="299">
@@ -25770,15 +25887,19 @@
         <v>416</v>
       </c>
       <c r="C40" s="299">
+        <f>C13*$I$40</f>
         <v>0</v>
       </c>
       <c r="D40" s="299">
+        <f>D13*$I$40</f>
         <v>0</v>
       </c>
       <c r="E40" s="299">
+        <f>E13*$I$40</f>
         <v>0</v>
       </c>
       <c r="F40" s="299">
+        <f>F13*$I$40</f>
         <v>0</v>
       </c>
       <c r="G40" s="299">
@@ -25796,15 +25917,19 @@
         <v>415</v>
       </c>
       <c r="C41" s="299">
+        <f>C14*$I$41</f>
         <v>0</v>
       </c>
       <c r="D41" s="299">
+        <f>D14*$I$41</f>
         <v>0</v>
       </c>
       <c r="E41" s="299">
+        <f>E14*$I$41</f>
         <v>0</v>
       </c>
       <c r="F41" s="299">
+        <f>F14*$I$41</f>
         <v>0</v>
       </c>
       <c r="G41" s="299">
@@ -25822,15 +25947,19 @@
         <v>414</v>
       </c>
       <c r="C42" s="299">
+        <f>C15*$I$42</f>
         <v>0</v>
       </c>
       <c r="D42" s="299">
+        <f>D15*$I$42</f>
         <v>0</v>
       </c>
       <c r="E42" s="299">
+        <f>E15*$I$42</f>
         <v>0</v>
       </c>
       <c r="F42" s="299">
+        <f>F15*$I$42</f>
         <v>0</v>
       </c>
       <c r="G42" s="299">
@@ -25848,15 +25977,19 @@
         <v>413</v>
       </c>
       <c r="C43" s="299">
+        <f>C18*$I$43</f>
         <v>0</v>
       </c>
       <c r="D43" s="299">
+        <f>D18*$I$43</f>
         <v>0</v>
       </c>
       <c r="E43" s="299">
+        <f>E18*$I$43</f>
         <v>0</v>
       </c>
       <c r="F43" s="299">
+        <f>F18*$I$43</f>
         <v>0</v>
       </c>
       <c r="G43" s="299">
@@ -25874,23 +26007,29 @@
         <v>412</v>
       </c>
       <c r="C44" s="299">
+        <f>C25</f>
         <v>0</v>
       </c>
       <c r="D44" s="299">
+        <f>D25</f>
         <v>0</v>
       </c>
       <c r="E44" s="299">
+        <f>E25</f>
         <v>0</v>
       </c>
       <c r="F44" s="299">
+        <f>F25</f>
         <v>0</v>
       </c>
       <c r="G44" s="299">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H44" s="298" t="s">
-        <v>406</v>
+      <c r="H44" s="298" t="inlineStr">
+        <is>
+          <t>Wholly disallowable</t>
+        </is>
       </c>
       <c r="I44" s="298"/>
     </row>
@@ -25900,15 +26039,19 @@
         <v>411</v>
       </c>
       <c r="C45" s="299">
+        <f>C21*$I$45</f>
         <v>0</v>
       </c>
       <c r="D45" s="299">
+        <f>D21*$I$45</f>
         <v>0</v>
       </c>
       <c r="E45" s="299">
+        <f>E21*$I$45</f>
         <v>0</v>
       </c>
       <c r="F45" s="299">
+        <f>F21*$I$45</f>
         <v>0</v>
       </c>
       <c r="G45" s="299">
@@ -25926,15 +26069,19 @@
         <v>410</v>
       </c>
       <c r="C46" s="299">
+        <f>C16*$I$46</f>
         <v>0</v>
       </c>
       <c r="D46" s="299">
+        <f>D16*$I$46</f>
         <v>0</v>
       </c>
       <c r="E46" s="299">
+        <f>E16*$I$46</f>
         <v>0</v>
       </c>
       <c r="F46" s="299">
+        <f>F16*$I$46</f>
         <v>0</v>
       </c>
       <c r="G46" s="299">
@@ -25952,15 +26099,19 @@
         <v>409</v>
       </c>
       <c r="C47" s="299">
+        <f>C20*$I$47</f>
         <v>0</v>
       </c>
       <c r="D47" s="299">
+        <f>D20*$I$47</f>
         <v>0</v>
       </c>
       <c r="E47" s="299">
+        <f>E20*$I$47</f>
         <v>0</v>
       </c>
       <c r="F47" s="299">
+        <f>F20*$I$47</f>
         <v>0</v>
       </c>
       <c r="G47" s="299">
@@ -25978,15 +26129,19 @@
         <v>408</v>
       </c>
       <c r="C48" s="299">
+        <f>C19*$I$48</f>
         <v>0</v>
       </c>
       <c r="D48" s="299">
+        <f>D19*$I$48</f>
         <v>0</v>
       </c>
       <c r="E48" s="299">
+        <f>E19*$I$48</f>
         <v>0</v>
       </c>
       <c r="F48" s="299">
+        <f>F19*$I$48</f>
         <v>0</v>
       </c>
       <c r="G48" s="299">
@@ -26004,23 +26159,29 @@
         <v>0</v>
       </c>
       <c r="C49" s="299">
+        <f>SUM('Profit &amp; Loss Account'!C34:E34)</f>
         <v>0</v>
       </c>
       <c r="D49" s="299">
+        <f>SUM('Profit &amp; Loss Account'!F34:H34)</f>
         <v>0</v>
       </c>
       <c r="E49" s="299">
+        <f>SUM('Profit &amp; Loss Account'!I34:K34)</f>
         <v>0</v>
       </c>
       <c r="F49" s="299">
+        <f>SUM('Profit &amp; Loss Account'!L34:N34)</f>
         <v>0</v>
       </c>
       <c r="G49" s="299">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="298" t="s">
-        <v>406</v>
+      <c r="H49" s="298" t="inlineStr">
+        <is>
+          <t>Reads the depreciation charge automatically</t>
+        </is>
       </c>
       <c r="I49" s="298"/>
     </row>
@@ -26030,15 +26191,19 @@
         <v>407</v>
       </c>
       <c r="C50" s="299">
+        <f>C22*$I$50</f>
         <v>0</v>
       </c>
       <c r="D50" s="299">
+        <f>D22*$I$50</f>
         <v>0</v>
       </c>
       <c r="E50" s="299">
+        <f>E22*$I$50</f>
         <v>0</v>
       </c>
       <c r="F50" s="299">
+        <f>F22*$I$50</f>
         <v>0</v>
       </c>
       <c r="G50" s="299">
